--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12044\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F67B4B-A8C6-4FDE-86FE-FC6022ED33E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C93A5CF-8A4F-4755-A9D8-2CB4B875FA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13772" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -18,12 +18,15 @@
     <sheet name="维度" sheetId="4" r:id="rId3"/>
     <sheet name="普通攻击" sheetId="1" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="248">
   <si>
     <t>最终攻击力=面板攻击+横扫之刃+评分等级+杀手附魔</t>
   </si>
@@ -364,7 +367,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -385,7 +388,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -402,7 +405,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -439,7 +442,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -544,7 +547,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -561,7 +564,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -1001,37 +1004,61 @@
   <si>
     <t>1~0.5</t>
   </si>
+  <si>
+    <t>其他耐久</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他单次扣血</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他模板</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>脆皮</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>坦克</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>重甲</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1039,7 +1066,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1048,7 +1075,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1056,23 +1083,29 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1465,7 +1498,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1679,15 +1712,54 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,43 +1883,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1879,6 +1918,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="数值分配-新"/>
+      <sheetName val="数值分配"/>
+      <sheetName val="维度"/>
+      <sheetName val="普通攻击"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="CALC_DMG"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2132,13 +2196,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{910BDCF1-C956-466C-8498-3FEEAEB62098}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:BF21"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="24.05" customHeight="1"/>
+  <dimension ref="B1:BF25"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="15.6640625" style="8"/>
+    <col min="1" max="16384" width="15.625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:58" ht="24.05" customHeight="1">
+    <row r="1" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D1" s="27" t="s">
         <v>65</v>
       </c>
@@ -2158,32 +2222,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:58" ht="24.05" customHeight="1">
+    <row r="2" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D2" s="27">
         <v>0.5</v>
       </c>
       <c r="X2" s="8">
         <v>20</v>
       </c>
-      <c r="AB2" s="118" t="s">
+      <c r="AB2" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="AF2" s="118" t="s">
+      <c r="AF2" s="72" t="s">
         <v>228</v>
       </c>
       <c r="AI2" s="27">
         <v>0.5</v>
       </c>
-      <c r="AJ2" s="120" t="s">
+      <c r="AJ2" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" s="121">
+      <c r="AK2" s="74">
         <v>4</v>
       </c>
-      <c r="AL2" s="121">
+      <c r="AL2" s="74">
         <v>4</v>
       </c>
-      <c r="AM2" s="121">
+      <c r="AM2" s="74">
         <v>1</v>
       </c>
       <c r="AP2" s="7" t="s">
@@ -2192,8 +2256,17 @@
       <c r="AR2" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="72" t="s">
         <v>236</v>
+      </c>
+      <c r="AV2" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="AW2" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AX2" s="8">
+        <v>0.6</v>
       </c>
       <c r="BB2" s="7" t="s">
         <v>240</v>
@@ -2201,79 +2274,79 @@
       <c r="BD2" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="BF2" s="118" t="s">
+      <c r="BF2" s="72" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="2:58" ht="24.05" customHeight="1">
+    <row r="3" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="117" t="s">
+      <c r="W3" s="83" t="s">
         <v>225</v>
       </c>
-      <c r="X3" s="116"/>
-      <c r="Y3" s="116"/>
-      <c r="Z3" s="116"/>
-      <c r="AA3" s="117" t="s">
+      <c r="X3" s="84"/>
+      <c r="Y3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="116"/>
-      <c r="AD3" s="116"/>
-      <c r="AE3" s="117" t="s">
+      <c r="AB3" s="84"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="84"/>
+      <c r="AE3" s="83" t="s">
         <v>227</v>
       </c>
-      <c r="AF3" s="116"/>
-      <c r="AG3" s="116"/>
-      <c r="AH3" s="116"/>
-      <c r="AJ3" s="122" t="s">
+      <c r="AF3" s="84"/>
+      <c r="AG3" s="84"/>
+      <c r="AH3" s="84"/>
+      <c r="AJ3" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" s="122"/>
-      <c r="AL3" s="122"/>
-      <c r="AM3" s="122"/>
-      <c r="AN3" s="122"/>
-      <c r="AO3" s="122"/>
-      <c r="AP3" s="122"/>
-      <c r="AQ3" s="122"/>
-      <c r="AR3" s="122"/>
-      <c r="AS3" s="122"/>
-      <c r="AT3" s="122"/>
-      <c r="AV3" s="119" t="s">
-        <v>59</v>
-      </c>
-      <c r="AW3" s="119"/>
-      <c r="AX3" s="119"/>
-      <c r="AY3" s="119"/>
-      <c r="AZ3" s="119"/>
-      <c r="BA3" s="119"/>
-      <c r="BB3" s="119"/>
-      <c r="BC3" s="119"/>
-      <c r="BD3" s="119"/>
-      <c r="BE3" s="119"/>
-      <c r="BF3" s="119"/>
-    </row>
-    <row r="4" spans="2:58" ht="24.05" customHeight="1">
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="85"/>
+      <c r="AM3" s="85"/>
+      <c r="AN3" s="85"/>
+      <c r="AO3" s="85"/>
+      <c r="AP3" s="85"/>
+      <c r="AQ3" s="85"/>
+      <c r="AR3" s="85"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AV3" s="129" t="s">
+        <v>244</v>
+      </c>
+      <c r="AW3" s="82"/>
+      <c r="AX3" s="82"/>
+      <c r="AY3" s="82"/>
+      <c r="AZ3" s="82"/>
+      <c r="BA3" s="82"/>
+      <c r="BB3" s="82"/>
+      <c r="BC3" s="82"/>
+      <c r="BD3" s="82"/>
+      <c r="BE3" s="82"/>
+      <c r="BF3" s="82"/>
+    </row>
+    <row r="4" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
         <v>71</v>
       </c>
@@ -2318,42 +2391,42 @@
       <c r="T4" s="21"/>
       <c r="U4" s="21"/>
       <c r="V4" s="21"/>
-      <c r="W4" s="115"/>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
-      <c r="AC4" s="115"/>
-      <c r="AD4" s="115"/>
-      <c r="AE4" s="115"/>
-      <c r="AF4" s="115"/>
-      <c r="AG4" s="115"/>
-      <c r="AH4" s="115"/>
-      <c r="AJ4" s="72"/>
-      <c r="AK4" s="72"/>
-      <c r="AL4" s="72"/>
-      <c r="AM4" s="72"/>
-      <c r="AN4" s="72"/>
-      <c r="AO4" s="72"/>
-      <c r="AP4" s="72"/>
-      <c r="AQ4" s="72"/>
-      <c r="AR4" s="72"/>
-      <c r="AS4" s="72"/>
-      <c r="AT4" s="72"/>
-      <c r="AV4" s="72"/>
-      <c r="AW4" s="72"/>
-      <c r="AX4" s="72"/>
-      <c r="AY4" s="72"/>
-      <c r="AZ4" s="72"/>
-      <c r="BA4" s="72"/>
-      <c r="BB4" s="72"/>
-      <c r="BC4" s="72"/>
-      <c r="BD4" s="72"/>
-      <c r="BE4" s="72"/>
-      <c r="BF4" s="72"/>
-    </row>
-    <row r="5" spans="2:58" ht="24.05" customHeight="1">
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="71"/>
+      <c r="AB4" s="71"/>
+      <c r="AC4" s="71"/>
+      <c r="AD4" s="71"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="71"/>
+      <c r="AG4" s="71"/>
+      <c r="AH4" s="71"/>
+      <c r="AJ4" s="86"/>
+      <c r="AK4" s="86"/>
+      <c r="AL4" s="86"/>
+      <c r="AM4" s="86"/>
+      <c r="AN4" s="86"/>
+      <c r="AO4" s="86"/>
+      <c r="AP4" s="86"/>
+      <c r="AQ4" s="86"/>
+      <c r="AR4" s="86"/>
+      <c r="AS4" s="86"/>
+      <c r="AT4" s="86"/>
+      <c r="AV4" s="86"/>
+      <c r="AW4" s="86"/>
+      <c r="AX4" s="86"/>
+      <c r="AY4" s="86"/>
+      <c r="AZ4" s="86"/>
+      <c r="BA4" s="86"/>
+      <c r="BB4" s="86"/>
+      <c r="BC4" s="86"/>
+      <c r="BD4" s="86"/>
+      <c r="BE4" s="86"/>
+      <c r="BF4" s="86"/>
+    </row>
+    <row r="5" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
       <c r="D5" s="12" t="s">
         <v>49</v>
@@ -2415,38 +2488,38 @@
       <c r="W5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="X5" s="127" t="s">
+      <c r="X5" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="Y5" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z5" s="127" t="s">
-        <v>68</v>
+      <c r="Y5" s="128" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z5" s="79" t="s">
+        <v>242</v>
       </c>
       <c r="AA5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="126" t="s">
+      <c r="AB5" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="AC5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD5" s="126" t="s">
-        <v>68</v>
+      <c r="AC5" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="AD5" s="78" t="s">
+        <v>242</v>
       </c>
       <c r="AE5" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="AF5" s="125" t="s">
+      <c r="AF5" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AG5" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH5" s="125" t="s">
-        <v>68</v>
+      <c r="AG5" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="AH5" s="77" t="s">
+        <v>242</v>
       </c>
       <c r="AJ5" s="12" t="s">
         <v>53</v>
@@ -2466,19 +2539,19 @@
       <c r="AO5" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="AP5" s="123" t="s">
+      <c r="AP5" s="75" t="s">
         <v>233</v>
       </c>
       <c r="AQ5" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="AR5" s="123" t="s">
+      <c r="AR5" s="75" t="s">
         <v>234</v>
       </c>
       <c r="AS5" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="AT5" s="123" t="s">
+      <c r="AT5" s="75" t="s">
         <v>235</v>
       </c>
       <c r="AV5" s="12" t="s">
@@ -2499,24 +2572,24 @@
       <c r="BA5" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="BB5" s="123" t="s">
+      <c r="BB5" s="75" t="s">
         <v>233</v>
       </c>
       <c r="BC5" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="BD5" s="123" t="s">
+      <c r="BD5" s="75" t="s">
         <v>234</v>
       </c>
       <c r="BE5" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="BF5" s="123" t="s">
+      <c r="BF5" s="75" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B6" s="73">
+    <row r="6" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="81">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2588,49 +2661,49 @@
         <f>CALC_DMG(AJ6,T6,$D$2, P6)</f>
         <v>0.5</v>
       </c>
-      <c r="X6" s="127">
+      <c r="X6" s="79">
         <f>K6/W6</f>
         <v>44</v>
       </c>
-      <c r="Y6" s="12">
-        <f>CALC_DMG(AV6,T6,$D$2, P6)</f>
-        <v>0.79999999999999982</v>
-      </c>
-      <c r="Z6" s="127">
-        <f>K6/Y6</f>
-        <v>27.500000000000007</v>
+      <c r="Y6" s="12" t="e">
+        <f ca="1">CALC_DMG(AV6,T6,$D$2, P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z6" s="79" t="e">
+        <f ca="1">K6/Y6</f>
+        <v>#NAME?</v>
       </c>
       <c r="AA6" s="15">
         <f>CALC_DMG(AJ6,U6,$D$2,P6)</f>
         <v>1.5</v>
       </c>
-      <c r="AB6" s="126">
+      <c r="AB6" s="78">
         <f>L6/AA6</f>
         <v>14</v>
       </c>
-      <c r="AC6" s="15">
-        <f>CALC_DMG(AV6,U6,$D$2,P6)</f>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AD6" s="126">
-        <f>L6/AC6</f>
-        <v>9.1304347826086971</v>
+      <c r="AC6" s="15" t="e">
+        <f ca="1">CALC_DMG(AV6,U6,$D$2,P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD6" s="78" t="e">
+        <f ca="1">L6/AC6</f>
+        <v>#NAME?</v>
       </c>
       <c r="AE6" s="22">
         <f>CALC_DMG(AJ6,V6,$D$2,P6)</f>
         <v>3</v>
       </c>
-      <c r="AF6" s="125">
+      <c r="AF6" s="77">
         <f>M6/AE6</f>
         <v>6.666666666666667</v>
       </c>
-      <c r="AG6" s="22">
-        <f>CALC_DMG(AV6,V6,$D$2,P6)</f>
-        <v>3.8</v>
-      </c>
-      <c r="AH6" s="125">
-        <f>M6/AG6</f>
-        <v>5.2631578947368425</v>
+      <c r="AG6" s="22" t="e">
+        <f ca="1">CALC_DMG(AV6,V6,$D$2,P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH6" s="77" t="e">
+        <f ca="1">M6/AG6</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI6" s="8">
         <v>0</v>
@@ -2655,7 +2728,7 @@
         <f>CALC_DMG(Q6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(Q6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(Q6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
         <v>16.760159999999999</v>
       </c>
-      <c r="AP6" s="123">
+      <c r="AP6" s="75">
         <f>AK6/AO6</f>
         <v>1.1933060304913559</v>
       </c>
@@ -2663,7 +2736,7 @@
         <f>CALC_DMG(R6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(R6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(R6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
         <v>10.912800000000001</v>
       </c>
-      <c r="AR6" s="123">
+      <c r="AR6" s="75">
         <f>AK6/AQ6</f>
         <v>1.8327102118613003</v>
       </c>
@@ -2671,20 +2744,20 @@
         <f>CALC_DMG(S6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(S6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(S6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
         <v>7.0399999999999991</v>
       </c>
-      <c r="AT6" s="123">
+      <c r="AT6" s="75">
         <f>AK6/AS6</f>
         <v>2.8409090909090913</v>
       </c>
       <c r="AV6" s="12">
-        <f>AJ6*1.2</f>
+        <f>AJ6*$AV$2</f>
         <v>4.8</v>
       </c>
       <c r="AW6" s="15">
-        <f>AK6*0.6</f>
+        <f>AK6*$AW$2</f>
         <v>12</v>
       </c>
       <c r="AX6" s="16">
-        <f>AL6*0.6</f>
+        <f>AL6*$AX$2</f>
         <v>1.2</v>
       </c>
       <c r="AY6" s="17">
@@ -2695,32 +2768,32 @@
         <v>1.2</v>
       </c>
       <c r="BA6" s="20">
-        <f>CALC_DMG(Q6*$AK$1,AZ6,$AI$2,1)*$AK$2+CALC_DMG(Q6*$AL$1,AZ6,$AI$2,1)*$AL$2+CALC_DMG(Q6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
-        <v>23.960159999999998</v>
-      </c>
-      <c r="BB6" s="123">
+        <f>[1]!CALC_DMG(Q6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
+        <v>23.96</v>
+      </c>
+      <c r="BB6" s="75">
         <f>AW6/BA6</f>
-        <v>0.50083138009095096</v>
+        <v>0.5008347245409015</v>
       </c>
       <c r="BC6" s="20">
-        <f>CALC_DMG(R6*$AK$1,AZ6,$AI$2,1)*$AK$2+CALC_DMG(R6*$AL$1,AZ6,$AI$2,1)*$AL$2+CALC_DMG(R6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
-        <v>18.052079999999997</v>
-      </c>
-      <c r="BD6" s="123">
+        <f>[1]!CALC_DMG(R6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(R6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(R6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
+        <v>18.052</v>
+      </c>
+      <c r="BD6" s="75">
         <f>AW6/BC6</f>
-        <v>0.664743342595424</v>
+        <v>0.66474628849988926</v>
       </c>
       <c r="BE6" s="20">
-        <f>CALC_DMG(S6*$AK$1,AZ6,$AI$2,1)*$AK$2+CALC_DMG(S6*$AL$1,AZ6,$AI$2,1)*$AL$2+CALC_DMG(S6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
-        <v>12.143999999999998</v>
-      </c>
-      <c r="BF6" s="123">
+        <f>[1]!CALC_DMG(S6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(S6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(S6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
+        <v>12.144000000000002</v>
+      </c>
+      <c r="BF6" s="75">
         <f>AW6/BE6</f>
-        <v>0.98814229249011876</v>
-      </c>
-    </row>
-    <row r="7" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B7" s="73"/>
+        <v>0.98814229249011842</v>
+      </c>
+    </row>
+    <row r="7" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="81"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2790,49 +2863,49 @@
         <f t="shared" ref="W7:W10" si="2">CALC_DMG(AJ7,T7,$D$2, P7)</f>
         <v>0.5</v>
       </c>
-      <c r="X7" s="127">
+      <c r="X7" s="79">
         <f t="shared" ref="X7:X10" si="3">K7/W7</f>
         <v>80</v>
       </c>
-      <c r="Y7" s="12">
-        <f t="shared" ref="Y7:Y10" si="4">CALC_DMG(AV7,T7,$D$2, P7)</f>
-        <v>1.2799999999999994</v>
-      </c>
-      <c r="Z7" s="127">
-        <f t="shared" ref="Z7:Z10" si="5">K7/Y7</f>
-        <v>31.250000000000014</v>
+      <c r="Y7" s="12" t="e">
+        <f t="shared" ref="Y7:Y10" ca="1" si="4">CALC_DMG(AV7,T7,$D$2, P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z7" s="79" t="e">
+        <f t="shared" ref="Z7:Z10" ca="1" si="5">K7/Y7</f>
+        <v>#NAME?</v>
       </c>
       <c r="AA7" s="15">
         <f t="shared" ref="AA7:AA10" si="6">CALC_DMG(AJ7,U7,$D$2,P7)</f>
         <v>2.34</v>
       </c>
-      <c r="AB7" s="126">
+      <c r="AB7" s="78">
         <f t="shared" ref="AB7:AB10" si="7">L7/AA7</f>
         <v>13.888888888888889</v>
       </c>
-      <c r="AC7" s="15">
-        <f t="shared" ref="AC7:AC10" si="8">CALC_DMG(AV7,U7,$D$2,P7)</f>
-        <v>3.9399999999999995</v>
-      </c>
-      <c r="AD7" s="126">
-        <f t="shared" ref="AD7:AD10" si="9">L7/AC7</f>
-        <v>8.2487309644670059</v>
+      <c r="AC7" s="15" t="e">
+        <f t="shared" ref="AC7:AC10" ca="1" si="8">CALC_DMG(AV7,U7,$D$2,P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD7" s="78" t="e">
+        <f t="shared" ref="AD7:AD10" ca="1" si="9">L7/AC7</f>
+        <v>#NAME?</v>
       </c>
       <c r="AE7" s="22">
         <f t="shared" ref="AE7:AE10" si="10">CALC_DMG(AJ7,V7,$D$2,P7)</f>
         <v>5</v>
       </c>
-      <c r="AF7" s="125">
+      <c r="AF7" s="77">
         <f t="shared" ref="AF7:AF21" si="11">M7/AE7</f>
         <v>5</v>
       </c>
-      <c r="AG7" s="22">
-        <f t="shared" ref="AG7:AG10" si="12">CALC_DMG(AV7,V7,$D$2,P7)</f>
-        <v>6.6</v>
-      </c>
-      <c r="AH7" s="125">
-        <f t="shared" ref="AH7:AH10" si="13">M7/AG7</f>
-        <v>3.7878787878787881</v>
+      <c r="AG7" s="22" t="e">
+        <f t="shared" ref="AG7:AG10" ca="1" si="12">CALC_DMG(AV7,V7,$D$2,P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH7" s="77" t="e">
+        <f t="shared" ref="AH7:AH10" ca="1" si="13">M7/AG7</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI7" s="7" t="s">
         <v>93</v>
@@ -2857,7 +2930,7 @@
         <f>CALC_DMG(Q7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(Q7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(Q7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
         <v>67.162392000000011</v>
       </c>
-      <c r="AP7" s="123">
+      <c r="AP7" s="75">
         <f>AK7/AO7</f>
         <v>0.67001782783436292</v>
       </c>
@@ -2865,7 +2938,7 @@
         <f>CALC_DMG(R7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(R7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(R7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
         <v>41.789196000000004</v>
       </c>
-      <c r="AR7" s="123">
+      <c r="AR7" s="75">
         <f>AK7/AQ7</f>
         <v>1.0768333518548669</v>
       </c>
@@ -2873,20 +2946,20 @@
         <f>CALC_DMG(S7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(S7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(S7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
         <v>16.415999999999997</v>
       </c>
-      <c r="AT7" s="123">
+      <c r="AT7" s="75">
         <f>AK7/AS7</f>
         <v>2.7412280701754392</v>
       </c>
       <c r="AV7" s="12">
-        <f t="shared" ref="AV7:AV10" si="14">AJ7*1.2</f>
+        <f t="shared" ref="AV7:AV10" si="14">AJ7*$AV$2</f>
         <v>9.6</v>
       </c>
       <c r="AW7" s="15">
-        <f t="shared" ref="AW7:AW10" si="15">AK7*0.6</f>
+        <f t="shared" ref="AW7:AW10" si="15">AK7*$AW$2</f>
         <v>27</v>
       </c>
       <c r="AX7" s="16">
-        <f t="shared" ref="AX7:AX10" si="16">AL7*0.6</f>
+        <f t="shared" ref="AX7:AX10" si="16">AL7*$AX$2</f>
         <v>1.2</v>
       </c>
       <c r="AY7" s="17">
@@ -2897,32 +2970,32 @@
         <v>1.2</v>
       </c>
       <c r="BA7" s="20">
-        <f>CALC_DMG(Q7*$AK$1,AZ7,$AI$2,1)*$AK$2+CALC_DMG(Q7*$AL$1,AZ7,$AI$2,1)*$AL$2+CALC_DMG(Q7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
-        <v>74.362392</v>
-      </c>
-      <c r="BB7" s="123">
+        <f>[1]!CALC_DMG(Q7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
+        <v>74.362200000000001</v>
+      </c>
+      <c r="BB7" s="75">
         <f t="shared" ref="BB7:BB10" si="17">AW7/BA7</f>
-        <v>0.36308676030754899</v>
+        <v>0.36308769778193761</v>
       </c>
       <c r="BC7" s="20">
-        <f>CALC_DMG(R7*$AK$1,AZ7,$AI$2,1)*$AK$2+CALC_DMG(R7*$AL$1,AZ7,$AI$2,1)*$AL$2+CALC_DMG(R7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
-        <v>48.989196</v>
-      </c>
-      <c r="BD7" s="123">
+        <f>[1]!CALC_DMG(R7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(R7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(R7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
+        <v>48.989100000000001</v>
+      </c>
+      <c r="BD7" s="75">
         <f t="shared" ref="BD7:BD10" si="18">AW7/BC7</f>
-        <v>0.55114192933478634</v>
+        <v>0.55114300936330729</v>
       </c>
       <c r="BE7" s="20">
-        <f>CALC_DMG(S7*$AK$1,AZ7,$AI$2,1)*$AK$2+CALC_DMG(S7*$AL$1,AZ7,$AI$2,1)*$AL$2+CALC_DMG(S7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(S7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(S7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
         <v>23.616</v>
       </c>
-      <c r="BF7" s="123">
+      <c r="BF7" s="75">
         <f t="shared" ref="BF7:BF10" si="19">AW7/BE7</f>
         <v>1.1432926829268293</v>
       </c>
     </row>
-    <row r="8" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B8" s="73">
+    <row r="8" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="81">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -2994,49 +3067,49 @@
         <f t="shared" si="2"/>
         <v>1.7649999999999988</v>
       </c>
-      <c r="X8" s="127">
+      <c r="X8" s="79">
         <f t="shared" si="3"/>
         <v>56.657223796034032</v>
       </c>
-      <c r="Y8" s="12">
-        <f t="shared" si="4"/>
-        <v>4.7099999999999973</v>
-      </c>
-      <c r="Z8" s="127">
-        <f t="shared" si="5"/>
-        <v>21.231422505307869</v>
+      <c r="Y8" s="12" t="e">
+        <f t="shared" ca="1" si="4"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z8" s="79" t="e">
+        <f t="shared" ca="1" si="5"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA8" s="15">
         <f t="shared" si="6"/>
         <v>4.2449999999999992</v>
       </c>
-      <c r="AB8" s="126">
+      <c r="AB8" s="78">
         <f t="shared" si="7"/>
         <v>16.489988221436988</v>
       </c>
-      <c r="AC8" s="15">
-        <f t="shared" si="8"/>
-        <v>7.1899999999999977</v>
-      </c>
-      <c r="AD8" s="126">
-        <f t="shared" si="9"/>
-        <v>9.7357440890125204</v>
+      <c r="AC8" s="15" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD8" s="78" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE8" s="22">
         <f t="shared" si="10"/>
         <v>6.7249999999999996</v>
       </c>
-      <c r="AF8" s="125">
+      <c r="AF8" s="77">
         <f t="shared" si="11"/>
         <v>5.947955390334573</v>
       </c>
-      <c r="AG8" s="22">
-        <f t="shared" si="12"/>
-        <v>9.6699999999999982</v>
-      </c>
-      <c r="AH8" s="125">
-        <f t="shared" si="13"/>
-        <v>4.1365046535677363</v>
+      <c r="AG8" s="22" t="e">
+        <f t="shared" ca="1" si="12"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH8" s="77" t="e">
+        <f t="shared" ca="1" si="13"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI8" s="8">
         <v>1</v>
@@ -3061,7 +3134,7 @@
         <f>CALC_DMG(Q8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(Q8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(Q8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
         <v>127.75176000000002</v>
       </c>
-      <c r="AP8" s="123">
+      <c r="AP8" s="75">
         <f>AK8/AO8</f>
         <v>1.095875313185509</v>
       </c>
@@ -3069,7 +3142,7 @@
         <f>CALC_DMG(R8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(R8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(R8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
         <v>89.291880000000006</v>
       </c>
-      <c r="AR8" s="123">
+      <c r="AR8" s="75">
         <f>AK8/AQ8</f>
         <v>1.567891727668854</v>
       </c>
@@ -3077,7 +3150,7 @@
         <f>CALC_DMG(S8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(S8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(S8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
         <v>50.831999999999994</v>
       </c>
-      <c r="AT8" s="123">
+      <c r="AT8" s="75">
         <f>AK8/AS8</f>
         <v>2.7541706011960971</v>
       </c>
@@ -3101,32 +3174,32 @@
         <v>1.2</v>
       </c>
       <c r="BA8" s="20">
-        <f>CALC_DMG(Q8*$AK$1,AZ8,$AI$2,1)*$AK$2+CALC_DMG(Q8*$AL$1,AZ8,$AI$2,1)*$AL$2+CALC_DMG(Q8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
-        <v>134.95176000000004</v>
-      </c>
-      <c r="BB8" s="123">
+        <f>[1]!CALC_DMG(Q8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
+        <v>134.95159999999998</v>
+      </c>
+      <c r="BB8" s="75">
         <f t="shared" si="17"/>
-        <v>0.62244464244112097</v>
+        <v>0.62244538041786845</v>
       </c>
       <c r="BC8" s="20">
-        <f>CALC_DMG(R8*$AK$1,AZ8,$AI$2,1)*$AK$2+CALC_DMG(R8*$AL$1,AZ8,$AI$2,1)*$AL$2+CALC_DMG(R8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
-        <v>96.491880000000009</v>
-      </c>
-      <c r="BD8" s="123">
+        <f>[1]!CALC_DMG(R8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(R8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(R8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
+        <v>96.492199999999997</v>
+      </c>
+      <c r="BD8" s="75">
         <f t="shared" si="18"/>
-        <v>0.87053957286354033</v>
+        <v>0.87053668586683697</v>
       </c>
       <c r="BE8" s="20">
-        <f>CALC_DMG(S8*$AK$1,AZ8,$AI$2,1)*$AK$2+CALC_DMG(S8*$AL$1,AZ8,$AI$2,1)*$AL$2+CALC_DMG(S8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(S8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(S8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
         <v>58.031999999999996</v>
       </c>
-      <c r="BF8" s="123">
+      <c r="BF8" s="75">
         <f t="shared" si="19"/>
         <v>1.4474772539288669</v>
       </c>
     </row>
-    <row r="9" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B9" s="73"/>
+    <row r="9" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="81"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3196,49 +3269,49 @@
         <f t="shared" si="2"/>
         <v>12.479999999999997</v>
       </c>
-      <c r="X9" s="127">
+      <c r="X9" s="79">
         <f t="shared" si="3"/>
         <v>16.025641025641029</v>
       </c>
-      <c r="Y9" s="12">
-        <f t="shared" si="4"/>
-        <v>18.559999999999995</v>
-      </c>
-      <c r="Z9" s="127">
-        <f t="shared" si="5"/>
-        <v>10.77586206896552</v>
+      <c r="Y9" s="12" t="e">
+        <f t="shared" ca="1" si="4"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z9" s="79" t="e">
+        <f t="shared" ca="1" si="5"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA9" s="15">
         <f t="shared" si="6"/>
         <v>15.439999999999998</v>
       </c>
-      <c r="AB9" s="126">
+      <c r="AB9" s="78">
         <f t="shared" si="7"/>
         <v>9.7150259067357521</v>
       </c>
-      <c r="AC9" s="15">
-        <f t="shared" si="8"/>
-        <v>21.519999999999996</v>
-      </c>
-      <c r="AD9" s="126">
-        <f t="shared" si="9"/>
-        <v>6.9702602230483288</v>
+      <c r="AC9" s="15" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD9" s="78" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE9" s="22">
         <f t="shared" si="10"/>
         <v>18.399999999999999</v>
       </c>
-      <c r="AF9" s="125">
+      <c r="AF9" s="77">
         <f t="shared" si="11"/>
         <v>5.4347826086956523</v>
       </c>
-      <c r="AG9" s="22">
-        <f t="shared" si="12"/>
-        <v>24.479999999999997</v>
-      </c>
-      <c r="AH9" s="125">
-        <f t="shared" si="13"/>
-        <v>4.0849673202614385</v>
+      <c r="AG9" s="22" t="e">
+        <f t="shared" ca="1" si="12"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH9" s="77" t="e">
+        <f t="shared" ca="1" si="13"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI9" s="36" t="s">
         <v>92</v>
@@ -3263,7 +3336,7 @@
         <f>CALC_DMG(Q9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(Q9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(Q9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
         <v>191.73024000000001</v>
       </c>
-      <c r="AP9" s="123">
+      <c r="AP9" s="75">
         <f>AK9/AO9</f>
         <v>1.0952888808776331</v>
       </c>
@@ -3271,7 +3344,7 @@
         <f>CALC_DMG(R9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(R9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(R9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
         <v>131.96111999999999</v>
       </c>
-      <c r="AR9" s="123">
+      <c r="AR9" s="75">
         <f>AK9/AQ9</f>
         <v>1.5913778240136187</v>
       </c>
@@ -3279,7 +3352,7 @@
         <f>CALC_DMG(S9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(S9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(S9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
         <v>72.192000000000007</v>
       </c>
-      <c r="AT9" s="123">
+      <c r="AT9" s="75">
         <f>AK9/AS9</f>
         <v>2.9089095744680846</v>
       </c>
@@ -3303,32 +3376,32 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="BA9" s="20">
-        <f>CALC_DMG(Q9*$AK$1,AZ9,$AI$2,1)*$AK$2+CALC_DMG(Q9*$AL$1,AZ9,$AI$2,1)*$AL$2+CALC_DMG(Q9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
-        <v>213.33024000000003</v>
-      </c>
-      <c r="BB9" s="123">
+        <f>[1]!CALC_DMG(Q9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
+        <v>213.3304</v>
+      </c>
+      <c r="BB9" s="75">
         <f t="shared" si="17"/>
-        <v>0.59063356418668067</v>
+        <v>0.59063312120541656</v>
       </c>
       <c r="BC9" s="20">
-        <f>CALC_DMG(R9*$AK$1,AZ9,$AI$2,1)*$AK$2+CALC_DMG(R9*$AL$1,AZ9,$AI$2,1)*$AL$2+CALC_DMG(R9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
-        <v>153.56111999999999</v>
-      </c>
-      <c r="BD9" s="123">
+        <f>[1]!CALC_DMG(R9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(R9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(R9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
+        <v>153.56119999999999</v>
+      </c>
+      <c r="BD9" s="75">
         <f t="shared" si="18"/>
-        <v>0.82052019417415034</v>
+        <v>0.82051976671190385</v>
       </c>
       <c r="BE9" s="20">
-        <f>CALC_DMG(S9*$AK$1,AZ9,$AI$2,1)*$AK$2+CALC_DMG(S9*$AL$1,AZ9,$AI$2,1)*$AL$2+CALC_DMG(S9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(S9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(S9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
         <v>93.792000000000002</v>
       </c>
-      <c r="BF9" s="123">
+      <c r="BF9" s="75">
         <f t="shared" si="19"/>
         <v>1.3433981576253837</v>
       </c>
     </row>
-    <row r="10" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B10" s="74">
+    <row r="10" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="87">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3400,49 +3473,49 @@
         <f t="shared" si="2"/>
         <v>19.100000000000005</v>
       </c>
-      <c r="X10" s="127">
+      <c r="X10" s="79">
         <f t="shared" si="3"/>
         <v>17.801047120418843</v>
       </c>
-      <c r="Y10" s="12">
-        <f t="shared" si="4"/>
-        <v>27.56</v>
-      </c>
-      <c r="Z10" s="127">
-        <f t="shared" si="5"/>
-        <v>12.336719883889696</v>
+      <c r="Y10" s="12" t="e">
+        <f t="shared" ca="1" si="4"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z10" s="79" t="e">
+        <f t="shared" ca="1" si="5"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA10" s="15">
         <f t="shared" si="6"/>
         <v>22.200000000000003</v>
       </c>
-      <c r="AB10" s="126">
+      <c r="AB10" s="78">
         <f t="shared" si="7"/>
         <v>10.360360360360358</v>
       </c>
-      <c r="AC10" s="15">
-        <f t="shared" si="8"/>
-        <v>30.659999999999997</v>
-      </c>
-      <c r="AD10" s="126">
-        <f t="shared" si="9"/>
-        <v>7.5016307893020233</v>
+      <c r="AC10" s="15" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD10" s="78" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE10" s="22">
         <f t="shared" si="10"/>
         <v>25.300000000000004</v>
       </c>
-      <c r="AF10" s="125">
+      <c r="AF10" s="77">
         <f t="shared" si="11"/>
         <v>4.7430830039525684</v>
       </c>
-      <c r="AG10" s="22">
-        <f t="shared" si="12"/>
-        <v>33.76</v>
-      </c>
-      <c r="AH10" s="125">
-        <f t="shared" si="13"/>
-        <v>3.5545023696682465</v>
+      <c r="AG10" s="22" t="e">
+        <f t="shared" ca="1" si="12"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH10" s="77" t="e">
+        <f t="shared" ca="1" si="13"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI10" s="7" t="s">
         <v>92</v>
@@ -3467,7 +3540,7 @@
         <f>CALC_DMG(Q10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(Q10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(Q10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
         <v>369.33888000000002</v>
       </c>
-      <c r="AP10" s="123">
+      <c r="AP10" s="75">
         <f>AK10/AO10</f>
         <v>0.81226216963673037</v>
       </c>
@@ -3475,7 +3548,7 @@
         <f>CALC_DMG(R10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(R10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(R10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
         <v>225.70944000000003</v>
       </c>
-      <c r="AR10" s="123">
+      <c r="AR10" s="75">
         <f>AK10/AQ10</f>
         <v>1.3291424585520215</v>
       </c>
@@ -3483,7 +3556,7 @@
         <f>CALC_DMG(S10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(S10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(S10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
         <v>82.08</v>
       </c>
-      <c r="AT10" s="123">
+      <c r="AT10" s="75">
         <f>AK10/AS10</f>
         <v>3.6549707602339181</v>
       </c>
@@ -3507,47 +3580,47 @@
         <v>6</v>
       </c>
       <c r="BA10" s="20">
-        <f>CALC_DMG(Q10*$AK$1,AZ10,$AI$2,1)*$AK$2+CALC_DMG(Q10*$AL$1,AZ10,$AI$2,1)*$AL$2+CALC_DMG(Q10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
-        <v>405.33888000000002</v>
-      </c>
-      <c r="BB10" s="123">
+        <f>[1]!CALC_DMG(Q10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
+        <v>405.33879999999999</v>
+      </c>
+      <c r="BB10" s="75">
         <f t="shared" si="17"/>
-        <v>0.44407287058177097</v>
+        <v>0.44407295822655024</v>
       </c>
       <c r="BC10" s="20">
-        <f>CALC_DMG(R10*$AK$1,AZ10,$AI$2,1)*$AK$2+CALC_DMG(R10*$AL$1,AZ10,$AI$2,1)*$AL$2+CALC_DMG(R10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
-        <v>261.70944000000003</v>
-      </c>
-      <c r="BD10" s="123">
+        <f>[1]!CALC_DMG(R10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(R10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(R10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
+        <v>261.70960000000002</v>
+      </c>
+      <c r="BD10" s="75">
         <f t="shared" si="18"/>
-        <v>0.6877856603109157</v>
+        <v>0.68778523982307105</v>
       </c>
       <c r="BE10" s="20">
-        <f>CALC_DMG(S10*$AK$1,AZ10,$AI$2,1)*$AK$2+CALC_DMG(S10*$AL$1,AZ10,$AI$2,1)*$AL$2+CALC_DMG(S10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(S10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(S10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
         <v>118.08</v>
       </c>
-      <c r="BF10" s="123">
+      <c r="BF10" s="75">
         <f t="shared" si="19"/>
         <v>1.524390243902439</v>
       </c>
     </row>
-    <row r="11" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B11" s="74"/>
-      <c r="X11" s="124"/>
-      <c r="Z11" s="124"/>
-      <c r="AB11" s="124"/>
-      <c r="AD11" s="124"/>
-      <c r="AF11" s="124"/>
-      <c r="AH11" s="124"/>
-      <c r="AP11" s="124"/>
-      <c r="AR11" s="124"/>
-      <c r="AT11" s="124"/>
-      <c r="BB11" s="124"/>
-      <c r="BD11" s="124"/>
-      <c r="BF11" s="124"/>
-    </row>
-    <row r="12" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B12" s="74"/>
+    <row r="11" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="87"/>
+      <c r="X11" s="76"/>
+      <c r="Z11" s="76"/>
+      <c r="AB11" s="76"/>
+      <c r="AD11" s="76"/>
+      <c r="AF11" s="76"/>
+      <c r="AH11" s="76"/>
+      <c r="AP11" s="76"/>
+      <c r="AR11" s="76"/>
+      <c r="AT11" s="76"/>
+      <c r="BB11" s="76"/>
+      <c r="BD11" s="76"/>
+      <c r="BF11" s="76"/>
+    </row>
+    <row r="12" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="87"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3617,49 +3690,49 @@
         <f t="shared" ref="W12:W14" si="24">CALC_DMG(AJ12,T12,$D$2, P12)</f>
         <v>30.299999999999997</v>
       </c>
-      <c r="X12" s="127">
+      <c r="X12" s="79">
         <f t="shared" ref="X12:X14" si="25">K12/W12</f>
         <v>17.821782178217823</v>
       </c>
-      <c r="Y12" s="12">
-        <f t="shared" ref="Y12:Y14" si="26">CALC_DMG(AV12,T12,$D$2, P12)</f>
-        <v>45.959999999999994</v>
-      </c>
-      <c r="Z12" s="127">
-        <f t="shared" ref="Z12:Z14" si="27">K12/Y12</f>
-        <v>11.749347258485642</v>
+      <c r="Y12" s="12" t="e">
+        <f t="shared" ref="Y12:Y14" ca="1" si="26">CALC_DMG(AV12,T12,$D$2, P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z12" s="79" t="e">
+        <f t="shared" ref="Z12:Z14" ca="1" si="27">K12/Y12</f>
+        <v>#NAME?</v>
       </c>
       <c r="AA12" s="15">
         <f t="shared" ref="AA12:AA14" si="28">CALC_DMG(AJ12,U12,$D$2,P12)</f>
         <v>44.3</v>
       </c>
-      <c r="AB12" s="126">
+      <c r="AB12" s="78">
         <f t="shared" ref="AB12:AB14" si="29">L12/AA12</f>
         <v>9.4808126410835225</v>
       </c>
-      <c r="AC12" s="15">
-        <f t="shared" ref="AC12:AC14" si="30">CALC_DMG(AV12,U12,$D$2,P12)</f>
-        <v>59.959999999999994</v>
-      </c>
-      <c r="AD12" s="126">
-        <f t="shared" ref="AD12:AD14" si="31">L12/AC12</f>
-        <v>7.004669779853236</v>
+      <c r="AC12" s="15" t="e">
+        <f t="shared" ref="AC12:AC14" ca="1" si="30">CALC_DMG(AV12,U12,$D$2,P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD12" s="78" t="e">
+        <f t="shared" ref="AD12:AD14" ca="1" si="31">L12/AC12</f>
+        <v>#NAME?</v>
       </c>
       <c r="AE12" s="22">
         <f t="shared" ref="AE12:AE14" si="32">CALC_DMG(AJ12,V12,$D$2,P12)</f>
         <v>58.3</v>
       </c>
-      <c r="AF12" s="125">
+      <c r="AF12" s="77">
         <f t="shared" si="11"/>
         <v>5.1457975986277873</v>
       </c>
-      <c r="AG12" s="22">
-        <f t="shared" ref="AG12:AG14" si="33">CALC_DMG(AV12,V12,$D$2,P12)</f>
-        <v>73.959999999999994</v>
-      </c>
-      <c r="AH12" s="125">
-        <f t="shared" ref="AH12:AH14" si="34">M12/AG12</f>
-        <v>4.056246619794484</v>
+      <c r="AG12" s="22" t="e">
+        <f t="shared" ref="AG12:AG14" ca="1" si="33">CALC_DMG(AV12,V12,$D$2,P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH12" s="77" t="e">
+        <f t="shared" ref="AH12:AH14" ca="1" si="34">M12/AG12</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI12" s="7" t="s">
         <v>92</v>
@@ -3684,7 +3757,7 @@
         <f>CALC_DMG(Q12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(Q12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(Q12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
         <v>586.50167999999985</v>
       </c>
-      <c r="AP12" s="123">
+      <c r="AP12" s="75">
         <f>AK12/AO12</f>
         <v>1.3640199632505745</v>
       </c>
@@ -3692,7 +3765,7 @@
         <f>CALC_DMG(R12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(R12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(R12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
         <v>409.74683999999985</v>
       </c>
-      <c r="AR12" s="123">
+      <c r="AR12" s="75">
         <f>AK12/AQ12</f>
         <v>1.952425063241489</v>
       </c>
@@ -3700,20 +3773,20 @@
         <f>CALC_DMG(S12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(S12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(S12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
         <v>232.99199999999996</v>
       </c>
-      <c r="AT12" s="123">
+      <c r="AT12" s="75">
         <f>AK12/AS12</f>
         <v>3.4335942864991078</v>
       </c>
       <c r="AV12" s="12">
-        <f t="shared" ref="AV12:AV14" si="36">AJ12*1.2</f>
+        <f t="shared" ref="AV12:AV14" si="36">AJ12*$AV$2</f>
         <v>104.39999999999999</v>
       </c>
       <c r="AW12" s="15">
-        <f t="shared" ref="AW12:AW14" si="37">AK12*0.6</f>
+        <f t="shared" ref="AW12:AW14" si="37">AK12*$AW$2</f>
         <v>480</v>
       </c>
       <c r="AX12" s="16">
-        <f t="shared" ref="AX12:AX14" si="38">AL12*0.6</f>
+        <f t="shared" ref="AX12:AX14" si="38">AL12*$AX$2</f>
         <v>12</v>
       </c>
       <c r="AY12" s="17">
@@ -3724,32 +3797,32 @@
         <v>12</v>
       </c>
       <c r="BA12" s="20">
-        <f>CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>658.50167999999985</v>
-      </c>
-      <c r="BB12" s="123">
+        <f>[1]!CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>658.50159999999994</v>
+      </c>
+      <c r="BB12" s="75">
         <f t="shared" ref="BB12:BB14" si="40">AW12/BA12</f>
-        <v>0.72892752528740723</v>
+        <v>0.7289276138433074</v>
       </c>
       <c r="BC12" s="20">
-        <f>CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>481.74683999999985</v>
-      </c>
-      <c r="BD12" s="123">
+        <f>[1]!CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>481.74700000000001</v>
+      </c>
+      <c r="BD12" s="75">
         <f t="shared" ref="BD12:BD14" si="41">AW12/BC12</f>
-        <v>0.99637394611659547</v>
+        <v>0.99637361519635825</v>
       </c>
       <c r="BE12" s="20">
-        <f>CALC_DMG(S12*$AK$1,AZ12,$AI$2,1)*$AK$2+CALC_DMG(S12*$AL$1,AZ12,$AI$2,1)*$AL$2+CALC_DMG(S12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>304.99199999999996</v>
-      </c>
-      <c r="BF12" s="123">
+        <f>[1]!CALC_DMG(S12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(S12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(S12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>304.99200000000002</v>
+      </c>
+      <c r="BF12" s="75">
         <f t="shared" ref="BF12:BF14" si="42">AW12/BE12</f>
-        <v>1.5738117721120557</v>
-      </c>
-    </row>
-    <row r="13" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B13" s="73">
+        <v>1.5738117721120553</v>
+      </c>
+    </row>
+    <row r="13" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="81">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3821,49 +3894,49 @@
         <f t="shared" si="24"/>
         <v>46.45</v>
       </c>
-      <c r="X13" s="127">
+      <c r="X13" s="79">
         <f t="shared" si="25"/>
         <v>15.931108719052745</v>
       </c>
-      <c r="Y13" s="12">
-        <f t="shared" si="26"/>
-        <v>71.100000000000009</v>
-      </c>
-      <c r="Z13" s="127">
-        <f t="shared" si="27"/>
-        <v>10.40787623066104</v>
+      <c r="Y13" s="12" t="e">
+        <f t="shared" ca="1" si="26"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z13" s="79" t="e">
+        <f t="shared" ca="1" si="27"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA13" s="15">
         <f t="shared" si="28"/>
         <v>63.85</v>
       </c>
-      <c r="AB13" s="126">
+      <c r="AB13" s="78">
         <f t="shared" si="29"/>
         <v>9.7102584181675802</v>
       </c>
-      <c r="AC13" s="15">
-        <f t="shared" si="30"/>
-        <v>88.5</v>
-      </c>
-      <c r="AD13" s="126">
-        <f t="shared" si="31"/>
-        <v>7.0056497175141246</v>
+      <c r="AC13" s="15" t="e">
+        <f t="shared" ca="1" si="30"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD13" s="78" t="e">
+        <f t="shared" ca="1" si="31"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE13" s="22">
         <f t="shared" si="32"/>
         <v>81.25</v>
       </c>
-      <c r="AF13" s="125">
+      <c r="AF13" s="77">
         <f t="shared" si="11"/>
         <v>6.1538461538461542</v>
       </c>
-      <c r="AG13" s="22">
-        <f t="shared" si="33"/>
-        <v>105.9</v>
-      </c>
-      <c r="AH13" s="125">
-        <f t="shared" si="34"/>
-        <v>4.7214353163361658</v>
+      <c r="AG13" s="22" t="e">
+        <f t="shared" ca="1" si="33"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH13" s="77" t="e">
+        <f t="shared" ca="1" si="34"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI13" s="8">
         <v>2</v>
@@ -3888,7 +3961,7 @@
         <f>CALC_DMG(Q13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(Q13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(Q13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
         <v>904.7879999999999</v>
       </c>
-      <c r="AP13" s="123">
+      <c r="AP13" s="75">
         <f>AK13/AO13</f>
         <v>1.2157544087675789</v>
       </c>
@@ -3896,7 +3969,7 @@
         <f>CALC_DMG(R13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(R13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(R13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
         <v>602.21399999999994</v>
       </c>
-      <c r="AR13" s="123">
+      <c r="AR13" s="75">
         <f>AK13/AQ13</f>
         <v>1.826593204409064</v>
       </c>
@@ -3904,7 +3977,7 @@
         <f>CALC_DMG(S13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(S13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(S13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
         <v>299.64</v>
       </c>
-      <c r="AT13" s="123">
+      <c r="AT13" s="75">
         <f>AK13/AS13</f>
         <v>3.6710719530102791</v>
       </c>
@@ -3928,32 +4001,32 @@
         <v>24</v>
       </c>
       <c r="BA13" s="20">
-        <f>CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
         <v>1048.788</v>
       </c>
-      <c r="BB13" s="123">
+      <c r="BB13" s="75">
         <f t="shared" si="40"/>
         <v>0.62929781805283813</v>
       </c>
       <c r="BC13" s="20">
-        <f>CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
         <v>746.21399999999994</v>
       </c>
-      <c r="BD13" s="123">
+      <c r="BD13" s="75">
         <f t="shared" si="41"/>
         <v>0.88446477820035552</v>
       </c>
       <c r="BE13" s="20">
-        <f>CALC_DMG(S13*$AK$1,AZ13,$AI$2,1)*$AK$2+CALC_DMG(S13*$AL$1,AZ13,$AI$2,1)*$AL$2+CALC_DMG(S13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(S13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(S13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
         <v>443.64</v>
       </c>
-      <c r="BF13" s="123">
+      <c r="BF13" s="75">
         <f t="shared" si="42"/>
         <v>1.4876927238301325</v>
       </c>
     </row>
-    <row r="14" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B14" s="73"/>
+    <row r="14" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="81"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4023,49 +4096,49 @@
         <f t="shared" si="24"/>
         <v>73.950000000000017</v>
       </c>
-      <c r="X14" s="127">
+      <c r="X14" s="79">
         <f t="shared" si="25"/>
         <v>13.522650439486137</v>
       </c>
-      <c r="Y14" s="12">
-        <f t="shared" si="26"/>
-        <v>110.5</v>
-      </c>
-      <c r="Z14" s="127">
-        <f t="shared" si="27"/>
-        <v>9.0497737556561084</v>
+      <c r="Y14" s="12" t="e">
+        <f t="shared" ca="1" si="26"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z14" s="79" t="e">
+        <f t="shared" ca="1" si="27"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA14" s="15">
         <f t="shared" si="28"/>
         <v>93.350000000000009</v>
       </c>
-      <c r="AB14" s="126">
+      <c r="AB14" s="78">
         <f t="shared" si="29"/>
         <v>9.1055168719871435</v>
       </c>
-      <c r="AC14" s="15">
-        <f t="shared" si="30"/>
-        <v>129.89999999999998</v>
-      </c>
-      <c r="AD14" s="126">
-        <f t="shared" si="31"/>
-        <v>6.5434949961508861</v>
+      <c r="AC14" s="15" t="e">
+        <f t="shared" ca="1" si="30"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD14" s="78" t="e">
+        <f t="shared" ca="1" si="31"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE14" s="22">
         <f t="shared" si="32"/>
         <v>112.75</v>
       </c>
-      <c r="AF14" s="125">
+      <c r="AF14" s="77">
         <f t="shared" si="11"/>
         <v>6.2084257206208422</v>
       </c>
-      <c r="AG14" s="22">
-        <f t="shared" si="33"/>
-        <v>149.29999999999998</v>
-      </c>
-      <c r="AH14" s="125">
-        <f t="shared" si="34"/>
-        <v>4.688546550569324</v>
+      <c r="AG14" s="22" t="e">
+        <f t="shared" ca="1" si="33"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH14" s="77" t="e">
+        <f t="shared" ca="1" si="34"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI14" s="7" t="s">
         <v>94</v>
@@ -4090,7 +4163,7 @@
         <f>CALC_DMG(Q14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(Q14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(Q14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
         <v>1514.7212399999996</v>
       </c>
-      <c r="AP14" s="123">
+      <c r="AP14" s="75">
         <f>AK14/AO14</f>
         <v>2.6407499243887282</v>
       </c>
@@ -4098,7 +4171,7 @@
         <f>CALC_DMG(R14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(R14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(R14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
         <v>1405.1206199999997</v>
       </c>
-      <c r="AR14" s="123">
+      <c r="AR14" s="75">
         <f>AK14/AQ14</f>
         <v>2.8467306956181462</v>
       </c>
@@ -4106,7 +4179,7 @@
         <f>CALC_DMG(S14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(S14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(S14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
         <v>1295.52</v>
       </c>
-      <c r="AT14" s="123">
+      <c r="AT14" s="75">
         <f>AK14/AS14</f>
         <v>3.0875632950475485</v>
       </c>
@@ -4130,46 +4203,46 @@
         <v>36</v>
       </c>
       <c r="BA14" s="20">
-        <f>CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>1730.7212399999996</v>
-      </c>
-      <c r="BB14" s="123">
+        <f>[1]!CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>1730.7213999999999</v>
+      </c>
+      <c r="BB14" s="75">
         <f t="shared" si="40"/>
-        <v>1.3867051172261575</v>
+        <v>1.3867049890294303</v>
       </c>
       <c r="BC14" s="20">
-        <f>CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>1621.1206199999997</v>
-      </c>
-      <c r="BD14" s="123">
+        <f>[1]!CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>1621.1206999999999</v>
+      </c>
+      <c r="BD14" s="75">
         <f t="shared" si="41"/>
-        <v>1.4804573887907246</v>
+        <v>1.4804573157322587</v>
       </c>
       <c r="BE14" s="20">
-        <f>CALC_DMG(S14*$AK$1,AZ14,$AI$2,1)*$AK$2+CALC_DMG(S14*$AL$1,AZ14,$AI$2,1)*$AL$2+CALC_DMG(S14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(S14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(S14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
         <v>1511.52</v>
       </c>
-      <c r="BF14" s="123">
+      <c r="BF14" s="75">
         <f t="shared" si="42"/>
         <v>1.5878056525881232</v>
       </c>
     </row>
-    <row r="15" spans="2:58" ht="24.05" customHeight="1">
-      <c r="X15" s="124"/>
-      <c r="Z15" s="124"/>
-      <c r="AB15" s="124"/>
-      <c r="AD15" s="124"/>
-      <c r="AF15" s="124"/>
-      <c r="AH15" s="124"/>
-      <c r="AP15" s="124"/>
-      <c r="AR15" s="124"/>
-      <c r="AT15" s="124"/>
-      <c r="BB15" s="124"/>
-      <c r="BD15" s="124"/>
-      <c r="BF15" s="124"/>
-    </row>
-    <row r="16" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B16" s="73">
+    <row r="15" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X15" s="76"/>
+      <c r="Z15" s="76"/>
+      <c r="AB15" s="76"/>
+      <c r="AD15" s="76"/>
+      <c r="AF15" s="76"/>
+      <c r="AH15" s="76"/>
+      <c r="AP15" s="76"/>
+      <c r="AR15" s="76"/>
+      <c r="AT15" s="76"/>
+      <c r="BB15" s="76"/>
+      <c r="BD15" s="76"/>
+      <c r="BF15" s="76"/>
+    </row>
+    <row r="16" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="81">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4241,49 +4314,49 @@
         <f t="shared" ref="W16:W18" si="46">CALC_DMG(AJ16,T16,$D$2, P16)</f>
         <v>92.800000000000011</v>
       </c>
-      <c r="X16" s="127">
+      <c r="X16" s="79">
         <f t="shared" ref="X16:X18" si="47">K16/W16</f>
         <v>14.008620689655171</v>
       </c>
-      <c r="Y16" s="12">
-        <f t="shared" ref="Y16:Y18" si="48">CALC_DMG(AV16,T16,$D$2, P16)</f>
-        <v>144.80000000000001</v>
-      </c>
-      <c r="Z16" s="127">
-        <f t="shared" ref="Z16:Z18" si="49">K16/Y16</f>
-        <v>8.9779005524861866</v>
+      <c r="Y16" s="12" t="e">
+        <f t="shared" ref="Y16:Y18" ca="1" si="48">CALC_DMG(AV16,T16,$D$2, P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z16" s="79" t="e">
+        <f t="shared" ref="Z16:Z18" ca="1" si="49">K16/Y16</f>
+        <v>#NAME?</v>
       </c>
       <c r="AA16" s="15">
         <f t="shared" ref="AA16:AA18" si="50">CALC_DMG(AJ16,U16,$D$2,P16)</f>
         <v>128.9</v>
       </c>
-      <c r="AB16" s="126">
+      <c r="AB16" s="78">
         <f t="shared" ref="AB16:AB18" si="51">L16/AA16</f>
         <v>8.9216446858029474</v>
       </c>
-      <c r="AC16" s="15">
-        <f t="shared" ref="AC16:AC18" si="52">CALC_DMG(AV16,U16,$D$2,P16)</f>
-        <v>180.9</v>
-      </c>
-      <c r="AD16" s="126">
-        <f t="shared" ref="AD16:AD18" si="53">L16/AC16</f>
-        <v>6.3571033720287451</v>
+      <c r="AC16" s="15" t="e">
+        <f t="shared" ref="AC16:AC18" ca="1" si="52">CALC_DMG(AV16,U16,$D$2,P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD16" s="78" t="e">
+        <f t="shared" ref="AD16:AD18" ca="1" si="53">L16/AC16</f>
+        <v>#NAME?</v>
       </c>
       <c r="AE16" s="22">
         <f t="shared" ref="AE16:AE18" si="54">CALC_DMG(AJ16,V16,$D$2,P16)</f>
         <v>165</v>
       </c>
-      <c r="AF16" s="125">
+      <c r="AF16" s="77">
         <f t="shared" si="11"/>
         <v>6.0606060606060606</v>
       </c>
-      <c r="AG16" s="22">
-        <f t="shared" ref="AG16:AG18" si="55">CALC_DMG(AV16,V16,$D$2,P16)</f>
-        <v>217</v>
-      </c>
-      <c r="AH16" s="125">
-        <f t="shared" ref="AH16:AH18" si="56">M16/AG16</f>
-        <v>4.6082949308755756</v>
+      <c r="AG16" s="22" t="e">
+        <f t="shared" ref="AG16:AG18" ca="1" si="55">CALC_DMG(AV16,V16,$D$2,P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH16" s="77" t="e">
+        <f t="shared" ref="AH16:AH18" ca="1" si="56">M16/AG16</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI16" s="8">
         <v>3</v>
@@ -4308,7 +4381,7 @@
         <f>CALC_DMG(Q16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(Q16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(Q16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
         <v>2402.2195199999996</v>
       </c>
-      <c r="AP16" s="123">
+      <c r="AP16" s="75">
         <f>AK16/AO16</f>
         <v>1.8732676021215582</v>
       </c>
@@ -4316,7 +4389,7 @@
         <f>CALC_DMG(R16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(R16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(R16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
         <v>1844.9097599999996</v>
       </c>
-      <c r="AR16" s="123">
+      <c r="AR16" s="75">
         <f>AK16/AQ16</f>
         <v>2.4391436901499186</v>
       </c>
@@ -4324,20 +4397,20 @@
         <f>CALC_DMG(S16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(S16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(S16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
         <v>1287.5999999999999</v>
       </c>
-      <c r="AT16" s="123">
+      <c r="AT16" s="75">
         <f>AK16/AS16</f>
         <v>3.4948741845293574</v>
       </c>
       <c r="AV16" s="12">
-        <f t="shared" ref="AV16:AV18" si="58">AJ16*1.2</f>
+        <f t="shared" ref="AV16:AV18" si="58">AJ16*$AV$2</f>
         <v>390</v>
       </c>
       <c r="AW16" s="15">
-        <f t="shared" ref="AW16:AW18" si="59">AK16*0.6</f>
+        <f t="shared" ref="AW16:AW18" si="59">AK16*$AW$2</f>
         <v>2700</v>
       </c>
       <c r="AX16" s="16">
-        <f t="shared" ref="AX16:AX18" si="60">AL16*0.6</f>
+        <f t="shared" ref="AX16:AX18" si="60">AL16*$AX$2</f>
         <v>48</v>
       </c>
       <c r="AY16" s="17">
@@ -4348,32 +4421,32 @@
         <v>48</v>
       </c>
       <c r="BA16" s="20">
-        <f>CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>2690.2195199999996</v>
-      </c>
-      <c r="BB16" s="123">
+        <f>[1]!CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>2690.2196000000004</v>
+      </c>
+      <c r="BB16" s="75">
         <f t="shared" ref="BB16:BB18" si="62">AW16/BA16</f>
-        <v>1.0036355694869095</v>
+        <v>1.0036355396414478</v>
       </c>
       <c r="BC16" s="20">
-        <f>CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>2132.9097599999996</v>
-      </c>
-      <c r="BD16" s="123">
+        <f>[1]!CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>2132.9096</v>
+      </c>
+      <c r="BD16" s="75">
         <f t="shared" ref="BD16:BD18" si="63">AW16/BC16</f>
-        <v>1.265876339747257</v>
+        <v>1.2658764347068436</v>
       </c>
       <c r="BE16" s="20">
-        <f>CALC_DMG(S16*$AK$1,AZ16,$AI$2,1)*$AK$2+CALC_DMG(S16*$AL$1,AZ16,$AI$2,1)*$AL$2+CALC_DMG(S16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(S16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(S16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
         <v>1575.6</v>
       </c>
-      <c r="BF16" s="123">
+      <c r="BF16" s="75">
         <f t="shared" ref="BF16:BF18" si="64">AW16/BE16</f>
         <v>1.7136329017517138</v>
       </c>
     </row>
-    <row r="17" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B17" s="73"/>
+    <row r="17" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="81"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4443,49 +4516,49 @@
         <f t="shared" si="46"/>
         <v>132.79999999999998</v>
       </c>
-      <c r="X17" s="127">
+      <c r="X17" s="79">
         <f t="shared" si="47"/>
         <v>12.04819277108434</v>
       </c>
-      <c r="Y17" s="12">
-        <f t="shared" si="48"/>
-        <v>206.4</v>
-      </c>
-      <c r="Z17" s="127">
-        <f t="shared" si="49"/>
-        <v>7.7519379844961236</v>
+      <c r="Y17" s="12" t="e">
+        <f t="shared" ca="1" si="48"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z17" s="79" t="e">
+        <f t="shared" ca="1" si="49"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA17" s="15">
         <f t="shared" si="50"/>
         <v>172.89999999999998</v>
       </c>
-      <c r="AB17" s="126">
+      <c r="AB17" s="78">
         <f t="shared" si="51"/>
         <v>8.3863504916136513</v>
       </c>
-      <c r="AC17" s="15">
-        <f t="shared" si="52"/>
-        <v>246.5</v>
-      </c>
-      <c r="AD17" s="126">
-        <f t="shared" si="53"/>
-        <v>5.882352941176471</v>
+      <c r="AC17" s="15" t="e">
+        <f t="shared" ca="1" si="52"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD17" s="78" t="e">
+        <f t="shared" ca="1" si="53"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE17" s="22">
         <f t="shared" si="54"/>
         <v>213</v>
       </c>
-      <c r="AF17" s="125">
+      <c r="AF17" s="77">
         <f t="shared" si="11"/>
         <v>6.103286384976526</v>
       </c>
-      <c r="AG17" s="22">
-        <f t="shared" si="55"/>
-        <v>286.60000000000002</v>
-      </c>
-      <c r="AH17" s="125">
-        <f t="shared" si="56"/>
-        <v>4.5359385903698533</v>
+      <c r="AG17" s="22" t="e">
+        <f t="shared" ca="1" si="55"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH17" s="77" t="e">
+        <f t="shared" ca="1" si="56"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI17" s="7" t="s">
         <v>95</v>
@@ -4510,7 +4583,7 @@
         <f>CALC_DMG(Q17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(Q17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(Q17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
         <v>3607.1171999999992</v>
       </c>
-      <c r="AP17" s="123">
+      <c r="AP17" s="75">
         <f>AK17/AO17</f>
         <v>2.2178375573712996</v>
       </c>
@@ -4518,7 +4591,7 @@
         <f>CALC_DMG(R17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(R17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(R17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
         <v>2857.2785999999992</v>
       </c>
-      <c r="AR17" s="123">
+      <c r="AR17" s="75">
         <f>AK17/AQ17</f>
         <v>2.7998669783198609</v>
       </c>
@@ -4526,7 +4599,7 @@
         <f>CALC_DMG(S17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(S17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(S17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
         <v>2107.4399999999996</v>
       </c>
-      <c r="AT17" s="123">
+      <c r="AT17" s="75">
         <f>AK17/AS17</f>
         <v>3.7960748585962123</v>
       </c>
@@ -4550,32 +4623,32 @@
         <v>66</v>
       </c>
       <c r="BA17" s="20">
-        <f>CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>4003.1171999999992</v>
-      </c>
-      <c r="BB17" s="123">
+        <f>[1]!CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>4003.1171999999997</v>
+      </c>
+      <c r="BB17" s="75">
         <f t="shared" si="62"/>
         <v>1.1990655682026998</v>
       </c>
       <c r="BC17" s="20">
-        <f>CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>3253.2785999999992</v>
-      </c>
-      <c r="BD17" s="123">
+        <f>[1]!CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>3253.279</v>
+      </c>
+      <c r="BD17" s="75">
         <f t="shared" si="63"/>
-        <v>1.4754346584396434</v>
+        <v>1.4754344770307126</v>
       </c>
       <c r="BE17" s="20">
-        <f>CALC_DMG(S17*$AK$1,AZ17,$AI$2,1)*$AK$2+CALC_DMG(S17*$AL$1,AZ17,$AI$2,1)*$AL$2+CALC_DMG(S17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>2503.4399999999996</v>
-      </c>
-      <c r="BF17" s="123">
+        <f>[1]!CALC_DMG(S17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(S17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(S17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>2503.44</v>
+      </c>
+      <c r="BF17" s="75">
         <f t="shared" si="64"/>
-        <v>1.9173617102866458</v>
-      </c>
-    </row>
-    <row r="18" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B18" s="73"/>
+        <v>1.9173617102866456</v>
+      </c>
+    </row>
+    <row r="18" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="81"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4645,49 +4718,49 @@
         <f t="shared" si="46"/>
         <v>177.2</v>
       </c>
-      <c r="X18" s="127">
+      <c r="X18" s="79">
         <f t="shared" si="47"/>
         <v>10.72234762979684</v>
       </c>
-      <c r="Y18" s="12">
-        <f t="shared" si="48"/>
-        <v>275.20000000000005</v>
-      </c>
-      <c r="Z18" s="127">
-        <f t="shared" si="49"/>
-        <v>6.9040697674418592</v>
+      <c r="Y18" s="12" t="e">
+        <f t="shared" ca="1" si="48"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z18" s="79" t="e">
+        <f t="shared" ca="1" si="49"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA18" s="15">
         <f t="shared" si="50"/>
         <v>218.59999999999997</v>
       </c>
-      <c r="AB18" s="126">
+      <c r="AB18" s="78">
         <f t="shared" si="51"/>
         <v>8.005489478499543</v>
       </c>
-      <c r="AC18" s="15">
-        <f t="shared" si="52"/>
-        <v>316.60000000000002</v>
-      </c>
-      <c r="AD18" s="126">
-        <f t="shared" si="53"/>
-        <v>5.5274794693619702</v>
+      <c r="AC18" s="15" t="e">
+        <f t="shared" ca="1" si="52"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD18" s="78" t="e">
+        <f t="shared" ca="1" si="53"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE18" s="22">
         <f t="shared" si="54"/>
         <v>259.99999999999994</v>
       </c>
-      <c r="AF18" s="125">
+      <c r="AF18" s="77">
         <f t="shared" si="11"/>
         <v>6.1538461538461551</v>
       </c>
-      <c r="AG18" s="22">
-        <f t="shared" si="55"/>
-        <v>358</v>
-      </c>
-      <c r="AH18" s="125">
-        <f t="shared" si="56"/>
-        <v>4.4692737430167595</v>
+      <c r="AG18" s="22" t="e">
+        <f t="shared" ca="1" si="55"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH18" s="77" t="e">
+        <f t="shared" ca="1" si="56"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI18" s="7" t="s">
         <v>95</v>
@@ -4712,7 +4785,7 @@
         <f>CALC_DMG(Q18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(Q18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(Q18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
         <v>5093.6227200000012</v>
       </c>
-      <c r="AP18" s="123">
+      <c r="AP18" s="75">
         <f>AK18/AO18</f>
         <v>2.5522110125973358</v>
       </c>
@@ -4720,7 +4793,7 @@
         <f>CALC_DMG(R18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(R18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(R18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
         <v>4188.7113600000002</v>
       </c>
-      <c r="AR18" s="123">
+      <c r="AR18" s="75">
         <f>AK18/AQ18</f>
         <v>3.1035798083733321</v>
       </c>
@@ -4728,7 +4801,7 @@
         <f>CALC_DMG(S18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(S18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(S18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
         <v>3283.8</v>
       </c>
-      <c r="AT18" s="123">
+      <c r="AT18" s="75">
         <f>AK18/AS18</f>
         <v>3.9588281868566901</v>
       </c>
@@ -4752,46 +4825,46 @@
         <v>87</v>
       </c>
       <c r="BA18" s="20">
-        <f>CALC_DMG(Q18*$AK$1,AZ18,$AI$2,1)*$AK$2+CALC_DMG(Q18*$AL$1,AZ18,$AI$2,1)*$AL$2+CALC_DMG(Q18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
-        <v>5615.6227200000012</v>
-      </c>
-      <c r="BB18" s="123">
+        <f>[1]!CALC_DMG(Q18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
+        <v>5615.6227999999992</v>
+      </c>
+      <c r="BB18" s="75">
         <f t="shared" si="62"/>
-        <v>1.3889822000007861</v>
+        <v>1.3889821802133864</v>
       </c>
       <c r="BC18" s="20">
-        <f>CALC_DMG(R18*$AK$1,AZ18,$AI$2,1)*$AK$2+CALC_DMG(R18*$AL$1,AZ18,$AI$2,1)*$AL$2+CALC_DMG(R18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
-        <v>4710.7113600000002</v>
-      </c>
-      <c r="BD18" s="123">
+        <f>[1]!CALC_DMG(R18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(R18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(R18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
+        <v>4710.7112000000006</v>
+      </c>
+      <c r="BD18" s="75">
         <f t="shared" si="63"/>
-        <v>1.6558008767491115</v>
+        <v>1.6558009329886321</v>
       </c>
       <c r="BE18" s="20">
-        <f>CALC_DMG(S18*$AK$1,AZ18,$AI$2,1)*$AK$2+CALC_DMG(S18*$AL$1,AZ18,$AI$2,1)*$AL$2+CALC_DMG(S18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(S18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(S18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
         <v>3805.8</v>
       </c>
-      <c r="BF18" s="123">
+      <c r="BF18" s="75">
         <f t="shared" si="64"/>
         <v>2.0495033895632981</v>
       </c>
     </row>
-    <row r="19" spans="2:58" ht="24.05" customHeight="1">
-      <c r="X19" s="124"/>
-      <c r="Z19" s="124"/>
-      <c r="AB19" s="124"/>
-      <c r="AD19" s="124"/>
-      <c r="AF19" s="124"/>
-      <c r="AH19" s="124"/>
-      <c r="AP19" s="124"/>
-      <c r="AR19" s="124"/>
-      <c r="AT19" s="124"/>
-      <c r="BB19" s="124"/>
-      <c r="BD19" s="124"/>
-      <c r="BF19" s="124"/>
-    </row>
-    <row r="20" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B20" s="73">
+    <row r="19" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X19" s="76"/>
+      <c r="Z19" s="76"/>
+      <c r="AB19" s="76"/>
+      <c r="AD19" s="76"/>
+      <c r="AF19" s="76"/>
+      <c r="AH19" s="76"/>
+      <c r="AP19" s="76"/>
+      <c r="AR19" s="76"/>
+      <c r="AT19" s="76"/>
+      <c r="BB19" s="76"/>
+      <c r="BD19" s="76"/>
+      <c r="BF19" s="76"/>
+    </row>
+    <row r="20" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="81">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4863,49 +4936,49 @@
         <f t="shared" ref="W20:W21" si="68">CALC_DMG(AJ20,T20,$D$2, P20)</f>
         <v>185.84999999999997</v>
       </c>
-      <c r="X20" s="127">
+      <c r="X20" s="79">
         <f t="shared" ref="X20:X21" si="69">K20/W20</f>
         <v>10.868980360505786</v>
       </c>
-      <c r="Y20" s="12">
-        <f t="shared" ref="Y20:Y21" si="70">CALC_DMG(AV20,T20,$D$2, P20)</f>
-        <v>308.7</v>
-      </c>
-      <c r="Z20" s="127">
-        <f t="shared" ref="Z20:Z21" si="71">K20/Y20</f>
-        <v>6.5435698088759313</v>
+      <c r="Y20" s="12" t="e">
+        <f t="shared" ref="Y20:Y21" ca="1" si="70">CALC_DMG(AV20,T20,$D$2, P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z20" s="79" t="e">
+        <f t="shared" ref="Z20:Z21" ca="1" si="71">K20/Y20</f>
+        <v>#NAME?</v>
       </c>
       <c r="AA20" s="15">
         <f t="shared" ref="AA20:AA21" si="72">CALC_DMG(AJ20,U20,$D$2,P20)</f>
         <v>245.04999999999995</v>
       </c>
-      <c r="AB20" s="126">
+      <c r="AB20" s="78">
         <f t="shared" ref="AB20:AB21" si="73">L20/AA20</f>
         <v>7.9983676800652939</v>
       </c>
-      <c r="AC20" s="15">
-        <f t="shared" ref="AC20:AC21" si="74">CALC_DMG(AV20,U20,$D$2,P20)</f>
-        <v>367.9</v>
-      </c>
-      <c r="AD20" s="126">
-        <f t="shared" ref="AD20:AD21" si="75">L20/AC20</f>
-        <v>5.3275346561565646</v>
+      <c r="AC20" s="15" t="e">
+        <f t="shared" ref="AC20:AC21" ca="1" si="74">CALC_DMG(AV20,U20,$D$2,P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD20" s="78" t="e">
+        <f t="shared" ref="AD20:AD21" ca="1" si="75">L20/AC20</f>
+        <v>#NAME?</v>
       </c>
       <c r="AE20" s="22">
         <f t="shared" ref="AE20:AE21" si="76">CALC_DMG(AJ20,V20,$D$2,P20)</f>
         <v>304.25</v>
       </c>
-      <c r="AF20" s="125">
+      <c r="AF20" s="77">
         <f t="shared" si="11"/>
         <v>6.2448644207066559</v>
       </c>
-      <c r="AG20" s="22">
-        <f t="shared" ref="AG20:AG21" si="77">CALC_DMG(AV20,V20,$D$2,P20)</f>
-        <v>427.1</v>
-      </c>
-      <c r="AH20" s="125">
-        <f t="shared" ref="AH20:AH21" si="78">M20/AG20</f>
-        <v>4.4486068836338095</v>
+      <c r="AG20" s="22" t="e">
+        <f t="shared" ref="AG20:AG21" ca="1" si="77">CALC_DMG(AV20,V20,$D$2,P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH20" s="77" t="e">
+        <f t="shared" ref="AH20:AH21" ca="1" si="78">M20/AG20</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI20" s="8">
         <v>4</v>
@@ -4930,7 +5003,7 @@
         <f>CALC_DMG(Q20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(Q20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(Q20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
         <v>9327.5144999999993</v>
       </c>
-      <c r="AP20" s="123">
+      <c r="AP20" s="75">
         <f>AK20/AO20</f>
         <v>2.0369842362614392</v>
       </c>
@@ -4938,7 +5011,7 @@
         <f>CALC_DMG(R20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(R20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(R20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
         <v>7008.5572499999998</v>
       </c>
-      <c r="AR20" s="123">
+      <c r="AR20" s="75">
         <f>AK20/AQ20</f>
         <v>2.710971648266125</v>
       </c>
@@ -4946,20 +5019,20 @@
         <f>CALC_DMG(S20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(S20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(S20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
         <v>4689.5999999999995</v>
       </c>
-      <c r="AT20" s="123">
+      <c r="AT20" s="75">
         <f>AK20/AS20</f>
         <v>4.05151825315592</v>
       </c>
       <c r="AV20" s="12">
-        <f t="shared" ref="AV20:AV21" si="80">AJ20*1.2</f>
+        <f t="shared" ref="AV20:AV21" si="80">AJ20*$AV$2</f>
         <v>1134</v>
       </c>
       <c r="AW20" s="15">
-        <f t="shared" ref="AW20:AW21" si="81">AK20*0.6</f>
+        <f t="shared" ref="AW20:AW21" si="81">AK20*$AW$2</f>
         <v>11400</v>
       </c>
       <c r="AX20" s="16">
-        <f t="shared" ref="AX20:AX21" si="82">AL20*0.6</f>
+        <f t="shared" ref="AX20:AX21" si="82">AL20*$AX$2</f>
         <v>108</v>
       </c>
       <c r="AY20" s="17">
@@ -4970,32 +5043,32 @@
         <v>108</v>
       </c>
       <c r="BA20" s="20">
-        <f>CALC_DMG(Q20*$AK$1,AZ20,$AI$2,1)*$AK$2+CALC_DMG(Q20*$AL$1,AZ20,$AI$2,1)*$AL$2+CALC_DMG(Q20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
-        <v>9975.5144999999993</v>
-      </c>
-      <c r="BB20" s="123">
+        <f>[1]!CALC_DMG(Q20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
+        <v>9975.5145000000011</v>
+      </c>
+      <c r="BB20" s="75">
         <f t="shared" ref="BB20:BB21" si="84">AW20/BA20</f>
-        <v>1.1427981985290083</v>
+        <v>1.1427981985290081</v>
       </c>
       <c r="BC20" s="20">
-        <f>CALC_DMG(R20*$AK$1,AZ20,$AI$2,1)*$AK$2+CALC_DMG(R20*$AL$1,AZ20,$AI$2,1)*$AL$2+CALC_DMG(R20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
-        <v>7656.5572499999998</v>
-      </c>
-      <c r="BD20" s="123">
+        <f>[1]!CALC_DMG(R20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(R20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(R20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
+        <v>7656.5573000000004</v>
+      </c>
+      <c r="BD20" s="75">
         <f t="shared" ref="BD20:BD21" si="85">AW20/BC20</f>
-        <v>1.488919840571949</v>
+        <v>1.488919830848781</v>
       </c>
       <c r="BE20" s="20">
-        <f>CALC_DMG(S20*$AK$1,AZ20,$AI$2,1)*$AK$2+CALC_DMG(S20*$AL$1,AZ20,$AI$2,1)*$AL$2+CALC_DMG(S20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
-        <v>5337.5999999999995</v>
-      </c>
-      <c r="BF20" s="123">
+        <f>[1]!CALC_DMG(S20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(S20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(S20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
+        <v>5337.6</v>
+      </c>
+      <c r="BF20" s="75">
         <f t="shared" ref="BF20:BF21" si="86">AW20/BE20</f>
-        <v>2.1357913669064752</v>
-      </c>
-    </row>
-    <row r="21" spans="2:58" ht="24.05" customHeight="1">
-      <c r="B21" s="73"/>
+        <v>2.1357913669064748</v>
+      </c>
+    </row>
+    <row r="21" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="81"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -5065,49 +5138,49 @@
         <f t="shared" si="68"/>
         <v>209.99999999999989</v>
       </c>
-      <c r="X21" s="127">
+      <c r="X21" s="79">
         <f t="shared" si="69"/>
         <v>13.809523809523817</v>
       </c>
-      <c r="Y21" s="12">
-        <f t="shared" si="70"/>
-        <v>365.99999999999989</v>
-      </c>
-      <c r="Z21" s="127">
-        <f t="shared" si="71"/>
-        <v>7.923497267759565</v>
+      <c r="Y21" s="12" t="e">
+        <f t="shared" ca="1" si="70"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z21" s="79" t="e">
+        <f t="shared" ca="1" si="71"/>
+        <v>#NAME?</v>
       </c>
       <c r="AA21" s="15">
         <f t="shared" si="72"/>
         <v>284.99999999999994</v>
       </c>
-      <c r="AB21" s="126">
+      <c r="AB21" s="78">
         <f t="shared" si="73"/>
         <v>8.5964912280701764</v>
       </c>
-      <c r="AC21" s="15">
-        <f t="shared" si="74"/>
-        <v>440.99999999999994</v>
-      </c>
-      <c r="AD21" s="126">
-        <f t="shared" si="75"/>
-        <v>5.5555555555555562</v>
+      <c r="AC21" s="15" t="e">
+        <f t="shared" ca="1" si="74"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD21" s="78" t="e">
+        <f t="shared" ca="1" si="75"/>
+        <v>#NAME?</v>
       </c>
       <c r="AE21" s="22">
         <f t="shared" si="76"/>
         <v>360</v>
       </c>
-      <c r="AF21" s="125">
+      <c r="AF21" s="77">
         <f t="shared" si="11"/>
         <v>5.5555555555555554</v>
       </c>
-      <c r="AG21" s="22">
-        <f t="shared" si="77"/>
-        <v>516</v>
-      </c>
-      <c r="AH21" s="125">
-        <f t="shared" si="78"/>
-        <v>3.8759689922480618</v>
+      <c r="AG21" s="22" t="e">
+        <f t="shared" ca="1" si="77"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH21" s="77" t="e">
+        <f t="shared" ca="1" si="78"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI21" s="8">
         <v>5</v>
@@ -5132,7 +5205,7 @@
         <f>CALC_DMG(Q21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(Q21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(Q21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
         <v>14289.131519999999</v>
       </c>
-      <c r="AP21" s="123">
+      <c r="AP21" s="75">
         <f>AK21/AO21</f>
         <v>2.6593638631440073</v>
       </c>
@@ -5140,7 +5213,7 @@
         <f>CALC_DMG(R21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(R21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(R21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
         <v>11603.765759999998</v>
       </c>
-      <c r="AR21" s="123">
+      <c r="AR21" s="75">
         <f>AK21/AQ21</f>
         <v>3.2747989563002009</v>
       </c>
@@ -5148,7 +5221,7 @@
         <f>CALC_DMG(S21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(S21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(S21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
         <v>8918.4</v>
       </c>
-      <c r="AT21" s="123">
+      <c r="AT21" s="75">
         <f>AK21/AS21</f>
         <v>4.2608539648367421</v>
       </c>
@@ -5172,28 +5245,70 @@
         <v>132</v>
       </c>
       <c r="BA21" s="20">
-        <f>CALC_DMG(Q21*$AK$1,AZ21,$AI$2,1)*$AK$2+CALC_DMG(Q21*$AL$1,AZ21,$AI$2,1)*$AL$2+CALC_DMG(Q21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
-        <v>15081.131519999999</v>
-      </c>
-      <c r="BB21" s="123">
+        <f>[1]!CALC_DMG(Q21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
+        <v>15081.131600000001</v>
+      </c>
+      <c r="BB21" s="75">
         <f t="shared" si="84"/>
-        <v>1.5118229006731718</v>
+        <v>1.5118228926534929</v>
       </c>
       <c r="BC21" s="20">
-        <f>CALC_DMG(R21*$AK$1,AZ21,$AI$2,1)*$AK$2+CALC_DMG(R21*$AL$1,AZ21,$AI$2,1)*$AL$2+CALC_DMG(R21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
-        <v>12395.765759999998</v>
-      </c>
-      <c r="BD21" s="123">
+        <f>[1]!CALC_DMG(R21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(R21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(R21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
+        <v>12395.765600000001</v>
+      </c>
+      <c r="BD21" s="75">
         <f t="shared" si="85"/>
-        <v>1.839337757863537</v>
+        <v>1.8393377816050345</v>
       </c>
       <c r="BE21" s="20">
-        <f>CALC_DMG(S21*$AK$1,AZ21,$AI$2,1)*$AK$2+CALC_DMG(S21*$AL$1,AZ21,$AI$2,1)*$AL$2+CALC_DMG(S21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
+        <f>[1]!CALC_DMG(S21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(S21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(S21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
         <v>9710.4</v>
       </c>
-      <c r="BF21" s="123">
+      <c r="BF21" s="75">
         <f t="shared" si="86"/>
         <v>2.3479980227385071</v>
+      </c>
+    </row>
+    <row r="23" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AU23" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="AV23" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="AW23" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AX23" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="24" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AU24" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="AV24" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AW24" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="AX24" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AU25" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="AV25" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AW25" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AX25" s="8">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>
@@ -5203,16 +5318,17 @@
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B12"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AA3:AD3"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="D3:T3"/>
     <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="AE3:AH3"/>
-    <mergeCell ref="AA3:AD3"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5220,12 +5336,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:AZ21"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="24.05" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="15.6640625" style="8"/>
+    <col min="1" max="16384" width="15.625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:52" ht="24.05" customHeight="1">
+    <row r="1" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D1" s="27" t="s">
         <v>65</v>
       </c>
@@ -5245,7 +5361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:52" ht="24.05" customHeight="1">
+    <row r="2" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D2" s="27">
         <v>0.5</v>
       </c>
@@ -5265,62 +5381,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:52" ht="24.05" customHeight="1">
+    <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="71" t="s">
+      <c r="V3" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
-      <c r="Z3" s="71"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="71"/>
-      <c r="AD3" s="71"/>
-      <c r="AE3" s="71"/>
-      <c r="AF3" s="71"/>
-      <c r="AG3" s="71"/>
-      <c r="AH3" s="71"/>
-      <c r="AI3" s="71"/>
-      <c r="AJ3" s="71"/>
-      <c r="AK3" s="71"/>
-      <c r="AL3" s="71"/>
-      <c r="AM3" s="71"/>
-      <c r="AN3" s="71"/>
-      <c r="AO3" s="71"/>
-      <c r="AP3" s="71"/>
-      <c r="AQ3" s="71"/>
-      <c r="AR3" s="71"/>
-      <c r="AS3" s="71"/>
-      <c r="AT3" s="71"/>
-      <c r="AU3" s="71"/>
-      <c r="AV3" s="71"/>
-      <c r="AW3" s="71"/>
-      <c r="AX3" s="71"/>
-      <c r="AY3" s="71"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="82"/>
+      <c r="AJ3" s="82"/>
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="82"/>
+      <c r="AM3" s="82"/>
+      <c r="AN3" s="82"/>
+      <c r="AO3" s="82"/>
+      <c r="AP3" s="82"/>
+      <c r="AQ3" s="82"/>
+      <c r="AR3" s="82"/>
+      <c r="AS3" s="82"/>
+      <c r="AT3" s="82"/>
+      <c r="AU3" s="82"/>
+      <c r="AV3" s="82"/>
+      <c r="AW3" s="82"/>
+      <c r="AX3" s="82"/>
+      <c r="AY3" s="82"/>
       <c r="AZ3" s="21"/>
     </row>
-    <row r="4" spans="2:52" ht="24.05" customHeight="1">
+    <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
         <v>71</v>
       </c>
@@ -5363,47 +5479,47 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="72" t="s">
+      <c r="V4" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="72"/>
-      <c r="X4" s="72"/>
-      <c r="Y4" s="72"/>
-      <c r="Z4" s="72"/>
-      <c r="AA4" s="72"/>
+      <c r="W4" s="86"/>
+      <c r="X4" s="86"/>
+      <c r="Y4" s="86"/>
+      <c r="Z4" s="86"/>
+      <c r="AA4" s="86"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="72" t="s">
+      <c r="AD4" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="72"/>
-      <c r="AF4" s="72"/>
-      <c r="AG4" s="72"/>
+      <c r="AE4" s="86"/>
+      <c r="AF4" s="86"/>
+      <c r="AG4" s="86"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="72" t="s">
+      <c r="AL4" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="72"/>
-      <c r="AN4" s="72"/>
-      <c r="AO4" s="72"/>
-      <c r="AP4" s="72"/>
-      <c r="AQ4" s="72"/>
+      <c r="AM4" s="86"/>
+      <c r="AN4" s="86"/>
+      <c r="AO4" s="86"/>
+      <c r="AP4" s="86"/>
+      <c r="AQ4" s="86"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="72" t="s">
+      <c r="AT4" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="72"/>
-      <c r="AV4" s="72"/>
-      <c r="AW4" s="72"/>
-      <c r="AX4" s="72"/>
-      <c r="AY4" s="72"/>
+      <c r="AU4" s="86"/>
+      <c r="AV4" s="86"/>
+      <c r="AW4" s="86"/>
+      <c r="AX4" s="86"/>
+      <c r="AY4" s="86"/>
       <c r="AZ4" s="21"/>
     </row>
-    <row r="5" spans="2:52" ht="24.05" customHeight="1">
+    <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
       <c r="D5" s="12" t="s">
         <v>49</v>
@@ -5541,8 +5657,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B6" s="73">
+    <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="81">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -5705,8 +5821,8 @@
         <v>2.0438194898626554</v>
       </c>
     </row>
-    <row r="7" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B7" s="73"/>
+    <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="81"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -5867,8 +5983,8 @@
         <v>2.4096681142200214</v>
       </c>
     </row>
-    <row r="8" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B8" s="73">
+    <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="81">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -6031,8 +6147,8 @@
         <v>2.9137714374111283</v>
       </c>
     </row>
-    <row r="9" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B9" s="73"/>
+    <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="81"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -6193,8 +6309,8 @@
         <v>3.1948765134586452</v>
       </c>
     </row>
-    <row r="10" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B10" s="74">
+    <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="87">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -6357,11 +6473,11 @@
         <v>3.1176630995058288</v>
       </c>
     </row>
-    <row r="11" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B11" s="74"/>
-    </row>
-    <row r="12" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B12" s="74"/>
+    <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="87"/>
+    </row>
+    <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="87"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -6522,8 +6638,8 @@
         <v>3.1787843692815017</v>
       </c>
     </row>
-    <row r="13" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B13" s="73">
+    <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="81">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -6686,8 +6802,8 @@
         <v>3.4266478063971411</v>
       </c>
     </row>
-    <row r="14" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B14" s="73"/>
+    <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="81"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -6848,8 +6964,8 @@
         <v>3.5788579551928295</v>
       </c>
     </row>
-    <row r="16" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B16" s="73">
+    <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="81">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -7012,8 +7128,8 @@
         <v>3.5334972210915043</v>
       </c>
     </row>
-    <row r="17" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B17" s="73"/>
+    <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="81"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -7174,8 +7290,8 @@
         <v>3.5933509739225009</v>
       </c>
     </row>
-    <row r="18" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B18" s="73"/>
+    <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="81"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -7336,8 +7452,8 @@
         <v>3.5600496082328954</v>
       </c>
     </row>
-    <row r="20" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B20" s="73">
+    <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="81">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -7500,8 +7616,8 @@
         <v>3.7358094278220939</v>
       </c>
     </row>
-    <row r="21" spans="2:52" ht="24.05" customHeight="1">
-      <c r="B21" s="73"/>
+    <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="81"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -7687,85 +7803,85 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F2A8C5-C710-4410-8433-B168C3A556B3}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:U35"/>
-  <sheetFormatPr defaultColWidth="16.6640625" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="5" customWidth="1"/>
-    <col min="2" max="4" width="16.6640625" style="5" customWidth="1"/>
-    <col min="5" max="8" width="16.6640625" style="5"/>
-    <col min="9" max="9" width="8.6640625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="5" customWidth="1"/>
-    <col min="11" max="14" width="16.6640625" style="5"/>
-    <col min="15" max="15" width="8.6640625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="2.6640625" style="5" customWidth="1"/>
-    <col min="17" max="20" width="16.6640625" style="5"/>
-    <col min="21" max="21" width="8.6640625" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="16.6640625" style="5"/>
+    <col min="1" max="1" width="12.625" style="5" customWidth="1"/>
+    <col min="2" max="4" width="16.625" style="5" customWidth="1"/>
+    <col min="5" max="8" width="16.625" style="5"/>
+    <col min="9" max="9" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="5" customWidth="1"/>
+    <col min="11" max="14" width="16.625" style="5"/>
+    <col min="15" max="15" width="8.625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="2.625" style="5" customWidth="1"/>
+    <col min="17" max="20" width="16.625" style="5"/>
+    <col min="21" max="21" width="8.625" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="16.625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18" customHeight="1">
-      <c r="E1" s="85" t="s">
+    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E1" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
       <c r="I1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="86" t="s">
+      <c r="K1" s="99" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
       <c r="O1" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="87" t="s">
+      <c r="Q1" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="87"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="100"/>
+      <c r="T1" s="100"/>
       <c r="U1" s="39" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1">
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="103" t="s">
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103" t="s">
+      <c r="F2" s="116"/>
+      <c r="G2" s="116" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="103"/>
-      <c r="K2" s="103" t="s">
+      <c r="H2" s="116"/>
+      <c r="K2" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103" t="s">
+      <c r="L2" s="116"/>
+      <c r="M2" s="116" t="s">
         <v>197</v>
       </c>
-      <c r="N2" s="103"/>
-      <c r="Q2" s="103" t="s">
+      <c r="N2" s="116"/>
+      <c r="Q2" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="R2" s="103"/>
-      <c r="S2" s="103" t="s">
+      <c r="R2" s="116"/>
+      <c r="S2" s="116" t="s">
         <v>197</v>
       </c>
-      <c r="T2" s="103"/>
-    </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1">
+      <c r="T2" s="116"/>
+    </row>
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
         <v>0.1</v>
       </c>
@@ -7776,29 +7892,29 @@
         <v>122</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="101" t="s">
+      <c r="E3" s="102"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="89"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="91"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="104"/>
       <c r="O3" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="90"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="91"/>
-      <c r="U3" s="83" t="s">
+      <c r="Q3" s="102"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="104"/>
+      <c r="U3" s="96" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" customHeight="1">
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="42">
         <v>1.1000000000000001</v>
       </c>
@@ -7807,11 +7923,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="102"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="115"/>
       <c r="K4" s="49" t="s">
         <v>133</v>
       </c>
@@ -7820,16 +7936,16 @@
         <v>134</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="98">
+      <c r="O4" s="111">
         <v>0</v>
       </c>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="96"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="84"/>
-    </row>
-    <row r="5" spans="1:21" ht="18" customHeight="1">
+      <c r="Q4" s="108"/>
+      <c r="R4" s="109"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="97"/>
+    </row>
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
         <v>1.2</v>
       </c>
@@ -7854,7 +7970,7 @@
       <c r="H5" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="78">
+      <c r="I5" s="91">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -7865,14 +7981,14 @@
         <v>194</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="99"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="97"/>
-      <c r="U5" s="84"/>
-    </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1">
+      <c r="O5" s="112"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="109"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="97"/>
+    </row>
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
         <v>1.3</v>
       </c>
@@ -7887,21 +8003,21 @@
         <v>160</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="78"/>
+      <c r="I6" s="91"/>
       <c r="K6" s="48" t="s">
         <v>165</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="99"/>
-      <c r="Q6" s="92"/>
-      <c r="R6" s="93"/>
-      <c r="S6" s="93"/>
-      <c r="T6" s="94"/>
-      <c r="U6" s="84"/>
-    </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1">
+      <c r="O6" s="112"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="106"/>
+      <c r="S6" s="106"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="97"/>
+    </row>
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
         <v>1.4</v>
       </c>
@@ -7920,7 +8036,7 @@
         <v>164</v>
       </c>
       <c r="H7" s="47"/>
-      <c r="I7" s="78"/>
+      <c r="I7" s="91"/>
       <c r="K7" s="48" t="s">
         <v>167</v>
       </c>
@@ -7929,7 +8045,7 @@
         <v>166</v>
       </c>
       <c r="N7" s="47"/>
-      <c r="O7" s="100"/>
+      <c r="O7" s="113"/>
       <c r="Q7" s="54" t="s">
         <v>199</v>
       </c>
@@ -7942,11 +8058,11 @@
       <c r="T7" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="79">
+      <c r="U7" s="92">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="18" customHeight="1">
+    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="43">
         <v>2.1</v>
       </c>
@@ -7967,7 +8083,7 @@
         <v>169</v>
       </c>
       <c r="H8" s="47"/>
-      <c r="I8" s="78"/>
+      <c r="I8" s="91"/>
       <c r="K8" s="53" t="s">
         <v>136</v>
       </c>
@@ -7980,7 +8096,7 @@
       <c r="N8" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="92">
         <v>1</v>
       </c>
       <c r="Q8" s="51" t="s">
@@ -7993,9 +8109,9 @@
       <c r="T8" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="U8" s="79"/>
-    </row>
-    <row r="9" spans="1:21" ht="18" customHeight="1">
+      <c r="U8" s="92"/>
+    </row>
+    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="43">
         <v>2.2000000000000002</v>
       </c>
@@ -8018,7 +8134,7 @@
       <c r="H9" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="I9" s="79">
+      <c r="I9" s="92">
         <v>1</v>
       </c>
       <c r="K9" s="51" t="s">
@@ -8033,7 +8149,7 @@
       <c r="N9" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="O9" s="79"/>
+      <c r="O9" s="92"/>
       <c r="Q9" s="33" t="s">
         <v>180</v>
       </c>
@@ -8042,11 +8158,11 @@
         <v>181</v>
       </c>
       <c r="T9" s="56"/>
-      <c r="U9" s="80">
+      <c r="U9" s="93">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1">
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
         <v>2.2999999999999998</v>
       </c>
@@ -8061,7 +8177,7 @@
       <c r="F10" s="52"/>
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
-      <c r="I10" s="79"/>
+      <c r="I10" s="92"/>
       <c r="K10" s="57" t="s">
         <v>141</v>
       </c>
@@ -8072,7 +8188,7 @@
       <c r="N10" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="80">
+      <c r="O10" s="93">
         <v>2</v>
       </c>
       <c r="Q10" s="33" t="s">
@@ -8081,9 +8197,9 @@
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
       <c r="T10" s="56"/>
-      <c r="U10" s="80"/>
-    </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1">
+      <c r="U10" s="93"/>
+    </row>
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
         <v>3.1</v>
       </c>
@@ -8104,7 +8220,7 @@
       <c r="H11" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="I11" s="80">
+      <c r="I11" s="93">
         <v>2</v>
       </c>
       <c r="K11" s="33"/>
@@ -8113,7 +8229,7 @@
         <v>184</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="80"/>
+      <c r="O11" s="93"/>
       <c r="Q11" s="61" t="s">
         <v>183</v>
       </c>
@@ -8122,11 +8238,11 @@
         <v>185</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="81">
+      <c r="U11" s="94">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1">
+    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="65">
         <v>3.2</v>
       </c>
@@ -8143,23 +8259,23 @@
         <v>186</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="80"/>
+      <c r="I12" s="93"/>
       <c r="K12" s="33"/>
       <c r="L12" s="56"/>
       <c r="M12" s="33" t="s">
         <v>187</v>
       </c>
       <c r="N12" s="56"/>
-      <c r="O12" s="80"/>
+      <c r="O12" s="93"/>
       <c r="Q12" s="69" t="s">
         <v>152</v>
       </c>
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="81"/>
-    </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1">
+      <c r="U12" s="94"/>
+    </row>
+    <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
         <v>3.3</v>
       </c>
@@ -8178,7 +8294,7 @@
       <c r="F13" s="33"/>
       <c r="G13" s="33"/>
       <c r="H13" s="56"/>
-      <c r="I13" s="80"/>
+      <c r="I13" s="93"/>
       <c r="K13" s="60" t="s">
         <v>146</v>
       </c>
@@ -8202,11 +8318,11 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="82">
+      <c r="U13" s="95">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1">
+    <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="44">
         <v>4.0999999999999996</v>
       </c>
@@ -8223,7 +8339,7 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="81">
+      <c r="I14" s="94">
         <v>3</v>
       </c>
       <c r="K14" s="62"/>
@@ -8232,7 +8348,7 @@
         <v>148</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="76">
+      <c r="O14" s="89">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -8241,9 +8357,9 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="82"/>
-    </row>
-    <row r="15" spans="1:21" ht="18" customHeight="1">
+      <c r="U14" s="95"/>
+    </row>
+    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
         <v>4.2</v>
       </c>
@@ -8258,14 +8374,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="81"/>
+      <c r="I15" s="94"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>151</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="77"/>
+      <c r="O15" s="90"/>
       <c r="Q15" s="68" t="s">
         <v>152</v>
       </c>
@@ -8276,13 +8392,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="18" customHeight="1">
-      <c r="C18" s="75" t="s">
+    <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C18" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="75"/>
-    </row>
-    <row r="19" spans="2:8" ht="18" customHeight="1">
+      <c r="D18" s="88"/>
+    </row>
+    <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>100</v>
       </c>
@@ -8293,7 +8409,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="18" customHeight="1">
+    <row r="20" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>124</v>
       </c>
@@ -8316,7 +8432,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="18" customHeight="1">
+    <row r="21" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>125</v>
       </c>
@@ -8339,7 +8455,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="18" customHeight="1">
+    <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
         <v>126</v>
       </c>
@@ -8356,7 +8472,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="18" customHeight="1">
+    <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
         <v>127</v>
       </c>
@@ -8373,7 +8489,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="18" customHeight="1">
+    <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>128</v>
       </c>
@@ -8390,12 +8506,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="18" customHeight="1">
+    <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="18" customHeight="1">
+    <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="5" t="s">
         <v>211</v>
       </c>
@@ -8406,7 +8522,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="18" customHeight="1">
+    <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="5">
         <v>0</v>
       </c>
@@ -8423,7 +8539,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="18" customHeight="1">
+    <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="5">
         <v>1</v>
       </c>
@@ -8440,7 +8556,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="18" customHeight="1">
+    <row r="31" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="5">
         <v>2</v>
       </c>
@@ -8457,7 +8573,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="18" customHeight="1">
+    <row r="32" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="5">
         <v>3</v>
       </c>
@@ -8477,7 +8593,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="18" customHeight="1">
+    <row r="33" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="5">
         <v>4</v>
       </c>
@@ -8494,7 +8610,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="18" customHeight="1">
+    <row r="34" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="5">
         <v>5</v>
       </c>
@@ -8511,7 +8627,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="18" customHeight="1">
+    <row r="35" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="5">
         <v>6</v>
       </c>
@@ -8567,40 +8683,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:W49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.05"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="5" max="5" width="10.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
-      <c r="A1" s="114" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A1" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="G1" s="114" t="s">
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="G1" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8620,7 +8736,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -8641,7 +8757,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -8652,7 +8768,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>0</v>
       </c>
@@ -8663,35 +8779,35 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
-      <c r="A8" s="104" t="s">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A8" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="106"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="4"/>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="105"/>
-      <c r="K8" s="105"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="105"/>
-      <c r="N8" s="106"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="119"/>
       <c r="O8" s="1"/>
-      <c r="Q8" s="104" t="s">
+      <c r="Q8" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="105"/>
-      <c r="S8" s="105"/>
-      <c r="T8" s="105"/>
-      <c r="U8" s="105"/>
-      <c r="V8" s="106"/>
-    </row>
-    <row r="9" spans="1:23">
+      <c r="R8" s="118"/>
+      <c r="S8" s="118"/>
+      <c r="T8" s="118"/>
+      <c r="U8" s="118"/>
+      <c r="V8" s="119"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -8753,7 +8869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -8771,11 +8887,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="110">
+      <c r="F10" s="123">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="88">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8795,11 +8911,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="123">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="75">
+      <c r="O10" s="88">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8819,12 +8935,12 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="107">
+      <c r="V10" s="120">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8842,8 +8958,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="113"/>
-      <c r="G11" s="75"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="88"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8861,8 +8977,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="113"/>
-      <c r="O11" s="75"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="88"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8880,9 +8996,9 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="108"/>
-    </row>
-    <row r="12" spans="1:23">
+      <c r="V11" s="121"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -8900,8 +9016,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="113"/>
-      <c r="G12" s="75"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="88"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -8919,8 +9035,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="113"/>
-      <c r="O12" s="75"/>
+      <c r="N12" s="126"/>
+      <c r="O12" s="88"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -8938,9 +9054,9 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="109"/>
-    </row>
-    <row r="13" spans="1:23">
+      <c r="V12" s="122"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -8958,8 +9074,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="111"/>
-      <c r="G13" s="75"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="88"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -8977,10 +9093,10 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="113"/>
-      <c r="O13" s="75"/>
-    </row>
-    <row r="14" spans="1:23">
+      <c r="N13" s="126"/>
+      <c r="O13" s="88"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -8998,11 +9114,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="110">
+      <c r="F14" s="123">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="88">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9022,10 +9138,10 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="113"/>
-      <c r="O14" s="75"/>
-    </row>
-    <row r="15" spans="1:23">
+      <c r="N14" s="126"/>
+      <c r="O14" s="88"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -9043,8 +9159,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="111"/>
-      <c r="G15" s="75"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="88"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9062,10 +9178,10 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="113"/>
-      <c r="O15" s="75"/>
-    </row>
-    <row r="16" spans="1:23">
+      <c r="N15" s="126"/>
+      <c r="O15" s="88"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
         <v>37</v>
       </c>
@@ -9094,10 +9210,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="111"/>
-      <c r="O16" s="75"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" s="124"/>
+      <c r="O16" s="88"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
         <v>38</v>
       </c>
@@ -9125,7 +9241,7 @@
       </c>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="E18" s="6" t="s">
         <v>40</v>
       </c>
@@ -9139,29 +9255,29 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="104" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A20" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="105"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="106"/>
-      <c r="I20" s="104" t="s">
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
+      <c r="I20" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="106"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="119"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -9197,7 +9313,7 @@
       </c>
       <c r="O21" s="5"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -9231,13 +9347,13 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="107">
+      <c r="N22" s="120">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -9271,10 +9387,10 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="108"/>
+      <c r="N23" s="121"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -9308,10 +9424,10 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="109"/>
+      <c r="N24" s="122"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -9345,13 +9461,13 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="107">
+      <c r="N25" s="120">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="I26" s="1" t="s">
         <v>25</v>
       </c>
@@ -9368,40 +9484,40 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="109"/>
+      <c r="N26" s="122"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="112" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A30" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="105"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="106"/>
+      <c r="B30" s="118"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="119"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="112" t="s">
+      <c r="I30" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="105"/>
-      <c r="K30" s="105"/>
-      <c r="L30" s="105"/>
-      <c r="M30" s="105"/>
-      <c r="N30" s="106"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="118"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="119"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>12</v>
       </c>
@@ -9445,7 +9561,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
@@ -9463,11 +9579,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="110">
+      <c r="F32" s="123">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="75">
+      <c r="G32" s="88">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9487,15 +9603,15 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="110">
+      <c r="N32" s="123">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="75">
+      <c r="O32" s="88">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9513,8 +9629,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="113"/>
-      <c r="G33" s="75"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="88"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9532,10 +9648,10 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="113"/>
-      <c r="O33" s="75"/>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" s="126"/>
+      <c r="O33" s="88"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9553,8 +9669,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="113"/>
-      <c r="G34" s="75"/>
+      <c r="F34" s="126"/>
+      <c r="G34" s="88"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9572,10 +9688,10 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="113"/>
-      <c r="O34" s="75"/>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" s="126"/>
+      <c r="O34" s="88"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>22</v>
       </c>
@@ -9593,8 +9709,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="111"/>
-      <c r="G35" s="75"/>
+      <c r="F35" s="124"/>
+      <c r="G35" s="88"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9612,10 +9728,10 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="113"/>
-      <c r="O35" s="75"/>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" s="126"/>
+      <c r="O35" s="88"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>24</v>
       </c>
@@ -9633,11 +9749,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="110">
+      <c r="F36" s="123">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="75">
+      <c r="G36" s="88">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9657,10 +9773,10 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="113"/>
-      <c r="O36" s="75"/>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" s="126"/>
+      <c r="O36" s="88"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>26</v>
       </c>
@@ -9678,8 +9794,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="111"/>
-      <c r="G37" s="75"/>
+      <c r="F37" s="124"/>
+      <c r="G37" s="88"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9697,10 +9813,10 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="113"/>
-      <c r="O37" s="75"/>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" s="126"/>
+      <c r="O37" s="88"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
         <v>37</v>
       </c>
@@ -9729,10 +9845,10 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="111"/>
-      <c r="O38" s="75"/>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" s="124"/>
+      <c r="O38" s="88"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
         <v>38</v>
       </c>
@@ -9760,7 +9876,7 @@
       </c>
       <c r="O39" s="5"/>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="E40" s="6" t="s">
         <v>40</v>
       </c>
@@ -9774,24 +9890,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
-      <c r="A43" s="104" t="s">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A43" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="105"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="105"/>
-      <c r="E43" s="106"/>
-      <c r="I43" s="104" t="s">
+      <c r="B43" s="118"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="119"/>
+      <c r="I43" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="J43" s="105"/>
-      <c r="K43" s="105"/>
-      <c r="L43" s="105"/>
-      <c r="M43" s="105"/>
-      <c r="N43" s="106"/>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="J43" s="118"/>
+      <c r="K43" s="118"/>
+      <c r="L43" s="118"/>
+      <c r="M43" s="118"/>
+      <c r="N43" s="119"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>12</v>
       </c>
@@ -9826,7 +9942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>31</v>
       </c>
@@ -9860,12 +9976,12 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="107">
+      <c r="N45" s="120">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
@@ -9899,9 +10015,9 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="108"/>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" s="121"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>33</v>
       </c>
@@ -9935,9 +10051,9 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="109"/>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" s="122"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>34</v>
       </c>
@@ -9971,12 +10087,12 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="107">
+      <c r="N48" s="120">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
     </row>
-    <row r="49" spans="9:14">
+    <row r="49" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I49" s="1" t="s">
         <v>25</v>
       </c>
@@ -9993,7 +10109,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="109"/>
+      <c r="N49" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C93A5CF-8A4F-4755-A9D8-2CB4B875FA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AFB8A4-87EB-4DA4-9069-973757417368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33684" yWindow="-5160" windowWidth="26436" windowHeight="15432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -2665,13 +2665,13 @@
         <f>K6/W6</f>
         <v>44</v>
       </c>
-      <c r="Y6" s="12" t="e">
-        <f ca="1">CALC_DMG(AV6,T6,$D$2, P6)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z6" s="79" t="e">
-        <f ca="1">K6/Y6</f>
-        <v>#NAME?</v>
+      <c r="Y6" s="12">
+        <f>[1]!CALC_DMG(AV6,T6,$D$2, P6)</f>
+        <v>0.8</v>
+      </c>
+      <c r="Z6" s="79">
+        <f>K6/Y6</f>
+        <v>27.5</v>
       </c>
       <c r="AA6" s="15">
         <f>CALC_DMG(AJ6,U6,$D$2,P6)</f>
@@ -2681,13 +2681,13 @@
         <f>L6/AA6</f>
         <v>14</v>
       </c>
-      <c r="AC6" s="15" t="e">
-        <f ca="1">CALC_DMG(AV6,U6,$D$2,P6)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD6" s="78" t="e">
-        <f ca="1">L6/AC6</f>
-        <v>#NAME?</v>
+      <c r="AC6" s="15">
+        <f>[1]!CALC_DMG(AV6,U6,$D$2,P6)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AD6" s="78">
+        <f>L6/AC6</f>
+        <v>9.1304347826086971</v>
       </c>
       <c r="AE6" s="22">
         <f>CALC_DMG(AJ6,V6,$D$2,P6)</f>
@@ -2697,13 +2697,13 @@
         <f>M6/AE6</f>
         <v>6.666666666666667</v>
       </c>
-      <c r="AG6" s="22" t="e">
-        <f ca="1">CALC_DMG(AV6,V6,$D$2,P6)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH6" s="77" t="e">
-        <f ca="1">M6/AG6</f>
-        <v>#NAME?</v>
+      <c r="AG6" s="22">
+        <f>[1]!CALC_DMG(AV6,V6,$D$2,P6)</f>
+        <v>3.8</v>
+      </c>
+      <c r="AH6" s="77">
+        <f>M6/AG6</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="AI6" s="8">
         <v>0</v>
@@ -2867,45 +2867,45 @@
         <f t="shared" ref="X7:X10" si="3">K7/W7</f>
         <v>80</v>
       </c>
-      <c r="Y7" s="12" t="e">
-        <f t="shared" ref="Y7:Y10" ca="1" si="4">CALC_DMG(AV7,T7,$D$2, P7)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z7" s="79" t="e">
-        <f t="shared" ref="Z7:Z10" ca="1" si="5">K7/Y7</f>
-        <v>#NAME?</v>
+      <c r="Y7" s="12">
+        <f>[1]!CALC_DMG(AV7,T7,$D$2, P7)</f>
+        <v>1.28</v>
+      </c>
+      <c r="Z7" s="79">
+        <f t="shared" ref="Z7:Z10" si="4">K7/Y7</f>
+        <v>31.25</v>
       </c>
       <c r="AA7" s="15">
-        <f t="shared" ref="AA7:AA10" si="6">CALC_DMG(AJ7,U7,$D$2,P7)</f>
+        <f t="shared" ref="AA7:AA10" si="5">CALC_DMG(AJ7,U7,$D$2,P7)</f>
         <v>2.34</v>
       </c>
       <c r="AB7" s="78">
-        <f t="shared" ref="AB7:AB10" si="7">L7/AA7</f>
+        <f t="shared" ref="AB7:AB10" si="6">L7/AA7</f>
         <v>13.888888888888889</v>
       </c>
-      <c r="AC7" s="15" t="e">
-        <f t="shared" ref="AC7:AC10" ca="1" si="8">CALC_DMG(AV7,U7,$D$2,P7)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD7" s="78" t="e">
-        <f t="shared" ref="AD7:AD10" ca="1" si="9">L7/AC7</f>
-        <v>#NAME?</v>
+      <c r="AC7" s="15">
+        <f>[1]!CALC_DMG(AV7,U7,$D$2,P7)</f>
+        <v>3.94</v>
+      </c>
+      <c r="AD7" s="78">
+        <f t="shared" ref="AD7:AD10" si="7">L7/AC7</f>
+        <v>8.2487309644670059</v>
       </c>
       <c r="AE7" s="22">
-        <f t="shared" ref="AE7:AE10" si="10">CALC_DMG(AJ7,V7,$D$2,P7)</f>
+        <f t="shared" ref="AE7:AE10" si="8">CALC_DMG(AJ7,V7,$D$2,P7)</f>
         <v>5</v>
       </c>
       <c r="AF7" s="77">
-        <f t="shared" ref="AF7:AF21" si="11">M7/AE7</f>
+        <f t="shared" ref="AF7:AF21" si="9">M7/AE7</f>
         <v>5</v>
       </c>
-      <c r="AG7" s="22" t="e">
-        <f t="shared" ref="AG7:AG10" ca="1" si="12">CALC_DMG(AV7,V7,$D$2,P7)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH7" s="77" t="e">
-        <f t="shared" ref="AH7:AH10" ca="1" si="13">M7/AG7</f>
-        <v>#NAME?</v>
+      <c r="AG7" s="22">
+        <f>[1]!CALC_DMG(AV7,V7,$D$2,P7)</f>
+        <v>6.6</v>
+      </c>
+      <c r="AH7" s="77">
+        <f t="shared" ref="AH7:AH10" si="10">M7/AG7</f>
+        <v>3.7878787878787881</v>
       </c>
       <c r="AI7" s="7" t="s">
         <v>93</v>
@@ -2951,15 +2951,15 @@
         <v>2.7412280701754392</v>
       </c>
       <c r="AV7" s="12">
-        <f t="shared" ref="AV7:AV10" si="14">AJ7*$AV$2</f>
+        <f t="shared" ref="AV7:AV10" si="11">AJ7*$AV$2</f>
         <v>9.6</v>
       </c>
       <c r="AW7" s="15">
-        <f t="shared" ref="AW7:AW10" si="15">AK7*$AW$2</f>
+        <f t="shared" ref="AW7:AW10" si="12">AK7*$AW$2</f>
         <v>27</v>
       </c>
       <c r="AX7" s="16">
-        <f t="shared" ref="AX7:AX10" si="16">AL7*$AX$2</f>
+        <f t="shared" ref="AX7:AX10" si="13">AL7*$AX$2</f>
         <v>1.2</v>
       </c>
       <c r="AY7" s="17">
@@ -2974,7 +2974,7 @@
         <v>74.362200000000001</v>
       </c>
       <c r="BB7" s="75">
-        <f t="shared" ref="BB7:BB10" si="17">AW7/BA7</f>
+        <f t="shared" ref="BB7:BB10" si="14">AW7/BA7</f>
         <v>0.36308769778193761</v>
       </c>
       <c r="BC7" s="20">
@@ -2982,7 +2982,7 @@
         <v>48.989100000000001</v>
       </c>
       <c r="BD7" s="75">
-        <f t="shared" ref="BD7:BD10" si="18">AW7/BC7</f>
+        <f t="shared" ref="BD7:BD10" si="15">AW7/BC7</f>
         <v>0.55114300936330729</v>
       </c>
       <c r="BE7" s="20">
@@ -2990,7 +2990,7 @@
         <v>23.616</v>
       </c>
       <c r="BF7" s="75">
-        <f t="shared" ref="BF7:BF10" si="19">AW7/BE7</f>
+        <f t="shared" ref="BF7:BF10" si="16">AW7/BE7</f>
         <v>1.1432926829268293</v>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
         <v>100</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" ref="L8:L10" si="20">AVERAGE(K8,M8)</f>
+        <f t="shared" ref="L8:L10" si="17">AVERAGE(K8,M8)</f>
         <v>70</v>
       </c>
       <c r="M8" s="15">
@@ -3071,45 +3071,45 @@
         <f t="shared" si="3"/>
         <v>56.657223796034032</v>
       </c>
-      <c r="Y8" s="12" t="e">
-        <f t="shared" ca="1" si="4"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z8" s="79" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#NAME?</v>
+      <c r="Y8" s="12">
+        <f>[1]!CALC_DMG(AV8,T8,$D$2, P8)</f>
+        <v>4.71</v>
+      </c>
+      <c r="Z8" s="79">
+        <f t="shared" si="4"/>
+        <v>21.231422505307854</v>
       </c>
       <c r="AA8" s="15">
+        <f t="shared" si="5"/>
+        <v>4.2449999999999992</v>
+      </c>
+      <c r="AB8" s="78">
         <f t="shared" si="6"/>
-        <v>4.2449999999999992</v>
-      </c>
-      <c r="AB8" s="78">
+        <v>16.489988221436988</v>
+      </c>
+      <c r="AC8" s="15">
+        <f>[1]!CALC_DMG(AV8,U8,$D$2,P8)</f>
+        <v>7.19</v>
+      </c>
+      <c r="AD8" s="78">
         <f t="shared" si="7"/>
-        <v>16.489988221436988</v>
-      </c>
-      <c r="AC8" s="15" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD8" s="78" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#NAME?</v>
+        <v>9.7357440890125169</v>
       </c>
       <c r="AE8" s="22">
+        <f t="shared" si="8"/>
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="AF8" s="77">
+        <f t="shared" si="9"/>
+        <v>5.947955390334573</v>
+      </c>
+      <c r="AG8" s="22">
+        <f>[1]!CALC_DMG(AV8,V8,$D$2,P8)</f>
+        <v>9.67</v>
+      </c>
+      <c r="AH8" s="77">
         <f t="shared" si="10"/>
-        <v>6.7249999999999996</v>
-      </c>
-      <c r="AF8" s="77">
-        <f t="shared" si="11"/>
-        <v>5.947955390334573</v>
-      </c>
-      <c r="AG8" s="22" t="e">
-        <f t="shared" ca="1" si="12"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH8" s="77" t="e">
-        <f t="shared" ca="1" si="13"/>
-        <v>#NAME?</v>
+        <v>4.1365046535677354</v>
       </c>
       <c r="AI8" s="8">
         <v>1</v>
@@ -3155,15 +3155,15 @@
         <v>2.7541706011960971</v>
       </c>
       <c r="AV8" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>18.599999999999998</v>
       </c>
       <c r="AW8" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AX8" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1.2</v>
       </c>
       <c r="AY8" s="17">
@@ -3178,7 +3178,7 @@
         <v>134.95159999999998</v>
       </c>
       <c r="BB8" s="75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0.62244538041786845</v>
       </c>
       <c r="BC8" s="20">
@@ -3186,7 +3186,7 @@
         <v>96.492199999999997</v>
       </c>
       <c r="BD8" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>0.87053668586683697</v>
       </c>
       <c r="BE8" s="20">
@@ -3194,7 +3194,7 @@
         <v>58.031999999999996</v>
       </c>
       <c r="BF8" s="75">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1.4474772539288669</v>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
         <v>200</v>
       </c>
       <c r="L9" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
       <c r="M9" s="15">
@@ -3273,45 +3273,45 @@
         <f t="shared" si="3"/>
         <v>16.025641025641029</v>
       </c>
-      <c r="Y9" s="12" t="e">
-        <f t="shared" ca="1" si="4"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z9" s="79" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#NAME?</v>
+      <c r="Y9" s="12">
+        <f>[1]!CALC_DMG(AV9,T9,$D$2, P9)</f>
+        <v>18.559999999999999</v>
+      </c>
+      <c r="Z9" s="79">
+        <f t="shared" si="4"/>
+        <v>10.775862068965518</v>
       </c>
       <c r="AA9" s="15">
+        <f t="shared" si="5"/>
+        <v>15.439999999999998</v>
+      </c>
+      <c r="AB9" s="78">
         <f t="shared" si="6"/>
-        <v>15.439999999999998</v>
-      </c>
-      <c r="AB9" s="78">
+        <v>9.7150259067357521</v>
+      </c>
+      <c r="AC9" s="15">
+        <f>[1]!CALC_DMG(AV9,U9,$D$2,P9)</f>
+        <v>21.52</v>
+      </c>
+      <c r="AD9" s="78">
         <f t="shared" si="7"/>
-        <v>9.7150259067357521</v>
-      </c>
-      <c r="AC9" s="15" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD9" s="78" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#NAME?</v>
+        <v>6.970260223048327</v>
       </c>
       <c r="AE9" s="22">
+        <f t="shared" si="8"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AF9" s="77">
+        <f t="shared" si="9"/>
+        <v>5.4347826086956523</v>
+      </c>
+      <c r="AG9" s="22">
+        <f>[1]!CALC_DMG(AV9,V9,$D$2,P9)</f>
+        <v>24.48</v>
+      </c>
+      <c r="AH9" s="77">
         <f t="shared" si="10"/>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="AF9" s="77">
-        <f t="shared" si="11"/>
-        <v>5.4347826086956523</v>
-      </c>
-      <c r="AG9" s="22" t="e">
-        <f t="shared" ca="1" si="12"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH9" s="77" t="e">
-        <f t="shared" ca="1" si="13"/>
-        <v>#NAME?</v>
+        <v>4.0849673202614376</v>
       </c>
       <c r="AI9" s="36" t="s">
         <v>92</v>
@@ -3357,15 +3357,15 @@
         <v>2.9089095744680846</v>
       </c>
       <c r="AV9" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>38.4</v>
       </c>
       <c r="AW9" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="AX9" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="AY9" s="17">
@@ -3380,7 +3380,7 @@
         <v>213.3304</v>
       </c>
       <c r="BB9" s="75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0.59063312120541656</v>
       </c>
       <c r="BC9" s="20">
@@ -3388,7 +3388,7 @@
         <v>153.56119999999999</v>
       </c>
       <c r="BD9" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>0.82051976671190385</v>
       </c>
       <c r="BE9" s="20">
@@ -3396,7 +3396,7 @@
         <v>93.792000000000002</v>
       </c>
       <c r="BF9" s="75">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1.3433981576253837</v>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
         <v>340</v>
       </c>
       <c r="L10" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>230</v>
       </c>
       <c r="M10" s="15">
@@ -3477,45 +3477,45 @@
         <f t="shared" si="3"/>
         <v>17.801047120418843</v>
       </c>
-      <c r="Y10" s="12" t="e">
-        <f t="shared" ca="1" si="4"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z10" s="79" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#NAME?</v>
+      <c r="Y10" s="12">
+        <f>[1]!CALC_DMG(AV10,T10,$D$2, P10)</f>
+        <v>27.56</v>
+      </c>
+      <c r="Z10" s="79">
+        <f t="shared" si="4"/>
+        <v>12.336719883889696</v>
       </c>
       <c r="AA10" s="15">
+        <f t="shared" si="5"/>
+        <v>22.200000000000003</v>
+      </c>
+      <c r="AB10" s="78">
         <f t="shared" si="6"/>
-        <v>22.200000000000003</v>
-      </c>
-      <c r="AB10" s="78">
+        <v>10.360360360360358</v>
+      </c>
+      <c r="AC10" s="15">
+        <f>[1]!CALC_DMG(AV10,U10,$D$2,P10)</f>
+        <v>30.66</v>
+      </c>
+      <c r="AD10" s="78">
         <f t="shared" si="7"/>
-        <v>10.360360360360358</v>
-      </c>
-      <c r="AC10" s="15" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD10" s="78" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#NAME?</v>
+        <v>7.5016307893020224</v>
       </c>
       <c r="AE10" s="22">
+        <f t="shared" si="8"/>
+        <v>25.300000000000004</v>
+      </c>
+      <c r="AF10" s="77">
+        <f t="shared" si="9"/>
+        <v>4.7430830039525684</v>
+      </c>
+      <c r="AG10" s="22">
+        <f>[1]!CALC_DMG(AV10,V10,$D$2,P10)</f>
+        <v>33.76</v>
+      </c>
+      <c r="AH10" s="77">
         <f t="shared" si="10"/>
-        <v>25.300000000000004</v>
-      </c>
-      <c r="AF10" s="77">
-        <f t="shared" si="11"/>
-        <v>4.7430830039525684</v>
-      </c>
-      <c r="AG10" s="22" t="e">
-        <f t="shared" ca="1" si="12"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH10" s="77" t="e">
-        <f t="shared" ca="1" si="13"/>
-        <v>#NAME?</v>
+        <v>3.5545023696682465</v>
       </c>
       <c r="AI10" s="7" t="s">
         <v>92</v>
@@ -3561,15 +3561,15 @@
         <v>3.6549707602339181</v>
       </c>
       <c r="AV10" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>56.4</v>
       </c>
       <c r="AW10" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>180</v>
       </c>
       <c r="AX10" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="AY10" s="17">
@@ -3584,7 +3584,7 @@
         <v>405.33879999999999</v>
       </c>
       <c r="BB10" s="75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0.44407295822655024</v>
       </c>
       <c r="BC10" s="20">
@@ -3592,7 +3592,7 @@
         <v>261.70960000000002</v>
       </c>
       <c r="BD10" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>0.68778523982307105</v>
       </c>
       <c r="BE10" s="20">
@@ -3600,7 +3600,7 @@
         <v>118.08</v>
       </c>
       <c r="BF10" s="75">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1.524390243902439</v>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
         <v>540</v>
       </c>
       <c r="L12" s="15">
-        <f t="shared" ref="L12:L14" si="21">AVERAGE(K12,M12)</f>
+        <f t="shared" ref="L12:L14" si="18">AVERAGE(K12,M12)</f>
         <v>420</v>
       </c>
       <c r="M12" s="15">
@@ -3669,7 +3669,7 @@
         <v>133.62999999999997</v>
       </c>
       <c r="R12" s="24">
-        <f t="shared" ref="R12:R14" si="22">AVERAGE(Q12,S12)</f>
+        <f t="shared" ref="R12:R14" si="19">AVERAGE(Q12,S12)</f>
         <v>102.81499999999998</v>
       </c>
       <c r="S12" s="24">
@@ -3680,59 +3680,59 @@
         <v>48</v>
       </c>
       <c r="U12" s="25">
-        <f t="shared" ref="U12:U14" si="23">AVERAGE(T12,V12)</f>
+        <f t="shared" ref="U12:U14" si="20">AVERAGE(T12,V12)</f>
         <v>34</v>
       </c>
       <c r="V12" s="25">
         <v>20</v>
       </c>
       <c r="W12" s="12">
-        <f t="shared" ref="W12:W14" si="24">CALC_DMG(AJ12,T12,$D$2, P12)</f>
+        <f t="shared" ref="W12:W14" si="21">CALC_DMG(AJ12,T12,$D$2, P12)</f>
         <v>30.299999999999997</v>
       </c>
       <c r="X12" s="79">
-        <f t="shared" ref="X12:X14" si="25">K12/W12</f>
+        <f t="shared" ref="X12:X14" si="22">K12/W12</f>
         <v>17.821782178217823</v>
       </c>
-      <c r="Y12" s="12" t="e">
-        <f t="shared" ref="Y12:Y14" ca="1" si="26">CALC_DMG(AV12,T12,$D$2, P12)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z12" s="79" t="e">
-        <f t="shared" ref="Z12:Z14" ca="1" si="27">K12/Y12</f>
-        <v>#NAME?</v>
+      <c r="Y12" s="12">
+        <f>[1]!CALC_DMG(AV12,T12,$D$2, P12)</f>
+        <v>45.96</v>
+      </c>
+      <c r="Z12" s="79">
+        <f t="shared" ref="Z12:Z14" si="23">K12/Y12</f>
+        <v>11.74934725848564</v>
       </c>
       <c r="AA12" s="15">
-        <f t="shared" ref="AA12:AA14" si="28">CALC_DMG(AJ12,U12,$D$2,P12)</f>
+        <f t="shared" ref="AA12:AA14" si="24">CALC_DMG(AJ12,U12,$D$2,P12)</f>
         <v>44.3</v>
       </c>
       <c r="AB12" s="78">
-        <f t="shared" ref="AB12:AB14" si="29">L12/AA12</f>
+        <f t="shared" ref="AB12:AB14" si="25">L12/AA12</f>
         <v>9.4808126410835225</v>
       </c>
-      <c r="AC12" s="15" t="e">
-        <f t="shared" ref="AC12:AC14" ca="1" si="30">CALC_DMG(AV12,U12,$D$2,P12)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD12" s="78" t="e">
-        <f t="shared" ref="AD12:AD14" ca="1" si="31">L12/AC12</f>
-        <v>#NAME?</v>
+      <c r="AC12" s="15">
+        <f>[1]!CALC_DMG(AV12,U12,$D$2,P12)</f>
+        <v>59.96</v>
+      </c>
+      <c r="AD12" s="78">
+        <f t="shared" ref="AD12:AD14" si="26">L12/AC12</f>
+        <v>7.0046697798532351</v>
       </c>
       <c r="AE12" s="22">
-        <f t="shared" ref="AE12:AE14" si="32">CALC_DMG(AJ12,V12,$D$2,P12)</f>
+        <f t="shared" ref="AE12:AE14" si="27">CALC_DMG(AJ12,V12,$D$2,P12)</f>
         <v>58.3</v>
       </c>
       <c r="AF12" s="77">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>5.1457975986277873</v>
       </c>
-      <c r="AG12" s="22" t="e">
-        <f t="shared" ref="AG12:AG14" ca="1" si="33">CALC_DMG(AV12,V12,$D$2,P12)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH12" s="77" t="e">
-        <f t="shared" ref="AH12:AH14" ca="1" si="34">M12/AG12</f>
-        <v>#NAME?</v>
+      <c r="AG12" s="22">
+        <f>[1]!CALC_DMG(AV12,V12,$D$2,P12)</f>
+        <v>73.959999999999994</v>
+      </c>
+      <c r="AH12" s="77">
+        <f t="shared" ref="AH12:AH14" si="28">M12/AG12</f>
+        <v>4.056246619794484</v>
       </c>
       <c r="AI12" s="7" t="s">
         <v>92</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="AN12" s="17">
-        <f t="shared" ref="AN12:AN14" si="35">AL12*(1+(0.02*AM12))</f>
+        <f t="shared" ref="AN12:AN14" si="29">AL12*(1+(0.02*AM12))</f>
         <v>20</v>
       </c>
       <c r="AO12" s="20">
@@ -3778,22 +3778,22 @@
         <v>3.4335942864991078</v>
       </c>
       <c r="AV12" s="12">
-        <f t="shared" ref="AV12:AV14" si="36">AJ12*$AV$2</f>
+        <f t="shared" ref="AV12:AV14" si="30">AJ12*$AV$2</f>
         <v>104.39999999999999</v>
       </c>
       <c r="AW12" s="15">
-        <f t="shared" ref="AW12:AW14" si="37">AK12*$AW$2</f>
+        <f t="shared" ref="AW12:AW14" si="31">AK12*$AW$2</f>
         <v>480</v>
       </c>
       <c r="AX12" s="16">
-        <f t="shared" ref="AX12:AX14" si="38">AL12*$AX$2</f>
+        <f t="shared" ref="AX12:AX14" si="32">AL12*$AX$2</f>
         <v>12</v>
       </c>
       <c r="AY12" s="17">
         <v>0</v>
       </c>
       <c r="AZ12" s="17">
-        <f t="shared" ref="AZ12:AZ14" si="39">AX12*(1+(0.02*AY12))</f>
+        <f t="shared" ref="AZ12:AZ14" si="33">AX12*(1+(0.02*AY12))</f>
         <v>12</v>
       </c>
       <c r="BA12" s="20">
@@ -3801,7 +3801,7 @@
         <v>658.50159999999994</v>
       </c>
       <c r="BB12" s="75">
-        <f t="shared" ref="BB12:BB14" si="40">AW12/BA12</f>
+        <f t="shared" ref="BB12:BB14" si="34">AW12/BA12</f>
         <v>0.7289276138433074</v>
       </c>
       <c r="BC12" s="20">
@@ -3809,7 +3809,7 @@
         <v>481.74700000000001</v>
       </c>
       <c r="BD12" s="75">
-        <f t="shared" ref="BD12:BD14" si="41">AW12/BC12</f>
+        <f t="shared" ref="BD12:BD14" si="35">AW12/BC12</f>
         <v>0.99637361519635825</v>
       </c>
       <c r="BE12" s="20">
@@ -3817,7 +3817,7 @@
         <v>304.99200000000002</v>
       </c>
       <c r="BF12" s="75">
-        <f t="shared" ref="BF12:BF14" si="42">AW12/BE12</f>
+        <f t="shared" ref="BF12:BF14" si="36">AW12/BE12</f>
         <v>1.5738117721120553</v>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
         <v>740</v>
       </c>
       <c r="L13" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>620</v>
       </c>
       <c r="M13" s="33">
@@ -3873,7 +3873,7 @@
         <v>220.5</v>
       </c>
       <c r="R13" s="24">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>167.75</v>
       </c>
       <c r="S13" s="24">
@@ -3884,59 +3884,59 @@
         <v>76.8</v>
       </c>
       <c r="U13" s="25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>59.4</v>
       </c>
       <c r="V13" s="25">
         <v>42</v>
       </c>
       <c r="W13" s="12">
+        <f t="shared" si="21"/>
+        <v>46.45</v>
+      </c>
+      <c r="X13" s="79">
+        <f t="shared" si="22"/>
+        <v>15.931108719052745</v>
+      </c>
+      <c r="Y13" s="12">
+        <f>[1]!CALC_DMG(AV13,T13,$D$2, P13)</f>
+        <v>71.099999999999994</v>
+      </c>
+      <c r="Z13" s="79">
+        <f t="shared" si="23"/>
+        <v>10.407876230661042</v>
+      </c>
+      <c r="AA13" s="15">
         <f t="shared" si="24"/>
-        <v>46.45</v>
-      </c>
-      <c r="X13" s="79">
+        <v>63.85</v>
+      </c>
+      <c r="AB13" s="78">
         <f t="shared" si="25"/>
-        <v>15.931108719052745</v>
-      </c>
-      <c r="Y13" s="12" t="e">
-        <f t="shared" ca="1" si="26"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z13" s="79" t="e">
-        <f t="shared" ca="1" si="27"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA13" s="15">
+        <v>9.7102584181675802</v>
+      </c>
+      <c r="AC13" s="15">
+        <f>[1]!CALC_DMG(AV13,U13,$D$2,P13)</f>
+        <v>88.5</v>
+      </c>
+      <c r="AD13" s="78">
+        <f t="shared" si="26"/>
+        <v>7.0056497175141246</v>
+      </c>
+      <c r="AE13" s="22">
+        <f t="shared" si="27"/>
+        <v>81.25</v>
+      </c>
+      <c r="AF13" s="77">
+        <f t="shared" si="9"/>
+        <v>6.1538461538461542</v>
+      </c>
+      <c r="AG13" s="22">
+        <f>[1]!CALC_DMG(AV13,V13,$D$2,P13)</f>
+        <v>105.9</v>
+      </c>
+      <c r="AH13" s="77">
         <f t="shared" si="28"/>
-        <v>63.85</v>
-      </c>
-      <c r="AB13" s="78">
-        <f t="shared" si="29"/>
-        <v>9.7102584181675802</v>
-      </c>
-      <c r="AC13" s="15" t="e">
-        <f t="shared" ca="1" si="30"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD13" s="78" t="e">
-        <f t="shared" ca="1" si="31"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AE13" s="22">
-        <f t="shared" si="32"/>
-        <v>81.25</v>
-      </c>
-      <c r="AF13" s="77">
-        <f t="shared" si="11"/>
-        <v>6.1538461538461542</v>
-      </c>
-      <c r="AG13" s="22" t="e">
-        <f t="shared" ca="1" si="33"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH13" s="77" t="e">
-        <f t="shared" ca="1" si="34"/>
-        <v>#NAME?</v>
+        <v>4.7214353163361658</v>
       </c>
       <c r="AI13" s="8">
         <v>2</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="AN13" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v>40</v>
       </c>
       <c r="AO13" s="20">
@@ -3982,22 +3982,22 @@
         <v>3.6710719530102791</v>
       </c>
       <c r="AV13" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>174</v>
       </c>
       <c r="AW13" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>660</v>
       </c>
       <c r="AX13" s="16">
-        <f t="shared" si="38"/>
+        <f t="shared" si="32"/>
         <v>24</v>
       </c>
       <c r="AY13" s="17">
         <v>0</v>
       </c>
       <c r="AZ13" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="33"/>
         <v>24</v>
       </c>
       <c r="BA13" s="20">
@@ -4005,7 +4005,7 @@
         <v>1048.788</v>
       </c>
       <c r="BB13" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>0.62929781805283813</v>
       </c>
       <c r="BC13" s="20">
@@ -4013,7 +4013,7 @@
         <v>746.21399999999994</v>
       </c>
       <c r="BD13" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="35"/>
         <v>0.88446477820035552</v>
       </c>
       <c r="BE13" s="20">
@@ -4021,7 +4021,7 @@
         <v>443.64</v>
       </c>
       <c r="BF13" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>1.4876927238301325</v>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>850</v>
       </c>
       <c r="M14" s="15">
@@ -4075,7 +4075,7 @@
         <v>358.21499999999997</v>
       </c>
       <c r="R14" s="24">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>339.10749999999996</v>
       </c>
       <c r="S14" s="24">
@@ -4086,59 +4086,59 @@
         <v>108.79999999999998</v>
       </c>
       <c r="U14" s="25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>89.399999999999991</v>
       </c>
       <c r="V14" s="25">
         <v>70</v>
       </c>
       <c r="W14" s="12">
+        <f t="shared" si="21"/>
+        <v>73.950000000000017</v>
+      </c>
+      <c r="X14" s="79">
+        <f t="shared" si="22"/>
+        <v>13.522650439486137</v>
+      </c>
+      <c r="Y14" s="12">
+        <f>[1]!CALC_DMG(AV14,T14,$D$2, P14)</f>
+        <v>110.5</v>
+      </c>
+      <c r="Z14" s="79">
+        <f t="shared" si="23"/>
+        <v>9.0497737556561084</v>
+      </c>
+      <c r="AA14" s="15">
         <f t="shared" si="24"/>
-        <v>73.950000000000017</v>
-      </c>
-      <c r="X14" s="79">
+        <v>93.350000000000009</v>
+      </c>
+      <c r="AB14" s="78">
         <f t="shared" si="25"/>
-        <v>13.522650439486137</v>
-      </c>
-      <c r="Y14" s="12" t="e">
-        <f t="shared" ca="1" si="26"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z14" s="79" t="e">
-        <f t="shared" ca="1" si="27"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA14" s="15">
+        <v>9.1055168719871435</v>
+      </c>
+      <c r="AC14" s="15">
+        <f>[1]!CALC_DMG(AV14,U14,$D$2,P14)</f>
+        <v>129.9</v>
+      </c>
+      <c r="AD14" s="78">
+        <f t="shared" si="26"/>
+        <v>6.5434949961508853</v>
+      </c>
+      <c r="AE14" s="22">
+        <f t="shared" si="27"/>
+        <v>112.75</v>
+      </c>
+      <c r="AF14" s="77">
+        <f t="shared" si="9"/>
+        <v>6.2084257206208422</v>
+      </c>
+      <c r="AG14" s="22">
+        <f>[1]!CALC_DMG(AV14,V14,$D$2,P14)</f>
+        <v>149.30000000000001</v>
+      </c>
+      <c r="AH14" s="77">
         <f t="shared" si="28"/>
-        <v>93.350000000000009</v>
-      </c>
-      <c r="AB14" s="78">
-        <f t="shared" si="29"/>
-        <v>9.1055168719871435</v>
-      </c>
-      <c r="AC14" s="15" t="e">
-        <f t="shared" ca="1" si="30"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD14" s="78" t="e">
-        <f t="shared" ca="1" si="31"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AE14" s="22">
-        <f t="shared" si="32"/>
-        <v>112.75</v>
-      </c>
-      <c r="AF14" s="77">
-        <f t="shared" si="11"/>
-        <v>6.2084257206208422</v>
-      </c>
-      <c r="AG14" s="22" t="e">
-        <f t="shared" ca="1" si="33"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH14" s="77" t="e">
-        <f t="shared" ca="1" si="34"/>
-        <v>#NAME?</v>
+        <v>4.6885465505693231</v>
       </c>
       <c r="AI14" s="7" t="s">
         <v>94</v>
@@ -4156,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v>60</v>
       </c>
       <c r="AO14" s="20">
@@ -4184,22 +4184,22 @@
         <v>3.0875632950475485</v>
       </c>
       <c r="AV14" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>258</v>
       </c>
       <c r="AW14" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>2400</v>
       </c>
       <c r="AX14" s="16">
-        <f t="shared" si="38"/>
+        <f t="shared" si="32"/>
         <v>36</v>
       </c>
       <c r="AY14" s="17">
         <v>0</v>
       </c>
       <c r="AZ14" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="33"/>
         <v>36</v>
       </c>
       <c r="BA14" s="20">
@@ -4207,7 +4207,7 @@
         <v>1730.7213999999999</v>
       </c>
       <c r="BB14" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>1.3867049890294303</v>
       </c>
       <c r="BC14" s="20">
@@ -4215,7 +4215,7 @@
         <v>1621.1206999999999</v>
       </c>
       <c r="BD14" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="35"/>
         <v>1.4804573157322587</v>
       </c>
       <c r="BE14" s="20">
@@ -4223,7 +4223,7 @@
         <v>1511.52</v>
       </c>
       <c r="BF14" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>1.5878056525881232</v>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v>1300</v>
       </c>
       <c r="L16" s="15">
-        <f t="shared" ref="L16:L18" si="43">AVERAGE(K16,M16)</f>
+        <f t="shared" ref="L16:L18" si="37">AVERAGE(K16,M16)</f>
         <v>1150</v>
       </c>
       <c r="M16" s="15">
@@ -4293,7 +4293,7 @@
         <v>544.31999999999994</v>
       </c>
       <c r="R16" s="24">
-        <f t="shared" ref="R16:R18" si="44">AVERAGE(Q16,S16)</f>
+        <f t="shared" ref="R16:R18" si="38">AVERAGE(Q16,S16)</f>
         <v>447.15999999999997</v>
       </c>
       <c r="S16" s="24">
@@ -4304,59 +4304,59 @@
         <v>167.2</v>
       </c>
       <c r="U16" s="25">
-        <f t="shared" ref="U16:U18" si="45">AVERAGE(T16,V16)</f>
+        <f t="shared" ref="U16:U18" si="39">AVERAGE(T16,V16)</f>
         <v>131.1</v>
       </c>
       <c r="V16" s="25">
         <v>95</v>
       </c>
       <c r="W16" s="12">
-        <f t="shared" ref="W16:W18" si="46">CALC_DMG(AJ16,T16,$D$2, P16)</f>
+        <f t="shared" ref="W16:W18" si="40">CALC_DMG(AJ16,T16,$D$2, P16)</f>
         <v>92.800000000000011</v>
       </c>
       <c r="X16" s="79">
-        <f t="shared" ref="X16:X18" si="47">K16/W16</f>
+        <f t="shared" ref="X16:X18" si="41">K16/W16</f>
         <v>14.008620689655171</v>
       </c>
-      <c r="Y16" s="12" t="e">
-        <f t="shared" ref="Y16:Y18" ca="1" si="48">CALC_DMG(AV16,T16,$D$2, P16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z16" s="79" t="e">
-        <f t="shared" ref="Z16:Z18" ca="1" si="49">K16/Y16</f>
-        <v>#NAME?</v>
+      <c r="Y16" s="12">
+        <f>[1]!CALC_DMG(AV16,T16,$D$2, P16)</f>
+        <v>144.80000000000001</v>
+      </c>
+      <c r="Z16" s="79">
+        <f t="shared" ref="Z16:Z18" si="42">K16/Y16</f>
+        <v>8.9779005524861866</v>
       </c>
       <c r="AA16" s="15">
-        <f t="shared" ref="AA16:AA18" si="50">CALC_DMG(AJ16,U16,$D$2,P16)</f>
+        <f t="shared" ref="AA16:AA18" si="43">CALC_DMG(AJ16,U16,$D$2,P16)</f>
         <v>128.9</v>
       </c>
       <c r="AB16" s="78">
-        <f t="shared" ref="AB16:AB18" si="51">L16/AA16</f>
+        <f t="shared" ref="AB16:AB18" si="44">L16/AA16</f>
         <v>8.9216446858029474</v>
       </c>
-      <c r="AC16" s="15" t="e">
-        <f t="shared" ref="AC16:AC18" ca="1" si="52">CALC_DMG(AV16,U16,$D$2,P16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD16" s="78" t="e">
-        <f t="shared" ref="AD16:AD18" ca="1" si="53">L16/AC16</f>
-        <v>#NAME?</v>
+      <c r="AC16" s="15">
+        <f>[1]!CALC_DMG(AV16,U16,$D$2,P16)</f>
+        <v>180.9</v>
+      </c>
+      <c r="AD16" s="78">
+        <f t="shared" ref="AD16:AD18" si="45">L16/AC16</f>
+        <v>6.3571033720287451</v>
       </c>
       <c r="AE16" s="22">
-        <f t="shared" ref="AE16:AE18" si="54">CALC_DMG(AJ16,V16,$D$2,P16)</f>
+        <f t="shared" ref="AE16:AE18" si="46">CALC_DMG(AJ16,V16,$D$2,P16)</f>
         <v>165</v>
       </c>
       <c r="AF16" s="77">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>6.0606060606060606</v>
       </c>
-      <c r="AG16" s="22" t="e">
-        <f t="shared" ref="AG16:AG18" ca="1" si="55">CALC_DMG(AV16,V16,$D$2,P16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH16" s="77" t="e">
-        <f t="shared" ref="AH16:AH18" ca="1" si="56">M16/AG16</f>
-        <v>#NAME?</v>
+      <c r="AG16" s="22">
+        <f>[1]!CALC_DMG(AV16,V16,$D$2,P16)</f>
+        <v>217</v>
+      </c>
+      <c r="AH16" s="77">
+        <f t="shared" ref="AH16:AH18" si="47">M16/AG16</f>
+        <v>4.6082949308755756</v>
       </c>
       <c r="AI16" s="8">
         <v>3</v>
@@ -4374,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="17">
-        <f t="shared" ref="AN16:AN18" si="57">AL16*(1+(0.02*AM16))</f>
+        <f t="shared" ref="AN16:AN18" si="48">AL16*(1+(0.02*AM16))</f>
         <v>80</v>
       </c>
       <c r="AO16" s="20">
@@ -4402,22 +4402,22 @@
         <v>3.4948741845293574</v>
       </c>
       <c r="AV16" s="12">
-        <f t="shared" ref="AV16:AV18" si="58">AJ16*$AV$2</f>
+        <f t="shared" ref="AV16:AV18" si="49">AJ16*$AV$2</f>
         <v>390</v>
       </c>
       <c r="AW16" s="15">
-        <f t="shared" ref="AW16:AW18" si="59">AK16*$AW$2</f>
+        <f t="shared" ref="AW16:AW18" si="50">AK16*$AW$2</f>
         <v>2700</v>
       </c>
       <c r="AX16" s="16">
-        <f t="shared" ref="AX16:AX18" si="60">AL16*$AX$2</f>
+        <f t="shared" ref="AX16:AX18" si="51">AL16*$AX$2</f>
         <v>48</v>
       </c>
       <c r="AY16" s="17">
         <v>0</v>
       </c>
       <c r="AZ16" s="17">
-        <f t="shared" ref="AZ16:AZ18" si="61">AX16*(1+(0.02*AY16))</f>
+        <f t="shared" ref="AZ16:AZ18" si="52">AX16*(1+(0.02*AY16))</f>
         <v>48</v>
       </c>
       <c r="BA16" s="20">
@@ -4425,7 +4425,7 @@
         <v>2690.2196000000004</v>
       </c>
       <c r="BB16" s="75">
-        <f t="shared" ref="BB16:BB18" si="62">AW16/BA16</f>
+        <f t="shared" ref="BB16:BB18" si="53">AW16/BA16</f>
         <v>1.0036355396414478</v>
       </c>
       <c r="BC16" s="20">
@@ -4433,7 +4433,7 @@
         <v>2132.9096</v>
       </c>
       <c r="BD16" s="75">
-        <f t="shared" ref="BD16:BD18" si="63">AW16/BC16</f>
+        <f t="shared" ref="BD16:BD18" si="54">AW16/BC16</f>
         <v>1.2658764347068436</v>
       </c>
       <c r="BE16" s="20">
@@ -4441,7 +4441,7 @@
         <v>1575.6</v>
       </c>
       <c r="BF16" s="75">
-        <f t="shared" ref="BF16:BF18" si="64">AW16/BE16</f>
+        <f t="shared" ref="BF16:BF18" si="55">AW16/BE16</f>
         <v>1.7136329017517138</v>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         <v>1600</v>
       </c>
       <c r="L17" s="15">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>1450</v>
       </c>
       <c r="M17" s="15">
@@ -4495,7 +4495,7 @@
         <v>801.44999999999993</v>
       </c>
       <c r="R17" s="24">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>670.72499999999991</v>
       </c>
       <c r="S17" s="24">
@@ -4506,59 +4506,59 @@
         <v>235.20000000000002</v>
       </c>
       <c r="U17" s="25">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>195.10000000000002</v>
       </c>
       <c r="V17" s="25">
         <v>155</v>
       </c>
       <c r="W17" s="12">
+        <f t="shared" si="40"/>
+        <v>132.79999999999998</v>
+      </c>
+      <c r="X17" s="79">
+        <f t="shared" si="41"/>
+        <v>12.04819277108434</v>
+      </c>
+      <c r="Y17" s="12">
+        <f>[1]!CALC_DMG(AV17,T17,$D$2, P17)</f>
+        <v>206.4</v>
+      </c>
+      <c r="Z17" s="79">
+        <f t="shared" si="42"/>
+        <v>7.7519379844961236</v>
+      </c>
+      <c r="AA17" s="15">
+        <f t="shared" si="43"/>
+        <v>172.89999999999998</v>
+      </c>
+      <c r="AB17" s="78">
+        <f t="shared" si="44"/>
+        <v>8.3863504916136513</v>
+      </c>
+      <c r="AC17" s="15">
+        <f>[1]!CALC_DMG(AV17,U17,$D$2,P17)</f>
+        <v>246.5</v>
+      </c>
+      <c r="AD17" s="78">
+        <f t="shared" si="45"/>
+        <v>5.882352941176471</v>
+      </c>
+      <c r="AE17" s="22">
         <f t="shared" si="46"/>
-        <v>132.79999999999998</v>
-      </c>
-      <c r="X17" s="79">
+        <v>213</v>
+      </c>
+      <c r="AF17" s="77">
+        <f t="shared" si="9"/>
+        <v>6.103286384976526</v>
+      </c>
+      <c r="AG17" s="22">
+        <f>[1]!CALC_DMG(AV17,V17,$D$2,P17)</f>
+        <v>286.60000000000002</v>
+      </c>
+      <c r="AH17" s="77">
         <f t="shared" si="47"/>
-        <v>12.04819277108434</v>
-      </c>
-      <c r="Y17" s="12" t="e">
-        <f t="shared" ca="1" si="48"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z17" s="79" t="e">
-        <f t="shared" ca="1" si="49"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA17" s="15">
-        <f t="shared" si="50"/>
-        <v>172.89999999999998</v>
-      </c>
-      <c r="AB17" s="78">
-        <f t="shared" si="51"/>
-        <v>8.3863504916136513</v>
-      </c>
-      <c r="AC17" s="15" t="e">
-        <f t="shared" ca="1" si="52"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD17" s="78" t="e">
-        <f t="shared" ca="1" si="53"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AE17" s="22">
-        <f t="shared" si="54"/>
-        <v>213</v>
-      </c>
-      <c r="AF17" s="77">
-        <f t="shared" si="11"/>
-        <v>6.103286384976526</v>
-      </c>
-      <c r="AG17" s="22" t="e">
-        <f t="shared" ca="1" si="55"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH17" s="77" t="e">
-        <f t="shared" ca="1" si="56"/>
-        <v>#NAME?</v>
+        <v>4.5359385903698533</v>
       </c>
       <c r="AI17" s="7" t="s">
         <v>95</v>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="AN17" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="48"/>
         <v>110</v>
       </c>
       <c r="AO17" s="20">
@@ -4604,22 +4604,22 @@
         <v>3.7960748585962123</v>
       </c>
       <c r="AV17" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="49"/>
         <v>552</v>
       </c>
       <c r="AW17" s="15">
-        <f t="shared" si="59"/>
+        <f t="shared" si="50"/>
         <v>4800</v>
       </c>
       <c r="AX17" s="16">
-        <f t="shared" si="60"/>
+        <f t="shared" si="51"/>
         <v>66</v>
       </c>
       <c r="AY17" s="17">
         <v>0</v>
       </c>
       <c r="AZ17" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="52"/>
         <v>66</v>
       </c>
       <c r="BA17" s="20">
@@ -4627,7 +4627,7 @@
         <v>4003.1171999999997</v>
       </c>
       <c r="BB17" s="75">
-        <f t="shared" si="62"/>
+        <f t="shared" si="53"/>
         <v>1.1990655682026998</v>
       </c>
       <c r="BC17" s="20">
@@ -4635,7 +4635,7 @@
         <v>3253.279</v>
       </c>
       <c r="BD17" s="75">
-        <f t="shared" si="63"/>
+        <f t="shared" si="54"/>
         <v>1.4754344770307126</v>
       </c>
       <c r="BE17" s="20">
@@ -4643,7 +4643,7 @@
         <v>2503.44</v>
       </c>
       <c r="BF17" s="75">
-        <f t="shared" si="64"/>
+        <f t="shared" si="55"/>
         <v>1.9173617102866456</v>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
         <v>1900</v>
       </c>
       <c r="L18" s="15">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>1750</v>
       </c>
       <c r="M18" s="15">
@@ -4697,7 +4697,7 @@
         <v>1115.5200000000002</v>
       </c>
       <c r="R18" s="24">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>957.7600000000001</v>
       </c>
       <c r="S18" s="24">
@@ -4708,59 +4708,59 @@
         <v>312.79999999999995</v>
       </c>
       <c r="U18" s="25">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>271.39999999999998</v>
       </c>
       <c r="V18" s="25">
         <v>230</v>
       </c>
       <c r="W18" s="12">
+        <f t="shared" si="40"/>
+        <v>177.2</v>
+      </c>
+      <c r="X18" s="79">
+        <f t="shared" si="41"/>
+        <v>10.72234762979684</v>
+      </c>
+      <c r="Y18" s="12">
+        <f>[1]!CALC_DMG(AV18,T18,$D$2, P18)</f>
+        <v>275.2</v>
+      </c>
+      <c r="Z18" s="79">
+        <f t="shared" si="42"/>
+        <v>6.904069767441861</v>
+      </c>
+      <c r="AA18" s="15">
+        <f t="shared" si="43"/>
+        <v>218.59999999999997</v>
+      </c>
+      <c r="AB18" s="78">
+        <f t="shared" si="44"/>
+        <v>8.005489478499543</v>
+      </c>
+      <c r="AC18" s="15">
+        <f>[1]!CALC_DMG(AV18,U18,$D$2,P18)</f>
+        <v>316.60000000000002</v>
+      </c>
+      <c r="AD18" s="78">
+        <f t="shared" si="45"/>
+        <v>5.5274794693619702</v>
+      </c>
+      <c r="AE18" s="22">
         <f t="shared" si="46"/>
-        <v>177.2</v>
-      </c>
-      <c r="X18" s="79">
+        <v>259.99999999999994</v>
+      </c>
+      <c r="AF18" s="77">
+        <f t="shared" si="9"/>
+        <v>6.1538461538461551</v>
+      </c>
+      <c r="AG18" s="22">
+        <f>[1]!CALC_DMG(AV18,V18,$D$2,P18)</f>
+        <v>358</v>
+      </c>
+      <c r="AH18" s="77">
         <f t="shared" si="47"/>
-        <v>10.72234762979684</v>
-      </c>
-      <c r="Y18" s="12" t="e">
-        <f t="shared" ca="1" si="48"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z18" s="79" t="e">
-        <f t="shared" ca="1" si="49"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA18" s="15">
-        <f t="shared" si="50"/>
-        <v>218.59999999999997</v>
-      </c>
-      <c r="AB18" s="78">
-        <f t="shared" si="51"/>
-        <v>8.005489478499543</v>
-      </c>
-      <c r="AC18" s="15" t="e">
-        <f t="shared" ca="1" si="52"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD18" s="78" t="e">
-        <f t="shared" ca="1" si="53"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AE18" s="22">
-        <f t="shared" si="54"/>
-        <v>259.99999999999994</v>
-      </c>
-      <c r="AF18" s="77">
-        <f t="shared" si="11"/>
-        <v>6.1538461538461551</v>
-      </c>
-      <c r="AG18" s="22" t="e">
-        <f t="shared" ca="1" si="55"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH18" s="77" t="e">
-        <f t="shared" ca="1" si="56"/>
-        <v>#NAME?</v>
+        <v>4.4692737430167595</v>
       </c>
       <c r="AI18" s="7" t="s">
         <v>95</v>
@@ -4778,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="48"/>
         <v>145</v>
       </c>
       <c r="AO18" s="20">
@@ -4806,22 +4806,22 @@
         <v>3.9588281868566901</v>
       </c>
       <c r="AV18" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="49"/>
         <v>840</v>
       </c>
       <c r="AW18" s="15">
-        <f t="shared" si="59"/>
+        <f t="shared" si="50"/>
         <v>7800</v>
       </c>
       <c r="AX18" s="16">
-        <f t="shared" si="60"/>
+        <f t="shared" si="51"/>
         <v>87</v>
       </c>
       <c r="AY18" s="17">
         <v>0</v>
       </c>
       <c r="AZ18" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="52"/>
         <v>87</v>
       </c>
       <c r="BA18" s="20">
@@ -4829,7 +4829,7 @@
         <v>5615.6227999999992</v>
       </c>
       <c r="BB18" s="75">
-        <f t="shared" si="62"/>
+        <f t="shared" si="53"/>
         <v>1.3889821802133864</v>
       </c>
       <c r="BC18" s="20">
@@ -4837,7 +4837,7 @@
         <v>4710.7112000000006</v>
       </c>
       <c r="BD18" s="75">
-        <f t="shared" si="63"/>
+        <f t="shared" si="54"/>
         <v>1.6558009329886321</v>
       </c>
       <c r="BE18" s="20">
@@ -4845,7 +4845,7 @@
         <v>3805.8</v>
       </c>
       <c r="BF18" s="75">
-        <f t="shared" si="64"/>
+        <f t="shared" si="55"/>
         <v>2.0495033895632981</v>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
         <v>2020</v>
       </c>
       <c r="L20" s="15">
-        <f t="shared" ref="L20:L21" si="65">AVERAGE(K20,M20)</f>
+        <f t="shared" ref="L20:L21" si="56">AVERAGE(K20,M20)</f>
         <v>1960</v>
       </c>
       <c r="M20" s="15">
@@ -4915,7 +4915,7 @@
         <v>1908.5625</v>
       </c>
       <c r="R20" s="24">
-        <f t="shared" ref="R20:R21" si="66">AVERAGE(Q20,S20)</f>
+        <f t="shared" ref="R20:R21" si="57">AVERAGE(Q20,S20)</f>
         <v>1504.28125</v>
       </c>
       <c r="S20" s="24">
@@ -4926,59 +4926,59 @@
         <v>428.40000000000003</v>
       </c>
       <c r="U20" s="25">
-        <f t="shared" ref="U20:U21" si="67">AVERAGE(T20,V20)</f>
+        <f t="shared" ref="U20:U21" si="58">AVERAGE(T20,V20)</f>
         <v>369.20000000000005</v>
       </c>
       <c r="V20" s="25">
         <v>310</v>
       </c>
       <c r="W20" s="12">
-        <f t="shared" ref="W20:W21" si="68">CALC_DMG(AJ20,T20,$D$2, P20)</f>
+        <f t="shared" ref="W20:W21" si="59">CALC_DMG(AJ20,T20,$D$2, P20)</f>
         <v>185.84999999999997</v>
       </c>
       <c r="X20" s="79">
-        <f t="shared" ref="X20:X21" si="69">K20/W20</f>
+        <f t="shared" ref="X20:X21" si="60">K20/W20</f>
         <v>10.868980360505786</v>
       </c>
-      <c r="Y20" s="12" t="e">
-        <f t="shared" ref="Y20:Y21" ca="1" si="70">CALC_DMG(AV20,T20,$D$2, P20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z20" s="79" t="e">
-        <f t="shared" ref="Z20:Z21" ca="1" si="71">K20/Y20</f>
-        <v>#NAME?</v>
+      <c r="Y20" s="12">
+        <f>[1]!CALC_DMG(AV20,T20,$D$2, P20)</f>
+        <v>308.7</v>
+      </c>
+      <c r="Z20" s="79">
+        <f t="shared" ref="Z20:Z21" si="61">K20/Y20</f>
+        <v>6.5435698088759313</v>
       </c>
       <c r="AA20" s="15">
-        <f t="shared" ref="AA20:AA21" si="72">CALC_DMG(AJ20,U20,$D$2,P20)</f>
+        <f t="shared" ref="AA20:AA21" si="62">CALC_DMG(AJ20,U20,$D$2,P20)</f>
         <v>245.04999999999995</v>
       </c>
       <c r="AB20" s="78">
-        <f t="shared" ref="AB20:AB21" si="73">L20/AA20</f>
+        <f t="shared" ref="AB20:AB21" si="63">L20/AA20</f>
         <v>7.9983676800652939</v>
       </c>
-      <c r="AC20" s="15" t="e">
-        <f t="shared" ref="AC20:AC21" ca="1" si="74">CALC_DMG(AV20,U20,$D$2,P20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD20" s="78" t="e">
-        <f t="shared" ref="AD20:AD21" ca="1" si="75">L20/AC20</f>
-        <v>#NAME?</v>
+      <c r="AC20" s="15">
+        <f>[1]!CALC_DMG(AV20,U20,$D$2,P20)</f>
+        <v>367.9</v>
+      </c>
+      <c r="AD20" s="78">
+        <f t="shared" ref="AD20:AD21" si="64">L20/AC20</f>
+        <v>5.3275346561565646</v>
       </c>
       <c r="AE20" s="22">
-        <f t="shared" ref="AE20:AE21" si="76">CALC_DMG(AJ20,V20,$D$2,P20)</f>
+        <f t="shared" ref="AE20:AE21" si="65">CALC_DMG(AJ20,V20,$D$2,P20)</f>
         <v>304.25</v>
       </c>
       <c r="AF20" s="77">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>6.2448644207066559</v>
       </c>
-      <c r="AG20" s="22" t="e">
-        <f t="shared" ref="AG20:AG21" ca="1" si="77">CALC_DMG(AV20,V20,$D$2,P20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH20" s="77" t="e">
-        <f t="shared" ref="AH20:AH21" ca="1" si="78">M20/AG20</f>
-        <v>#NAME?</v>
+      <c r="AG20" s="22">
+        <f>[1]!CALC_DMG(AV20,V20,$D$2,P20)</f>
+        <v>427.1</v>
+      </c>
+      <c r="AH20" s="77">
+        <f t="shared" ref="AH20:AH21" si="66">M20/AG20</f>
+        <v>4.4486068836338095</v>
       </c>
       <c r="AI20" s="8">
         <v>4</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="AN20" s="17">
-        <f t="shared" ref="AN20:AN21" si="79">AL20*(1+(0.02*AM20))</f>
+        <f t="shared" ref="AN20:AN21" si="67">AL20*(1+(0.02*AM20))</f>
         <v>180</v>
       </c>
       <c r="AO20" s="20">
@@ -5024,22 +5024,22 @@
         <v>4.05151825315592</v>
       </c>
       <c r="AV20" s="12">
-        <f t="shared" ref="AV20:AV21" si="80">AJ20*$AV$2</f>
+        <f t="shared" ref="AV20:AV21" si="68">AJ20*$AV$2</f>
         <v>1134</v>
       </c>
       <c r="AW20" s="15">
-        <f t="shared" ref="AW20:AW21" si="81">AK20*$AW$2</f>
+        <f t="shared" ref="AW20:AW21" si="69">AK20*$AW$2</f>
         <v>11400</v>
       </c>
       <c r="AX20" s="16">
-        <f t="shared" ref="AX20:AX21" si="82">AL20*$AX$2</f>
+        <f t="shared" ref="AX20:AX21" si="70">AL20*$AX$2</f>
         <v>108</v>
       </c>
       <c r="AY20" s="17">
         <v>0</v>
       </c>
       <c r="AZ20" s="17">
-        <f t="shared" ref="AZ20:AZ21" si="83">AX20*(1+(0.02*AY20))</f>
+        <f t="shared" ref="AZ20:AZ21" si="71">AX20*(1+(0.02*AY20))</f>
         <v>108</v>
       </c>
       <c r="BA20" s="20">
@@ -5047,7 +5047,7 @@
         <v>9975.5145000000011</v>
       </c>
       <c r="BB20" s="75">
-        <f t="shared" ref="BB20:BB21" si="84">AW20/BA20</f>
+        <f t="shared" ref="BB20:BB21" si="72">AW20/BA20</f>
         <v>1.1427981985290081</v>
       </c>
       <c r="BC20" s="20">
@@ -5055,7 +5055,7 @@
         <v>7656.5573000000004</v>
       </c>
       <c r="BD20" s="75">
-        <f t="shared" ref="BD20:BD21" si="85">AW20/BC20</f>
+        <f t="shared" ref="BD20:BD21" si="73">AW20/BC20</f>
         <v>1.488919830848781</v>
       </c>
       <c r="BE20" s="20">
@@ -5063,7 +5063,7 @@
         <v>5337.6</v>
       </c>
       <c r="BF20" s="75">
-        <f t="shared" ref="BF20:BF21" si="86">AW20/BE20</f>
+        <f t="shared" ref="BF20:BF21" si="74">AW20/BE20</f>
         <v>2.1357913669064748</v>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
         <v>2900</v>
       </c>
       <c r="L21" s="15">
-        <f t="shared" si="65"/>
+        <f t="shared" si="56"/>
         <v>2450</v>
       </c>
       <c r="M21" s="15">
@@ -5117,7 +5117,7 @@
         <v>2836.3199999999997</v>
       </c>
       <c r="R21" s="24">
-        <f t="shared" si="66"/>
+        <f t="shared" si="57"/>
         <v>2368.16</v>
       </c>
       <c r="S21" s="24">
@@ -5128,59 +5128,59 @@
         <v>570.00000000000011</v>
       </c>
       <c r="U21" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="58"/>
         <v>495.00000000000006</v>
       </c>
       <c r="V21" s="25">
         <v>420</v>
       </c>
       <c r="W21" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="59"/>
         <v>209.99999999999989</v>
       </c>
       <c r="X21" s="79">
-        <f t="shared" si="69"/>
+        <f t="shared" si="60"/>
         <v>13.809523809523817</v>
       </c>
-      <c r="Y21" s="12" t="e">
-        <f t="shared" ca="1" si="70"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="Z21" s="79" t="e">
-        <f t="shared" ca="1" si="71"/>
-        <v>#NAME?</v>
+      <c r="Y21" s="12">
+        <f>[1]!CALC_DMG(AV21,T21,$D$2, P21)</f>
+        <v>366</v>
+      </c>
+      <c r="Z21" s="79">
+        <f t="shared" si="61"/>
+        <v>7.9234972677595632</v>
       </c>
       <c r="AA21" s="15">
-        <f t="shared" si="72"/>
+        <f t="shared" si="62"/>
         <v>284.99999999999994</v>
       </c>
       <c r="AB21" s="78">
-        <f t="shared" si="73"/>
+        <f t="shared" si="63"/>
         <v>8.5964912280701764</v>
       </c>
-      <c r="AC21" s="15" t="e">
-        <f t="shared" ca="1" si="74"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AD21" s="78" t="e">
-        <f t="shared" ca="1" si="75"/>
-        <v>#NAME?</v>
+      <c r="AC21" s="15">
+        <f>[1]!CALC_DMG(AV21,U21,$D$2,P21)</f>
+        <v>441</v>
+      </c>
+      <c r="AD21" s="78">
+        <f t="shared" si="64"/>
+        <v>5.5555555555555554</v>
       </c>
       <c r="AE21" s="22">
-        <f t="shared" si="76"/>
+        <f t="shared" si="65"/>
         <v>360</v>
       </c>
       <c r="AF21" s="77">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>5.5555555555555554</v>
       </c>
-      <c r="AG21" s="22" t="e">
-        <f t="shared" ca="1" si="77"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="AH21" s="77" t="e">
-        <f t="shared" ca="1" si="78"/>
-        <v>#NAME?</v>
+      <c r="AG21" s="22">
+        <f>[1]!CALC_DMG(AV21,V21,$D$2,P21)</f>
+        <v>516</v>
+      </c>
+      <c r="AH21" s="77">
+        <f t="shared" si="66"/>
+        <v>3.8759689922480618</v>
       </c>
       <c r="AI21" s="8">
         <v>5</v>
@@ -5198,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="AN21" s="17">
-        <f t="shared" si="79"/>
+        <f t="shared" si="67"/>
         <v>220</v>
       </c>
       <c r="AO21" s="20">
@@ -5226,22 +5226,22 @@
         <v>4.2608539648367421</v>
       </c>
       <c r="AV21" s="12">
-        <f t="shared" si="80"/>
+        <f t="shared" si="68"/>
         <v>1560</v>
       </c>
       <c r="AW21" s="15">
-        <f t="shared" si="81"/>
+        <f t="shared" si="69"/>
         <v>22800</v>
       </c>
       <c r="AX21" s="16">
-        <f t="shared" si="82"/>
+        <f t="shared" si="70"/>
         <v>132</v>
       </c>
       <c r="AY21" s="17">
         <v>0</v>
       </c>
       <c r="AZ21" s="17">
-        <f t="shared" si="83"/>
+        <f t="shared" si="71"/>
         <v>132</v>
       </c>
       <c r="BA21" s="20">
@@ -5249,7 +5249,7 @@
         <v>15081.131600000001</v>
       </c>
       <c r="BB21" s="75">
-        <f t="shared" si="84"/>
+        <f t="shared" si="72"/>
         <v>1.5118228926534929</v>
       </c>
       <c r="BC21" s="20">
@@ -5257,7 +5257,7 @@
         <v>12395.765600000001</v>
       </c>
       <c r="BD21" s="75">
-        <f t="shared" si="85"/>
+        <f t="shared" si="73"/>
         <v>1.8393377816050345</v>
       </c>
       <c r="BE21" s="20">
@@ -5265,7 +5265,7 @@
         <v>9710.4</v>
       </c>
       <c r="BF21" s="75">
-        <f t="shared" si="86"/>
+        <f t="shared" si="74"/>
         <v>2.3479980227385071</v>
       </c>
     </row>

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AFB8A4-87EB-4DA4-9069-973757417368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9015CA88-227C-4CC2-BFB9-E95A3EBE1CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33684" yWindow="-5160" windowWidth="26436" windowHeight="15432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="243">
   <si>
     <t>最终攻击力=面板攻击+横扫之刃+评分等级+杀手附魔</t>
   </si>
@@ -435,23 +435,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>豆腐</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -713,10 +696,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>紫金</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>暮色（牛头雪怪后）</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -725,28 +704,10 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>牛头人肉</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>恶魂泪</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>砷铅铁</t>
-  </si>
-  <si>
-    <t>极地毛坯</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>硫磺块</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>远古金属粒</t>
-  </si>
-  <si>
     <t>骸龙之骨</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -795,10 +756,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>紫菘结晶</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>风暴精华</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -846,10 +803,6 @@
     <t>天晶混合</t>
   </si>
   <si>
-    <t>金</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -860,9 +813,6 @@
   <si>
     <t>MS3C</t>
     <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>下界合金碎片</t>
   </si>
   <si>
     <t>凋零合金锭</t>
@@ -1027,6 +977,25 @@
   <si>
     <t>重甲</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>下界合金锭</t>
+  </si>
+  <si>
+    <t>凛冰冻结装置</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>砷铅铁</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>耀魂宝珠</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>首领毛皮</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1498,7 +1467,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1742,10 +1711,28 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1754,13 +1741,70 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1775,81 +1819,6 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1859,6 +1828,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1868,25 +1849,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1931,6 +1924,7 @@
       <sheetName val="数值分配"/>
       <sheetName val="维度"/>
       <sheetName val="普通攻击"/>
+      <sheetName val="伤害计算宏"/>
     </sheetNames>
     <definedNames>
       <definedName name="CALC_DMG"/>
@@ -1940,6 +1934,7 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2230,10 +2225,10 @@
         <v>20</v>
       </c>
       <c r="AB2" s="72" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="AF2" s="72" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="AI2" s="27">
         <v>0.5</v>
@@ -2251,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="AP2" s="7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="AR2" s="7" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AT2" s="72" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AV2" s="8">
         <v>1.2</v>
@@ -2269,82 +2264,82 @@
         <v>0.6</v>
       </c>
       <c r="BB2" s="7" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="BD2" s="7" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="BF2" s="72" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="86"/>
+      <c r="T3" s="86"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="83" t="s">
-        <v>225</v>
-      </c>
-      <c r="X3" s="84"/>
-      <c r="Y3" s="84"/>
-      <c r="Z3" s="84"/>
-      <c r="AA3" s="83" t="s">
-        <v>226</v>
-      </c>
-      <c r="AB3" s="84"/>
-      <c r="AC3" s="84"/>
-      <c r="AD3" s="84"/>
-      <c r="AE3" s="83" t="s">
-        <v>227</v>
-      </c>
-      <c r="AF3" s="84"/>
-      <c r="AG3" s="84"/>
-      <c r="AH3" s="84"/>
-      <c r="AJ3" s="85" t="s">
+      <c r="W3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X3" s="90"/>
+      <c r="Y3" s="90"/>
+      <c r="Z3" s="90"/>
+      <c r="AA3" s="89" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB3" s="90"/>
+      <c r="AC3" s="90"/>
+      <c r="AD3" s="90"/>
+      <c r="AE3" s="89" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF3" s="90"/>
+      <c r="AG3" s="90"/>
+      <c r="AH3" s="90"/>
+      <c r="AJ3" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="85"/>
-      <c r="AM3" s="85"/>
-      <c r="AN3" s="85"/>
-      <c r="AO3" s="85"/>
-      <c r="AP3" s="85"/>
-      <c r="AQ3" s="85"/>
-      <c r="AR3" s="85"/>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AV3" s="129" t="s">
-        <v>244</v>
-      </c>
-      <c r="AW3" s="82"/>
-      <c r="AX3" s="82"/>
-      <c r="AY3" s="82"/>
-      <c r="AZ3" s="82"/>
-      <c r="BA3" s="82"/>
-      <c r="BB3" s="82"/>
-      <c r="BC3" s="82"/>
-      <c r="BD3" s="82"/>
-      <c r="BE3" s="82"/>
-      <c r="BF3" s="82"/>
+      <c r="AK3" s="83"/>
+      <c r="AL3" s="83"/>
+      <c r="AM3" s="83"/>
+      <c r="AN3" s="83"/>
+      <c r="AO3" s="83"/>
+      <c r="AP3" s="83"/>
+      <c r="AQ3" s="83"/>
+      <c r="AR3" s="83"/>
+      <c r="AS3" s="83"/>
+      <c r="AT3" s="83"/>
+      <c r="AV3" s="85" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW3" s="86"/>
+      <c r="AX3" s="86"/>
+      <c r="AY3" s="86"/>
+      <c r="AZ3" s="86"/>
+      <c r="BA3" s="86"/>
+      <c r="BB3" s="86"/>
+      <c r="BC3" s="86"/>
+      <c r="BD3" s="86"/>
+      <c r="BE3" s="86"/>
+      <c r="BF3" s="86"/>
     </row>
     <row r="4" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
@@ -2403,28 +2398,28 @@
       <c r="AF4" s="71"/>
       <c r="AG4" s="71"/>
       <c r="AH4" s="71"/>
-      <c r="AJ4" s="86"/>
-      <c r="AK4" s="86"/>
-      <c r="AL4" s="86"/>
-      <c r="AM4" s="86"/>
-      <c r="AN4" s="86"/>
-      <c r="AO4" s="86"/>
-      <c r="AP4" s="86"/>
-      <c r="AQ4" s="86"/>
-      <c r="AR4" s="86"/>
-      <c r="AS4" s="86"/>
-      <c r="AT4" s="86"/>
-      <c r="AV4" s="86"/>
-      <c r="AW4" s="86"/>
-      <c r="AX4" s="86"/>
-      <c r="AY4" s="86"/>
-      <c r="AZ4" s="86"/>
-      <c r="BA4" s="86"/>
-      <c r="BB4" s="86"/>
-      <c r="BC4" s="86"/>
-      <c r="BD4" s="86"/>
-      <c r="BE4" s="86"/>
-      <c r="BF4" s="86"/>
+      <c r="AJ4" s="84"/>
+      <c r="AK4" s="84"/>
+      <c r="AL4" s="84"/>
+      <c r="AM4" s="84"/>
+      <c r="AN4" s="84"/>
+      <c r="AO4" s="84"/>
+      <c r="AP4" s="84"/>
+      <c r="AQ4" s="84"/>
+      <c r="AR4" s="84"/>
+      <c r="AS4" s="84"/>
+      <c r="AT4" s="84"/>
+      <c r="AV4" s="84"/>
+      <c r="AW4" s="84"/>
+      <c r="AX4" s="84"/>
+      <c r="AY4" s="84"/>
+      <c r="AZ4" s="84"/>
+      <c r="BA4" s="84"/>
+      <c r="BB4" s="84"/>
+      <c r="BC4" s="84"/>
+      <c r="BD4" s="84"/>
+      <c r="BE4" s="84"/>
+      <c r="BF4" s="84"/>
     </row>
     <row r="5" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
@@ -2450,40 +2445,40 @@
         <v>48</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="L5" s="33" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="N5" s="28" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="O5" s="30" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="P5" s="23" t="s">
         <v>66</v>
       </c>
       <c r="Q5" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="R5" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="S5" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="T5" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="U5" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="V5" s="48" t="s">
         <v>214</v>
-      </c>
-      <c r="R5" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="S5" s="61" t="s">
-        <v>221</v>
-      </c>
-      <c r="T5" s="48" t="s">
-        <v>222</v>
-      </c>
-      <c r="U5" s="48" t="s">
-        <v>223</v>
-      </c>
-      <c r="V5" s="48" t="s">
-        <v>224</v>
       </c>
       <c r="W5" s="12" t="s">
         <v>69</v>
@@ -2491,11 +2486,11 @@
       <c r="X5" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="Y5" s="128" t="s">
-        <v>243</v>
+      <c r="Y5" s="82" t="s">
+        <v>233</v>
       </c>
       <c r="Z5" s="79" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="AA5" s="15" t="s">
         <v>69</v>
@@ -2504,10 +2499,10 @@
         <v>67</v>
       </c>
       <c r="AC5" s="33" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="AD5" s="78" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="AE5" s="22" t="s">
         <v>69</v>
@@ -2516,10 +2511,10 @@
         <v>67</v>
       </c>
       <c r="AG5" s="80" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="AH5" s="77" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="AJ5" s="12" t="s">
         <v>53</v>
@@ -2537,22 +2532,22 @@
         <v>77</v>
       </c>
       <c r="AO5" s="31" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP5" s="75" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="AQ5" s="31" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="AR5" s="75" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="AS5" s="31" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="AT5" s="75" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="AV5" s="12" t="s">
         <v>53</v>
@@ -2570,26 +2565,26 @@
         <v>77</v>
       </c>
       <c r="BA5" s="31" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="BB5" s="75" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="BC5" s="31" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="BD5" s="75" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="BE5" s="31" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="BF5" s="75" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="81">
+      <c r="B6" s="87">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2793,7 +2788,7 @@
       </c>
     </row>
     <row r="7" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="81"/>
+      <c r="B7" s="87"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2995,7 +2990,7 @@
       </c>
     </row>
     <row r="8" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="81">
+      <c r="B8" s="87">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3199,7 +3194,7 @@
       </c>
     </row>
     <row r="9" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="81"/>
+      <c r="B9" s="87"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3401,7 +3396,7 @@
       </c>
     </row>
     <row r="10" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="87">
+      <c r="B10" s="88">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3605,7 +3600,7 @@
       </c>
     </row>
     <row r="11" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="87"/>
+      <c r="B11" s="88"/>
       <c r="X11" s="76"/>
       <c r="Z11" s="76"/>
       <c r="AB11" s="76"/>
@@ -3620,7 +3615,7 @@
       <c r="BF11" s="76"/>
     </row>
     <row r="12" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="87"/>
+      <c r="B12" s="88"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3822,7 +3817,7 @@
       </c>
     </row>
     <row r="13" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="81">
+      <c r="B13" s="87">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -4026,7 +4021,7 @@
       </c>
     </row>
     <row r="14" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="81"/>
+      <c r="B14" s="87"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4242,7 +4237,7 @@
       <c r="BF15" s="76"/>
     </row>
     <row r="16" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="81">
+      <c r="B16" s="87">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4446,7 +4441,7 @@
       </c>
     </row>
     <row r="17" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="81"/>
+      <c r="B17" s="87"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4648,7 +4643,7 @@
       </c>
     </row>
     <row r="18" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="81"/>
+      <c r="B18" s="87"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4864,7 +4859,7 @@
       <c r="BF19" s="76"/>
     </row>
     <row r="20" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="81">
+      <c r="B20" s="87">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -5068,7 +5063,7 @@
       </c>
     </row>
     <row r="21" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="81"/>
+      <c r="B21" s="87"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -5271,7 +5266,7 @@
     </row>
     <row r="23" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AU23" s="7" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="AV23" s="8">
         <v>1.2</v>
@@ -5285,7 +5280,7 @@
     </row>
     <row r="24" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AU24" s="7" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AV24" s="8">
         <v>0.8</v>
@@ -5299,7 +5294,7 @@
     </row>
     <row r="25" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AU25" s="7" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AV25" s="8">
         <v>0.9</v>
@@ -5313,6 +5308,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D3:T3"/>
+    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="AJ3:AT4"/>
     <mergeCell ref="AV3:BF4"/>
     <mergeCell ref="B6:B7"/>
@@ -5320,11 +5320,6 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AA3:AD3"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D3:T3"/>
-    <mergeCell ref="W3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5383,57 +5378,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="82" t="s">
+      <c r="V3" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="82"/>
-      <c r="AC3" s="82"/>
-      <c r="AD3" s="82"/>
-      <c r="AE3" s="82"/>
-      <c r="AF3" s="82"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="82"/>
-      <c r="AI3" s="82"/>
-      <c r="AJ3" s="82"/>
-      <c r="AK3" s="82"/>
-      <c r="AL3" s="82"/>
-      <c r="AM3" s="82"/>
-      <c r="AN3" s="82"/>
-      <c r="AO3" s="82"/>
-      <c r="AP3" s="82"/>
-      <c r="AQ3" s="82"/>
-      <c r="AR3" s="82"/>
-      <c r="AS3" s="82"/>
-      <c r="AT3" s="82"/>
-      <c r="AU3" s="82"/>
-      <c r="AV3" s="82"/>
-      <c r="AW3" s="82"/>
-      <c r="AX3" s="82"/>
-      <c r="AY3" s="82"/>
+      <c r="W3" s="86"/>
+      <c r="X3" s="86"/>
+      <c r="Y3" s="86"/>
+      <c r="Z3" s="86"/>
+      <c r="AA3" s="86"/>
+      <c r="AB3" s="86"/>
+      <c r="AC3" s="86"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="86"/>
+      <c r="AF3" s="86"/>
+      <c r="AG3" s="86"/>
+      <c r="AH3" s="86"/>
+      <c r="AI3" s="86"/>
+      <c r="AJ3" s="86"/>
+      <c r="AK3" s="86"/>
+      <c r="AL3" s="86"/>
+      <c r="AM3" s="86"/>
+      <c r="AN3" s="86"/>
+      <c r="AO3" s="86"/>
+      <c r="AP3" s="86"/>
+      <c r="AQ3" s="86"/>
+      <c r="AR3" s="86"/>
+      <c r="AS3" s="86"/>
+      <c r="AT3" s="86"/>
+      <c r="AU3" s="86"/>
+      <c r="AV3" s="86"/>
+      <c r="AW3" s="86"/>
+      <c r="AX3" s="86"/>
+      <c r="AY3" s="86"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5479,44 +5474,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="86" t="s">
+      <c r="V4" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="86"/>
-      <c r="X4" s="86"/>
-      <c r="Y4" s="86"/>
-      <c r="Z4" s="86"/>
-      <c r="AA4" s="86"/>
+      <c r="W4" s="84"/>
+      <c r="X4" s="84"/>
+      <c r="Y4" s="84"/>
+      <c r="Z4" s="84"/>
+      <c r="AA4" s="84"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="86" t="s">
+      <c r="AD4" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="86"/>
-      <c r="AF4" s="86"/>
-      <c r="AG4" s="86"/>
+      <c r="AE4" s="84"/>
+      <c r="AF4" s="84"/>
+      <c r="AG4" s="84"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="86" t="s">
+      <c r="AL4" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="86"/>
-      <c r="AN4" s="86"/>
-      <c r="AO4" s="86"/>
-      <c r="AP4" s="86"/>
-      <c r="AQ4" s="86"/>
+      <c r="AM4" s="84"/>
+      <c r="AN4" s="84"/>
+      <c r="AO4" s="84"/>
+      <c r="AP4" s="84"/>
+      <c r="AQ4" s="84"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="86" t="s">
+      <c r="AT4" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="86"/>
-      <c r="AV4" s="86"/>
-      <c r="AW4" s="86"/>
-      <c r="AX4" s="86"/>
-      <c r="AY4" s="86"/>
+      <c r="AU4" s="84"/>
+      <c r="AV4" s="84"/>
+      <c r="AW4" s="84"/>
+      <c r="AX4" s="84"/>
+      <c r="AY4" s="84"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5658,7 +5653,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="81">
+      <c r="B6" s="87">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -5822,7 +5817,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="81"/>
+      <c r="B7" s="87"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -5984,7 +5979,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="81">
+      <c r="B8" s="87">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -6148,7 +6143,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="81"/>
+      <c r="B9" s="87"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -6310,7 +6305,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="87">
+      <c r="B10" s="88">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -6474,10 +6469,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="87"/>
+      <c r="B11" s="88"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="87"/>
+      <c r="B12" s="88"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -6639,7 +6634,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="81">
+      <c r="B13" s="87">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -6803,7 +6798,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="81"/>
+      <c r="B14" s="87"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -6965,7 +6960,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="81">
+      <c r="B16" s="87">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -7129,7 +7124,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="81"/>
+      <c r="B17" s="87"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -7291,7 +7286,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="81"/>
+      <c r="B18" s="87"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -7453,7 +7448,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="81">
+      <c r="B20" s="87">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -7617,7 +7612,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="81"/>
+      <c r="B21" s="87"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -7780,18 +7775,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="V3:AY3"/>
+    <mergeCell ref="AT4:AY4"/>
+    <mergeCell ref="AL4:AQ4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="V4:AA4"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="V3:AY3"/>
-    <mergeCell ref="AT4:AY4"/>
-    <mergeCell ref="AL4:AQ4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="V4:AA4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7819,99 +7814,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="98" t="s">
+      <c r="E1" s="91" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
       <c r="I1" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="K1" s="99" t="s">
+        <v>158</v>
+      </c>
+      <c r="K1" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
       <c r="O1" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q1" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q1" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="100"/>
-      <c r="S1" s="100"/>
-      <c r="T1" s="100"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
       <c r="U1" s="39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="116" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116" t="s">
-        <v>197</v>
-      </c>
-      <c r="H2" s="116"/>
-      <c r="K2" s="116" t="s">
-        <v>196</v>
-      </c>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116" t="s">
-        <v>197</v>
-      </c>
-      <c r="N2" s="116"/>
-      <c r="Q2" s="116" t="s">
-        <v>196</v>
-      </c>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116" t="s">
-        <v>197</v>
-      </c>
-      <c r="T2" s="116"/>
+      <c r="B2" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="107" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="H2" s="107"/>
+      <c r="K2" s="107" t="s">
+        <v>187</v>
+      </c>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="N2" s="107"/>
+      <c r="Q2" s="107" t="s">
+        <v>187</v>
+      </c>
+      <c r="R2" s="107"/>
+      <c r="S2" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="T2" s="107"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
         <v>0.1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="114" t="s">
-        <v>129</v>
-      </c>
-      <c r="K3" s="102"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="104"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="95"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="97"/>
       <c r="O3" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
-      <c r="T3" s="104"/>
-      <c r="U3" s="96" t="s">
-        <v>156</v>
+        <v>128</v>
+      </c>
+      <c r="Q3" s="95"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="111" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -7919,146 +7914,146 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="115"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="106"/>
       <c r="K4" s="49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L4" s="49"/>
       <c r="M4" s="49" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="111">
+      <c r="O4" s="116">
         <v>0</v>
       </c>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="109"/>
-      <c r="S4" s="109"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="97"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="102"/>
+      <c r="U4" s="112"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
         <v>1.2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>195</v>
-      </c>
+      <c r="E5" s="46"/>
       <c r="F5" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="H5" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="H5" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="I5" s="91">
+      <c r="I5" s="103">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="L5" s="48"/>
       <c r="M5" s="48" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="112"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="109"/>
-      <c r="S5" s="109"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="97"/>
+      <c r="O5" s="116"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="131"/>
+      <c r="S5" s="131"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="112"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
         <v>1.3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="1"/>
       <c r="E6" s="48"/>
       <c r="F6" s="47"/>
       <c r="G6" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="91"/>
+      <c r="I6" s="104"/>
       <c r="K6" s="48" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="112"/>
-      <c r="Q6" s="105"/>
-      <c r="R6" s="106"/>
-      <c r="S6" s="106"/>
-      <c r="T6" s="107"/>
-      <c r="U6" s="97"/>
+      <c r="O6" s="116"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="99"/>
+      <c r="S6" s="99"/>
+      <c r="T6" s="100"/>
+      <c r="U6" s="112"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
         <v>1.4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="91"/>
-      <c r="K7" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="L7" s="48"/>
-      <c r="M7" s="47" t="s">
+      <c r="E7" s="51"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="I7" s="129">
+        <v>1</v>
+      </c>
+      <c r="K7" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="L7" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="N7" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="108">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="T7" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="N7" s="47"/>
-      <c r="O7" s="113"/>
-      <c r="Q7" s="54" t="s">
-        <v>199</v>
-      </c>
-      <c r="R7" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="S7" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="T7" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="U7" s="92">
+      <c r="U7" s="81">
         <v>1</v>
       </c>
     </row>
@@ -8067,178 +8062,168 @@
         <v>2.1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="91"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="130"/>
       <c r="K8" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="L8" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="L8" s="53" t="s">
-        <v>137</v>
-      </c>
       <c r="M8" s="53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N8" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="O8" s="92">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="T8" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="U8" s="92"/>
+        <v>163</v>
+      </c>
+      <c r="O8" s="108"/>
+      <c r="Q8" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="T8" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="U8" s="132">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="43">
         <v>2.2000000000000002</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="50" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G9" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="H9" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="92">
-        <v>1</v>
-      </c>
+      <c r="I9" s="130"/>
       <c r="K9" s="51" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="L9" s="51" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="M9" s="51" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="N9" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="O9" s="92"/>
+        <v>172</v>
+      </c>
+      <c r="O9" s="108"/>
       <c r="Q9" s="33" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="R9" s="33"/>
       <c r="S9" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="T9" s="56"/>
-      <c r="U9" s="93">
-        <v>2</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="T9" s="128"/>
+      <c r="U9" s="133"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
         <v>2.2999999999999998</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="51" t="s">
-        <v>182</v>
-      </c>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="92"/>
+      <c r="E10" s="56" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="133">
+        <v>2</v>
+      </c>
       <c r="K10" s="57" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L10" s="57"/>
       <c r="M10" s="57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="O10" s="93">
+        <v>139</v>
+      </c>
+      <c r="O10" s="132">
         <v>2</v>
       </c>
-      <c r="Q10" s="33" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q10" s="33"/>
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="93"/>
+      <c r="T10" s="128"/>
+      <c r="U10" s="134"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
         <v>3.1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="1"/>
       <c r="E11" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="G11" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="H11" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="H11" s="55" t="s">
-        <v>145</v>
-      </c>
-      <c r="I11" s="93">
-        <v>2</v>
-      </c>
+      <c r="I11" s="133"/>
       <c r="K11" s="33"/>
       <c r="L11" s="56"/>
       <c r="M11" s="33" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="93"/>
+      <c r="O11" s="134"/>
       <c r="Q11" s="61" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="R11" s="61"/>
       <c r="S11" s="61" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="94">
+      <c r="U11" s="109">
         <v>3</v>
       </c>
     </row>
@@ -8247,78 +8232,80 @@
         <v>3.2</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="33"/>
       <c r="F12" s="56"/>
       <c r="G12" s="33" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="93"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="N12" s="56"/>
-      <c r="O12" s="93"/>
+      <c r="I12" s="133"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60" t="s">
+        <v>179</v>
+      </c>
+      <c r="N12" s="60"/>
+      <c r="O12" s="135">
+        <v>3</v>
+      </c>
       <c r="Q12" s="69" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="94"/>
+      <c r="U12" s="109"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
         <v>3.3</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="93"/>
+        <v>122</v>
+      </c>
+      <c r="E13" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="137">
+        <v>3</v>
+      </c>
       <c r="K13" s="60" t="s">
+        <v>145</v>
+      </c>
+      <c r="L13" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="L13" s="60" t="s">
-        <v>147</v>
-      </c>
       <c r="M13" s="61" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="N13" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="O13" s="43">
-        <v>3</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O13" s="136"/>
       <c r="Q13" s="28" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="R13" s="28" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="95">
+      <c r="U13" s="110">
         <v>4</v>
       </c>
     </row>
@@ -8327,63 +8314,61 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="66" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="94">
-        <v>3</v>
-      </c>
+      <c r="I14" s="137"/>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="89">
+      <c r="O14" s="114">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="95"/>
+      <c r="U14" s="110"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
         <v>4.2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="1"/>
       <c r="E15" s="58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="94"/>
+      <c r="I15" s="136"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="N15" s="63"/>
+      <c r="O15" s="115"/>
+      <c r="Q15" s="68" t="s">
         <v>151</v>
-      </c>
-      <c r="N15" s="63"/>
-      <c r="O15" s="90"/>
-      <c r="Q15" s="68" t="s">
-        <v>152</v>
       </c>
       <c r="R15" s="64"/>
       <c r="S15" s="64"/>
@@ -8393,10 +8378,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="113" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="88"/>
+      <c r="D18" s="113"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -8411,7 +8396,7 @@
     </row>
     <row r="20" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="3">
         <v>1.2</v>
@@ -8420,21 +8405,21 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C21" s="1">
         <v>2.1</v>
@@ -8443,21 +8428,21 @@
         <v>1.4</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="1">
         <v>3.1</v>
@@ -8466,15 +8451,15 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C23" s="1">
         <v>4.0999999999999996</v>
@@ -8483,43 +8468,43 @@
         <v>3.3</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" s="1">
         <v>4.2</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="5" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="5" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -8638,19 +8623,32 @@
         <v>55</v>
       </c>
       <c r="E35" s="70" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F35" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="O4:O6"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="U3:U6"/>
+    <mergeCell ref="U8:U10"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E3:H4"/>
     <mergeCell ref="Q3:T6"/>
-    <mergeCell ref="O4:O7"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="M2:N2"/>
@@ -8659,19 +8657,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="U3:U6"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="O10:O12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8689,32 +8674,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="G1" s="127" t="s">
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="G1" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
+      <c r="W1" s="123"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -8887,11 +8872,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="123">
+      <c r="F10" s="120">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="88">
+      <c r="G10" s="113">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8911,11 +8896,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="123">
+      <c r="N10" s="120">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="88">
+      <c r="O10" s="113">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8935,7 +8920,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="120">
+      <c r="V10" s="124">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -8958,8 +8943,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="126"/>
-      <c r="G11" s="88"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="113"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8977,8 +8962,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="126"/>
-      <c r="O11" s="88"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="113"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8996,7 +8981,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="121"/>
+      <c r="V11" s="125"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -9016,8 +9001,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="126"/>
-      <c r="G12" s="88"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="113"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9035,8 +9020,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="126"/>
-      <c r="O12" s="88"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="113"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -9054,7 +9039,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="122"/>
+      <c r="V12" s="126"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -9074,8 +9059,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="124"/>
-      <c r="G13" s="88"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="113"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -9093,8 +9078,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="126"/>
-      <c r="O13" s="88"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="113"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -9114,11 +9099,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="123">
+      <c r="F14" s="120">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="88">
+      <c r="G14" s="113">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9138,8 +9123,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="126"/>
-      <c r="O14" s="88"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="113"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -9159,8 +9144,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="124"/>
-      <c r="G15" s="88"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="113"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9178,8 +9163,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="126"/>
-      <c r="O15" s="88"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="113"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -9210,8 +9195,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="124"/>
-      <c r="O16" s="88"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="113"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -9347,7 +9332,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="120">
+      <c r="N22" s="124">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9387,7 +9372,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="121"/>
+      <c r="N23" s="125"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -9424,7 +9409,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="122"/>
+      <c r="N24" s="126"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -9461,7 +9446,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="120">
+      <c r="N25" s="124">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -9484,7 +9469,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="122"/>
+      <c r="N26" s="126"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -9498,7 +9483,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="125" t="s">
+      <c r="A30" s="127" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="118"/>
@@ -9507,7 +9492,7 @@
       <c r="E30" s="118"/>
       <c r="F30" s="119"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="125" t="s">
+      <c r="I30" s="127" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="118"/>
@@ -9579,11 +9564,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="123">
+      <c r="F32" s="120">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="88">
+      <c r="G32" s="113">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9603,11 +9588,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="123">
+      <c r="N32" s="120">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="88">
+      <c r="O32" s="113">
         <v>4</v>
       </c>
     </row>
@@ -9629,8 +9614,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="126"/>
-      <c r="G33" s="88"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="113"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9648,8 +9633,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="126"/>
-      <c r="O33" s="88"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="113"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -9669,8 +9654,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="126"/>
-      <c r="G34" s="88"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="113"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9688,8 +9673,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="126"/>
-      <c r="O34" s="88"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="113"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -9709,8 +9694,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="124"/>
-      <c r="G35" s="88"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="113"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9728,8 +9713,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="126"/>
-      <c r="O35" s="88"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="113"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -9749,11 +9734,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="123">
+      <c r="F36" s="120">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="88">
+      <c r="G36" s="113">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9773,8 +9758,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="126"/>
-      <c r="O36" s="88"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="113"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -9794,8 +9779,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="124"/>
-      <c r="G37" s="88"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="113"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9813,8 +9798,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="126"/>
-      <c r="O37" s="88"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="113"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -9845,8 +9830,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="124"/>
-      <c r="O38" s="88"/>
+      <c r="N38" s="122"/>
+      <c r="O38" s="113"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -9976,7 +9961,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="120">
+      <c r="N45" s="124">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -10015,7 +10000,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="121"/>
+      <c r="N46" s="125"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -10051,7 +10036,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="122"/>
+      <c r="N47" s="126"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -10087,7 +10072,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="120">
+      <c r="N48" s="124">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -10109,10 +10094,29 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="122"/>
+      <c r="N49" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -10122,25 +10126,6 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9015CA88-227C-4CC2-BFB9-E95A3EBE1CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216462CB-CFBF-4E29-8F97-7067DC5CC91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -1717,6 +1717,21 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1726,19 +1741,64 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
@@ -1774,15 +1834,12 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1792,33 +1849,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1828,58 +1858,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2275,71 +2275,71 @@
     </row>
     <row r="3" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="89" t="s">
+      <c r="W3" s="86" t="s">
         <v>215</v>
       </c>
-      <c r="X3" s="90"/>
-      <c r="Y3" s="90"/>
-      <c r="Z3" s="90"/>
-      <c r="AA3" s="89" t="s">
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="86" t="s">
         <v>216</v>
       </c>
-      <c r="AB3" s="90"/>
-      <c r="AC3" s="90"/>
-      <c r="AD3" s="90"/>
-      <c r="AE3" s="89" t="s">
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="86" t="s">
         <v>217</v>
       </c>
-      <c r="AF3" s="90"/>
-      <c r="AG3" s="90"/>
-      <c r="AH3" s="90"/>
-      <c r="AJ3" s="83" t="s">
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AJ3" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" s="83"/>
-      <c r="AL3" s="83"/>
-      <c r="AM3" s="83"/>
-      <c r="AN3" s="83"/>
-      <c r="AO3" s="83"/>
-      <c r="AP3" s="83"/>
-      <c r="AQ3" s="83"/>
-      <c r="AR3" s="83"/>
-      <c r="AS3" s="83"/>
-      <c r="AT3" s="83"/>
-      <c r="AV3" s="85" t="s">
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="88"/>
+      <c r="AM3" s="88"/>
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88"/>
+      <c r="AS3" s="88"/>
+      <c r="AT3" s="88"/>
+      <c r="AV3" s="90" t="s">
         <v>234</v>
       </c>
-      <c r="AW3" s="86"/>
-      <c r="AX3" s="86"/>
-      <c r="AY3" s="86"/>
-      <c r="AZ3" s="86"/>
-      <c r="BA3" s="86"/>
-      <c r="BB3" s="86"/>
-      <c r="BC3" s="86"/>
-      <c r="BD3" s="86"/>
-      <c r="BE3" s="86"/>
-      <c r="BF3" s="86"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
+      <c r="AY3" s="85"/>
+      <c r="AZ3" s="85"/>
+      <c r="BA3" s="85"/>
+      <c r="BB3" s="85"/>
+      <c r="BC3" s="85"/>
+      <c r="BD3" s="85"/>
+      <c r="BE3" s="85"/>
+      <c r="BF3" s="85"/>
     </row>
     <row r="4" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
@@ -2398,28 +2398,28 @@
       <c r="AF4" s="71"/>
       <c r="AG4" s="71"/>
       <c r="AH4" s="71"/>
-      <c r="AJ4" s="84"/>
-      <c r="AK4" s="84"/>
-      <c r="AL4" s="84"/>
-      <c r="AM4" s="84"/>
-      <c r="AN4" s="84"/>
-      <c r="AO4" s="84"/>
-      <c r="AP4" s="84"/>
-      <c r="AQ4" s="84"/>
-      <c r="AR4" s="84"/>
-      <c r="AS4" s="84"/>
-      <c r="AT4" s="84"/>
-      <c r="AV4" s="84"/>
-      <c r="AW4" s="84"/>
-      <c r="AX4" s="84"/>
-      <c r="AY4" s="84"/>
-      <c r="AZ4" s="84"/>
-      <c r="BA4" s="84"/>
-      <c r="BB4" s="84"/>
-      <c r="BC4" s="84"/>
-      <c r="BD4" s="84"/>
-      <c r="BE4" s="84"/>
-      <c r="BF4" s="84"/>
+      <c r="AJ4" s="89"/>
+      <c r="AK4" s="89"/>
+      <c r="AL4" s="89"/>
+      <c r="AM4" s="89"/>
+      <c r="AN4" s="89"/>
+      <c r="AO4" s="89"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="89"/>
+      <c r="AR4" s="89"/>
+      <c r="AS4" s="89"/>
+      <c r="AT4" s="89"/>
+      <c r="AV4" s="89"/>
+      <c r="AW4" s="89"/>
+      <c r="AX4" s="89"/>
+      <c r="AY4" s="89"/>
+      <c r="AZ4" s="89"/>
+      <c r="BA4" s="89"/>
+      <c r="BB4" s="89"/>
+      <c r="BC4" s="89"/>
+      <c r="BD4" s="89"/>
+      <c r="BE4" s="89"/>
+      <c r="BF4" s="89"/>
     </row>
     <row r="5" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
@@ -2584,7 +2584,7 @@
       </c>
     </row>
     <row r="6" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="87">
+      <c r="B6" s="84">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2788,7 +2788,7 @@
       </c>
     </row>
     <row r="7" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="87"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2990,7 +2990,7 @@
       </c>
     </row>
     <row r="8" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="87">
+      <c r="B8" s="84">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3194,7 +3194,7 @@
       </c>
     </row>
     <row r="9" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="87"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3396,7 +3396,7 @@
       </c>
     </row>
     <row r="10" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="88">
+      <c r="B10" s="91">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3600,7 +3600,7 @@
       </c>
     </row>
     <row r="11" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="88"/>
+      <c r="B11" s="91"/>
       <c r="X11" s="76"/>
       <c r="Z11" s="76"/>
       <c r="AB11" s="76"/>
@@ -3615,7 +3615,7 @@
       <c r="BF11" s="76"/>
     </row>
     <row r="12" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="88"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3817,7 +3817,7 @@
       </c>
     </row>
     <row r="13" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="87">
+      <c r="B13" s="84">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -4021,7 +4021,7 @@
       </c>
     </row>
     <row r="14" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="87"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="BF15" s="76"/>
     </row>
     <row r="16" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="87">
+      <c r="B16" s="84">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4441,7 +4441,7 @@
       </c>
     </row>
     <row r="17" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="87"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4643,7 +4643,7 @@
       </c>
     </row>
     <row r="18" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="87"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4859,7 +4859,7 @@
       <c r="BF19" s="76"/>
     </row>
     <row r="20" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="87">
+      <c r="B20" s="84">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -5063,7 +5063,7 @@
       </c>
     </row>
     <row r="21" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="87"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -5308,11 +5308,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D3:T3"/>
-    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="AJ3:AT4"/>
     <mergeCell ref="AV3:BF4"/>
     <mergeCell ref="B6:B7"/>
@@ -5320,6 +5315,11 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AA3:AD3"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D3:T3"/>
+    <mergeCell ref="W3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5378,57 +5378,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="86" t="s">
+      <c r="V3" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="86"/>
-      <c r="X3" s="86"/>
-      <c r="Y3" s="86"/>
-      <c r="Z3" s="86"/>
-      <c r="AA3" s="86"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="86"/>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="86"/>
-      <c r="AF3" s="86"/>
-      <c r="AG3" s="86"/>
-      <c r="AH3" s="86"/>
-      <c r="AI3" s="86"/>
-      <c r="AJ3" s="86"/>
-      <c r="AK3" s="86"/>
-      <c r="AL3" s="86"/>
-      <c r="AM3" s="86"/>
-      <c r="AN3" s="86"/>
-      <c r="AO3" s="86"/>
-      <c r="AP3" s="86"/>
-      <c r="AQ3" s="86"/>
-      <c r="AR3" s="86"/>
-      <c r="AS3" s="86"/>
-      <c r="AT3" s="86"/>
-      <c r="AU3" s="86"/>
-      <c r="AV3" s="86"/>
-      <c r="AW3" s="86"/>
-      <c r="AX3" s="86"/>
-      <c r="AY3" s="86"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="85"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="85"/>
+      <c r="AI3" s="85"/>
+      <c r="AJ3" s="85"/>
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="85"/>
+      <c r="AM3" s="85"/>
+      <c r="AN3" s="85"/>
+      <c r="AO3" s="85"/>
+      <c r="AP3" s="85"/>
+      <c r="AQ3" s="85"/>
+      <c r="AR3" s="85"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
+      <c r="AY3" s="85"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5474,44 +5474,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="84" t="s">
+      <c r="V4" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="84"/>
-      <c r="X4" s="84"/>
-      <c r="Y4" s="84"/>
-      <c r="Z4" s="84"/>
-      <c r="AA4" s="84"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="84" t="s">
+      <c r="AD4" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="84"/>
-      <c r="AF4" s="84"/>
-      <c r="AG4" s="84"/>
+      <c r="AE4" s="89"/>
+      <c r="AF4" s="89"/>
+      <c r="AG4" s="89"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="84" t="s">
+      <c r="AL4" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="84"/>
-      <c r="AN4" s="84"/>
-      <c r="AO4" s="84"/>
-      <c r="AP4" s="84"/>
-      <c r="AQ4" s="84"/>
+      <c r="AM4" s="89"/>
+      <c r="AN4" s="89"/>
+      <c r="AO4" s="89"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="89"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="84" t="s">
+      <c r="AT4" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="84"/>
-      <c r="AV4" s="84"/>
-      <c r="AW4" s="84"/>
-      <c r="AX4" s="84"/>
-      <c r="AY4" s="84"/>
+      <c r="AU4" s="89"/>
+      <c r="AV4" s="89"/>
+      <c r="AW4" s="89"/>
+      <c r="AX4" s="89"/>
+      <c r="AY4" s="89"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5653,7 +5653,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="87">
+      <c r="B6" s="84">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -5817,7 +5817,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="87"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -5979,7 +5979,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="87">
+      <c r="B8" s="84">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="87"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -6305,7 +6305,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="88">
+      <c r="B10" s="91">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -6469,10 +6469,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="88"/>
+      <c r="B11" s="91"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="88"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -6634,7 +6634,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="87">
+      <c r="B13" s="84">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -6798,7 +6798,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="87"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -6960,7 +6960,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="87">
+      <c r="B16" s="84">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -7124,7 +7124,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="87"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -7286,7 +7286,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="87"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -7448,7 +7448,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="87">
+      <c r="B20" s="84">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -7612,7 +7612,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="87"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -7775,18 +7775,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="V3:AY3"/>
     <mergeCell ref="AT4:AY4"/>
     <mergeCell ref="AL4:AQ4"/>
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7814,30 +7814,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="91" t="s">
+      <c r="E1" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
       <c r="I1" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K1" s="92" t="s">
+      <c r="K1" s="112" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
       <c r="O1" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="Q1" s="93" t="s">
+      <c r="Q1" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
       <c r="U1" s="39" t="s">
         <v>158</v>
       </c>
@@ -7846,35 +7846,35 @@
       <c r="A2" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="107" t="s">
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107" t="s">
+      <c r="F2" s="126"/>
+      <c r="G2" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="H2" s="107"/>
-      <c r="K2" s="107" t="s">
+      <c r="H2" s="126"/>
+      <c r="K2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107" t="s">
+      <c r="L2" s="126"/>
+      <c r="M2" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="N2" s="107"/>
-      <c r="Q2" s="107" t="s">
+      <c r="N2" s="126"/>
+      <c r="Q2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="R2" s="107"/>
-      <c r="S2" s="107" t="s">
+      <c r="R2" s="126"/>
+      <c r="S2" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="T2" s="107"/>
+      <c r="T2" s="126"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -7887,25 +7887,25 @@
         <v>121</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="105" t="s">
+      <c r="E3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="124" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="95"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="97"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="117"/>
       <c r="O3" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="111" t="s">
+      <c r="Q3" s="115"/>
+      <c r="R3" s="116"/>
+      <c r="S3" s="116"/>
+      <c r="T3" s="117"/>
+      <c r="U3" s="109" t="s">
         <v>155</v>
       </c>
     </row>
@@ -7918,11 +7918,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="106"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="125"/>
       <c r="K4" s="49" t="s">
         <v>132</v>
       </c>
@@ -7931,14 +7931,14 @@
         <v>133</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="116">
+      <c r="O4" s="103">
         <v>0</v>
       </c>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="131"/>
-      <c r="T4" s="102"/>
-      <c r="U4" s="112"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="110"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -7963,7 +7963,7 @@
       <c r="H5" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="103">
+      <c r="I5" s="101">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -7974,12 +7974,12 @@
         <v>186</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="116"/>
-      <c r="Q5" s="101"/>
-      <c r="R5" s="131"/>
-      <c r="S5" s="131"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="112"/>
+      <c r="O5" s="103"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="110"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -7996,19 +7996,19 @@
         <v>159</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="104"/>
+      <c r="I6" s="102"/>
       <c r="K6" s="48" t="s">
         <v>162</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="116"/>
-      <c r="Q6" s="98"/>
-      <c r="R6" s="99"/>
-      <c r="S6" s="99"/>
-      <c r="T6" s="100"/>
-      <c r="U6" s="112"/>
+      <c r="O6" s="103"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="119"/>
+      <c r="S6" s="119"/>
+      <c r="T6" s="120"/>
+      <c r="U6" s="110"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -8027,7 +8027,7 @@
       <c r="H7" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="I7" s="129">
+      <c r="I7" s="105">
         <v>1</v>
       </c>
       <c r="K7" s="53" t="s">
@@ -8042,7 +8042,7 @@
       <c r="N7" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="O7" s="108">
+      <c r="O7" s="104">
         <v>1</v>
       </c>
       <c r="Q7" s="54"/>
@@ -8074,7 +8074,7 @@
       <c r="F8" s="52"/>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
-      <c r="I8" s="130"/>
+      <c r="I8" s="106"/>
       <c r="K8" s="53" t="s">
         <v>135</v>
       </c>
@@ -8087,7 +8087,7 @@
       <c r="N8" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="O8" s="108"/>
+      <c r="O8" s="104"/>
       <c r="Q8" s="33" t="s">
         <v>164</v>
       </c>
@@ -8098,7 +8098,7 @@
       <c r="T8" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="U8" s="132">
+      <c r="U8" s="92">
         <v>2</v>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       <c r="H9" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="130"/>
+      <c r="I9" s="106"/>
       <c r="K9" s="51" t="s">
         <v>169</v>
       </c>
@@ -8138,7 +8138,7 @@
       <c r="N9" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="108"/>
+      <c r="O9" s="104"/>
       <c r="Q9" s="33" t="s">
         <v>173</v>
       </c>
@@ -8146,8 +8146,8 @@
       <c r="S9" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="T9" s="128"/>
-      <c r="U9" s="133"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="96"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
@@ -8164,7 +8164,7 @@
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="133">
+      <c r="I10" s="96">
         <v>2</v>
       </c>
       <c r="K10" s="57" t="s">
@@ -8177,14 +8177,14 @@
       <c r="N10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="O10" s="132">
+      <c r="O10" s="92">
         <v>2</v>
       </c>
       <c r="Q10" s="33"/>
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
-      <c r="T10" s="128"/>
-      <c r="U10" s="134"/>
+      <c r="T10" s="83"/>
+      <c r="U10" s="93"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -8207,14 +8207,14 @@
       <c r="H11" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="133"/>
+      <c r="I11" s="96"/>
       <c r="K11" s="33"/>
       <c r="L11" s="56"/>
       <c r="M11" s="33" t="s">
         <v>176</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="134"/>
+      <c r="O11" s="93"/>
       <c r="Q11" s="61" t="s">
         <v>175</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>177</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="109">
+      <c r="U11" s="107">
         <v>3</v>
       </c>
     </row>
@@ -8244,14 +8244,14 @@
         <v>178</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="133"/>
+      <c r="I12" s="96"/>
       <c r="K12" s="60"/>
       <c r="L12" s="60"/>
       <c r="M12" s="60" t="s">
         <v>179</v>
       </c>
       <c r="N12" s="60"/>
-      <c r="O12" s="135">
+      <c r="O12" s="94">
         <v>3</v>
       </c>
       <c r="Q12" s="69" t="s">
@@ -8260,7 +8260,7 @@
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="109"/>
+      <c r="U12" s="107"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -8281,7 +8281,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="137">
+      <c r="I13" s="97">
         <v>3</v>
       </c>
       <c r="K13" s="60" t="s">
@@ -8296,7 +8296,7 @@
       <c r="N13" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="O13" s="136"/>
+      <c r="O13" s="95"/>
       <c r="Q13" s="28" t="s">
         <v>183</v>
       </c>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="110">
+      <c r="U13" s="108">
         <v>4</v>
       </c>
     </row>
@@ -8326,14 +8326,14 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="137"/>
+      <c r="I14" s="97"/>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
         <v>147</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="114">
+      <c r="O14" s="99">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -8342,7 +8342,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="110"/>
+      <c r="U14" s="108"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -8359,14 +8359,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="136"/>
+      <c r="I15" s="95"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>150</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="115"/>
+      <c r="O15" s="100"/>
       <c r="Q15" s="68" t="s">
         <v>151</v>
       </c>
@@ -8378,10 +8378,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="113" t="s">
+      <c r="C18" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="113"/>
+      <c r="D18" s="98"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -8413,9 +8413,6 @@
       <c r="G20" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>193</v>
-      </c>
     </row>
     <row r="21" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
@@ -8437,7 +8434,7 @@
         <v>196</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -8456,6 +8453,9 @@
       <c r="F22" s="7" t="s">
         <v>199</v>
       </c>
+      <c r="G22" s="7" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
@@ -8629,23 +8629,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="O10:O11"/>
-    <mergeCell ref="O12:O13"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="O4:O6"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="U3:U6"/>
-    <mergeCell ref="U8:U10"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="Q1:T1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E3:H4"/>
     <mergeCell ref="Q3:T6"/>
@@ -8657,6 +8640,23 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="U3:U6"/>
+    <mergeCell ref="U8:U10"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="O4:O6"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O14:O15"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8674,32 +8674,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="G1" s="123" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="G1" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
-      <c r="O1" s="123"/>
-      <c r="P1" s="123"/>
-      <c r="Q1" s="123"/>
-      <c r="R1" s="123"/>
-      <c r="S1" s="123"/>
-      <c r="T1" s="123"/>
-      <c r="U1" s="123"/>
-      <c r="V1" s="123"/>
-      <c r="W1" s="123"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -8765,32 +8765,32 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A8" s="117" t="s">
+      <c r="A8" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="119"/>
+      <c r="B8" s="128"/>
+      <c r="C8" s="128"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="129"/>
       <c r="G8" s="4"/>
-      <c r="I8" s="117" t="s">
+      <c r="I8" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="118"/>
-      <c r="K8" s="118"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="118"/>
-      <c r="N8" s="119"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="128"/>
+      <c r="N8" s="129"/>
       <c r="O8" s="1"/>
-      <c r="Q8" s="117" t="s">
+      <c r="Q8" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="118"/>
-      <c r="S8" s="118"/>
-      <c r="T8" s="118"/>
-      <c r="U8" s="118"/>
-      <c r="V8" s="119"/>
+      <c r="R8" s="128"/>
+      <c r="S8" s="128"/>
+      <c r="T8" s="128"/>
+      <c r="U8" s="128"/>
+      <c r="V8" s="129"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
@@ -8872,11 +8872,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="120">
+      <c r="F10" s="133">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="113">
+      <c r="G10" s="98">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8896,11 +8896,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="120">
+      <c r="N10" s="133">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="98">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8920,7 +8920,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="124">
+      <c r="V10" s="130">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -8943,8 +8943,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="121"/>
-      <c r="G11" s="113"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="98"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8962,8 +8962,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="121"/>
-      <c r="O11" s="113"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="98"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8981,7 +8981,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="125"/>
+      <c r="V11" s="131"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -9001,8 +9001,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="121"/>
-      <c r="G12" s="113"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="98"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9020,8 +9020,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="121"/>
-      <c r="O12" s="113"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="98"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -9039,7 +9039,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="126"/>
+      <c r="V12" s="132"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -9059,8 +9059,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="122"/>
-      <c r="G13" s="113"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="98"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -9078,8 +9078,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="121"/>
-      <c r="O13" s="113"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="98"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -9099,11 +9099,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="120">
+      <c r="F14" s="133">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="113">
+      <c r="G14" s="98">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9123,8 +9123,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="121"/>
-      <c r="O14" s="113"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="98"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -9144,8 +9144,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="122"/>
-      <c r="G15" s="113"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="98"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9163,8 +9163,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="121"/>
-      <c r="O15" s="113"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="98"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -9195,8 +9195,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="122"/>
-      <c r="O16" s="113"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="98"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -9245,21 +9245,21 @@
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A20" s="117" t="s">
+      <c r="A20" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="118"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="119"/>
-      <c r="I20" s="117" t="s">
+      <c r="B20" s="128"/>
+      <c r="C20" s="128"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="129"/>
+      <c r="I20" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="119"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="129"/>
       <c r="O20" s="5"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.15">
@@ -9332,7 +9332,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="124">
+      <c r="N22" s="130">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9372,7 +9372,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="125"/>
+      <c r="N23" s="131"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -9409,7 +9409,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="126"/>
+      <c r="N24" s="132"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -9446,7 +9446,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="124">
+      <c r="N25" s="130">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -9469,7 +9469,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="126"/>
+      <c r="N26" s="132"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -9483,23 +9483,23 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="127" t="s">
+      <c r="A30" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="118"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="129"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="127" t="s">
+      <c r="I30" s="135" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="119"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="128"/>
+      <c r="L30" s="128"/>
+      <c r="M30" s="128"/>
+      <c r="N30" s="129"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.15">
@@ -9564,11 +9564,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="120">
+      <c r="F32" s="133">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="113">
+      <c r="G32" s="98">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9588,11 +9588,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="120">
+      <c r="N32" s="133">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="113">
+      <c r="O32" s="98">
         <v>4</v>
       </c>
     </row>
@@ -9614,8 +9614,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="121"/>
-      <c r="G33" s="113"/>
+      <c r="F33" s="136"/>
+      <c r="G33" s="98"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9633,8 +9633,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="121"/>
-      <c r="O33" s="113"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="98"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -9654,8 +9654,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="121"/>
-      <c r="G34" s="113"/>
+      <c r="F34" s="136"/>
+      <c r="G34" s="98"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9673,8 +9673,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="121"/>
-      <c r="O34" s="113"/>
+      <c r="N34" s="136"/>
+      <c r="O34" s="98"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -9694,8 +9694,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="122"/>
-      <c r="G35" s="113"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="98"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9713,8 +9713,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="121"/>
-      <c r="O35" s="113"/>
+      <c r="N35" s="136"/>
+      <c r="O35" s="98"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -9734,11 +9734,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="120">
+      <c r="F36" s="133">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="113">
+      <c r="G36" s="98">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9758,8 +9758,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="121"/>
-      <c r="O36" s="113"/>
+      <c r="N36" s="136"/>
+      <c r="O36" s="98"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -9779,8 +9779,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="122"/>
-      <c r="G37" s="113"/>
+      <c r="F37" s="134"/>
+      <c r="G37" s="98"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9798,8 +9798,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="121"/>
-      <c r="O37" s="113"/>
+      <c r="N37" s="136"/>
+      <c r="O37" s="98"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -9830,8 +9830,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="122"/>
-      <c r="O38" s="113"/>
+      <c r="N38" s="134"/>
+      <c r="O38" s="98"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -9876,21 +9876,21 @@
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A43" s="117" t="s">
+      <c r="A43" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="118"/>
-      <c r="C43" s="118"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="119"/>
-      <c r="I43" s="117" t="s">
+      <c r="B43" s="128"/>
+      <c r="C43" s="128"/>
+      <c r="D43" s="128"/>
+      <c r="E43" s="129"/>
+      <c r="I43" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="J43" s="118"/>
-      <c r="K43" s="118"/>
-      <c r="L43" s="118"/>
-      <c r="M43" s="118"/>
-      <c r="N43" s="119"/>
+      <c r="J43" s="128"/>
+      <c r="K43" s="128"/>
+      <c r="L43" s="128"/>
+      <c r="M43" s="128"/>
+      <c r="N43" s="129"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
@@ -9961,7 +9961,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="124">
+      <c r="N45" s="130">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -10000,7 +10000,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="125"/>
+      <c r="N46" s="131"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -10036,7 +10036,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="126"/>
+      <c r="N47" s="132"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -10072,7 +10072,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="124">
+      <c r="N48" s="130">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -10094,29 +10094,10 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="126"/>
+      <c r="N49" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -10126,6 +10107,25 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216462CB-CFBF-4E29-8F97-7067DC5CC91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04601985-3EB5-446C-8239-F0ED39650E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -1720,10 +1720,22 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1732,33 +1744,99 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1771,84 +1849,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1858,6 +1858,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1867,19 +1879,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2275,71 +2275,71 @@
     </row>
     <row r="3" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="87"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="86" t="s">
+      <c r="W3" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="X3" s="87"/>
-      <c r="Y3" s="87"/>
-      <c r="Z3" s="87"/>
-      <c r="AA3" s="86" t="s">
+      <c r="X3" s="91"/>
+      <c r="Y3" s="91"/>
+      <c r="Z3" s="91"/>
+      <c r="AA3" s="90" t="s">
         <v>216</v>
       </c>
-      <c r="AB3" s="87"/>
-      <c r="AC3" s="87"/>
-      <c r="AD3" s="87"/>
-      <c r="AE3" s="86" t="s">
+      <c r="AB3" s="91"/>
+      <c r="AC3" s="91"/>
+      <c r="AD3" s="91"/>
+      <c r="AE3" s="90" t="s">
         <v>217</v>
       </c>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AJ3" s="88" t="s">
+      <c r="AF3" s="91"/>
+      <c r="AG3" s="91"/>
+      <c r="AH3" s="91"/>
+      <c r="AJ3" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" s="88"/>
-      <c r="AL3" s="88"/>
-      <c r="AM3" s="88"/>
-      <c r="AN3" s="88"/>
-      <c r="AO3" s="88"/>
-      <c r="AP3" s="88"/>
-      <c r="AQ3" s="88"/>
-      <c r="AR3" s="88"/>
-      <c r="AS3" s="88"/>
-      <c r="AT3" s="88"/>
-      <c r="AV3" s="90" t="s">
+      <c r="AK3" s="84"/>
+      <c r="AL3" s="84"/>
+      <c r="AM3" s="84"/>
+      <c r="AN3" s="84"/>
+      <c r="AO3" s="84"/>
+      <c r="AP3" s="84"/>
+      <c r="AQ3" s="84"/>
+      <c r="AR3" s="84"/>
+      <c r="AS3" s="84"/>
+      <c r="AT3" s="84"/>
+      <c r="AV3" s="86" t="s">
         <v>234</v>
       </c>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
-      <c r="AY3" s="85"/>
-      <c r="AZ3" s="85"/>
-      <c r="BA3" s="85"/>
-      <c r="BB3" s="85"/>
-      <c r="BC3" s="85"/>
-      <c r="BD3" s="85"/>
-      <c r="BE3" s="85"/>
-      <c r="BF3" s="85"/>
+      <c r="AW3" s="87"/>
+      <c r="AX3" s="87"/>
+      <c r="AY3" s="87"/>
+      <c r="AZ3" s="87"/>
+      <c r="BA3" s="87"/>
+      <c r="BB3" s="87"/>
+      <c r="BC3" s="87"/>
+      <c r="BD3" s="87"/>
+      <c r="BE3" s="87"/>
+      <c r="BF3" s="87"/>
     </row>
     <row r="4" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
@@ -2398,28 +2398,28 @@
       <c r="AF4" s="71"/>
       <c r="AG4" s="71"/>
       <c r="AH4" s="71"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="89"/>
-      <c r="AQ4" s="89"/>
-      <c r="AR4" s="89"/>
-      <c r="AS4" s="89"/>
-      <c r="AT4" s="89"/>
-      <c r="AV4" s="89"/>
-      <c r="AW4" s="89"/>
-      <c r="AX4" s="89"/>
-      <c r="AY4" s="89"/>
-      <c r="AZ4" s="89"/>
-      <c r="BA4" s="89"/>
-      <c r="BB4" s="89"/>
-      <c r="BC4" s="89"/>
-      <c r="BD4" s="89"/>
-      <c r="BE4" s="89"/>
-      <c r="BF4" s="89"/>
+      <c r="AJ4" s="85"/>
+      <c r="AK4" s="85"/>
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="85"/>
+      <c r="AN4" s="85"/>
+      <c r="AO4" s="85"/>
+      <c r="AP4" s="85"/>
+      <c r="AQ4" s="85"/>
+      <c r="AR4" s="85"/>
+      <c r="AS4" s="85"/>
+      <c r="AT4" s="85"/>
+      <c r="AV4" s="85"/>
+      <c r="AW4" s="85"/>
+      <c r="AX4" s="85"/>
+      <c r="AY4" s="85"/>
+      <c r="AZ4" s="85"/>
+      <c r="BA4" s="85"/>
+      <c r="BB4" s="85"/>
+      <c r="BC4" s="85"/>
+      <c r="BD4" s="85"/>
+      <c r="BE4" s="85"/>
+      <c r="BF4" s="85"/>
     </row>
     <row r="5" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
@@ -2584,7 +2584,7 @@
       </c>
     </row>
     <row r="6" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="84">
+      <c r="B6" s="88">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2788,7 +2788,7 @@
       </c>
     </row>
     <row r="7" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="84"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2990,7 +2990,7 @@
       </c>
     </row>
     <row r="8" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="84">
+      <c r="B8" s="88">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3194,7 +3194,7 @@
       </c>
     </row>
     <row r="9" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="84"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3396,7 +3396,7 @@
       </c>
     </row>
     <row r="10" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="91">
+      <c r="B10" s="89">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3600,7 +3600,7 @@
       </c>
     </row>
     <row r="11" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="91"/>
+      <c r="B11" s="89"/>
       <c r="X11" s="76"/>
       <c r="Z11" s="76"/>
       <c r="AB11" s="76"/>
@@ -3615,7 +3615,7 @@
       <c r="BF11" s="76"/>
     </row>
     <row r="12" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="91"/>
+      <c r="B12" s="89"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3817,7 +3817,7 @@
       </c>
     </row>
     <row r="13" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="84">
+      <c r="B13" s="88">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -4021,7 +4021,7 @@
       </c>
     </row>
     <row r="14" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="84"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="BF15" s="76"/>
     </row>
     <row r="16" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="84">
+      <c r="B16" s="88">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4441,7 +4441,7 @@
       </c>
     </row>
     <row r="17" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="84"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4643,7 +4643,7 @@
       </c>
     </row>
     <row r="18" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="84"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4859,7 +4859,7 @@
       <c r="BF19" s="76"/>
     </row>
     <row r="20" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="84">
+      <c r="B20" s="88">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -5063,7 +5063,7 @@
       </c>
     </row>
     <row r="21" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="84"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -5308,6 +5308,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D3:T3"/>
+    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="AJ3:AT4"/>
     <mergeCell ref="AV3:BF4"/>
     <mergeCell ref="B6:B7"/>
@@ -5315,11 +5320,6 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AA3:AD3"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D3:T3"/>
-    <mergeCell ref="W3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5378,57 +5378,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="85" t="s">
+      <c r="V3" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="85"/>
-      <c r="X3" s="85"/>
-      <c r="Y3" s="85"/>
-      <c r="Z3" s="85"/>
-      <c r="AA3" s="85"/>
-      <c r="AB3" s="85"/>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="85"/>
-      <c r="AF3" s="85"/>
-      <c r="AG3" s="85"/>
-      <c r="AH3" s="85"/>
-      <c r="AI3" s="85"/>
-      <c r="AJ3" s="85"/>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="85"/>
-      <c r="AM3" s="85"/>
-      <c r="AN3" s="85"/>
-      <c r="AO3" s="85"/>
-      <c r="AP3" s="85"/>
-      <c r="AQ3" s="85"/>
-      <c r="AR3" s="85"/>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AU3" s="85"/>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
-      <c r="AY3" s="85"/>
+      <c r="W3" s="87"/>
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="87"/>
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="87"/>
+      <c r="AJ3" s="87"/>
+      <c r="AK3" s="87"/>
+      <c r="AL3" s="87"/>
+      <c r="AM3" s="87"/>
+      <c r="AN3" s="87"/>
+      <c r="AO3" s="87"/>
+      <c r="AP3" s="87"/>
+      <c r="AQ3" s="87"/>
+      <c r="AR3" s="87"/>
+      <c r="AS3" s="87"/>
+      <c r="AT3" s="87"/>
+      <c r="AU3" s="87"/>
+      <c r="AV3" s="87"/>
+      <c r="AW3" s="87"/>
+      <c r="AX3" s="87"/>
+      <c r="AY3" s="87"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5474,44 +5474,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="89" t="s">
+      <c r="V4" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="89"/>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="85"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="89" t="s">
+      <c r="AD4" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="89" t="s">
+      <c r="AL4" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="89"/>
-      <c r="AQ4" s="89"/>
+      <c r="AM4" s="85"/>
+      <c r="AN4" s="85"/>
+      <c r="AO4" s="85"/>
+      <c r="AP4" s="85"/>
+      <c r="AQ4" s="85"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="89" t="s">
+      <c r="AT4" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="89"/>
-      <c r="AV4" s="89"/>
-      <c r="AW4" s="89"/>
-      <c r="AX4" s="89"/>
-      <c r="AY4" s="89"/>
+      <c r="AU4" s="85"/>
+      <c r="AV4" s="85"/>
+      <c r="AW4" s="85"/>
+      <c r="AX4" s="85"/>
+      <c r="AY4" s="85"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5653,7 +5653,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="84">
+      <c r="B6" s="88">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -5817,7 +5817,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="84"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -5979,7 +5979,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="84">
+      <c r="B8" s="88">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="84"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -6305,7 +6305,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="91">
+      <c r="B10" s="89">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -6469,10 +6469,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="91"/>
+      <c r="B11" s="89"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="91"/>
+      <c r="B12" s="89"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -6634,7 +6634,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="84">
+      <c r="B13" s="88">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -6798,7 +6798,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="84"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -6960,7 +6960,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="84">
+      <c r="B16" s="88">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -7124,7 +7124,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="84"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -7286,7 +7286,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="84"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -7448,7 +7448,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="84">
+      <c r="B20" s="88">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -7612,7 +7612,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="84"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -7775,18 +7775,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="V3:AY3"/>
+    <mergeCell ref="AT4:AY4"/>
+    <mergeCell ref="AL4:AQ4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="V4:AA4"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="V3:AY3"/>
-    <mergeCell ref="AT4:AY4"/>
-    <mergeCell ref="AL4:AQ4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="V4:AA4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7846,35 +7846,35 @@
       <c r="A2" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="126" t="s">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126" t="s">
+      <c r="F2" s="104"/>
+      <c r="G2" s="104" t="s">
         <v>188</v>
       </c>
-      <c r="H2" s="126"/>
-      <c r="K2" s="126" t="s">
+      <c r="H2" s="104"/>
+      <c r="K2" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126" t="s">
+      <c r="L2" s="104"/>
+      <c r="M2" s="104" t="s">
         <v>188</v>
       </c>
-      <c r="N2" s="126"/>
-      <c r="Q2" s="126" t="s">
+      <c r="N2" s="104"/>
+      <c r="Q2" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="R2" s="126"/>
-      <c r="S2" s="126" t="s">
+      <c r="R2" s="104"/>
+      <c r="S2" s="104" t="s">
         <v>188</v>
       </c>
-      <c r="T2" s="126"/>
+      <c r="T2" s="104"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -7887,25 +7887,25 @@
         <v>121</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="124" t="s">
+      <c r="E3" s="93"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="102" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="115"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="117"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="95"/>
       <c r="O3" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="109" t="s">
+      <c r="Q3" s="93"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="95"/>
+      <c r="U3" s="106" t="s">
         <v>155</v>
       </c>
     </row>
@@ -7918,11 +7918,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="125"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="103"/>
       <c r="K4" s="49" t="s">
         <v>132</v>
       </c>
@@ -7931,14 +7931,14 @@
         <v>133</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="103">
+      <c r="O4" s="116">
         <v>0</v>
       </c>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="110"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="107"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -7963,7 +7963,7 @@
       <c r="H5" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="101">
+      <c r="I5" s="114">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -7974,12 +7974,12 @@
         <v>186</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="103"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="110"/>
+      <c r="O5" s="116"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="101"/>
+      <c r="U5" s="107"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -7996,19 +7996,19 @@
         <v>159</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="102"/>
+      <c r="I6" s="115"/>
       <c r="K6" s="48" t="s">
         <v>162</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="103"/>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="119"/>
-      <c r="T6" s="120"/>
-      <c r="U6" s="110"/>
+      <c r="O6" s="116"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
+      <c r="S6" s="97"/>
+      <c r="T6" s="98"/>
+      <c r="U6" s="107"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -8027,7 +8027,7 @@
       <c r="H7" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="I7" s="105">
+      <c r="I7" s="118">
         <v>1</v>
       </c>
       <c r="K7" s="53" t="s">
@@ -8042,7 +8042,7 @@
       <c r="N7" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="O7" s="104">
+      <c r="O7" s="117">
         <v>1</v>
       </c>
       <c r="Q7" s="54"/>
@@ -8074,20 +8074,16 @@
       <c r="F8" s="52"/>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
-      <c r="I8" s="106"/>
-      <c r="K8" s="53" t="s">
-        <v>135</v>
-      </c>
+      <c r="I8" s="119"/>
+      <c r="K8" s="53"/>
       <c r="L8" s="53" t="s">
         <v>136</v>
       </c>
       <c r="M8" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="N8" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="O8" s="104"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="117"/>
       <c r="Q8" s="33" t="s">
         <v>164</v>
       </c>
@@ -8098,7 +8094,7 @@
       <c r="T8" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="U8" s="92">
+      <c r="U8" s="108">
         <v>2</v>
       </c>
     </row>
@@ -8125,20 +8121,18 @@
       <c r="H9" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="106"/>
+      <c r="I9" s="119"/>
       <c r="K9" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="L9" s="51" t="s">
-        <v>170</v>
-      </c>
+      <c r="L9" s="51"/>
       <c r="M9" s="51" t="s">
         <v>171</v>
       </c>
       <c r="N9" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="104"/>
+      <c r="O9" s="117"/>
       <c r="Q9" s="33" t="s">
         <v>173</v>
       </c>
@@ -8146,8 +8140,10 @@
       <c r="S9" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="T9" s="83"/>
-      <c r="U9" s="96"/>
+      <c r="T9" s="83" t="s">
+        <v>163</v>
+      </c>
+      <c r="U9" s="109"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
@@ -8164,7 +8160,7 @@
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="96">
+      <c r="I10" s="109">
         <v>2</v>
       </c>
       <c r="K10" s="57" t="s">
@@ -8177,14 +8173,18 @@
       <c r="N10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="O10" s="92">
+      <c r="O10" s="108">
         <v>2</v>
       </c>
       <c r="Q10" s="33"/>
       <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="83"/>
-      <c r="U10" s="93"/>
+      <c r="S10" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="T10" s="83" t="s">
+        <v>170</v>
+      </c>
+      <c r="U10" s="110"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -8207,14 +8207,14 @@
       <c r="H11" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="96"/>
+      <c r="I11" s="109"/>
       <c r="K11" s="33"/>
       <c r="L11" s="56"/>
       <c r="M11" s="33" t="s">
         <v>176</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="93"/>
+      <c r="O11" s="110"/>
       <c r="Q11" s="61" t="s">
         <v>175</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>177</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="107">
+      <c r="U11" s="120">
         <v>3</v>
       </c>
     </row>
@@ -8244,14 +8244,14 @@
         <v>178</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="96"/>
+      <c r="I12" s="109"/>
       <c r="K12" s="60"/>
       <c r="L12" s="60"/>
       <c r="M12" s="60" t="s">
         <v>179</v>
       </c>
       <c r="N12" s="60"/>
-      <c r="O12" s="94">
+      <c r="O12" s="121">
         <v>3</v>
       </c>
       <c r="Q12" s="69" t="s">
@@ -8260,7 +8260,7 @@
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="107"/>
+      <c r="U12" s="120"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -8281,7 +8281,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="97">
+      <c r="I13" s="123">
         <v>3</v>
       </c>
       <c r="K13" s="60" t="s">
@@ -8296,7 +8296,7 @@
       <c r="N13" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="O13" s="95"/>
+      <c r="O13" s="122"/>
       <c r="Q13" s="28" t="s">
         <v>183</v>
       </c>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="108">
+      <c r="U13" s="105">
         <v>4</v>
       </c>
     </row>
@@ -8326,14 +8326,14 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="97"/>
+      <c r="I14" s="123"/>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
         <v>147</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="99">
+      <c r="O14" s="125">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -8342,7 +8342,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="108"/>
+      <c r="U14" s="105"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -8359,14 +8359,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="95"/>
+      <c r="I15" s="122"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>150</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="100"/>
+      <c r="O15" s="126"/>
       <c r="Q15" s="68" t="s">
         <v>151</v>
       </c>
@@ -8378,10 +8378,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="98" t="s">
+      <c r="C18" s="124" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="98"/>
+      <c r="D18" s="124"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -8629,17 +8629,8 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E3:H4"/>
-    <mergeCell ref="Q3:T6"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O14:O15"/>
     <mergeCell ref="U13:U14"/>
     <mergeCell ref="U3:U6"/>
     <mergeCell ref="U8:U10"/>
@@ -8655,8 +8646,17 @@
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="I13:I15"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E3:H4"/>
+    <mergeCell ref="Q3:T6"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8674,32 +8674,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="G1" s="137" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="G1" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+      <c r="W1" s="133"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -8872,11 +8872,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="133">
+      <c r="F10" s="130">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="98">
+      <c r="G10" s="124">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8896,11 +8896,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="133">
+      <c r="N10" s="130">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="98">
+      <c r="O10" s="124">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8920,7 +8920,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="130">
+      <c r="V10" s="134">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -8943,8 +8943,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="136"/>
-      <c r="G11" s="98"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="124"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8962,8 +8962,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="136"/>
-      <c r="O11" s="98"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="124"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8981,7 +8981,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="131"/>
+      <c r="V11" s="135"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -9001,8 +9001,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="136"/>
-      <c r="G12" s="98"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="124"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9020,8 +9020,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="136"/>
-      <c r="O12" s="98"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="124"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -9039,7 +9039,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="132"/>
+      <c r="V12" s="136"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -9059,8 +9059,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="134"/>
-      <c r="G13" s="98"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="124"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -9078,8 +9078,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="136"/>
-      <c r="O13" s="98"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="124"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -9099,11 +9099,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="133">
+      <c r="F14" s="130">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="98">
+      <c r="G14" s="124">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9123,8 +9123,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="136"/>
-      <c r="O14" s="98"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="124"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -9144,8 +9144,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="134"/>
-      <c r="G15" s="98"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="124"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9163,8 +9163,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="136"/>
-      <c r="O15" s="98"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="124"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -9195,8 +9195,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="134"/>
-      <c r="O16" s="98"/>
+      <c r="N16" s="132"/>
+      <c r="O16" s="124"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -9332,7 +9332,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="130">
+      <c r="N22" s="134">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9372,7 +9372,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="131"/>
+      <c r="N23" s="135"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -9409,7 +9409,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="132"/>
+      <c r="N24" s="136"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -9446,7 +9446,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="130">
+      <c r="N25" s="134">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -9469,7 +9469,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="132"/>
+      <c r="N26" s="136"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -9483,7 +9483,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="137" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="128"/>
@@ -9492,7 +9492,7 @@
       <c r="E30" s="128"/>
       <c r="F30" s="129"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="135" t="s">
+      <c r="I30" s="137" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="128"/>
@@ -9564,11 +9564,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="133">
+      <c r="F32" s="130">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="98">
+      <c r="G32" s="124">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9588,11 +9588,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="133">
+      <c r="N32" s="130">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="98">
+      <c r="O32" s="124">
         <v>4</v>
       </c>
     </row>
@@ -9614,8 +9614,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="136"/>
-      <c r="G33" s="98"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="124"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9633,8 +9633,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="136"/>
-      <c r="O33" s="98"/>
+      <c r="N33" s="131"/>
+      <c r="O33" s="124"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -9654,8 +9654,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="136"/>
-      <c r="G34" s="98"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="124"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9673,8 +9673,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="136"/>
-      <c r="O34" s="98"/>
+      <c r="N34" s="131"/>
+      <c r="O34" s="124"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -9694,8 +9694,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="134"/>
-      <c r="G35" s="98"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="124"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9713,8 +9713,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="136"/>
-      <c r="O35" s="98"/>
+      <c r="N35" s="131"/>
+      <c r="O35" s="124"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -9734,11 +9734,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="133">
+      <c r="F36" s="130">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="98">
+      <c r="G36" s="124">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9758,8 +9758,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="136"/>
-      <c r="O36" s="98"/>
+      <c r="N36" s="131"/>
+      <c r="O36" s="124"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -9779,8 +9779,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="134"/>
-      <c r="G37" s="98"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="124"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9798,8 +9798,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="136"/>
-      <c r="O37" s="98"/>
+      <c r="N37" s="131"/>
+      <c r="O37" s="124"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -9830,8 +9830,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="134"/>
-      <c r="O38" s="98"/>
+      <c r="N38" s="132"/>
+      <c r="O38" s="124"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -9961,7 +9961,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="130">
+      <c r="N45" s="134">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -10000,7 +10000,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="131"/>
+      <c r="N46" s="135"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -10036,7 +10036,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="132"/>
+      <c r="N47" s="136"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -10072,7 +10072,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="130">
+      <c r="N48" s="134">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -10094,10 +10094,29 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="132"/>
+      <c r="N49" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -10107,25 +10126,6 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04601985-3EB5-446C-8239-F0ED39650E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7085E9F3-C66C-4354-9D56-30ADDD8DCC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34608" yWindow="-4152" windowWidth="26436" windowHeight="15432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -1783,6 +1783,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1801,24 +1828,6 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1838,15 +1847,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3748,21 +3748,21 @@
         <f t="shared" ref="AN12:AN14" si="29">AL12*(1+(0.02*AM12))</f>
         <v>20</v>
       </c>
-      <c r="AO12" s="20">
-        <f>CALC_DMG(Q12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(Q12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(Q12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
-        <v>586.50167999999985</v>
-      </c>
-      <c r="AP12" s="75">
-        <f>AK12/AO12</f>
-        <v>1.3640199632505745</v>
-      </c>
-      <c r="AQ12" s="20">
-        <f>CALC_DMG(R12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(R12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(R12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
-        <v>409.74683999999985</v>
-      </c>
-      <c r="AR12" s="75">
-        <f>AK12/AQ12</f>
-        <v>1.952425063241489</v>
+      <c r="AO12" s="20" t="e">
+        <f ca="1">CALC_DMG(Q12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(Q12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(Q12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP12" s="75" t="e">
+        <f ca="1">AK12/AO12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ12" s="20" t="e">
+        <f ca="1">CALC_DMG(R12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(R12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(R12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR12" s="75" t="e">
+        <f ca="1">AK12/AQ12</f>
+        <v>#NAME?</v>
       </c>
       <c r="AS12" s="20">
         <f>CALC_DMG(S12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(S12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(S12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
@@ -3791,21 +3791,21 @@
         <f t="shared" ref="AZ12:AZ14" si="33">AX12*(1+(0.02*AY12))</f>
         <v>12</v>
       </c>
-      <c r="BA12" s="20">
-        <f>[1]!CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>658.50159999999994</v>
-      </c>
-      <c r="BB12" s="75">
-        <f t="shared" ref="BB12:BB14" si="34">AW12/BA12</f>
-        <v>0.7289276138433074</v>
-      </c>
-      <c r="BC12" s="20">
-        <f>[1]!CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>481.74700000000001</v>
-      </c>
-      <c r="BD12" s="75">
-        <f t="shared" ref="BD12:BD14" si="35">AW12/BC12</f>
-        <v>0.99637361519635825</v>
+      <c r="BA12" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB12" s="75" t="e">
+        <f t="shared" ref="BB12:BB14" ca="1" si="34">AW12/BA12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC12" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD12" s="75" t="e">
+        <f t="shared" ref="BD12:BD14" ca="1" si="35">AW12/BC12</f>
+        <v>#NAME?</v>
       </c>
       <c r="BE12" s="20">
         <f>[1]!CALC_DMG(S12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(S12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(S12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
@@ -3952,21 +3952,21 @@
         <f t="shared" si="29"/>
         <v>40</v>
       </c>
-      <c r="AO13" s="20">
-        <f>CALC_DMG(Q13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(Q13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(Q13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
-        <v>904.7879999999999</v>
-      </c>
-      <c r="AP13" s="75">
-        <f>AK13/AO13</f>
-        <v>1.2157544087675789</v>
-      </c>
-      <c r="AQ13" s="20">
-        <f>CALC_DMG(R13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(R13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(R13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
-        <v>602.21399999999994</v>
-      </c>
-      <c r="AR13" s="75">
-        <f>AK13/AQ13</f>
-        <v>1.826593204409064</v>
+      <c r="AO13" s="20" t="e">
+        <f ca="1">CALC_DMG(Q13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(Q13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(Q13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP13" s="75" t="e">
+        <f ca="1">AK13/AO13</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ13" s="20" t="e">
+        <f ca="1">CALC_DMG(R13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(R13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(R13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR13" s="75" t="e">
+        <f ca="1">AK13/AQ13</f>
+        <v>#NAME?</v>
       </c>
       <c r="AS13" s="20">
         <f>CALC_DMG(S13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(S13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(S13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
@@ -3995,21 +3995,21 @@
         <f t="shared" si="33"/>
         <v>24</v>
       </c>
-      <c r="BA13" s="20">
-        <f>[1]!CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
-        <v>1048.788</v>
-      </c>
-      <c r="BB13" s="75">
-        <f t="shared" si="34"/>
-        <v>0.62929781805283813</v>
-      </c>
-      <c r="BC13" s="20">
-        <f>[1]!CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
-        <v>746.21399999999994</v>
-      </c>
-      <c r="BD13" s="75">
-        <f t="shared" si="35"/>
-        <v>0.88446477820035552</v>
+      <c r="BA13" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB13" s="75" t="e">
+        <f t="shared" ca="1" si="34"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC13" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD13" s="75" t="e">
+        <f t="shared" ca="1" si="35"/>
+        <v>#NAME?</v>
       </c>
       <c r="BE13" s="20">
         <f>[1]!CALC_DMG(S13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(S13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(S13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
@@ -4154,21 +4154,21 @@
         <f t="shared" si="29"/>
         <v>60</v>
       </c>
-      <c r="AO14" s="20">
-        <f>CALC_DMG(Q14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(Q14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(Q14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
-        <v>1514.7212399999996</v>
-      </c>
-      <c r="AP14" s="75">
-        <f>AK14/AO14</f>
-        <v>2.6407499243887282</v>
-      </c>
-      <c r="AQ14" s="20">
-        <f>CALC_DMG(R14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(R14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(R14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
-        <v>1405.1206199999997</v>
-      </c>
-      <c r="AR14" s="75">
-        <f>AK14/AQ14</f>
-        <v>2.8467306956181462</v>
+      <c r="AO14" s="20" t="e">
+        <f ca="1">CALC_DMG(Q14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(Q14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(Q14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP14" s="75" t="e">
+        <f ca="1">AK14/AO14</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ14" s="20" t="e">
+        <f ca="1">CALC_DMG(R14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(R14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(R14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR14" s="75" t="e">
+        <f ca="1">AK14/AQ14</f>
+        <v>#NAME?</v>
       </c>
       <c r="AS14" s="20">
         <f>CALC_DMG(S14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(S14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(S14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
@@ -4197,21 +4197,21 @@
         <f t="shared" si="33"/>
         <v>36</v>
       </c>
-      <c r="BA14" s="20">
-        <f>[1]!CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>1730.7213999999999</v>
-      </c>
-      <c r="BB14" s="75">
-        <f t="shared" si="34"/>
-        <v>1.3867049890294303</v>
-      </c>
-      <c r="BC14" s="20">
-        <f>[1]!CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>1621.1206999999999</v>
-      </c>
-      <c r="BD14" s="75">
-        <f t="shared" si="35"/>
-        <v>1.4804573157322587</v>
+      <c r="BA14" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB14" s="75" t="e">
+        <f t="shared" ca="1" si="34"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC14" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD14" s="75" t="e">
+        <f t="shared" ca="1" si="35"/>
+        <v>#NAME?</v>
       </c>
       <c r="BE14" s="20">
         <f>[1]!CALC_DMG(S14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(S14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(S14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
@@ -4372,21 +4372,21 @@
         <f t="shared" ref="AN16:AN18" si="48">AL16*(1+(0.02*AM16))</f>
         <v>80</v>
       </c>
-      <c r="AO16" s="20">
-        <f>CALC_DMG(Q16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(Q16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(Q16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
-        <v>2402.2195199999996</v>
-      </c>
-      <c r="AP16" s="75">
-        <f>AK16/AO16</f>
-        <v>1.8732676021215582</v>
-      </c>
-      <c r="AQ16" s="20">
-        <f>CALC_DMG(R16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(R16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(R16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
-        <v>1844.9097599999996</v>
-      </c>
-      <c r="AR16" s="75">
-        <f>AK16/AQ16</f>
-        <v>2.4391436901499186</v>
+      <c r="AO16" s="20" t="e">
+        <f ca="1">CALC_DMG(Q16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(Q16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(Q16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP16" s="75" t="e">
+        <f ca="1">AK16/AO16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ16" s="20" t="e">
+        <f ca="1">CALC_DMG(R16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(R16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(R16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR16" s="75" t="e">
+        <f ca="1">AK16/AQ16</f>
+        <v>#NAME?</v>
       </c>
       <c r="AS16" s="20">
         <f>CALC_DMG(S16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(S16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(S16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
@@ -4415,21 +4415,21 @@
         <f t="shared" ref="AZ16:AZ18" si="52">AX16*(1+(0.02*AY16))</f>
         <v>48</v>
       </c>
-      <c r="BA16" s="20">
-        <f>[1]!CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>2690.2196000000004</v>
-      </c>
-      <c r="BB16" s="75">
-        <f t="shared" ref="BB16:BB18" si="53">AW16/BA16</f>
-        <v>1.0036355396414478</v>
-      </c>
-      <c r="BC16" s="20">
-        <f>[1]!CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>2132.9096</v>
-      </c>
-      <c r="BD16" s="75">
-        <f t="shared" ref="BD16:BD18" si="54">AW16/BC16</f>
-        <v>1.2658764347068436</v>
+      <c r="BA16" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB16" s="75" t="e">
+        <f t="shared" ref="BB16:BB18" ca="1" si="53">AW16/BA16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC16" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD16" s="75" t="e">
+        <f t="shared" ref="BD16:BD18" ca="1" si="54">AW16/BC16</f>
+        <v>#NAME?</v>
       </c>
       <c r="BE16" s="20">
         <f>[1]!CALC_DMG(S16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(S16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(S16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
@@ -4574,21 +4574,21 @@
         <f t="shared" si="48"/>
         <v>110</v>
       </c>
-      <c r="AO17" s="20">
-        <f>CALC_DMG(Q17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(Q17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(Q17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
-        <v>3607.1171999999992</v>
-      </c>
-      <c r="AP17" s="75">
-        <f>AK17/AO17</f>
-        <v>2.2178375573712996</v>
-      </c>
-      <c r="AQ17" s="20">
-        <f>CALC_DMG(R17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(R17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(R17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
-        <v>2857.2785999999992</v>
-      </c>
-      <c r="AR17" s="75">
-        <f>AK17/AQ17</f>
-        <v>2.7998669783198609</v>
+      <c r="AO17" s="20" t="e">
+        <f ca="1">CALC_DMG(Q17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(Q17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(Q17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP17" s="75" t="e">
+        <f ca="1">AK17/AO17</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ17" s="20" t="e">
+        <f ca="1">CALC_DMG(R17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(R17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(R17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR17" s="75" t="e">
+        <f ca="1">AK17/AQ17</f>
+        <v>#NAME?</v>
       </c>
       <c r="AS17" s="20">
         <f>CALC_DMG(S17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(S17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(S17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
@@ -4617,21 +4617,21 @@
         <f t="shared" si="52"/>
         <v>66</v>
       </c>
-      <c r="BA17" s="20">
-        <f>[1]!CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>4003.1171999999997</v>
-      </c>
-      <c r="BB17" s="75">
-        <f t="shared" si="53"/>
-        <v>1.1990655682026998</v>
-      </c>
-      <c r="BC17" s="20">
-        <f>[1]!CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>3253.279</v>
-      </c>
-      <c r="BD17" s="75">
-        <f t="shared" si="54"/>
-        <v>1.4754344770307126</v>
+      <c r="BA17" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB17" s="75" t="e">
+        <f t="shared" ca="1" si="53"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC17" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD17" s="75" t="e">
+        <f t="shared" ca="1" si="54"/>
+        <v>#NAME?</v>
       </c>
       <c r="BE17" s="20">
         <f>[1]!CALC_DMG(S17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(S17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(S17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
@@ -7814,30 +7814,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="111" t="s">
+      <c r="E1" s="105" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
       <c r="I1" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K1" s="112" t="s">
+      <c r="K1" s="106" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
       <c r="O1" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="Q1" s="113" t="s">
+      <c r="Q1" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
       <c r="U1" s="39" t="s">
         <v>158</v>
       </c>
@@ -7905,7 +7905,7 @@
       <c r="R3" s="94"/>
       <c r="S3" s="94"/>
       <c r="T3" s="95"/>
-      <c r="U3" s="106" t="s">
+      <c r="U3" s="115" t="s">
         <v>155</v>
       </c>
     </row>
@@ -7931,14 +7931,14 @@
         <v>133</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="116">
+      <c r="O4" s="110">
         <v>0</v>
       </c>
       <c r="Q4" s="99"/>
       <c r="R4" s="100"/>
       <c r="S4" s="100"/>
       <c r="T4" s="101"/>
-      <c r="U4" s="107"/>
+      <c r="U4" s="116"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -7963,7 +7963,7 @@
       <c r="H5" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="114">
+      <c r="I5" s="108">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -7974,12 +7974,12 @@
         <v>186</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="116"/>
+      <c r="O5" s="110"/>
       <c r="Q5" s="99"/>
       <c r="R5" s="100"/>
       <c r="S5" s="100"/>
       <c r="T5" s="101"/>
-      <c r="U5" s="107"/>
+      <c r="U5" s="116"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -7996,19 +7996,19 @@
         <v>159</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="115"/>
+      <c r="I6" s="109"/>
       <c r="K6" s="48" t="s">
         <v>162</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="116"/>
+      <c r="O6" s="110"/>
       <c r="Q6" s="96"/>
       <c r="R6" s="97"/>
       <c r="S6" s="97"/>
       <c r="T6" s="98"/>
-      <c r="U6" s="107"/>
+      <c r="U6" s="116"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -8027,7 +8027,7 @@
       <c r="H7" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="I7" s="118">
+      <c r="I7" s="121">
         <v>1</v>
       </c>
       <c r="K7" s="53" t="s">
@@ -8042,7 +8042,7 @@
       <c r="N7" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="O7" s="117">
+      <c r="O7" s="120">
         <v>1</v>
       </c>
       <c r="Q7" s="54"/>
@@ -8074,7 +8074,7 @@
       <c r="F8" s="52"/>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
-      <c r="I8" s="119"/>
+      <c r="I8" s="122"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53" t="s">
         <v>136</v>
@@ -8083,7 +8083,7 @@
         <v>153</v>
       </c>
       <c r="N8" s="51"/>
-      <c r="O8" s="117"/>
+      <c r="O8" s="120"/>
       <c r="Q8" s="33" t="s">
         <v>164</v>
       </c>
@@ -8094,7 +8094,7 @@
       <c r="T8" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="U8" s="108">
+      <c r="U8" s="117">
         <v>2</v>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       <c r="H9" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="119"/>
+      <c r="I9" s="122"/>
       <c r="K9" s="51" t="s">
         <v>169</v>
       </c>
@@ -8132,7 +8132,7 @@
       <c r="N9" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="117"/>
+      <c r="O9" s="120"/>
       <c r="Q9" s="33" t="s">
         <v>173</v>
       </c>
@@ -8143,7 +8143,7 @@
       <c r="T9" s="83" t="s">
         <v>163</v>
       </c>
-      <c r="U9" s="109"/>
+      <c r="U9" s="118"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
@@ -8160,7 +8160,7 @@
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="109">
+      <c r="I10" s="118">
         <v>2</v>
       </c>
       <c r="K10" s="57" t="s">
@@ -8173,7 +8173,7 @@
       <c r="N10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="117">
         <v>2</v>
       </c>
       <c r="Q10" s="33"/>
@@ -8184,7 +8184,7 @@
       <c r="T10" s="83" t="s">
         <v>170</v>
       </c>
-      <c r="U10" s="110"/>
+      <c r="U10" s="119"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -8207,14 +8207,14 @@
       <c r="H11" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="109"/>
+      <c r="I11" s="118"/>
       <c r="K11" s="33"/>
       <c r="L11" s="56"/>
       <c r="M11" s="33" t="s">
         <v>176</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="110"/>
+      <c r="O11" s="119"/>
       <c r="Q11" s="61" t="s">
         <v>175</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>177</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="120">
+      <c r="U11" s="123">
         <v>3</v>
       </c>
     </row>
@@ -8244,14 +8244,14 @@
         <v>178</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="109"/>
+      <c r="I12" s="118"/>
       <c r="K12" s="60"/>
       <c r="L12" s="60"/>
       <c r="M12" s="60" t="s">
         <v>179</v>
       </c>
       <c r="N12" s="60"/>
-      <c r="O12" s="121">
+      <c r="O12" s="124">
         <v>3</v>
       </c>
       <c r="Q12" s="69" t="s">
@@ -8260,7 +8260,7 @@
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="120"/>
+      <c r="U12" s="123"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -8281,7 +8281,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="123">
+      <c r="I13" s="126">
         <v>3</v>
       </c>
       <c r="K13" s="60" t="s">
@@ -8296,7 +8296,7 @@
       <c r="N13" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="O13" s="122"/>
+      <c r="O13" s="125"/>
       <c r="Q13" s="28" t="s">
         <v>183</v>
       </c>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="105">
+      <c r="U13" s="114">
         <v>4</v>
       </c>
     </row>
@@ -8326,14 +8326,14 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="123"/>
+      <c r="I14" s="126"/>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
         <v>147</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="125">
+      <c r="O14" s="112">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -8342,7 +8342,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="105"/>
+      <c r="U14" s="114"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -8359,14 +8359,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="122"/>
+      <c r="I15" s="125"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>150</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="126"/>
+      <c r="O15" s="113"/>
       <c r="Q15" s="68" t="s">
         <v>151</v>
       </c>
@@ -8378,10 +8378,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="124" t="s">
+      <c r="C18" s="111" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="124"/>
+      <c r="D18" s="111"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -8634,11 +8634,6 @@
     <mergeCell ref="U13:U14"/>
     <mergeCell ref="U3:U6"/>
     <mergeCell ref="U8:U10"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="O4:O6"/>
     <mergeCell ref="O7:O9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="U11:U12"/>
@@ -8646,6 +8641,11 @@
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="I13:I15"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="O4:O6"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E3:H4"/>
     <mergeCell ref="Q3:T6"/>
@@ -8876,7 +8876,7 @@
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="124">
+      <c r="G10" s="111">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8900,7 +8900,7 @@
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="124">
+      <c r="O10" s="111">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8944,7 +8944,7 @@
         <v>0.5</v>
       </c>
       <c r="F11" s="131"/>
-      <c r="G11" s="124"/>
+      <c r="G11" s="111"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0.5</v>
       </c>
       <c r="N11" s="131"/>
-      <c r="O11" s="124"/>
+      <c r="O11" s="111"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="131"/>
-      <c r="G12" s="124"/>
+      <c r="G12" s="111"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="131"/>
-      <c r="O12" s="124"/>
+      <c r="O12" s="111"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -9060,7 +9060,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="132"/>
-      <c r="G13" s="124"/>
+      <c r="G13" s="111"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>5</v>
       </c>
       <c r="N13" s="131"/>
-      <c r="O13" s="124"/>
+      <c r="O13" s="111"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -9103,7 +9103,7 @@
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="124">
+      <c r="G14" s="111">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9124,7 +9124,7 @@
         <v>3.5</v>
       </c>
       <c r="N14" s="131"/>
-      <c r="O14" s="124"/>
+      <c r="O14" s="111"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -9145,7 +9145,7 @@
         <v>2.4187500000000002</v>
       </c>
       <c r="F15" s="132"/>
-      <c r="G15" s="124"/>
+      <c r="G15" s="111"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9164,7 +9164,7 @@
         <v>5</v>
       </c>
       <c r="N15" s="131"/>
-      <c r="O15" s="124"/>
+      <c r="O15" s="111"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -9196,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="132"/>
-      <c r="O16" s="124"/>
+      <c r="O16" s="111"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -9568,7 +9568,7 @@
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="124">
+      <c r="G32" s="111">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9592,7 +9592,7 @@
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="124">
+      <c r="O32" s="111">
         <v>4</v>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
         <v>0.70724999999999993</v>
       </c>
       <c r="F33" s="131"/>
-      <c r="G33" s="124"/>
+      <c r="G33" s="111"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>0.70724999999999993</v>
       </c>
       <c r="N33" s="131"/>
-      <c r="O33" s="124"/>
+      <c r="O33" s="111"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -9655,7 +9655,7 @@
         <v>1.4489999999999998</v>
       </c>
       <c r="F34" s="131"/>
-      <c r="G34" s="124"/>
+      <c r="G34" s="111"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9674,7 +9674,7 @@
         <v>1.4489999999999998</v>
       </c>
       <c r="N34" s="131"/>
-      <c r="O34" s="124"/>
+      <c r="O34" s="111"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -9695,7 +9695,7 @@
         <v>1.4489999999999998</v>
       </c>
       <c r="F35" s="132"/>
-      <c r="G35" s="124"/>
+      <c r="G35" s="111"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>6.1749999999999989</v>
       </c>
       <c r="N35" s="131"/>
-      <c r="O35" s="124"/>
+      <c r="O35" s="111"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -9738,7 +9738,7 @@
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="124">
+      <c r="G36" s="111">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9759,7 +9759,7 @@
         <v>4.0631500000000003</v>
       </c>
       <c r="N36" s="131"/>
-      <c r="O36" s="124"/>
+      <c r="O36" s="111"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -9780,7 +9780,7 @@
         <v>3.2249999999999996</v>
       </c>
       <c r="F37" s="132"/>
-      <c r="G37" s="124"/>
+      <c r="G37" s="111"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9799,7 +9799,7 @@
         <v>6.1749999999999989</v>
       </c>
       <c r="N37" s="131"/>
-      <c r="O37" s="124"/>
+      <c r="O37" s="111"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -9831,7 +9831,7 @@
         <v>1.0373999999999999</v>
       </c>
       <c r="N38" s="132"/>
-      <c r="O38" s="124"/>
+      <c r="O38" s="111"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7085E9F3-C66C-4354-9D56-30ADDD8DCC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A897DB23-B385-4D90-BE30-D962E851907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34608" yWindow="-4152" windowWidth="26436" windowHeight="15432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -1720,6 +1720,18 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1729,19 +1741,73 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1783,72 +1849,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1858,28 +1858,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1924,7 +1924,6 @@
       <sheetName val="数值分配"/>
       <sheetName val="维度"/>
       <sheetName val="普通攻击"/>
-      <sheetName val="伤害计算宏"/>
     </sheetNames>
     <definedNames>
       <definedName name="CALC_DMG"/>
@@ -1934,7 +1933,6 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2275,71 +2273,71 @@
     </row>
     <row r="3" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="87"/>
-      <c r="S3" s="87"/>
-      <c r="T3" s="87"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="90" t="s">
+      <c r="W3" s="86" t="s">
         <v>215</v>
       </c>
-      <c r="X3" s="91"/>
-      <c r="Y3" s="91"/>
-      <c r="Z3" s="91"/>
-      <c r="AA3" s="90" t="s">
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="86" t="s">
         <v>216</v>
       </c>
-      <c r="AB3" s="91"/>
-      <c r="AC3" s="91"/>
-      <c r="AD3" s="91"/>
-      <c r="AE3" s="90" t="s">
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="86" t="s">
         <v>217</v>
       </c>
-      <c r="AF3" s="91"/>
-      <c r="AG3" s="91"/>
-      <c r="AH3" s="91"/>
-      <c r="AJ3" s="84" t="s">
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AJ3" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" s="84"/>
-      <c r="AL3" s="84"/>
-      <c r="AM3" s="84"/>
-      <c r="AN3" s="84"/>
-      <c r="AO3" s="84"/>
-      <c r="AP3" s="84"/>
-      <c r="AQ3" s="84"/>
-      <c r="AR3" s="84"/>
-      <c r="AS3" s="84"/>
-      <c r="AT3" s="84"/>
-      <c r="AV3" s="86" t="s">
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="88"/>
+      <c r="AM3" s="88"/>
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88"/>
+      <c r="AS3" s="88"/>
+      <c r="AT3" s="88"/>
+      <c r="AV3" s="90" t="s">
         <v>234</v>
       </c>
-      <c r="AW3" s="87"/>
-      <c r="AX3" s="87"/>
-      <c r="AY3" s="87"/>
-      <c r="AZ3" s="87"/>
-      <c r="BA3" s="87"/>
-      <c r="BB3" s="87"/>
-      <c r="BC3" s="87"/>
-      <c r="BD3" s="87"/>
-      <c r="BE3" s="87"/>
-      <c r="BF3" s="87"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
+      <c r="AY3" s="85"/>
+      <c r="AZ3" s="85"/>
+      <c r="BA3" s="85"/>
+      <c r="BB3" s="85"/>
+      <c r="BC3" s="85"/>
+      <c r="BD3" s="85"/>
+      <c r="BE3" s="85"/>
+      <c r="BF3" s="85"/>
     </row>
     <row r="4" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
@@ -2398,28 +2396,28 @@
       <c r="AF4" s="71"/>
       <c r="AG4" s="71"/>
       <c r="AH4" s="71"/>
-      <c r="AJ4" s="85"/>
-      <c r="AK4" s="85"/>
-      <c r="AL4" s="85"/>
-      <c r="AM4" s="85"/>
-      <c r="AN4" s="85"/>
-      <c r="AO4" s="85"/>
-      <c r="AP4" s="85"/>
-      <c r="AQ4" s="85"/>
-      <c r="AR4" s="85"/>
-      <c r="AS4" s="85"/>
-      <c r="AT4" s="85"/>
-      <c r="AV4" s="85"/>
-      <c r="AW4" s="85"/>
-      <c r="AX4" s="85"/>
-      <c r="AY4" s="85"/>
-      <c r="AZ4" s="85"/>
-      <c r="BA4" s="85"/>
-      <c r="BB4" s="85"/>
-      <c r="BC4" s="85"/>
-      <c r="BD4" s="85"/>
-      <c r="BE4" s="85"/>
-      <c r="BF4" s="85"/>
+      <c r="AJ4" s="89"/>
+      <c r="AK4" s="89"/>
+      <c r="AL4" s="89"/>
+      <c r="AM4" s="89"/>
+      <c r="AN4" s="89"/>
+      <c r="AO4" s="89"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="89"/>
+      <c r="AR4" s="89"/>
+      <c r="AS4" s="89"/>
+      <c r="AT4" s="89"/>
+      <c r="AV4" s="89"/>
+      <c r="AW4" s="89"/>
+      <c r="AX4" s="89"/>
+      <c r="AY4" s="89"/>
+      <c r="AZ4" s="89"/>
+      <c r="BA4" s="89"/>
+      <c r="BB4" s="89"/>
+      <c r="BC4" s="89"/>
+      <c r="BD4" s="89"/>
+      <c r="BE4" s="89"/>
+      <c r="BF4" s="89"/>
     </row>
     <row r="5" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
@@ -2584,7 +2582,7 @@
       </c>
     </row>
     <row r="6" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="88">
+      <c r="B6" s="84">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2788,7 +2786,7 @@
       </c>
     </row>
     <row r="7" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="88"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2990,7 +2988,7 @@
       </c>
     </row>
     <row r="8" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="88">
+      <c r="B8" s="84">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3194,7 +3192,7 @@
       </c>
     </row>
     <row r="9" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="88"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3396,7 +3394,7 @@
       </c>
     </row>
     <row r="10" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="89">
+      <c r="B10" s="91">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3600,7 +3598,7 @@
       </c>
     </row>
     <row r="11" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="89"/>
+      <c r="B11" s="91"/>
       <c r="X11" s="76"/>
       <c r="Z11" s="76"/>
       <c r="AB11" s="76"/>
@@ -3615,7 +3613,7 @@
       <c r="BF11" s="76"/>
     </row>
     <row r="12" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="89"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3748,21 +3746,21 @@
         <f t="shared" ref="AN12:AN14" si="29">AL12*(1+(0.02*AM12))</f>
         <v>20</v>
       </c>
-      <c r="AO12" s="20" t="e">
-        <f ca="1">CALC_DMG(Q12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(Q12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(Q12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AP12" s="75" t="e">
-        <f ca="1">AK12/AO12</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AQ12" s="20" t="e">
-        <f ca="1">CALC_DMG(R12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(R12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(R12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AR12" s="75" t="e">
-        <f ca="1">AK12/AQ12</f>
-        <v>#NAME?</v>
+      <c r="AO12" s="20">
+        <f>[1]!CALC_DMG(Q12*$AK$1,AN12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AN12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
+        <v>586.50160000000005</v>
+      </c>
+      <c r="AP12" s="75">
+        <f>AK12/AO12</f>
+        <v>1.3640201493056454</v>
+      </c>
+      <c r="AQ12" s="20">
+        <f>[1]!CALC_DMG(R12*$AK$1,AN12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AN12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
+        <v>409.74700000000001</v>
+      </c>
+      <c r="AR12" s="75">
+        <f>AK12/AQ12</f>
+        <v>1.9524243008490605</v>
       </c>
       <c r="AS12" s="20">
         <f>CALC_DMG(S12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(S12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(S12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
@@ -3791,21 +3789,21 @@
         <f t="shared" ref="AZ12:AZ14" si="33">AX12*(1+(0.02*AY12))</f>
         <v>12</v>
       </c>
-      <c r="BA12" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BB12" s="75" t="e">
-        <f t="shared" ref="BB12:BB14" ca="1" si="34">AW12/BA12</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BC12" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BD12" s="75" t="e">
-        <f t="shared" ref="BD12:BD14" ca="1" si="35">AW12/BC12</f>
-        <v>#NAME?</v>
+      <c r="BA12" s="20">
+        <f>[1]!CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>658.50159999999994</v>
+      </c>
+      <c r="BB12" s="75">
+        <f t="shared" ref="BB12:BB14" si="34">AW12/BA12</f>
+        <v>0.7289276138433074</v>
+      </c>
+      <c r="BC12" s="20">
+        <f>[1]!CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>481.74700000000001</v>
+      </c>
+      <c r="BD12" s="75">
+        <f t="shared" ref="BD12:BD14" si="35">AW12/BC12</f>
+        <v>0.99637361519635825</v>
       </c>
       <c r="BE12" s="20">
         <f>[1]!CALC_DMG(S12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(S12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(S12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
@@ -3817,7 +3815,7 @@
       </c>
     </row>
     <row r="13" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="88">
+      <c r="B13" s="84">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3952,21 +3950,21 @@
         <f t="shared" si="29"/>
         <v>40</v>
       </c>
-      <c r="AO13" s="20" t="e">
-        <f ca="1">CALC_DMG(Q13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(Q13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(Q13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AP13" s="75" t="e">
-        <f ca="1">AK13/AO13</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AQ13" s="20" t="e">
-        <f ca="1">CALC_DMG(R13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(R13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(R13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AR13" s="75" t="e">
-        <f ca="1">AK13/AQ13</f>
-        <v>#NAME?</v>
+      <c r="AO13" s="20">
+        <f>[1]!CALC_DMG(Q13*$AK$1,AN13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AN13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
+        <v>904.78800000000001</v>
+      </c>
+      <c r="AP13" s="75">
+        <f>AK13/AO13</f>
+        <v>1.2157544087675787</v>
+      </c>
+      <c r="AQ13" s="20">
+        <f>[1]!CALC_DMG(R13*$AK$1,AN13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AN13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
+        <v>602.21399999999994</v>
+      </c>
+      <c r="AR13" s="75">
+        <f>AK13/AQ13</f>
+        <v>1.826593204409064</v>
       </c>
       <c r="AS13" s="20">
         <f>CALC_DMG(S13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(S13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(S13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
@@ -3995,21 +3993,21 @@
         <f t="shared" si="33"/>
         <v>24</v>
       </c>
-      <c r="BA13" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BB13" s="75" t="e">
-        <f t="shared" ca="1" si="34"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="BC13" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BD13" s="75" t="e">
-        <f t="shared" ca="1" si="35"/>
-        <v>#NAME?</v>
+      <c r="BA13" s="20">
+        <f>[1]!CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <v>1048.788</v>
+      </c>
+      <c r="BB13" s="75">
+        <f t="shared" si="34"/>
+        <v>0.62929781805283813</v>
+      </c>
+      <c r="BC13" s="20">
+        <f>[1]!CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <v>746.21399999999994</v>
+      </c>
+      <c r="BD13" s="75">
+        <f t="shared" si="35"/>
+        <v>0.88446477820035552</v>
       </c>
       <c r="BE13" s="20">
         <f>[1]!CALC_DMG(S13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(S13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(S13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
@@ -4021,7 +4019,7 @@
       </c>
     </row>
     <row r="14" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="88"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4154,21 +4152,21 @@
         <f t="shared" si="29"/>
         <v>60</v>
       </c>
-      <c r="AO14" s="20" t="e">
-        <f ca="1">CALC_DMG(Q14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(Q14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(Q14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AP14" s="75" t="e">
-        <f ca="1">AK14/AO14</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AQ14" s="20" t="e">
-        <f ca="1">CALC_DMG(R14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(R14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(R14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AR14" s="75" t="e">
-        <f ca="1">AK14/AQ14</f>
-        <v>#NAME?</v>
+      <c r="AO14" s="20">
+        <f>[1]!CALC_DMG(Q14*$AK$1,AN14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AN14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
+        <v>1514.7213999999999</v>
+      </c>
+      <c r="AP14" s="75">
+        <f>AK14/AO14</f>
+        <v>2.640749645446351</v>
+      </c>
+      <c r="AQ14" s="20">
+        <f>[1]!CALC_DMG(R14*$AK$1,AN14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AN14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
+        <v>1405.1206999999999</v>
+      </c>
+      <c r="AR14" s="75">
+        <f>AK14/AQ14</f>
+        <v>2.8467305335406419</v>
       </c>
       <c r="AS14" s="20">
         <f>CALC_DMG(S14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(S14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(S14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
@@ -4197,21 +4195,21 @@
         <f t="shared" si="33"/>
         <v>36</v>
       </c>
-      <c r="BA14" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BB14" s="75" t="e">
-        <f t="shared" ca="1" si="34"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="BC14" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BD14" s="75" t="e">
-        <f t="shared" ca="1" si="35"/>
-        <v>#NAME?</v>
+      <c r="BA14" s="20">
+        <f>[1]!CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>1730.7213999999999</v>
+      </c>
+      <c r="BB14" s="75">
+        <f t="shared" si="34"/>
+        <v>1.3867049890294303</v>
+      </c>
+      <c r="BC14" s="20">
+        <f>[1]!CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>1621.1206999999999</v>
+      </c>
+      <c r="BD14" s="75">
+        <f t="shared" si="35"/>
+        <v>1.4804573157322587</v>
       </c>
       <c r="BE14" s="20">
         <f>[1]!CALC_DMG(S14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(S14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(S14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
@@ -4237,7 +4235,7 @@
       <c r="BF15" s="76"/>
     </row>
     <row r="16" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="88">
+      <c r="B16" s="84">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4372,21 +4370,21 @@
         <f t="shared" ref="AN16:AN18" si="48">AL16*(1+(0.02*AM16))</f>
         <v>80</v>
       </c>
-      <c r="AO16" s="20" t="e">
-        <f ca="1">CALC_DMG(Q16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(Q16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(Q16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AP16" s="75" t="e">
-        <f ca="1">AK16/AO16</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AQ16" s="20" t="e">
-        <f ca="1">CALC_DMG(R16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(R16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(R16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AR16" s="75" t="e">
-        <f ca="1">AK16/AQ16</f>
-        <v>#NAME?</v>
+      <c r="AO16" s="20">
+        <f>[1]!CALC_DMG(Q16*$AK$1,AN16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AN16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
+        <v>2402.2196000000004</v>
+      </c>
+      <c r="AP16" s="75">
+        <f>AK16/AO16</f>
+        <v>1.8732675397369996</v>
+      </c>
+      <c r="AQ16" s="20">
+        <f>[1]!CALC_DMG(R16*$AK$1,AN16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AN16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
+        <v>1844.9096000000002</v>
+      </c>
+      <c r="AR16" s="75">
+        <f>AK16/AQ16</f>
+        <v>2.4391439016849388</v>
       </c>
       <c r="AS16" s="20">
         <f>CALC_DMG(S16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(S16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(S16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
@@ -4415,21 +4413,21 @@
         <f t="shared" ref="AZ16:AZ18" si="52">AX16*(1+(0.02*AY16))</f>
         <v>48</v>
       </c>
-      <c r="BA16" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BB16" s="75" t="e">
-        <f t="shared" ref="BB16:BB18" ca="1" si="53">AW16/BA16</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BC16" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BD16" s="75" t="e">
-        <f t="shared" ref="BD16:BD18" ca="1" si="54">AW16/BC16</f>
-        <v>#NAME?</v>
+      <c r="BA16" s="20">
+        <f>[1]!CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>2690.2196000000004</v>
+      </c>
+      <c r="BB16" s="75">
+        <f t="shared" ref="BB16:BB18" si="53">AW16/BA16</f>
+        <v>1.0036355396414478</v>
+      </c>
+      <c r="BC16" s="20">
+        <f>[1]!CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>2132.9096</v>
+      </c>
+      <c r="BD16" s="75">
+        <f t="shared" ref="BD16:BD18" si="54">AW16/BC16</f>
+        <v>1.2658764347068436</v>
       </c>
       <c r="BE16" s="20">
         <f>[1]!CALC_DMG(S16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(S16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(S16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
@@ -4441,7 +4439,7 @@
       </c>
     </row>
     <row r="17" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="88"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4574,21 +4572,21 @@
         <f t="shared" si="48"/>
         <v>110</v>
       </c>
-      <c r="AO17" s="20" t="e">
-        <f ca="1">CALC_DMG(Q17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(Q17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(Q17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AP17" s="75" t="e">
-        <f ca="1">AK17/AO17</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AQ17" s="20" t="e">
-        <f ca="1">CALC_DMG(R17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(R17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(R17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AR17" s="75" t="e">
-        <f ca="1">AK17/AQ17</f>
-        <v>#NAME?</v>
+      <c r="AO17" s="20">
+        <f>[1]!CALC_DMG(Q17*$AK$1,AN17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AN17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
+        <v>3607.1171999999997</v>
+      </c>
+      <c r="AP17" s="75">
+        <f>AK17/AO17</f>
+        <v>2.2178375573712992</v>
+      </c>
+      <c r="AQ17" s="20">
+        <f>[1]!CALC_DMG(R17*$AK$1,AN17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AN17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
+        <v>2857.279</v>
+      </c>
+      <c r="AR17" s="75">
+        <f>AK17/AQ17</f>
+        <v>2.7998665863571599</v>
       </c>
       <c r="AS17" s="20">
         <f>CALC_DMG(S17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(S17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(S17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
@@ -4617,21 +4615,21 @@
         <f t="shared" si="52"/>
         <v>66</v>
       </c>
-      <c r="BA17" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BB17" s="75" t="e">
-        <f t="shared" ca="1" si="53"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="BC17" s="20" t="e">
-        <f ca="1">[1]!CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="BD17" s="75" t="e">
-        <f t="shared" ca="1" si="54"/>
-        <v>#NAME?</v>
+      <c r="BA17" s="20">
+        <f>[1]!CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>4003.1171999999997</v>
+      </c>
+      <c r="BB17" s="75">
+        <f t="shared" si="53"/>
+        <v>1.1990655682026998</v>
+      </c>
+      <c r="BC17" s="20">
+        <f>[1]!CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>3253.279</v>
+      </c>
+      <c r="BD17" s="75">
+        <f t="shared" si="54"/>
+        <v>1.4754344770307126</v>
       </c>
       <c r="BE17" s="20">
         <f>[1]!CALC_DMG(S17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(S17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(S17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
@@ -4643,7 +4641,7 @@
       </c>
     </row>
     <row r="18" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4859,7 +4857,7 @@
       <c r="BF19" s="76"/>
     </row>
     <row r="20" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="88">
+      <c r="B20" s="84">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -5063,7 +5061,7 @@
       </c>
     </row>
     <row r="21" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="88"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -5308,11 +5306,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D3:T3"/>
-    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="AJ3:AT4"/>
     <mergeCell ref="AV3:BF4"/>
     <mergeCell ref="B6:B7"/>
@@ -5320,6 +5313,11 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AA3:AD3"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D3:T3"/>
+    <mergeCell ref="W3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5378,57 +5376,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="87" t="s">
+      <c r="V3" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="87"/>
-      <c r="X3" s="87"/>
-      <c r="Y3" s="87"/>
-      <c r="Z3" s="87"/>
-      <c r="AA3" s="87"/>
-      <c r="AB3" s="87"/>
-      <c r="AC3" s="87"/>
-      <c r="AD3" s="87"/>
-      <c r="AE3" s="87"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AI3" s="87"/>
-      <c r="AJ3" s="87"/>
-      <c r="AK3" s="87"/>
-      <c r="AL3" s="87"/>
-      <c r="AM3" s="87"/>
-      <c r="AN3" s="87"/>
-      <c r="AO3" s="87"/>
-      <c r="AP3" s="87"/>
-      <c r="AQ3" s="87"/>
-      <c r="AR3" s="87"/>
-      <c r="AS3" s="87"/>
-      <c r="AT3" s="87"/>
-      <c r="AU3" s="87"/>
-      <c r="AV3" s="87"/>
-      <c r="AW3" s="87"/>
-      <c r="AX3" s="87"/>
-      <c r="AY3" s="87"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="85"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="85"/>
+      <c r="AI3" s="85"/>
+      <c r="AJ3" s="85"/>
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="85"/>
+      <c r="AM3" s="85"/>
+      <c r="AN3" s="85"/>
+      <c r="AO3" s="85"/>
+      <c r="AP3" s="85"/>
+      <c r="AQ3" s="85"/>
+      <c r="AR3" s="85"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
+      <c r="AY3" s="85"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5474,44 +5472,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="85" t="s">
+      <c r="V4" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="85"/>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="85"/>
-      <c r="Z4" s="85"/>
-      <c r="AA4" s="85"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="85" t="s">
+      <c r="AD4" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="85"/>
-      <c r="AF4" s="85"/>
-      <c r="AG4" s="85"/>
+      <c r="AE4" s="89"/>
+      <c r="AF4" s="89"/>
+      <c r="AG4" s="89"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="85" t="s">
+      <c r="AL4" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="85"/>
-      <c r="AN4" s="85"/>
-      <c r="AO4" s="85"/>
-      <c r="AP4" s="85"/>
-      <c r="AQ4" s="85"/>
+      <c r="AM4" s="89"/>
+      <c r="AN4" s="89"/>
+      <c r="AO4" s="89"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="89"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="85" t="s">
+      <c r="AT4" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="85"/>
-      <c r="AV4" s="85"/>
-      <c r="AW4" s="85"/>
-      <c r="AX4" s="85"/>
-      <c r="AY4" s="85"/>
+      <c r="AU4" s="89"/>
+      <c r="AV4" s="89"/>
+      <c r="AW4" s="89"/>
+      <c r="AX4" s="89"/>
+      <c r="AY4" s="89"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5653,7 +5651,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="88">
+      <c r="B6" s="84">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -5817,7 +5815,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="88"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -5979,7 +5977,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="88">
+      <c r="B8" s="84">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -6143,7 +6141,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="88"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -6305,7 +6303,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="89">
+      <c r="B10" s="91">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -6469,10 +6467,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="89"/>
+      <c r="B11" s="91"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="89"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -6634,7 +6632,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="88">
+      <c r="B13" s="84">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -6798,7 +6796,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="88"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -6960,7 +6958,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="88">
+      <c r="B16" s="84">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -7124,7 +7122,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="88"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -7286,7 +7284,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -7448,7 +7446,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="88">
+      <c r="B20" s="84">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -7612,7 +7610,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="88"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -7775,18 +7773,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="V3:AY3"/>
     <mergeCell ref="AT4:AY4"/>
     <mergeCell ref="AL4:AQ4"/>
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7814,30 +7812,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="105" t="s">
+      <c r="E1" s="108" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
       <c r="I1" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K1" s="106" t="s">
+      <c r="K1" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
       <c r="O1" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="Q1" s="107" t="s">
+      <c r="Q1" s="110" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
       <c r="U1" s="39" t="s">
         <v>158</v>
       </c>
@@ -7846,35 +7844,35 @@
       <c r="A2" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="104" t="s">
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104" t="s">
+      <c r="F2" s="126"/>
+      <c r="G2" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="H2" s="104"/>
-      <c r="K2" s="104" t="s">
+      <c r="H2" s="126"/>
+      <c r="K2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104" t="s">
+      <c r="L2" s="126"/>
+      <c r="M2" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="N2" s="104"/>
-      <c r="Q2" s="104" t="s">
+      <c r="N2" s="126"/>
+      <c r="Q2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="R2" s="104"/>
-      <c r="S2" s="104" t="s">
+      <c r="R2" s="126"/>
+      <c r="S2" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="T2" s="104"/>
+      <c r="T2" s="126"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -7887,25 +7885,25 @@
         <v>121</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="102" t="s">
+      <c r="E3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="124" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="95"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="117"/>
       <c r="O3" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="95"/>
-      <c r="U3" s="115" t="s">
+      <c r="Q3" s="115"/>
+      <c r="R3" s="116"/>
+      <c r="S3" s="116"/>
+      <c r="T3" s="117"/>
+      <c r="U3" s="96" t="s">
         <v>155</v>
       </c>
     </row>
@@ -7918,11 +7916,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="103"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="125"/>
       <c r="K4" s="49" t="s">
         <v>132</v>
       </c>
@@ -7931,14 +7929,14 @@
         <v>133</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="110">
+      <c r="O4" s="113">
         <v>0</v>
       </c>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="116"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="97"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -7963,7 +7961,7 @@
       <c r="H5" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="108">
+      <c r="I5" s="111">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -7974,12 +7972,12 @@
         <v>186</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="110"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="101"/>
-      <c r="U5" s="116"/>
+      <c r="O5" s="113"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="97"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -7996,19 +7994,19 @@
         <v>159</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="109"/>
+      <c r="I6" s="112"/>
       <c r="K6" s="48" t="s">
         <v>162</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="110"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="97"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="98"/>
-      <c r="U6" s="116"/>
+      <c r="O6" s="113"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="119"/>
+      <c r="S6" s="119"/>
+      <c r="T6" s="120"/>
+      <c r="U6" s="97"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -8027,7 +8025,7 @@
       <c r="H7" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="I7" s="121">
+      <c r="I7" s="102">
         <v>1</v>
       </c>
       <c r="K7" s="53" t="s">
@@ -8042,7 +8040,7 @@
       <c r="N7" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="O7" s="120">
+      <c r="O7" s="101">
         <v>1</v>
       </c>
       <c r="Q7" s="54"/>
@@ -8074,7 +8072,7 @@
       <c r="F8" s="52"/>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
-      <c r="I8" s="122"/>
+      <c r="I8" s="103"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53" t="s">
         <v>136</v>
@@ -8083,7 +8081,7 @@
         <v>153</v>
       </c>
       <c r="N8" s="51"/>
-      <c r="O8" s="120"/>
+      <c r="O8" s="101"/>
       <c r="Q8" s="33" t="s">
         <v>164</v>
       </c>
@@ -8094,7 +8092,7 @@
       <c r="T8" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="U8" s="117">
+      <c r="U8" s="98">
         <v>2</v>
       </c>
     </row>
@@ -8121,7 +8119,7 @@
       <c r="H9" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="122"/>
+      <c r="I9" s="103"/>
       <c r="K9" s="51" t="s">
         <v>169</v>
       </c>
@@ -8132,7 +8130,7 @@
       <c r="N9" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="120"/>
+      <c r="O9" s="101"/>
       <c r="Q9" s="33" t="s">
         <v>173</v>
       </c>
@@ -8143,7 +8141,7 @@
       <c r="T9" s="83" t="s">
         <v>163</v>
       </c>
-      <c r="U9" s="118"/>
+      <c r="U9" s="99"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
@@ -8160,7 +8158,7 @@
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="118">
+      <c r="I10" s="99">
         <v>2</v>
       </c>
       <c r="K10" s="57" t="s">
@@ -8173,7 +8171,7 @@
       <c r="N10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="O10" s="117">
+      <c r="O10" s="98">
         <v>2</v>
       </c>
       <c r="Q10" s="33"/>
@@ -8184,7 +8182,7 @@
       <c r="T10" s="83" t="s">
         <v>170</v>
       </c>
-      <c r="U10" s="119"/>
+      <c r="U10" s="100"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -8207,14 +8205,14 @@
       <c r="H11" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="118"/>
+      <c r="I11" s="99"/>
       <c r="K11" s="33"/>
       <c r="L11" s="56"/>
       <c r="M11" s="33" t="s">
         <v>176</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="119"/>
+      <c r="O11" s="100"/>
       <c r="Q11" s="61" t="s">
         <v>175</v>
       </c>
@@ -8223,7 +8221,7 @@
         <v>177</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="123">
+      <c r="U11" s="104">
         <v>3</v>
       </c>
     </row>
@@ -8244,14 +8242,14 @@
         <v>178</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="118"/>
+      <c r="I12" s="99"/>
       <c r="K12" s="60"/>
       <c r="L12" s="60"/>
       <c r="M12" s="60" t="s">
         <v>179</v>
       </c>
       <c r="N12" s="60"/>
-      <c r="O12" s="124">
+      <c r="O12" s="105">
         <v>3</v>
       </c>
       <c r="Q12" s="69" t="s">
@@ -8260,7 +8258,7 @@
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="123"/>
+      <c r="U12" s="104"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -8281,7 +8279,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="126">
+      <c r="I13" s="107">
         <v>3</v>
       </c>
       <c r="K13" s="60" t="s">
@@ -8296,7 +8294,7 @@
       <c r="N13" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="O13" s="125"/>
+      <c r="O13" s="106"/>
       <c r="Q13" s="28" t="s">
         <v>183</v>
       </c>
@@ -8305,7 +8303,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="114">
+      <c r="U13" s="95">
         <v>4</v>
       </c>
     </row>
@@ -8326,14 +8324,14 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="126"/>
+      <c r="I14" s="107"/>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
         <v>147</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="112">
+      <c r="O14" s="93">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -8342,7 +8340,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="114"/>
+      <c r="U14" s="95"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -8359,14 +8357,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="125"/>
+      <c r="I15" s="106"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>150</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="113"/>
+      <c r="O15" s="94"/>
       <c r="Q15" s="68" t="s">
         <v>151</v>
       </c>
@@ -8378,10 +8376,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="111" t="s">
+      <c r="C18" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="111"/>
+      <c r="D18" s="92"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -8629,6 +8627,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E3:H4"/>
+    <mergeCell ref="Q3:T6"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="O4:O6"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="O14:O15"/>
     <mergeCell ref="U13:U14"/>
@@ -8641,22 +8655,6 @@
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="I13:I15"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="O4:O6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E3:H4"/>
-    <mergeCell ref="Q3:T6"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8674,32 +8672,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="G1" s="133" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="G1" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -8872,11 +8870,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="130">
+      <c r="F10" s="133">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="111">
+      <c r="G10" s="92">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8896,11 +8894,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="130">
+      <c r="N10" s="133">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="92">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8920,7 +8918,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="134">
+      <c r="V10" s="130">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -8943,8 +8941,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="131"/>
-      <c r="G11" s="111"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="92"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8962,8 +8960,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="131"/>
-      <c r="O11" s="111"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="92"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8981,7 +8979,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="135"/>
+      <c r="V11" s="131"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -9001,8 +8999,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="131"/>
-      <c r="G12" s="111"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="92"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9020,8 +9018,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="131"/>
-      <c r="O12" s="111"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="92"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -9039,7 +9037,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="136"/>
+      <c r="V12" s="132"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -9059,8 +9057,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="132"/>
-      <c r="G13" s="111"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="92"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -9078,8 +9076,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="131"/>
-      <c r="O13" s="111"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="92"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -9099,11 +9097,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="130">
+      <c r="F14" s="133">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="111">
+      <c r="G14" s="92">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9123,8 +9121,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="131"/>
-      <c r="O14" s="111"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="92"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -9144,8 +9142,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="132"/>
-      <c r="G15" s="111"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="92"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9163,8 +9161,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="131"/>
-      <c r="O15" s="111"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="92"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -9195,8 +9193,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="132"/>
-      <c r="O16" s="111"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="92"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -9332,7 +9330,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="134">
+      <c r="N22" s="130">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9372,7 +9370,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="135"/>
+      <c r="N23" s="131"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -9409,7 +9407,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="136"/>
+      <c r="N24" s="132"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -9446,7 +9444,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="134">
+      <c r="N25" s="130">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -9469,7 +9467,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="136"/>
+      <c r="N26" s="132"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -9483,7 +9481,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="137" t="s">
+      <c r="A30" s="135" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="128"/>
@@ -9492,7 +9490,7 @@
       <c r="E30" s="128"/>
       <c r="F30" s="129"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="137" t="s">
+      <c r="I30" s="135" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="128"/>
@@ -9564,11 +9562,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="130">
+      <c r="F32" s="133">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="111">
+      <c r="G32" s="92">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9588,11 +9586,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="130">
+      <c r="N32" s="133">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="111">
+      <c r="O32" s="92">
         <v>4</v>
       </c>
     </row>
@@ -9614,8 +9612,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="131"/>
-      <c r="G33" s="111"/>
+      <c r="F33" s="136"/>
+      <c r="G33" s="92"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9633,8 +9631,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="131"/>
-      <c r="O33" s="111"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="92"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -9654,8 +9652,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="131"/>
-      <c r="G34" s="111"/>
+      <c r="F34" s="136"/>
+      <c r="G34" s="92"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9673,8 +9671,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="131"/>
-      <c r="O34" s="111"/>
+      <c r="N34" s="136"/>
+      <c r="O34" s="92"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -9694,8 +9692,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="132"/>
-      <c r="G35" s="111"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="92"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9713,8 +9711,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="131"/>
-      <c r="O35" s="111"/>
+      <c r="N35" s="136"/>
+      <c r="O35" s="92"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -9734,11 +9732,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="130">
+      <c r="F36" s="133">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="111">
+      <c r="G36" s="92">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9758,8 +9756,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="131"/>
-      <c r="O36" s="111"/>
+      <c r="N36" s="136"/>
+      <c r="O36" s="92"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -9779,8 +9777,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="132"/>
-      <c r="G37" s="111"/>
+      <c r="F37" s="134"/>
+      <c r="G37" s="92"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9798,8 +9796,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="131"/>
-      <c r="O37" s="111"/>
+      <c r="N37" s="136"/>
+      <c r="O37" s="92"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -9830,8 +9828,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="132"/>
-      <c r="O38" s="111"/>
+      <c r="N38" s="134"/>
+      <c r="O38" s="92"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -9961,7 +9959,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="134">
+      <c r="N45" s="130">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -10000,7 +9998,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="135"/>
+      <c r="N46" s="131"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -10036,7 +10034,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="136"/>
+      <c r="N47" s="132"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -10072,7 +10070,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="134">
+      <c r="N48" s="130">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -10094,29 +10092,10 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="136"/>
+      <c r="N49" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -10126,6 +10105,25 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A897DB23-B385-4D90-BE30-D962E851907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20B6B5F-D079-4832-86F8-7BF845ECABC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -21,12 +21,12 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="242">
   <si>
     <t>最终攻击力=面板攻击+横扫之刃+评分等级+杀手附魔</t>
   </si>
@@ -500,10 +500,6 @@
   </si>
   <si>
     <t>末地里</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>冥王星</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -1720,10 +1716,22 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1732,16 +1740,61 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1792,63 +1845,6 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1858,6 +1854,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1867,19 +1875,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1924,6 +1920,7 @@
       <sheetName val="数值分配"/>
       <sheetName val="维度"/>
       <sheetName val="普通攻击"/>
+      <sheetName val="伤害计算宏"/>
     </sheetNames>
     <definedNames>
       <definedName name="CALC_DMG"/>
@@ -1933,6 +1930,7 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2223,10 +2221,10 @@
         <v>20</v>
       </c>
       <c r="AB2" s="72" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AF2" s="72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AI2" s="27">
         <v>0.5</v>
@@ -2244,13 +2242,13 @@
         <v>1</v>
       </c>
       <c r="AP2" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AR2" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AT2" s="72" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AV2" s="8">
         <v>1.2</v>
@@ -2262,82 +2260,82 @@
         <v>0.6</v>
       </c>
       <c r="BB2" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="BD2" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="BD2" s="7" t="s">
-        <v>231</v>
-      </c>
       <c r="BF2" s="72" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="87"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="86" t="s">
+      <c r="W3" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="X3" s="91"/>
+      <c r="Y3" s="91"/>
+      <c r="Z3" s="91"/>
+      <c r="AA3" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="X3" s="87"/>
-      <c r="Y3" s="87"/>
-      <c r="Z3" s="87"/>
-      <c r="AA3" s="86" t="s">
+      <c r="AB3" s="91"/>
+      <c r="AC3" s="91"/>
+      <c r="AD3" s="91"/>
+      <c r="AE3" s="90" t="s">
         <v>216</v>
       </c>
-      <c r="AB3" s="87"/>
-      <c r="AC3" s="87"/>
-      <c r="AD3" s="87"/>
-      <c r="AE3" s="86" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AJ3" s="88" t="s">
+      <c r="AF3" s="91"/>
+      <c r="AG3" s="91"/>
+      <c r="AH3" s="91"/>
+      <c r="AJ3" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" s="88"/>
-      <c r="AL3" s="88"/>
-      <c r="AM3" s="88"/>
-      <c r="AN3" s="88"/>
-      <c r="AO3" s="88"/>
-      <c r="AP3" s="88"/>
-      <c r="AQ3" s="88"/>
-      <c r="AR3" s="88"/>
-      <c r="AS3" s="88"/>
-      <c r="AT3" s="88"/>
-      <c r="AV3" s="90" t="s">
-        <v>234</v>
-      </c>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
-      <c r="AY3" s="85"/>
-      <c r="AZ3" s="85"/>
-      <c r="BA3" s="85"/>
-      <c r="BB3" s="85"/>
-      <c r="BC3" s="85"/>
-      <c r="BD3" s="85"/>
-      <c r="BE3" s="85"/>
-      <c r="BF3" s="85"/>
+      <c r="AK3" s="84"/>
+      <c r="AL3" s="84"/>
+      <c r="AM3" s="84"/>
+      <c r="AN3" s="84"/>
+      <c r="AO3" s="84"/>
+      <c r="AP3" s="84"/>
+      <c r="AQ3" s="84"/>
+      <c r="AR3" s="84"/>
+      <c r="AS3" s="84"/>
+      <c r="AT3" s="84"/>
+      <c r="AV3" s="86" t="s">
+        <v>233</v>
+      </c>
+      <c r="AW3" s="87"/>
+      <c r="AX3" s="87"/>
+      <c r="AY3" s="87"/>
+      <c r="AZ3" s="87"/>
+      <c r="BA3" s="87"/>
+      <c r="BB3" s="87"/>
+      <c r="BC3" s="87"/>
+      <c r="BD3" s="87"/>
+      <c r="BE3" s="87"/>
+      <c r="BF3" s="87"/>
     </row>
     <row r="4" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
@@ -2396,28 +2394,28 @@
       <c r="AF4" s="71"/>
       <c r="AG4" s="71"/>
       <c r="AH4" s="71"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="89"/>
-      <c r="AQ4" s="89"/>
-      <c r="AR4" s="89"/>
-      <c r="AS4" s="89"/>
-      <c r="AT4" s="89"/>
-      <c r="AV4" s="89"/>
-      <c r="AW4" s="89"/>
-      <c r="AX4" s="89"/>
-      <c r="AY4" s="89"/>
-      <c r="AZ4" s="89"/>
-      <c r="BA4" s="89"/>
-      <c r="BB4" s="89"/>
-      <c r="BC4" s="89"/>
-      <c r="BD4" s="89"/>
-      <c r="BE4" s="89"/>
-      <c r="BF4" s="89"/>
+      <c r="AJ4" s="85"/>
+      <c r="AK4" s="85"/>
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="85"/>
+      <c r="AN4" s="85"/>
+      <c r="AO4" s="85"/>
+      <c r="AP4" s="85"/>
+      <c r="AQ4" s="85"/>
+      <c r="AR4" s="85"/>
+      <c r="AS4" s="85"/>
+      <c r="AT4" s="85"/>
+      <c r="AV4" s="85"/>
+      <c r="AW4" s="85"/>
+      <c r="AX4" s="85"/>
+      <c r="AY4" s="85"/>
+      <c r="AZ4" s="85"/>
+      <c r="BA4" s="85"/>
+      <c r="BB4" s="85"/>
+      <c r="BC4" s="85"/>
+      <c r="BD4" s="85"/>
+      <c r="BE4" s="85"/>
+      <c r="BF4" s="85"/>
     </row>
     <row r="5" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
@@ -2443,40 +2441,40 @@
         <v>48</v>
       </c>
       <c r="K5" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="L5" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="N5" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="L5" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="M5" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="N5" s="28" t="s">
+      <c r="O5" s="30" t="s">
         <v>206</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>207</v>
       </c>
       <c r="P5" s="23" t="s">
         <v>66</v>
       </c>
       <c r="Q5" s="61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R5" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="S5" s="61" t="s">
         <v>210</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="T5" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="T5" s="48" t="s">
+      <c r="U5" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="U5" s="48" t="s">
+      <c r="V5" s="48" t="s">
         <v>213</v>
-      </c>
-      <c r="V5" s="48" t="s">
-        <v>214</v>
       </c>
       <c r="W5" s="12" t="s">
         <v>69</v>
@@ -2485,10 +2483,10 @@
         <v>67</v>
       </c>
       <c r="Y5" s="82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Z5" s="79" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AA5" s="15" t="s">
         <v>69</v>
@@ -2497,10 +2495,10 @@
         <v>67</v>
       </c>
       <c r="AC5" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AD5" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AE5" s="22" t="s">
         <v>69</v>
@@ -2509,10 +2507,10 @@
         <v>67</v>
       </c>
       <c r="AG5" s="80" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AH5" s="77" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AJ5" s="12" t="s">
         <v>53</v>
@@ -2530,22 +2528,22 @@
         <v>77</v>
       </c>
       <c r="AO5" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="AP5" s="75" t="s">
+        <v>222</v>
+      </c>
+      <c r="AQ5" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="AP5" s="75" t="s">
+      <c r="AR5" s="75" t="s">
         <v>223</v>
       </c>
-      <c r="AQ5" s="31" t="s">
+      <c r="AS5" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="AR5" s="75" t="s">
+      <c r="AT5" s="75" t="s">
         <v>224</v>
-      </c>
-      <c r="AS5" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="AT5" s="75" t="s">
-        <v>225</v>
       </c>
       <c r="AV5" s="12" t="s">
         <v>53</v>
@@ -2563,26 +2561,26 @@
         <v>77</v>
       </c>
       <c r="BA5" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="BB5" s="75" t="s">
+        <v>222</v>
+      </c>
+      <c r="BC5" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="BB5" s="75" t="s">
+      <c r="BD5" s="75" t="s">
         <v>223</v>
       </c>
-      <c r="BC5" s="31" t="s">
+      <c r="BE5" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="BD5" s="75" t="s">
+      <c r="BF5" s="75" t="s">
         <v>224</v>
       </c>
-      <c r="BE5" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="BF5" s="75" t="s">
-        <v>225</v>
-      </c>
     </row>
     <row r="6" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="84">
+      <c r="B6" s="88">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2650,53 +2648,53 @@
       <c r="V6" s="25">
         <v>1</v>
       </c>
-      <c r="W6" s="12">
-        <f>CALC_DMG(AJ6,T6,$D$2, P6)</f>
-        <v>0.5</v>
-      </c>
-      <c r="X6" s="79">
-        <f>K6/W6</f>
-        <v>44</v>
-      </c>
-      <c r="Y6" s="12">
-        <f>[1]!CALC_DMG(AV6,T6,$D$2, P6)</f>
-        <v>0.8</v>
-      </c>
-      <c r="Z6" s="79">
-        <f>K6/Y6</f>
-        <v>27.5</v>
-      </c>
-      <c r="AA6" s="15">
-        <f>CALC_DMG(AJ6,U6,$D$2,P6)</f>
-        <v>1.5</v>
-      </c>
-      <c r="AB6" s="78">
-        <f>L6/AA6</f>
-        <v>14</v>
-      </c>
-      <c r="AC6" s="15">
-        <f>[1]!CALC_DMG(AV6,U6,$D$2,P6)</f>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AD6" s="78">
-        <f>L6/AC6</f>
-        <v>9.1304347826086971</v>
-      </c>
-      <c r="AE6" s="22">
-        <f>CALC_DMG(AJ6,V6,$D$2,P6)</f>
-        <v>3</v>
-      </c>
-      <c r="AF6" s="77">
-        <f>M6/AE6</f>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="AG6" s="22">
-        <f>[1]!CALC_DMG(AV6,V6,$D$2,P6)</f>
-        <v>3.8</v>
-      </c>
-      <c r="AH6" s="77">
-        <f>M6/AG6</f>
-        <v>5.2631578947368425</v>
+      <c r="W6" s="12" t="e">
+        <f ca="1">CALC_DMG(AJ6,T6,$D$2, P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="X6" s="79" t="e">
+        <f ca="1">K6/W6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y6" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV6,T6,$D$2, P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z6" s="79" t="e">
+        <f ca="1">K6/Y6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA6" s="15" t="e">
+        <f ca="1">CALC_DMG(AJ6,U6,$D$2,P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB6" s="78" t="e">
+        <f ca="1">L6/AA6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC6" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV6,U6,$D$2,P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD6" s="78" t="e">
+        <f ca="1">L6/AC6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE6" s="22" t="e">
+        <f ca="1">CALC_DMG(AJ6,V6,$D$2,P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF6" s="77" t="e">
+        <f ca="1">M6/AE6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG6" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV6,V6,$D$2,P6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH6" s="77" t="e">
+        <f ca="1">M6/AG6</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI6" s="8">
         <v>0</v>
@@ -2717,29 +2715,29 @@
         <f>AL6*(1+(0.02*AM6))</f>
         <v>2</v>
       </c>
-      <c r="AO6" s="20">
-        <f>CALC_DMG(Q6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(Q6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(Q6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
-        <v>16.760159999999999</v>
-      </c>
-      <c r="AP6" s="75">
-        <f>AK6/AO6</f>
-        <v>1.1933060304913559</v>
-      </c>
-      <c r="AQ6" s="20">
-        <f>CALC_DMG(R6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(R6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(R6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
-        <v>10.912800000000001</v>
-      </c>
-      <c r="AR6" s="75">
-        <f>AK6/AQ6</f>
-        <v>1.8327102118613003</v>
-      </c>
-      <c r="AS6" s="20">
-        <f>CALC_DMG(S6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(S6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(S6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
-        <v>7.0399999999999991</v>
-      </c>
-      <c r="AT6" s="75">
-        <f>AK6/AS6</f>
-        <v>2.8409090909090913</v>
+      <c r="AO6" s="20" t="e">
+        <f ca="1">CALC_DMG(Q6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(Q6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(Q6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP6" s="75" t="e">
+        <f ca="1">AK6/AO6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ6" s="20" t="e">
+        <f ca="1">CALC_DMG(R6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(R6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(R6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR6" s="75" t="e">
+        <f ca="1">AK6/AQ6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS6" s="20" t="e">
+        <f ca="1">CALC_DMG(S6*$AK$1,AN6,$AI$2,1)*$AK$2+CALC_DMG(S6*$AL$1,AN6,$AI$2,1)*$AL$2+CALC_DMG(S6*$AM$1,AN6,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT6" s="75" t="e">
+        <f ca="1">AK6/AS6</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV6" s="12">
         <f>AJ6*$AV$2</f>
@@ -2760,33 +2758,33 @@
         <f>AX6*(1+(0.02*AY6))</f>
         <v>1.2</v>
       </c>
-      <c r="BA6" s="20">
-        <f>[1]!CALC_DMG(Q6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
-        <v>23.96</v>
-      </c>
-      <c r="BB6" s="75">
-        <f>AW6/BA6</f>
-        <v>0.5008347245409015</v>
-      </c>
-      <c r="BC6" s="20">
-        <f>[1]!CALC_DMG(R6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(R6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(R6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
-        <v>18.052</v>
-      </c>
-      <c r="BD6" s="75">
-        <f>AW6/BC6</f>
-        <v>0.66474628849988926</v>
-      </c>
-      <c r="BE6" s="20">
-        <f>[1]!CALC_DMG(S6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(S6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(S6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
-        <v>12.144000000000002</v>
-      </c>
-      <c r="BF6" s="75">
-        <f>AW6/BE6</f>
-        <v>0.98814229249011842</v>
+      <c r="BA6" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB6" s="75" t="e">
+        <f ca="1">AW6/BA6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC6" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(R6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(R6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD6" s="75" t="e">
+        <f ca="1">AW6/BC6</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE6" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S6*$AK$1,AZ6,$AI$2,1)*$AK$2+[1]!CALC_DMG(S6*$AL$1,AZ6,$AI$2,1)*$AL$2+[1]!CALC_DMG(S6*$AM$1,AZ6,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF6" s="75" t="e">
+        <f ca="1">AW6/BE6</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="7" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="84"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2852,53 +2850,53 @@
       <c r="V7" s="25">
         <v>3</v>
       </c>
-      <c r="W7" s="12">
-        <f t="shared" ref="W7:W10" si="2">CALC_DMG(AJ7,T7,$D$2, P7)</f>
-        <v>0.5</v>
-      </c>
-      <c r="X7" s="79">
-        <f t="shared" ref="X7:X10" si="3">K7/W7</f>
-        <v>80</v>
-      </c>
-      <c r="Y7" s="12">
-        <f>[1]!CALC_DMG(AV7,T7,$D$2, P7)</f>
-        <v>1.28</v>
-      </c>
-      <c r="Z7" s="79">
-        <f t="shared" ref="Z7:Z10" si="4">K7/Y7</f>
-        <v>31.25</v>
-      </c>
-      <c r="AA7" s="15">
-        <f t="shared" ref="AA7:AA10" si="5">CALC_DMG(AJ7,U7,$D$2,P7)</f>
-        <v>2.34</v>
-      </c>
-      <c r="AB7" s="78">
-        <f t="shared" ref="AB7:AB10" si="6">L7/AA7</f>
-        <v>13.888888888888889</v>
-      </c>
-      <c r="AC7" s="15">
-        <f>[1]!CALC_DMG(AV7,U7,$D$2,P7)</f>
-        <v>3.94</v>
-      </c>
-      <c r="AD7" s="78">
-        <f t="shared" ref="AD7:AD10" si="7">L7/AC7</f>
-        <v>8.2487309644670059</v>
-      </c>
-      <c r="AE7" s="22">
-        <f t="shared" ref="AE7:AE10" si="8">CALC_DMG(AJ7,V7,$D$2,P7)</f>
-        <v>5</v>
-      </c>
-      <c r="AF7" s="77">
-        <f t="shared" ref="AF7:AF21" si="9">M7/AE7</f>
-        <v>5</v>
-      </c>
-      <c r="AG7" s="22">
-        <f>[1]!CALC_DMG(AV7,V7,$D$2,P7)</f>
-        <v>6.6</v>
-      </c>
-      <c r="AH7" s="77">
-        <f t="shared" ref="AH7:AH10" si="10">M7/AG7</f>
-        <v>3.7878787878787881</v>
+      <c r="W7" s="12" t="e">
+        <f t="shared" ref="W7:W10" ca="1" si="2">CALC_DMG(AJ7,T7,$D$2, P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="X7" s="79" t="e">
+        <f t="shared" ref="X7:X10" ca="1" si="3">K7/W7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y7" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV7,T7,$D$2, P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z7" s="79" t="e">
+        <f t="shared" ref="Z7:Z10" ca="1" si="4">K7/Y7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA7" s="15" t="e">
+        <f t="shared" ref="AA7:AA10" ca="1" si="5">CALC_DMG(AJ7,U7,$D$2,P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB7" s="78" t="e">
+        <f t="shared" ref="AB7:AB10" ca="1" si="6">L7/AA7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC7" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV7,U7,$D$2,P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD7" s="78" t="e">
+        <f t="shared" ref="AD7:AD10" ca="1" si="7">L7/AC7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE7" s="22" t="e">
+        <f t="shared" ref="AE7:AE10" ca="1" si="8">CALC_DMG(AJ7,V7,$D$2,P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF7" s="77" t="e">
+        <f t="shared" ref="AF7:AF21" ca="1" si="9">M7/AE7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG7" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV7,V7,$D$2,P7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH7" s="77" t="e">
+        <f t="shared" ref="AH7:AH10" ca="1" si="10">M7/AG7</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI7" s="7" t="s">
         <v>93</v>
@@ -2919,29 +2917,29 @@
         <f>AL7*(1+(0.02*AM7))</f>
         <v>2</v>
       </c>
-      <c r="AO7" s="20">
-        <f>CALC_DMG(Q7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(Q7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(Q7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
-        <v>67.162392000000011</v>
-      </c>
-      <c r="AP7" s="75">
-        <f>AK7/AO7</f>
-        <v>0.67001782783436292</v>
-      </c>
-      <c r="AQ7" s="20">
-        <f>CALC_DMG(R7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(R7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(R7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
-        <v>41.789196000000004</v>
-      </c>
-      <c r="AR7" s="75">
-        <f>AK7/AQ7</f>
-        <v>1.0768333518548669</v>
-      </c>
-      <c r="AS7" s="20">
-        <f>CALC_DMG(S7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(S7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(S7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
-        <v>16.415999999999997</v>
-      </c>
-      <c r="AT7" s="75">
-        <f>AK7/AS7</f>
-        <v>2.7412280701754392</v>
+      <c r="AO7" s="20" t="e">
+        <f ca="1">CALC_DMG(Q7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(Q7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(Q7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP7" s="75" t="e">
+        <f ca="1">AK7/AO7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ7" s="20" t="e">
+        <f ca="1">CALC_DMG(R7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(R7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(R7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR7" s="75" t="e">
+        <f ca="1">AK7/AQ7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS7" s="20" t="e">
+        <f ca="1">CALC_DMG(S7*$AK$1,AN7,$AI$2,1)*$AK$2+CALC_DMG(S7*$AL$1,AN7,$AI$2,1)*$AL$2+CALC_DMG(S7*$AM$1,AN7,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT7" s="75" t="e">
+        <f ca="1">AK7/AS7</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV7" s="12">
         <f t="shared" ref="AV7:AV10" si="11">AJ7*$AV$2</f>
@@ -2962,33 +2960,33 @@
         <f>AX7*(1+(0.02*AY7))</f>
         <v>1.2</v>
       </c>
-      <c r="BA7" s="20">
-        <f>[1]!CALC_DMG(Q7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
-        <v>74.362200000000001</v>
-      </c>
-      <c r="BB7" s="75">
-        <f t="shared" ref="BB7:BB10" si="14">AW7/BA7</f>
-        <v>0.36308769778193761</v>
-      </c>
-      <c r="BC7" s="20">
-        <f>[1]!CALC_DMG(R7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(R7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(R7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
-        <v>48.989100000000001</v>
-      </c>
-      <c r="BD7" s="75">
-        <f t="shared" ref="BD7:BD10" si="15">AW7/BC7</f>
-        <v>0.55114300936330729</v>
-      </c>
-      <c r="BE7" s="20">
-        <f>[1]!CALC_DMG(S7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(S7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(S7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
-        <v>23.616</v>
-      </c>
-      <c r="BF7" s="75">
-        <f t="shared" ref="BF7:BF10" si="16">AW7/BE7</f>
-        <v>1.1432926829268293</v>
+      <c r="BA7" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB7" s="75" t="e">
+        <f t="shared" ref="BB7:BB10" ca="1" si="14">AW7/BA7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC7" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(R7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(R7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD7" s="75" t="e">
+        <f t="shared" ref="BD7:BD10" ca="1" si="15">AW7/BC7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE7" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S7*$AK$1,AZ7,$AI$2,1)*$AK$2+[1]!CALC_DMG(S7*$AL$1,AZ7,$AI$2,1)*$AL$2+[1]!CALC_DMG(S7*$AM$1,AZ7,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF7" s="75" t="e">
+        <f t="shared" ref="BF7:BF10" ca="1" si="16">AW7/BE7</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="8" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="84">
+      <c r="B8" s="88">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3056,53 +3054,53 @@
       <c r="V8" s="25">
         <v>8</v>
       </c>
-      <c r="W8" s="12">
-        <f t="shared" si="2"/>
-        <v>1.7649999999999988</v>
-      </c>
-      <c r="X8" s="79">
-        <f t="shared" si="3"/>
-        <v>56.657223796034032</v>
-      </c>
-      <c r="Y8" s="12">
-        <f>[1]!CALC_DMG(AV8,T8,$D$2, P8)</f>
-        <v>4.71</v>
-      </c>
-      <c r="Z8" s="79">
-        <f t="shared" si="4"/>
-        <v>21.231422505307854</v>
-      </c>
-      <c r="AA8" s="15">
-        <f t="shared" si="5"/>
-        <v>4.2449999999999992</v>
-      </c>
-      <c r="AB8" s="78">
-        <f t="shared" si="6"/>
-        <v>16.489988221436988</v>
-      </c>
-      <c r="AC8" s="15">
-        <f>[1]!CALC_DMG(AV8,U8,$D$2,P8)</f>
-        <v>7.19</v>
-      </c>
-      <c r="AD8" s="78">
-        <f t="shared" si="7"/>
-        <v>9.7357440890125169</v>
-      </c>
-      <c r="AE8" s="22">
-        <f t="shared" si="8"/>
-        <v>6.7249999999999996</v>
-      </c>
-      <c r="AF8" s="77">
-        <f t="shared" si="9"/>
-        <v>5.947955390334573</v>
-      </c>
-      <c r="AG8" s="22">
-        <f>[1]!CALC_DMG(AV8,V8,$D$2,P8)</f>
-        <v>9.67</v>
-      </c>
-      <c r="AH8" s="77">
-        <f t="shared" si="10"/>
-        <v>4.1365046535677354</v>
+      <c r="W8" s="12" t="e">
+        <f t="shared" ca="1" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X8" s="79" t="e">
+        <f t="shared" ca="1" si="3"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y8" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV8,T8,$D$2, P8)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z8" s="79" t="e">
+        <f t="shared" ca="1" si="4"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA8" s="15" t="e">
+        <f t="shared" ca="1" si="5"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB8" s="78" t="e">
+        <f t="shared" ca="1" si="6"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC8" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV8,U8,$D$2,P8)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD8" s="78" t="e">
+        <f t="shared" ca="1" si="7"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE8" s="22" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF8" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG8" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV8,V8,$D$2,P8)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH8" s="77" t="e">
+        <f t="shared" ca="1" si="10"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI8" s="8">
         <v>1</v>
@@ -3123,29 +3121,29 @@
         <f>AL8*(1+(0.02*AM8))</f>
         <v>2</v>
       </c>
-      <c r="AO8" s="20">
-        <f>CALC_DMG(Q8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(Q8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(Q8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
-        <v>127.75176000000002</v>
-      </c>
-      <c r="AP8" s="75">
-        <f>AK8/AO8</f>
-        <v>1.095875313185509</v>
-      </c>
-      <c r="AQ8" s="20">
-        <f>CALC_DMG(R8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(R8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(R8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
-        <v>89.291880000000006</v>
-      </c>
-      <c r="AR8" s="75">
-        <f>AK8/AQ8</f>
-        <v>1.567891727668854</v>
-      </c>
-      <c r="AS8" s="20">
-        <f>CALC_DMG(S8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(S8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(S8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
-        <v>50.831999999999994</v>
-      </c>
-      <c r="AT8" s="75">
-        <f>AK8/AS8</f>
-        <v>2.7541706011960971</v>
+      <c r="AO8" s="20" t="e">
+        <f ca="1">CALC_DMG(Q8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(Q8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(Q8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP8" s="75" t="e">
+        <f ca="1">AK8/AO8</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ8" s="20" t="e">
+        <f ca="1">CALC_DMG(R8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(R8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(R8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR8" s="75" t="e">
+        <f ca="1">AK8/AQ8</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS8" s="20" t="e">
+        <f ca="1">CALC_DMG(S8*$AK$1,AN8,$AI$2,1)*$AK$2+CALC_DMG(S8*$AL$1,AN8,$AI$2,1)*$AL$2+CALC_DMG(S8*$AM$1,AN8,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT8" s="75" t="e">
+        <f ca="1">AK8/AS8</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV8" s="12">
         <f t="shared" si="11"/>
@@ -3166,33 +3164,33 @@
         <f>AX8*(1+(0.02*AY8))</f>
         <v>1.2</v>
       </c>
-      <c r="BA8" s="20">
-        <f>[1]!CALC_DMG(Q8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
-        <v>134.95159999999998</v>
-      </c>
-      <c r="BB8" s="75">
-        <f t="shared" si="14"/>
-        <v>0.62244538041786845</v>
-      </c>
-      <c r="BC8" s="20">
-        <f>[1]!CALC_DMG(R8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(R8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(R8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
-        <v>96.492199999999997</v>
-      </c>
-      <c r="BD8" s="75">
-        <f t="shared" si="15"/>
-        <v>0.87053668586683697</v>
-      </c>
-      <c r="BE8" s="20">
-        <f>[1]!CALC_DMG(S8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(S8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(S8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
-        <v>58.031999999999996</v>
-      </c>
-      <c r="BF8" s="75">
-        <f t="shared" si="16"/>
-        <v>1.4474772539288669</v>
+      <c r="BA8" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB8" s="75" t="e">
+        <f t="shared" ca="1" si="14"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC8" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(R8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(R8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD8" s="75" t="e">
+        <f t="shared" ca="1" si="15"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE8" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S8*$AK$1,AZ8,$AI$2,1)*$AK$2+[1]!CALC_DMG(S8*$AL$1,AZ8,$AI$2,1)*$AL$2+[1]!CALC_DMG(S8*$AM$1,AZ8,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF8" s="75" t="e">
+        <f t="shared" ca="1" si="16"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="9" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="84"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3258,53 +3256,53 @@
       <c r="V9" s="25">
         <v>12</v>
       </c>
-      <c r="W9" s="12">
-        <f t="shared" si="2"/>
-        <v>12.479999999999997</v>
-      </c>
-      <c r="X9" s="79">
-        <f t="shared" si="3"/>
-        <v>16.025641025641029</v>
-      </c>
-      <c r="Y9" s="12">
-        <f>[1]!CALC_DMG(AV9,T9,$D$2, P9)</f>
-        <v>18.559999999999999</v>
-      </c>
-      <c r="Z9" s="79">
-        <f t="shared" si="4"/>
-        <v>10.775862068965518</v>
-      </c>
-      <c r="AA9" s="15">
-        <f t="shared" si="5"/>
-        <v>15.439999999999998</v>
-      </c>
-      <c r="AB9" s="78">
-        <f t="shared" si="6"/>
-        <v>9.7150259067357521</v>
-      </c>
-      <c r="AC9" s="15">
-        <f>[1]!CALC_DMG(AV9,U9,$D$2,P9)</f>
-        <v>21.52</v>
-      </c>
-      <c r="AD9" s="78">
-        <f t="shared" si="7"/>
-        <v>6.970260223048327</v>
-      </c>
-      <c r="AE9" s="22">
-        <f t="shared" si="8"/>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="AF9" s="77">
-        <f t="shared" si="9"/>
-        <v>5.4347826086956523</v>
-      </c>
-      <c r="AG9" s="22">
-        <f>[1]!CALC_DMG(AV9,V9,$D$2,P9)</f>
-        <v>24.48</v>
-      </c>
-      <c r="AH9" s="77">
-        <f t="shared" si="10"/>
-        <v>4.0849673202614376</v>
+      <c r="W9" s="12" t="e">
+        <f t="shared" ca="1" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X9" s="79" t="e">
+        <f t="shared" ca="1" si="3"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y9" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV9,T9,$D$2, P9)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z9" s="79" t="e">
+        <f t="shared" ca="1" si="4"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA9" s="15" t="e">
+        <f t="shared" ca="1" si="5"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB9" s="78" t="e">
+        <f t="shared" ca="1" si="6"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC9" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV9,U9,$D$2,P9)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD9" s="78" t="e">
+        <f t="shared" ca="1" si="7"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE9" s="22" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF9" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG9" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV9,V9,$D$2,P9)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH9" s="77" t="e">
+        <f t="shared" ca="1" si="10"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI9" s="36" t="s">
         <v>92</v>
@@ -3325,29 +3323,29 @@
         <f>AL9*(1+(0.02*AM9))</f>
         <v>6</v>
       </c>
-      <c r="AO9" s="20">
-        <f>CALC_DMG(Q9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(Q9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(Q9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
-        <v>191.73024000000001</v>
-      </c>
-      <c r="AP9" s="75">
-        <f>AK9/AO9</f>
-        <v>1.0952888808776331</v>
-      </c>
-      <c r="AQ9" s="20">
-        <f>CALC_DMG(R9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(R9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(R9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
-        <v>131.96111999999999</v>
-      </c>
-      <c r="AR9" s="75">
-        <f>AK9/AQ9</f>
-        <v>1.5913778240136187</v>
-      </c>
-      <c r="AS9" s="20">
-        <f>CALC_DMG(S9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(S9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(S9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
-        <v>72.192000000000007</v>
-      </c>
-      <c r="AT9" s="75">
-        <f>AK9/AS9</f>
-        <v>2.9089095744680846</v>
+      <c r="AO9" s="20" t="e">
+        <f ca="1">CALC_DMG(Q9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(Q9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(Q9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP9" s="75" t="e">
+        <f ca="1">AK9/AO9</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ9" s="20" t="e">
+        <f ca="1">CALC_DMG(R9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(R9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(R9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR9" s="75" t="e">
+        <f ca="1">AK9/AQ9</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS9" s="20" t="e">
+        <f ca="1">CALC_DMG(S9*$AK$1,AN9,$AI$2,1)*$AK$2+CALC_DMG(S9*$AL$1,AN9,$AI$2,1)*$AL$2+CALC_DMG(S9*$AM$1,AN9,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT9" s="75" t="e">
+        <f ca="1">AK9/AS9</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV9" s="12">
         <f t="shared" si="11"/>
@@ -3368,33 +3366,33 @@
         <f>AX9*(1+(0.02*AY9))</f>
         <v>3.5999999999999996</v>
       </c>
-      <c r="BA9" s="20">
-        <f>[1]!CALC_DMG(Q9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
-        <v>213.3304</v>
-      </c>
-      <c r="BB9" s="75">
-        <f t="shared" si="14"/>
-        <v>0.59063312120541656</v>
-      </c>
-      <c r="BC9" s="20">
-        <f>[1]!CALC_DMG(R9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(R9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(R9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
-        <v>153.56119999999999</v>
-      </c>
-      <c r="BD9" s="75">
-        <f t="shared" si="15"/>
-        <v>0.82051976671190385</v>
-      </c>
-      <c r="BE9" s="20">
-        <f>[1]!CALC_DMG(S9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(S9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(S9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
-        <v>93.792000000000002</v>
-      </c>
-      <c r="BF9" s="75">
-        <f t="shared" si="16"/>
-        <v>1.3433981576253837</v>
+      <c r="BA9" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB9" s="75" t="e">
+        <f t="shared" ca="1" si="14"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC9" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(R9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(R9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD9" s="75" t="e">
+        <f t="shared" ca="1" si="15"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE9" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S9*$AK$1,AZ9,$AI$2,1)*$AK$2+[1]!CALC_DMG(S9*$AL$1,AZ9,$AI$2,1)*$AL$2+[1]!CALC_DMG(S9*$AM$1,AZ9,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF9" s="75" t="e">
+        <f t="shared" ca="1" si="16"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="10" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="91">
+      <c r="B10" s="89">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3462,53 +3460,53 @@
       <c r="V10" s="25">
         <v>17</v>
       </c>
-      <c r="W10" s="12">
-        <f t="shared" si="2"/>
-        <v>19.100000000000005</v>
-      </c>
-      <c r="X10" s="79">
-        <f t="shared" si="3"/>
-        <v>17.801047120418843</v>
-      </c>
-      <c r="Y10" s="12">
-        <f>[1]!CALC_DMG(AV10,T10,$D$2, P10)</f>
-        <v>27.56</v>
-      </c>
-      <c r="Z10" s="79">
-        <f t="shared" si="4"/>
-        <v>12.336719883889696</v>
-      </c>
-      <c r="AA10" s="15">
-        <f t="shared" si="5"/>
-        <v>22.200000000000003</v>
-      </c>
-      <c r="AB10" s="78">
-        <f t="shared" si="6"/>
-        <v>10.360360360360358</v>
-      </c>
-      <c r="AC10" s="15">
-        <f>[1]!CALC_DMG(AV10,U10,$D$2,P10)</f>
-        <v>30.66</v>
-      </c>
-      <c r="AD10" s="78">
-        <f t="shared" si="7"/>
-        <v>7.5016307893020224</v>
-      </c>
-      <c r="AE10" s="22">
-        <f t="shared" si="8"/>
-        <v>25.300000000000004</v>
-      </c>
-      <c r="AF10" s="77">
-        <f t="shared" si="9"/>
-        <v>4.7430830039525684</v>
-      </c>
-      <c r="AG10" s="22">
-        <f>[1]!CALC_DMG(AV10,V10,$D$2,P10)</f>
-        <v>33.76</v>
-      </c>
-      <c r="AH10" s="77">
-        <f t="shared" si="10"/>
-        <v>3.5545023696682465</v>
+      <c r="W10" s="12" t="e">
+        <f t="shared" ca="1" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X10" s="79" t="e">
+        <f t="shared" ca="1" si="3"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y10" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV10,T10,$D$2, P10)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z10" s="79" t="e">
+        <f t="shared" ca="1" si="4"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA10" s="15" t="e">
+        <f t="shared" ca="1" si="5"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB10" s="78" t="e">
+        <f t="shared" ca="1" si="6"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC10" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV10,U10,$D$2,P10)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD10" s="78" t="e">
+        <f t="shared" ca="1" si="7"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE10" s="22" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF10" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG10" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV10,V10,$D$2,P10)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH10" s="77" t="e">
+        <f t="shared" ca="1" si="10"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI10" s="7" t="s">
         <v>92</v>
@@ -3529,29 +3527,29 @@
         <f>AL10*(1+(0.02*AM10))</f>
         <v>10</v>
       </c>
-      <c r="AO10" s="20">
-        <f>CALC_DMG(Q10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(Q10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(Q10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
-        <v>369.33888000000002</v>
-      </c>
-      <c r="AP10" s="75">
-        <f>AK10/AO10</f>
-        <v>0.81226216963673037</v>
-      </c>
-      <c r="AQ10" s="20">
-        <f>CALC_DMG(R10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(R10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(R10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
-        <v>225.70944000000003</v>
-      </c>
-      <c r="AR10" s="75">
-        <f>AK10/AQ10</f>
-        <v>1.3291424585520215</v>
-      </c>
-      <c r="AS10" s="20">
-        <f>CALC_DMG(S10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(S10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(S10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
-        <v>82.08</v>
-      </c>
-      <c r="AT10" s="75">
-        <f>AK10/AS10</f>
-        <v>3.6549707602339181</v>
+      <c r="AO10" s="20" t="e">
+        <f ca="1">CALC_DMG(Q10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(Q10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(Q10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP10" s="75" t="e">
+        <f ca="1">AK10/AO10</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ10" s="20" t="e">
+        <f ca="1">CALC_DMG(R10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(R10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(R10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR10" s="75" t="e">
+        <f ca="1">AK10/AQ10</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS10" s="20" t="e">
+        <f ca="1">CALC_DMG(S10*$AK$1,AN10,$AI$2,1)*$AK$2+CALC_DMG(S10*$AL$1,AN10,$AI$2,1)*$AL$2+CALC_DMG(S10*$AM$1,AN10,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT10" s="75" t="e">
+        <f ca="1">AK10/AS10</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV10" s="12">
         <f t="shared" si="11"/>
@@ -3572,33 +3570,33 @@
         <f>AX10*(1+(0.02*AY10))</f>
         <v>6</v>
       </c>
-      <c r="BA10" s="20">
-        <f>[1]!CALC_DMG(Q10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
-        <v>405.33879999999999</v>
-      </c>
-      <c r="BB10" s="75">
-        <f t="shared" si="14"/>
-        <v>0.44407295822655024</v>
-      </c>
-      <c r="BC10" s="20">
-        <f>[1]!CALC_DMG(R10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(R10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(R10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
-        <v>261.70960000000002</v>
-      </c>
-      <c r="BD10" s="75">
-        <f t="shared" si="15"/>
-        <v>0.68778523982307105</v>
-      </c>
-      <c r="BE10" s="20">
-        <f>[1]!CALC_DMG(S10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(S10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(S10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
-        <v>118.08</v>
-      </c>
-      <c r="BF10" s="75">
-        <f t="shared" si="16"/>
-        <v>1.524390243902439</v>
+      <c r="BA10" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB10" s="75" t="e">
+        <f t="shared" ca="1" si="14"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC10" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(R10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(R10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD10" s="75" t="e">
+        <f t="shared" ca="1" si="15"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE10" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S10*$AK$1,AZ10,$AI$2,1)*$AK$2+[1]!CALC_DMG(S10*$AL$1,AZ10,$AI$2,1)*$AL$2+[1]!CALC_DMG(S10*$AM$1,AZ10,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF10" s="75" t="e">
+        <f t="shared" ca="1" si="16"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="11" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="91"/>
+      <c r="B11" s="89"/>
       <c r="X11" s="76"/>
       <c r="Z11" s="76"/>
       <c r="AB11" s="76"/>
@@ -3613,7 +3611,7 @@
       <c r="BF11" s="76"/>
     </row>
     <row r="12" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="91"/>
+      <c r="B12" s="89"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3679,53 +3677,53 @@
       <c r="V12" s="25">
         <v>20</v>
       </c>
-      <c r="W12" s="12">
-        <f t="shared" ref="W12:W14" si="21">CALC_DMG(AJ12,T12,$D$2, P12)</f>
-        <v>30.299999999999997</v>
-      </c>
-      <c r="X12" s="79">
-        <f t="shared" ref="X12:X14" si="22">K12/W12</f>
-        <v>17.821782178217823</v>
-      </c>
-      <c r="Y12" s="12">
-        <f>[1]!CALC_DMG(AV12,T12,$D$2, P12)</f>
-        <v>45.96</v>
-      </c>
-      <c r="Z12" s="79">
-        <f t="shared" ref="Z12:Z14" si="23">K12/Y12</f>
-        <v>11.74934725848564</v>
-      </c>
-      <c r="AA12" s="15">
-        <f t="shared" ref="AA12:AA14" si="24">CALC_DMG(AJ12,U12,$D$2,P12)</f>
-        <v>44.3</v>
-      </c>
-      <c r="AB12" s="78">
-        <f t="shared" ref="AB12:AB14" si="25">L12/AA12</f>
-        <v>9.4808126410835225</v>
-      </c>
-      <c r="AC12" s="15">
-        <f>[1]!CALC_DMG(AV12,U12,$D$2,P12)</f>
-        <v>59.96</v>
-      </c>
-      <c r="AD12" s="78">
-        <f t="shared" ref="AD12:AD14" si="26">L12/AC12</f>
-        <v>7.0046697798532351</v>
-      </c>
-      <c r="AE12" s="22">
-        <f t="shared" ref="AE12:AE14" si="27">CALC_DMG(AJ12,V12,$D$2,P12)</f>
-        <v>58.3</v>
-      </c>
-      <c r="AF12" s="77">
-        <f t="shared" si="9"/>
-        <v>5.1457975986277873</v>
-      </c>
-      <c r="AG12" s="22">
-        <f>[1]!CALC_DMG(AV12,V12,$D$2,P12)</f>
-        <v>73.959999999999994</v>
-      </c>
-      <c r="AH12" s="77">
-        <f t="shared" ref="AH12:AH14" si="28">M12/AG12</f>
-        <v>4.056246619794484</v>
+      <c r="W12" s="12" t="e">
+        <f t="shared" ref="W12:W14" ca="1" si="21">CALC_DMG(AJ12,T12,$D$2, P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="X12" s="79" t="e">
+        <f t="shared" ref="X12:X14" ca="1" si="22">K12/W12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y12" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV12,T12,$D$2, P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z12" s="79" t="e">
+        <f t="shared" ref="Z12:Z14" ca="1" si="23">K12/Y12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA12" s="15" t="e">
+        <f t="shared" ref="AA12:AA14" ca="1" si="24">CALC_DMG(AJ12,U12,$D$2,P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB12" s="78" t="e">
+        <f t="shared" ref="AB12:AB14" ca="1" si="25">L12/AA12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC12" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV12,U12,$D$2,P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD12" s="78" t="e">
+        <f t="shared" ref="AD12:AD14" ca="1" si="26">L12/AC12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE12" s="22" t="e">
+        <f t="shared" ref="AE12:AE14" ca="1" si="27">CALC_DMG(AJ12,V12,$D$2,P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF12" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG12" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV12,V12,$D$2,P12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH12" s="77" t="e">
+        <f t="shared" ref="AH12:AH14" ca="1" si="28">M12/AG12</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI12" s="7" t="s">
         <v>92</v>
@@ -3746,29 +3744,29 @@
         <f t="shared" ref="AN12:AN14" si="29">AL12*(1+(0.02*AM12))</f>
         <v>20</v>
       </c>
-      <c r="AO12" s="20">
-        <f>[1]!CALC_DMG(Q12*$AK$1,AN12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AN12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
-        <v>586.50160000000005</v>
-      </c>
-      <c r="AP12" s="75">
-        <f>AK12/AO12</f>
-        <v>1.3640201493056454</v>
-      </c>
-      <c r="AQ12" s="20">
-        <f>[1]!CALC_DMG(R12*$AK$1,AN12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AN12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
-        <v>409.74700000000001</v>
-      </c>
-      <c r="AR12" s="75">
-        <f>AK12/AQ12</f>
-        <v>1.9524243008490605</v>
-      </c>
-      <c r="AS12" s="20">
-        <f>CALC_DMG(S12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(S12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(S12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
-        <v>232.99199999999996</v>
-      </c>
-      <c r="AT12" s="75">
-        <f>AK12/AS12</f>
-        <v>3.4335942864991078</v>
+      <c r="AO12" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q12*$AK$1,AN12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AN12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP12" s="75" t="e">
+        <f ca="1">AK12/AO12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ12" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R12*$AK$1,AN12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AN12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR12" s="75" t="e">
+        <f ca="1">AK12/AQ12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS12" s="20" t="e">
+        <f ca="1">CALC_DMG(S12*$AK$1,AN12,$AI$2,1)*$AK$2+CALC_DMG(S12*$AL$1,AN12,$AI$2,1)*$AL$2+CALC_DMG(S12*$AM$1,AN12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT12" s="75" t="e">
+        <f ca="1">AK12/AS12</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV12" s="12">
         <f t="shared" ref="AV12:AV14" si="30">AJ12*$AV$2</f>
@@ -3789,33 +3787,33 @@
         <f t="shared" ref="AZ12:AZ14" si="33">AX12*(1+(0.02*AY12))</f>
         <v>12</v>
       </c>
-      <c r="BA12" s="20">
-        <f>[1]!CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>658.50159999999994</v>
-      </c>
-      <c r="BB12" s="75">
-        <f t="shared" ref="BB12:BB14" si="34">AW12/BA12</f>
-        <v>0.7289276138433074</v>
-      </c>
-      <c r="BC12" s="20">
-        <f>[1]!CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>481.74700000000001</v>
-      </c>
-      <c r="BD12" s="75">
-        <f t="shared" ref="BD12:BD14" si="35">AW12/BC12</f>
-        <v>0.99637361519635825</v>
-      </c>
-      <c r="BE12" s="20">
-        <f>[1]!CALC_DMG(S12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(S12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(S12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
-        <v>304.99200000000002</v>
-      </c>
-      <c r="BF12" s="75">
-        <f t="shared" ref="BF12:BF14" si="36">AW12/BE12</f>
-        <v>1.5738117721120553</v>
+      <c r="BA12" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB12" s="75" t="e">
+        <f t="shared" ref="BB12:BB14" ca="1" si="34">AW12/BA12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC12" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(R12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(R12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD12" s="75" t="e">
+        <f t="shared" ref="BD12:BD14" ca="1" si="35">AW12/BC12</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE12" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S12*$AK$1,AZ12,$AI$2,1)*$AK$2+[1]!CALC_DMG(S12*$AL$1,AZ12,$AI$2,1)*$AL$2+[1]!CALC_DMG(S12*$AM$1,AZ12,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF12" s="75" t="e">
+        <f t="shared" ref="BF12:BF14" ca="1" si="36">AW12/BE12</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="13" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="84">
+      <c r="B13" s="88">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3883,53 +3881,53 @@
       <c r="V13" s="25">
         <v>42</v>
       </c>
-      <c r="W13" s="12">
-        <f t="shared" si="21"/>
-        <v>46.45</v>
-      </c>
-      <c r="X13" s="79">
-        <f t="shared" si="22"/>
-        <v>15.931108719052745</v>
-      </c>
-      <c r="Y13" s="12">
-        <f>[1]!CALC_DMG(AV13,T13,$D$2, P13)</f>
-        <v>71.099999999999994</v>
-      </c>
-      <c r="Z13" s="79">
-        <f t="shared" si="23"/>
-        <v>10.407876230661042</v>
-      </c>
-      <c r="AA13" s="15">
-        <f t="shared" si="24"/>
-        <v>63.85</v>
-      </c>
-      <c r="AB13" s="78">
-        <f t="shared" si="25"/>
-        <v>9.7102584181675802</v>
-      </c>
-      <c r="AC13" s="15">
-        <f>[1]!CALC_DMG(AV13,U13,$D$2,P13)</f>
-        <v>88.5</v>
-      </c>
-      <c r="AD13" s="78">
-        <f t="shared" si="26"/>
-        <v>7.0056497175141246</v>
-      </c>
-      <c r="AE13" s="22">
-        <f t="shared" si="27"/>
-        <v>81.25</v>
-      </c>
-      <c r="AF13" s="77">
-        <f t="shared" si="9"/>
-        <v>6.1538461538461542</v>
-      </c>
-      <c r="AG13" s="22">
-        <f>[1]!CALC_DMG(AV13,V13,$D$2,P13)</f>
-        <v>105.9</v>
-      </c>
-      <c r="AH13" s="77">
-        <f t="shared" si="28"/>
-        <v>4.7214353163361658</v>
+      <c r="W13" s="12" t="e">
+        <f t="shared" ca="1" si="21"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X13" s="79" t="e">
+        <f t="shared" ca="1" si="22"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y13" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV13,T13,$D$2, P13)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z13" s="79" t="e">
+        <f t="shared" ca="1" si="23"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA13" s="15" t="e">
+        <f t="shared" ca="1" si="24"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB13" s="78" t="e">
+        <f t="shared" ca="1" si="25"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC13" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV13,U13,$D$2,P13)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD13" s="78" t="e">
+        <f t="shared" ca="1" si="26"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE13" s="22" t="e">
+        <f t="shared" ca="1" si="27"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF13" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG13" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV13,V13,$D$2,P13)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH13" s="77" t="e">
+        <f t="shared" ca="1" si="28"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI13" s="8">
         <v>2</v>
@@ -3950,29 +3948,29 @@
         <f t="shared" si="29"/>
         <v>40</v>
       </c>
-      <c r="AO13" s="20">
-        <f>[1]!CALC_DMG(Q13*$AK$1,AN13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AN13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
-        <v>904.78800000000001</v>
-      </c>
-      <c r="AP13" s="75">
-        <f>AK13/AO13</f>
-        <v>1.2157544087675787</v>
-      </c>
-      <c r="AQ13" s="20">
-        <f>[1]!CALC_DMG(R13*$AK$1,AN13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AN13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
-        <v>602.21399999999994</v>
-      </c>
-      <c r="AR13" s="75">
-        <f>AK13/AQ13</f>
-        <v>1.826593204409064</v>
-      </c>
-      <c r="AS13" s="20">
-        <f>CALC_DMG(S13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(S13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(S13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
-        <v>299.64</v>
-      </c>
-      <c r="AT13" s="75">
-        <f>AK13/AS13</f>
-        <v>3.6710719530102791</v>
+      <c r="AO13" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q13*$AK$1,AN13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AN13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP13" s="75" t="e">
+        <f ca="1">AK13/AO13</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ13" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R13*$AK$1,AN13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AN13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR13" s="75" t="e">
+        <f ca="1">AK13/AQ13</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS13" s="20" t="e">
+        <f ca="1">CALC_DMG(S13*$AK$1,AN13,$AI$2,1)*$AK$2+CALC_DMG(S13*$AL$1,AN13,$AI$2,1)*$AL$2+CALC_DMG(S13*$AM$1,AN13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT13" s="75" t="e">
+        <f ca="1">AK13/AS13</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV13" s="12">
         <f t="shared" si="30"/>
@@ -3993,33 +3991,33 @@
         <f t="shared" si="33"/>
         <v>24</v>
       </c>
-      <c r="BA13" s="20">
-        <f>[1]!CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
-        <v>1048.788</v>
-      </c>
-      <c r="BB13" s="75">
-        <f t="shared" si="34"/>
-        <v>0.62929781805283813</v>
-      </c>
-      <c r="BC13" s="20">
-        <f>[1]!CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
-        <v>746.21399999999994</v>
-      </c>
-      <c r="BD13" s="75">
-        <f t="shared" si="35"/>
-        <v>0.88446477820035552</v>
-      </c>
-      <c r="BE13" s="20">
-        <f>[1]!CALC_DMG(S13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(S13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(S13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
-        <v>443.64</v>
-      </c>
-      <c r="BF13" s="75">
-        <f t="shared" si="36"/>
-        <v>1.4876927238301325</v>
+      <c r="BA13" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB13" s="75" t="e">
+        <f t="shared" ca="1" si="34"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC13" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(R13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(R13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD13" s="75" t="e">
+        <f t="shared" ca="1" si="35"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE13" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S13*$AK$1,AZ13,$AI$2,1)*$AK$2+[1]!CALC_DMG(S13*$AL$1,AZ13,$AI$2,1)*$AL$2+[1]!CALC_DMG(S13*$AM$1,AZ13,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF13" s="75" t="e">
+        <f t="shared" ca="1" si="36"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="14" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="84"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4085,53 +4083,53 @@
       <c r="V14" s="25">
         <v>70</v>
       </c>
-      <c r="W14" s="12">
-        <f t="shared" si="21"/>
-        <v>73.950000000000017</v>
-      </c>
-      <c r="X14" s="79">
-        <f t="shared" si="22"/>
-        <v>13.522650439486137</v>
-      </c>
-      <c r="Y14" s="12">
-        <f>[1]!CALC_DMG(AV14,T14,$D$2, P14)</f>
-        <v>110.5</v>
-      </c>
-      <c r="Z14" s="79">
-        <f t="shared" si="23"/>
-        <v>9.0497737556561084</v>
-      </c>
-      <c r="AA14" s="15">
-        <f t="shared" si="24"/>
-        <v>93.350000000000009</v>
-      </c>
-      <c r="AB14" s="78">
-        <f t="shared" si="25"/>
-        <v>9.1055168719871435</v>
-      </c>
-      <c r="AC14" s="15">
-        <f>[1]!CALC_DMG(AV14,U14,$D$2,P14)</f>
-        <v>129.9</v>
-      </c>
-      <c r="AD14" s="78">
-        <f t="shared" si="26"/>
-        <v>6.5434949961508853</v>
-      </c>
-      <c r="AE14" s="22">
-        <f t="shared" si="27"/>
-        <v>112.75</v>
-      </c>
-      <c r="AF14" s="77">
-        <f t="shared" si="9"/>
-        <v>6.2084257206208422</v>
-      </c>
-      <c r="AG14" s="22">
-        <f>[1]!CALC_DMG(AV14,V14,$D$2,P14)</f>
-        <v>149.30000000000001</v>
-      </c>
-      <c r="AH14" s="77">
-        <f t="shared" si="28"/>
-        <v>4.6885465505693231</v>
+      <c r="W14" s="12" t="e">
+        <f t="shared" ca="1" si="21"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X14" s="79" t="e">
+        <f t="shared" ca="1" si="22"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y14" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV14,T14,$D$2, P14)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z14" s="79" t="e">
+        <f t="shared" ca="1" si="23"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA14" s="15" t="e">
+        <f t="shared" ca="1" si="24"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB14" s="78" t="e">
+        <f t="shared" ca="1" si="25"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC14" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV14,U14,$D$2,P14)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD14" s="78" t="e">
+        <f t="shared" ca="1" si="26"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE14" s="22" t="e">
+        <f t="shared" ca="1" si="27"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF14" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG14" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV14,V14,$D$2,P14)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH14" s="77" t="e">
+        <f t="shared" ca="1" si="28"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI14" s="7" t="s">
         <v>94</v>
@@ -4152,29 +4150,29 @@
         <f t="shared" si="29"/>
         <v>60</v>
       </c>
-      <c r="AO14" s="20">
-        <f>[1]!CALC_DMG(Q14*$AK$1,AN14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AN14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
-        <v>1514.7213999999999</v>
-      </c>
-      <c r="AP14" s="75">
-        <f>AK14/AO14</f>
-        <v>2.640749645446351</v>
-      </c>
-      <c r="AQ14" s="20">
-        <f>[1]!CALC_DMG(R14*$AK$1,AN14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AN14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
-        <v>1405.1206999999999</v>
-      </c>
-      <c r="AR14" s="75">
-        <f>AK14/AQ14</f>
-        <v>2.8467305335406419</v>
-      </c>
-      <c r="AS14" s="20">
-        <f>CALC_DMG(S14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(S14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(S14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
-        <v>1295.52</v>
-      </c>
-      <c r="AT14" s="75">
-        <f>AK14/AS14</f>
-        <v>3.0875632950475485</v>
+      <c r="AO14" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q14*$AK$1,AN14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AN14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP14" s="75" t="e">
+        <f ca="1">AK14/AO14</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ14" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R14*$AK$1,AN14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AN14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR14" s="75" t="e">
+        <f ca="1">AK14/AQ14</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS14" s="20" t="e">
+        <f ca="1">CALC_DMG(S14*$AK$1,AN14,$AI$2,1)*$AK$2+CALC_DMG(S14*$AL$1,AN14,$AI$2,1)*$AL$2+CALC_DMG(S14*$AM$1,AN14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT14" s="75" t="e">
+        <f ca="1">AK14/AS14</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV14" s="12">
         <f t="shared" si="30"/>
@@ -4195,29 +4193,29 @@
         <f t="shared" si="33"/>
         <v>36</v>
       </c>
-      <c r="BA14" s="20">
-        <f>[1]!CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>1730.7213999999999</v>
-      </c>
-      <c r="BB14" s="75">
-        <f t="shared" si="34"/>
-        <v>1.3867049890294303</v>
-      </c>
-      <c r="BC14" s="20">
-        <f>[1]!CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>1621.1206999999999</v>
-      </c>
-      <c r="BD14" s="75">
-        <f t="shared" si="35"/>
-        <v>1.4804573157322587</v>
-      </c>
-      <c r="BE14" s="20">
-        <f>[1]!CALC_DMG(S14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(S14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(S14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
-        <v>1511.52</v>
-      </c>
-      <c r="BF14" s="75">
-        <f t="shared" si="36"/>
-        <v>1.5878056525881232</v>
+      <c r="BA14" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB14" s="75" t="e">
+        <f t="shared" ca="1" si="34"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC14" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(R14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(R14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD14" s="75" t="e">
+        <f t="shared" ca="1" si="35"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE14" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S14*$AK$1,AZ14,$AI$2,1)*$AK$2+[1]!CALC_DMG(S14*$AL$1,AZ14,$AI$2,1)*$AL$2+[1]!CALC_DMG(S14*$AM$1,AZ14,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF14" s="75" t="e">
+        <f t="shared" ca="1" si="36"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="15" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -4235,7 +4233,7 @@
       <c r="BF15" s="76"/>
     </row>
     <row r="16" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="84">
+      <c r="B16" s="88">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4303,53 +4301,53 @@
       <c r="V16" s="25">
         <v>95</v>
       </c>
-      <c r="W16" s="12">
-        <f t="shared" ref="W16:W18" si="40">CALC_DMG(AJ16,T16,$D$2, P16)</f>
-        <v>92.800000000000011</v>
-      </c>
-      <c r="X16" s="79">
-        <f t="shared" ref="X16:X18" si="41">K16/W16</f>
-        <v>14.008620689655171</v>
-      </c>
-      <c r="Y16" s="12">
-        <f>[1]!CALC_DMG(AV16,T16,$D$2, P16)</f>
-        <v>144.80000000000001</v>
-      </c>
-      <c r="Z16" s="79">
-        <f t="shared" ref="Z16:Z18" si="42">K16/Y16</f>
-        <v>8.9779005524861866</v>
-      </c>
-      <c r="AA16" s="15">
-        <f t="shared" ref="AA16:AA18" si="43">CALC_DMG(AJ16,U16,$D$2,P16)</f>
-        <v>128.9</v>
-      </c>
-      <c r="AB16" s="78">
-        <f t="shared" ref="AB16:AB18" si="44">L16/AA16</f>
-        <v>8.9216446858029474</v>
-      </c>
-      <c r="AC16" s="15">
-        <f>[1]!CALC_DMG(AV16,U16,$D$2,P16)</f>
-        <v>180.9</v>
-      </c>
-      <c r="AD16" s="78">
-        <f t="shared" ref="AD16:AD18" si="45">L16/AC16</f>
-        <v>6.3571033720287451</v>
-      </c>
-      <c r="AE16" s="22">
-        <f t="shared" ref="AE16:AE18" si="46">CALC_DMG(AJ16,V16,$D$2,P16)</f>
-        <v>165</v>
-      </c>
-      <c r="AF16" s="77">
-        <f t="shared" si="9"/>
-        <v>6.0606060606060606</v>
-      </c>
-      <c r="AG16" s="22">
-        <f>[1]!CALC_DMG(AV16,V16,$D$2,P16)</f>
-        <v>217</v>
-      </c>
-      <c r="AH16" s="77">
-        <f t="shared" ref="AH16:AH18" si="47">M16/AG16</f>
-        <v>4.6082949308755756</v>
+      <c r="W16" s="12" t="e">
+        <f t="shared" ref="W16:W18" ca="1" si="40">CALC_DMG(AJ16,T16,$D$2, P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="X16" s="79" t="e">
+        <f t="shared" ref="X16:X18" ca="1" si="41">K16/W16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y16" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV16,T16,$D$2, P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z16" s="79" t="e">
+        <f t="shared" ref="Z16:Z18" ca="1" si="42">K16/Y16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA16" s="15" t="e">
+        <f t="shared" ref="AA16:AA18" ca="1" si="43">CALC_DMG(AJ16,U16,$D$2,P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB16" s="78" t="e">
+        <f t="shared" ref="AB16:AB18" ca="1" si="44">L16/AA16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC16" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV16,U16,$D$2,P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD16" s="78" t="e">
+        <f t="shared" ref="AD16:AD18" ca="1" si="45">L16/AC16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE16" s="22" t="e">
+        <f t="shared" ref="AE16:AE18" ca="1" si="46">CALC_DMG(AJ16,V16,$D$2,P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF16" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG16" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV16,V16,$D$2,P16)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH16" s="77" t="e">
+        <f t="shared" ref="AH16:AH18" ca="1" si="47">M16/AG16</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI16" s="8">
         <v>3</v>
@@ -4370,29 +4368,29 @@
         <f t="shared" ref="AN16:AN18" si="48">AL16*(1+(0.02*AM16))</f>
         <v>80</v>
       </c>
-      <c r="AO16" s="20">
-        <f>[1]!CALC_DMG(Q16*$AK$1,AN16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AN16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
-        <v>2402.2196000000004</v>
-      </c>
-      <c r="AP16" s="75">
-        <f>AK16/AO16</f>
-        <v>1.8732675397369996</v>
-      </c>
-      <c r="AQ16" s="20">
-        <f>[1]!CALC_DMG(R16*$AK$1,AN16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AN16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
-        <v>1844.9096000000002</v>
-      </c>
-      <c r="AR16" s="75">
-        <f>AK16/AQ16</f>
-        <v>2.4391439016849388</v>
-      </c>
-      <c r="AS16" s="20">
-        <f>CALC_DMG(S16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(S16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(S16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
-        <v>1287.5999999999999</v>
-      </c>
-      <c r="AT16" s="75">
-        <f>AK16/AS16</f>
-        <v>3.4948741845293574</v>
+      <c r="AO16" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q16*$AK$1,AN16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AN16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP16" s="75" t="e">
+        <f ca="1">AK16/AO16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ16" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R16*$AK$1,AN16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AN16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR16" s="75" t="e">
+        <f ca="1">AK16/AQ16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS16" s="20" t="e">
+        <f ca="1">CALC_DMG(S16*$AK$1,AN16,$AI$2,1)*$AK$2+CALC_DMG(S16*$AL$1,AN16,$AI$2,1)*$AL$2+CALC_DMG(S16*$AM$1,AN16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT16" s="75" t="e">
+        <f ca="1">AK16/AS16</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV16" s="12">
         <f t="shared" ref="AV16:AV18" si="49">AJ16*$AV$2</f>
@@ -4413,33 +4411,33 @@
         <f t="shared" ref="AZ16:AZ18" si="52">AX16*(1+(0.02*AY16))</f>
         <v>48</v>
       </c>
-      <c r="BA16" s="20">
-        <f>[1]!CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>2690.2196000000004</v>
-      </c>
-      <c r="BB16" s="75">
-        <f t="shared" ref="BB16:BB18" si="53">AW16/BA16</f>
-        <v>1.0036355396414478</v>
-      </c>
-      <c r="BC16" s="20">
-        <f>[1]!CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>2132.9096</v>
-      </c>
-      <c r="BD16" s="75">
-        <f t="shared" ref="BD16:BD18" si="54">AW16/BC16</f>
-        <v>1.2658764347068436</v>
-      </c>
-      <c r="BE16" s="20">
-        <f>[1]!CALC_DMG(S16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(S16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(S16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
-        <v>1575.6</v>
-      </c>
-      <c r="BF16" s="75">
-        <f t="shared" ref="BF16:BF18" si="55">AW16/BE16</f>
-        <v>1.7136329017517138</v>
+      <c r="BA16" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB16" s="75" t="e">
+        <f t="shared" ref="BB16:BB18" ca="1" si="53">AW16/BA16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC16" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(R16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(R16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD16" s="75" t="e">
+        <f t="shared" ref="BD16:BD18" ca="1" si="54">AW16/BC16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE16" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S16*$AK$1,AZ16,$AI$2,1)*$AK$2+[1]!CALC_DMG(S16*$AL$1,AZ16,$AI$2,1)*$AL$2+[1]!CALC_DMG(S16*$AM$1,AZ16,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF16" s="75" t="e">
+        <f t="shared" ref="BF16:BF18" ca="1" si="55">AW16/BE16</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="17" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="84"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4505,53 +4503,53 @@
       <c r="V17" s="25">
         <v>155</v>
       </c>
-      <c r="W17" s="12">
-        <f t="shared" si="40"/>
-        <v>132.79999999999998</v>
-      </c>
-      <c r="X17" s="79">
-        <f t="shared" si="41"/>
-        <v>12.04819277108434</v>
-      </c>
-      <c r="Y17" s="12">
-        <f>[1]!CALC_DMG(AV17,T17,$D$2, P17)</f>
-        <v>206.4</v>
-      </c>
-      <c r="Z17" s="79">
-        <f t="shared" si="42"/>
-        <v>7.7519379844961236</v>
-      </c>
-      <c r="AA17" s="15">
-        <f t="shared" si="43"/>
-        <v>172.89999999999998</v>
-      </c>
-      <c r="AB17" s="78">
-        <f t="shared" si="44"/>
-        <v>8.3863504916136513</v>
-      </c>
-      <c r="AC17" s="15">
-        <f>[1]!CALC_DMG(AV17,U17,$D$2,P17)</f>
-        <v>246.5</v>
-      </c>
-      <c r="AD17" s="78">
-        <f t="shared" si="45"/>
-        <v>5.882352941176471</v>
-      </c>
-      <c r="AE17" s="22">
-        <f t="shared" si="46"/>
-        <v>213</v>
-      </c>
-      <c r="AF17" s="77">
-        <f t="shared" si="9"/>
-        <v>6.103286384976526</v>
-      </c>
-      <c r="AG17" s="22">
-        <f>[1]!CALC_DMG(AV17,V17,$D$2,P17)</f>
-        <v>286.60000000000002</v>
-      </c>
-      <c r="AH17" s="77">
-        <f t="shared" si="47"/>
-        <v>4.5359385903698533</v>
+      <c r="W17" s="12" t="e">
+        <f t="shared" ca="1" si="40"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X17" s="79" t="e">
+        <f t="shared" ca="1" si="41"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y17" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV17,T17,$D$2, P17)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z17" s="79" t="e">
+        <f t="shared" ca="1" si="42"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA17" s="15" t="e">
+        <f t="shared" ca="1" si="43"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB17" s="78" t="e">
+        <f t="shared" ca="1" si="44"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC17" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV17,U17,$D$2,P17)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD17" s="78" t="e">
+        <f t="shared" ca="1" si="45"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE17" s="22" t="e">
+        <f t="shared" ca="1" si="46"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF17" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG17" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV17,V17,$D$2,P17)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH17" s="77" t="e">
+        <f t="shared" ca="1" si="47"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI17" s="7" t="s">
         <v>95</v>
@@ -4572,29 +4570,29 @@
         <f t="shared" si="48"/>
         <v>110</v>
       </c>
-      <c r="AO17" s="20">
-        <f>[1]!CALC_DMG(Q17*$AK$1,AN17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AN17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
-        <v>3607.1171999999997</v>
-      </c>
-      <c r="AP17" s="75">
-        <f>AK17/AO17</f>
-        <v>2.2178375573712992</v>
-      </c>
-      <c r="AQ17" s="20">
-        <f>[1]!CALC_DMG(R17*$AK$1,AN17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AN17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
-        <v>2857.279</v>
-      </c>
-      <c r="AR17" s="75">
-        <f>AK17/AQ17</f>
-        <v>2.7998665863571599</v>
-      </c>
-      <c r="AS17" s="20">
-        <f>CALC_DMG(S17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(S17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(S17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
-        <v>2107.4399999999996</v>
-      </c>
-      <c r="AT17" s="75">
-        <f>AK17/AS17</f>
-        <v>3.7960748585962123</v>
+      <c r="AO17" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q17*$AK$1,AN17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AN17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP17" s="75" t="e">
+        <f ca="1">AK17/AO17</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ17" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R17*$AK$1,AN17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AN17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR17" s="75" t="e">
+        <f ca="1">AK17/AQ17</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS17" s="20" t="e">
+        <f ca="1">CALC_DMG(S17*$AK$1,AN17,$AI$2,1)*$AK$2+CALC_DMG(S17*$AL$1,AN17,$AI$2,1)*$AL$2+CALC_DMG(S17*$AM$1,AN17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT17" s="75" t="e">
+        <f ca="1">AK17/AS17</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV17" s="12">
         <f t="shared" si="49"/>
@@ -4615,33 +4613,33 @@
         <f t="shared" si="52"/>
         <v>66</v>
       </c>
-      <c r="BA17" s="20">
-        <f>[1]!CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>4003.1171999999997</v>
-      </c>
-      <c r="BB17" s="75">
-        <f t="shared" si="53"/>
-        <v>1.1990655682026998</v>
-      </c>
-      <c r="BC17" s="20">
-        <f>[1]!CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>3253.279</v>
-      </c>
-      <c r="BD17" s="75">
-        <f t="shared" si="54"/>
-        <v>1.4754344770307126</v>
-      </c>
-      <c r="BE17" s="20">
-        <f>[1]!CALC_DMG(S17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(S17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(S17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
-        <v>2503.44</v>
-      </c>
-      <c r="BF17" s="75">
-        <f t="shared" si="55"/>
-        <v>1.9173617102866456</v>
+      <c r="BA17" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB17" s="75" t="e">
+        <f t="shared" ca="1" si="53"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC17" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(R17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(R17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD17" s="75" t="e">
+        <f t="shared" ca="1" si="54"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE17" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S17*$AK$1,AZ17,$AI$2,1)*$AK$2+[1]!CALC_DMG(S17*$AL$1,AZ17,$AI$2,1)*$AL$2+[1]!CALC_DMG(S17*$AM$1,AZ17,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF17" s="75" t="e">
+        <f t="shared" ca="1" si="55"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="18" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="84"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4707,53 +4705,53 @@
       <c r="V18" s="25">
         <v>230</v>
       </c>
-      <c r="W18" s="12">
-        <f t="shared" si="40"/>
-        <v>177.2</v>
-      </c>
-      <c r="X18" s="79">
-        <f t="shared" si="41"/>
-        <v>10.72234762979684</v>
-      </c>
-      <c r="Y18" s="12">
-        <f>[1]!CALC_DMG(AV18,T18,$D$2, P18)</f>
-        <v>275.2</v>
-      </c>
-      <c r="Z18" s="79">
-        <f t="shared" si="42"/>
-        <v>6.904069767441861</v>
-      </c>
-      <c r="AA18" s="15">
-        <f t="shared" si="43"/>
-        <v>218.59999999999997</v>
-      </c>
-      <c r="AB18" s="78">
-        <f t="shared" si="44"/>
-        <v>8.005489478499543</v>
-      </c>
-      <c r="AC18" s="15">
-        <f>[1]!CALC_DMG(AV18,U18,$D$2,P18)</f>
-        <v>316.60000000000002</v>
-      </c>
-      <c r="AD18" s="78">
-        <f t="shared" si="45"/>
-        <v>5.5274794693619702</v>
-      </c>
-      <c r="AE18" s="22">
-        <f t="shared" si="46"/>
-        <v>259.99999999999994</v>
-      </c>
-      <c r="AF18" s="77">
-        <f t="shared" si="9"/>
-        <v>6.1538461538461551</v>
-      </c>
-      <c r="AG18" s="22">
-        <f>[1]!CALC_DMG(AV18,V18,$D$2,P18)</f>
-        <v>358</v>
-      </c>
-      <c r="AH18" s="77">
-        <f t="shared" si="47"/>
-        <v>4.4692737430167595</v>
+      <c r="W18" s="12" t="e">
+        <f t="shared" ca="1" si="40"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X18" s="79" t="e">
+        <f t="shared" ca="1" si="41"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y18" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV18,T18,$D$2, P18)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z18" s="79" t="e">
+        <f t="shared" ca="1" si="42"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA18" s="15" t="e">
+        <f t="shared" ca="1" si="43"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB18" s="78" t="e">
+        <f t="shared" ca="1" si="44"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC18" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV18,U18,$D$2,P18)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD18" s="78" t="e">
+        <f t="shared" ca="1" si="45"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE18" s="22" t="e">
+        <f t="shared" ca="1" si="46"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF18" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG18" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV18,V18,$D$2,P18)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH18" s="77" t="e">
+        <f t="shared" ca="1" si="47"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI18" s="7" t="s">
         <v>95</v>
@@ -4774,29 +4772,29 @@
         <f t="shared" si="48"/>
         <v>145</v>
       </c>
-      <c r="AO18" s="20">
-        <f>CALC_DMG(Q18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(Q18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(Q18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
-        <v>5093.6227200000012</v>
-      </c>
-      <c r="AP18" s="75">
-        <f>AK18/AO18</f>
-        <v>2.5522110125973358</v>
-      </c>
-      <c r="AQ18" s="20">
-        <f>CALC_DMG(R18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(R18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(R18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
-        <v>4188.7113600000002</v>
-      </c>
-      <c r="AR18" s="75">
-        <f>AK18/AQ18</f>
-        <v>3.1035798083733321</v>
-      </c>
-      <c r="AS18" s="20">
-        <f>CALC_DMG(S18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(S18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(S18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
-        <v>3283.8</v>
-      </c>
-      <c r="AT18" s="75">
-        <f>AK18/AS18</f>
-        <v>3.9588281868566901</v>
+      <c r="AO18" s="20" t="e">
+        <f ca="1">CALC_DMG(Q18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(Q18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(Q18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP18" s="75" t="e">
+        <f ca="1">AK18/AO18</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ18" s="20" t="e">
+        <f ca="1">CALC_DMG(R18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(R18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(R18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR18" s="75" t="e">
+        <f ca="1">AK18/AQ18</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS18" s="20" t="e">
+        <f ca="1">CALC_DMG(S18*$AK$1,AN18,$AI$2,1)*$AK$2+CALC_DMG(S18*$AL$1,AN18,$AI$2,1)*$AL$2+CALC_DMG(S18*$AM$1,AN18,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT18" s="75" t="e">
+        <f ca="1">AK18/AS18</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV18" s="12">
         <f t="shared" si="49"/>
@@ -4817,29 +4815,29 @@
         <f t="shared" si="52"/>
         <v>87</v>
       </c>
-      <c r="BA18" s="20">
-        <f>[1]!CALC_DMG(Q18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
-        <v>5615.6227999999992</v>
-      </c>
-      <c r="BB18" s="75">
-        <f t="shared" si="53"/>
-        <v>1.3889821802133864</v>
-      </c>
-      <c r="BC18" s="20">
-        <f>[1]!CALC_DMG(R18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(R18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(R18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
-        <v>4710.7112000000006</v>
-      </c>
-      <c r="BD18" s="75">
-        <f t="shared" si="54"/>
-        <v>1.6558009329886321</v>
-      </c>
-      <c r="BE18" s="20">
-        <f>[1]!CALC_DMG(S18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(S18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(S18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
-        <v>3805.8</v>
-      </c>
-      <c r="BF18" s="75">
-        <f t="shared" si="55"/>
-        <v>2.0495033895632981</v>
+      <c r="BA18" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB18" s="75" t="e">
+        <f t="shared" ca="1" si="53"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC18" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(R18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(R18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD18" s="75" t="e">
+        <f t="shared" ca="1" si="54"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE18" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S18*$AK$1,AZ18,$AI$2,1)*$AK$2+[1]!CALC_DMG(S18*$AL$1,AZ18,$AI$2,1)*$AL$2+[1]!CALC_DMG(S18*$AM$1,AZ18,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF18" s="75" t="e">
+        <f t="shared" ca="1" si="55"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="19" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -4857,7 +4855,7 @@
       <c r="BF19" s="76"/>
     </row>
     <row r="20" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="84">
+      <c r="B20" s="88">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4925,53 +4923,53 @@
       <c r="V20" s="25">
         <v>310</v>
       </c>
-      <c r="W20" s="12">
-        <f t="shared" ref="W20:W21" si="59">CALC_DMG(AJ20,T20,$D$2, P20)</f>
-        <v>185.84999999999997</v>
-      </c>
-      <c r="X20" s="79">
-        <f t="shared" ref="X20:X21" si="60">K20/W20</f>
-        <v>10.868980360505786</v>
-      </c>
-      <c r="Y20" s="12">
-        <f>[1]!CALC_DMG(AV20,T20,$D$2, P20)</f>
-        <v>308.7</v>
-      </c>
-      <c r="Z20" s="79">
-        <f t="shared" ref="Z20:Z21" si="61">K20/Y20</f>
-        <v>6.5435698088759313</v>
-      </c>
-      <c r="AA20" s="15">
-        <f t="shared" ref="AA20:AA21" si="62">CALC_DMG(AJ20,U20,$D$2,P20)</f>
-        <v>245.04999999999995</v>
-      </c>
-      <c r="AB20" s="78">
-        <f t="shared" ref="AB20:AB21" si="63">L20/AA20</f>
-        <v>7.9983676800652939</v>
-      </c>
-      <c r="AC20" s="15">
-        <f>[1]!CALC_DMG(AV20,U20,$D$2,P20)</f>
-        <v>367.9</v>
-      </c>
-      <c r="AD20" s="78">
-        <f t="shared" ref="AD20:AD21" si="64">L20/AC20</f>
-        <v>5.3275346561565646</v>
-      </c>
-      <c r="AE20" s="22">
-        <f t="shared" ref="AE20:AE21" si="65">CALC_DMG(AJ20,V20,$D$2,P20)</f>
-        <v>304.25</v>
-      </c>
-      <c r="AF20" s="77">
-        <f t="shared" si="9"/>
-        <v>6.2448644207066559</v>
-      </c>
-      <c r="AG20" s="22">
-        <f>[1]!CALC_DMG(AV20,V20,$D$2,P20)</f>
-        <v>427.1</v>
-      </c>
-      <c r="AH20" s="77">
-        <f t="shared" ref="AH20:AH21" si="66">M20/AG20</f>
-        <v>4.4486068836338095</v>
+      <c r="W20" s="12" t="e">
+        <f t="shared" ref="W20:W21" ca="1" si="59">CALC_DMG(AJ20,T20,$D$2, P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="X20" s="79" t="e">
+        <f t="shared" ref="X20:X21" ca="1" si="60">K20/W20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y20" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV20,T20,$D$2, P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z20" s="79" t="e">
+        <f t="shared" ref="Z20:Z21" ca="1" si="61">K20/Y20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA20" s="15" t="e">
+        <f t="shared" ref="AA20:AA21" ca="1" si="62">CALC_DMG(AJ20,U20,$D$2,P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB20" s="78" t="e">
+        <f t="shared" ref="AB20:AB21" ca="1" si="63">L20/AA20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC20" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV20,U20,$D$2,P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD20" s="78" t="e">
+        <f t="shared" ref="AD20:AD21" ca="1" si="64">L20/AC20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE20" s="22" t="e">
+        <f t="shared" ref="AE20:AE21" ca="1" si="65">CALC_DMG(AJ20,V20,$D$2,P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF20" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG20" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV20,V20,$D$2,P20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH20" s="77" t="e">
+        <f t="shared" ref="AH20:AH21" ca="1" si="66">M20/AG20</f>
+        <v>#NAME?</v>
       </c>
       <c r="AI20" s="8">
         <v>4</v>
@@ -4992,29 +4990,29 @@
         <f t="shared" ref="AN20:AN21" si="67">AL20*(1+(0.02*AM20))</f>
         <v>180</v>
       </c>
-      <c r="AO20" s="20">
-        <f>CALC_DMG(Q20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(Q20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(Q20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
-        <v>9327.5144999999993</v>
-      </c>
-      <c r="AP20" s="75">
-        <f>AK20/AO20</f>
-        <v>2.0369842362614392</v>
-      </c>
-      <c r="AQ20" s="20">
-        <f>CALC_DMG(R20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(R20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(R20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
-        <v>7008.5572499999998</v>
-      </c>
-      <c r="AR20" s="75">
-        <f>AK20/AQ20</f>
-        <v>2.710971648266125</v>
-      </c>
-      <c r="AS20" s="20">
-        <f>CALC_DMG(S20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(S20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(S20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
-        <v>4689.5999999999995</v>
-      </c>
-      <c r="AT20" s="75">
-        <f>AK20/AS20</f>
-        <v>4.05151825315592</v>
+      <c r="AO20" s="20" t="e">
+        <f ca="1">CALC_DMG(Q20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(Q20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(Q20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP20" s="75" t="e">
+        <f ca="1">AK20/AO20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ20" s="20" t="e">
+        <f ca="1">CALC_DMG(R20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(R20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(R20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR20" s="75" t="e">
+        <f ca="1">AK20/AQ20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS20" s="20" t="e">
+        <f ca="1">CALC_DMG(S20*$AK$1,AN20,$AI$2,1)*$AK$2+CALC_DMG(S20*$AL$1,AN20,$AI$2,1)*$AL$2+CALC_DMG(S20*$AM$1,AN20,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT20" s="75" t="e">
+        <f ca="1">AK20/AS20</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV20" s="12">
         <f t="shared" ref="AV20:AV21" si="68">AJ20*$AV$2</f>
@@ -5035,33 +5033,33 @@
         <f t="shared" ref="AZ20:AZ21" si="71">AX20*(1+(0.02*AY20))</f>
         <v>108</v>
       </c>
-      <c r="BA20" s="20">
-        <f>[1]!CALC_DMG(Q20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
-        <v>9975.5145000000011</v>
-      </c>
-      <c r="BB20" s="75">
-        <f t="shared" ref="BB20:BB21" si="72">AW20/BA20</f>
-        <v>1.1427981985290081</v>
-      </c>
-      <c r="BC20" s="20">
-        <f>[1]!CALC_DMG(R20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(R20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(R20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
-        <v>7656.5573000000004</v>
-      </c>
-      <c r="BD20" s="75">
-        <f t="shared" ref="BD20:BD21" si="73">AW20/BC20</f>
-        <v>1.488919830848781</v>
-      </c>
-      <c r="BE20" s="20">
-        <f>[1]!CALC_DMG(S20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(S20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(S20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
-        <v>5337.6</v>
-      </c>
-      <c r="BF20" s="75">
-        <f t="shared" ref="BF20:BF21" si="74">AW20/BE20</f>
-        <v>2.1357913669064748</v>
+      <c r="BA20" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB20" s="75" t="e">
+        <f t="shared" ref="BB20:BB21" ca="1" si="72">AW20/BA20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC20" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(R20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(R20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD20" s="75" t="e">
+        <f t="shared" ref="BD20:BD21" ca="1" si="73">AW20/BC20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE20" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S20*$AK$1,AZ20,$AI$2,1)*$AK$2+[1]!CALC_DMG(S20*$AL$1,AZ20,$AI$2,1)*$AL$2+[1]!CALC_DMG(S20*$AM$1,AZ20,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF20" s="75" t="e">
+        <f t="shared" ref="BF20:BF21" ca="1" si="74">AW20/BE20</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="21" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="84"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -5127,53 +5125,53 @@
       <c r="V21" s="25">
         <v>420</v>
       </c>
-      <c r="W21" s="12">
-        <f t="shared" si="59"/>
-        <v>209.99999999999989</v>
-      </c>
-      <c r="X21" s="79">
-        <f t="shared" si="60"/>
-        <v>13.809523809523817</v>
-      </c>
-      <c r="Y21" s="12">
-        <f>[1]!CALC_DMG(AV21,T21,$D$2, P21)</f>
-        <v>366</v>
-      </c>
-      <c r="Z21" s="79">
-        <f t="shared" si="61"/>
-        <v>7.9234972677595632</v>
-      </c>
-      <c r="AA21" s="15">
-        <f t="shared" si="62"/>
-        <v>284.99999999999994</v>
-      </c>
-      <c r="AB21" s="78">
-        <f t="shared" si="63"/>
-        <v>8.5964912280701764</v>
-      </c>
-      <c r="AC21" s="15">
-        <f>[1]!CALC_DMG(AV21,U21,$D$2,P21)</f>
-        <v>441</v>
-      </c>
-      <c r="AD21" s="78">
-        <f t="shared" si="64"/>
-        <v>5.5555555555555554</v>
-      </c>
-      <c r="AE21" s="22">
-        <f t="shared" si="65"/>
-        <v>360</v>
-      </c>
-      <c r="AF21" s="77">
-        <f t="shared" si="9"/>
-        <v>5.5555555555555554</v>
-      </c>
-      <c r="AG21" s="22">
-        <f>[1]!CALC_DMG(AV21,V21,$D$2,P21)</f>
-        <v>516</v>
-      </c>
-      <c r="AH21" s="77">
-        <f t="shared" si="66"/>
-        <v>3.8759689922480618</v>
+      <c r="W21" s="12" t="e">
+        <f t="shared" ca="1" si="59"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="X21" s="79" t="e">
+        <f t="shared" ca="1" si="60"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y21" s="12" t="e">
+        <f ca="1">[1]!CALC_DMG(AV21,T21,$D$2, P21)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Z21" s="79" t="e">
+        <f t="shared" ca="1" si="61"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA21" s="15" t="e">
+        <f t="shared" ca="1" si="62"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AB21" s="78" t="e">
+        <f t="shared" ca="1" si="63"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AC21" s="15" t="e">
+        <f ca="1">[1]!CALC_DMG(AV21,U21,$D$2,P21)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD21" s="78" t="e">
+        <f t="shared" ca="1" si="64"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AE21" s="22" t="e">
+        <f t="shared" ca="1" si="65"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AF21" s="77" t="e">
+        <f t="shared" ca="1" si="9"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="AG21" s="22" t="e">
+        <f ca="1">[1]!CALC_DMG(AV21,V21,$D$2,P21)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AH21" s="77" t="e">
+        <f t="shared" ca="1" si="66"/>
+        <v>#NAME?</v>
       </c>
       <c r="AI21" s="8">
         <v>5</v>
@@ -5194,29 +5192,29 @@
         <f t="shared" si="67"/>
         <v>220</v>
       </c>
-      <c r="AO21" s="20">
-        <f>CALC_DMG(Q21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(Q21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(Q21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
-        <v>14289.131519999999</v>
-      </c>
-      <c r="AP21" s="75">
-        <f>AK21/AO21</f>
-        <v>2.6593638631440073</v>
-      </c>
-      <c r="AQ21" s="20">
-        <f>CALC_DMG(R21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(R21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(R21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
-        <v>11603.765759999998</v>
-      </c>
-      <c r="AR21" s="75">
-        <f>AK21/AQ21</f>
-        <v>3.2747989563002009</v>
-      </c>
-      <c r="AS21" s="20">
-        <f>CALC_DMG(S21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(S21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(S21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
-        <v>8918.4</v>
-      </c>
-      <c r="AT21" s="75">
-        <f>AK21/AS21</f>
-        <v>4.2608539648367421</v>
+      <c r="AO21" s="20" t="e">
+        <f ca="1">CALC_DMG(Q21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(Q21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(Q21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AP21" s="75" t="e">
+        <f ca="1">AK21/AO21</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AQ21" s="20" t="e">
+        <f ca="1">CALC_DMG(R21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(R21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(R21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AR21" s="75" t="e">
+        <f ca="1">AK21/AQ21</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AS21" s="20" t="e">
+        <f ca="1">CALC_DMG(S21*$AK$1,AN21,$AI$2,1)*$AK$2+CALC_DMG(S21*$AL$1,AN21,$AI$2,1)*$AL$2+CALC_DMG(S21*$AM$1,AN21,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AT21" s="75" t="e">
+        <f ca="1">AK21/AS21</f>
+        <v>#NAME?</v>
       </c>
       <c r="AV21" s="12">
         <f t="shared" si="68"/>
@@ -5237,34 +5235,34 @@
         <f t="shared" si="71"/>
         <v>132</v>
       </c>
-      <c r="BA21" s="20">
-        <f>[1]!CALC_DMG(Q21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
-        <v>15081.131600000001</v>
-      </c>
-      <c r="BB21" s="75">
-        <f t="shared" si="72"/>
-        <v>1.5118228926534929</v>
-      </c>
-      <c r="BC21" s="20">
-        <f>[1]!CALC_DMG(R21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(R21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(R21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
-        <v>12395.765600000001</v>
-      </c>
-      <c r="BD21" s="75">
-        <f t="shared" si="73"/>
-        <v>1.8393377816050345</v>
-      </c>
-      <c r="BE21" s="20">
-        <f>[1]!CALC_DMG(S21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(S21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(S21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
-        <v>9710.4</v>
-      </c>
-      <c r="BF21" s="75">
-        <f t="shared" si="74"/>
-        <v>2.3479980227385071</v>
+      <c r="BA21" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(Q21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(Q21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(Q21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BB21" s="75" t="e">
+        <f t="shared" ca="1" si="72"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BC21" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(R21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(R21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(R21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BD21" s="75" t="e">
+        <f t="shared" ca="1" si="73"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="BE21" s="20" t="e">
+        <f ca="1">[1]!CALC_DMG(S21*$AK$1,AZ21,$AI$2,1)*$AK$2+[1]!CALC_DMG(S21*$AL$1,AZ21,$AI$2,1)*$AL$2+[1]!CALC_DMG(S21*$AM$1,AZ21,$AI$2,1)*$AM$2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="BF21" s="75" t="e">
+        <f t="shared" ca="1" si="74"/>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="23" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AU23" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AV23" s="8">
         <v>1.2</v>
@@ -5278,7 +5276,7 @@
     </row>
     <row r="24" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AU24" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AV24" s="8">
         <v>0.8</v>
@@ -5292,7 +5290,7 @@
     </row>
     <row r="25" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AU25" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AV25" s="8">
         <v>0.9</v>
@@ -5306,6 +5304,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D3:T3"/>
+    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="AJ3:AT4"/>
     <mergeCell ref="AV3:BF4"/>
     <mergeCell ref="B6:B7"/>
@@ -5313,11 +5316,6 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AA3:AD3"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D3:T3"/>
-    <mergeCell ref="W3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5376,57 +5374,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="85" t="s">
+      <c r="V3" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="85"/>
-      <c r="X3" s="85"/>
-      <c r="Y3" s="85"/>
-      <c r="Z3" s="85"/>
-      <c r="AA3" s="85"/>
-      <c r="AB3" s="85"/>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="85"/>
-      <c r="AF3" s="85"/>
-      <c r="AG3" s="85"/>
-      <c r="AH3" s="85"/>
-      <c r="AI3" s="85"/>
-      <c r="AJ3" s="85"/>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="85"/>
-      <c r="AM3" s="85"/>
-      <c r="AN3" s="85"/>
-      <c r="AO3" s="85"/>
-      <c r="AP3" s="85"/>
-      <c r="AQ3" s="85"/>
-      <c r="AR3" s="85"/>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AU3" s="85"/>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
-      <c r="AY3" s="85"/>
+      <c r="W3" s="87"/>
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="87"/>
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="87"/>
+      <c r="AJ3" s="87"/>
+      <c r="AK3" s="87"/>
+      <c r="AL3" s="87"/>
+      <c r="AM3" s="87"/>
+      <c r="AN3" s="87"/>
+      <c r="AO3" s="87"/>
+      <c r="AP3" s="87"/>
+      <c r="AQ3" s="87"/>
+      <c r="AR3" s="87"/>
+      <c r="AS3" s="87"/>
+      <c r="AT3" s="87"/>
+      <c r="AU3" s="87"/>
+      <c r="AV3" s="87"/>
+      <c r="AW3" s="87"/>
+      <c r="AX3" s="87"/>
+      <c r="AY3" s="87"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5472,44 +5470,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="89" t="s">
+      <c r="V4" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="89"/>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="85"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="89" t="s">
+      <c r="AD4" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="89" t="s">
+      <c r="AL4" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="89"/>
-      <c r="AQ4" s="89"/>
+      <c r="AM4" s="85"/>
+      <c r="AN4" s="85"/>
+      <c r="AO4" s="85"/>
+      <c r="AP4" s="85"/>
+      <c r="AQ4" s="85"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="89" t="s">
+      <c r="AT4" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="89"/>
-      <c r="AV4" s="89"/>
-      <c r="AW4" s="89"/>
-      <c r="AX4" s="89"/>
-      <c r="AY4" s="89"/>
+      <c r="AU4" s="85"/>
+      <c r="AV4" s="85"/>
+      <c r="AW4" s="85"/>
+      <c r="AX4" s="85"/>
+      <c r="AY4" s="85"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5651,7 +5649,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="84">
+      <c r="B6" s="88">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -5815,7 +5813,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="84"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -5977,7 +5975,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="84">
+      <c r="B8" s="88">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -6141,7 +6139,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="84"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -6303,7 +6301,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="91">
+      <c r="B10" s="89">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -6467,10 +6465,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="91"/>
+      <c r="B11" s="89"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="91"/>
+      <c r="B12" s="89"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -6632,7 +6630,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="84">
+      <c r="B13" s="88">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -6796,7 +6794,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="84"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -6958,7 +6956,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="84">
+      <c r="B16" s="88">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -7122,7 +7120,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="84"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -7284,7 +7282,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="84"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -7446,7 +7444,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="84">
+      <c r="B20" s="88">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -7610,7 +7608,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="84"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -7773,18 +7771,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="V3:AY3"/>
+    <mergeCell ref="AT4:AY4"/>
+    <mergeCell ref="AL4:AQ4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="V4:AA4"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="V3:AY3"/>
-    <mergeCell ref="AT4:AY4"/>
-    <mergeCell ref="AL4:AQ4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="V4:AA4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7812,67 +7810,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="105" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
       <c r="I1" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="K1" s="109" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" s="106" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
       <c r="O1" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q1" s="110" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q1" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
       <c r="U1" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="B2" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="126" t="s">
+      <c r="B2" s="92" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="104" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126" t="s">
-        <v>188</v>
-      </c>
-      <c r="H2" s="126"/>
-      <c r="K2" s="126" t="s">
+      <c r="H2" s="104"/>
+      <c r="K2" s="104" t="s">
+        <v>186</v>
+      </c>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126" t="s">
-        <v>188</v>
-      </c>
-      <c r="N2" s="126"/>
-      <c r="Q2" s="126" t="s">
+      <c r="N2" s="104"/>
+      <c r="Q2" s="104" t="s">
+        <v>186</v>
+      </c>
+      <c r="R2" s="104"/>
+      <c r="S2" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="R2" s="126"/>
-      <c r="S2" s="126" t="s">
-        <v>188</v>
-      </c>
-      <c r="T2" s="126"/>
+      <c r="T2" s="104"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -7882,29 +7880,29 @@
         <v>101</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="124" t="s">
-        <v>128</v>
-      </c>
-      <c r="K3" s="115"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="117"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="102" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="93"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="95"/>
       <c r="O3" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="96" t="s">
-        <v>155</v>
+        <v>127</v>
+      </c>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="95"/>
+      <c r="U3" s="115" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -7916,34 +7914,34 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="125"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="103"/>
       <c r="K4" s="49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L4" s="49"/>
       <c r="M4" s="49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="113">
+      <c r="O4" s="110">
         <v>0</v>
       </c>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="97"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="116"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
         <v>1.2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>103</v>
@@ -7953,31 +7951,31 @@
       </c>
       <c r="E5" s="46"/>
       <c r="F5" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="H5" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="I5" s="111">
+      <c r="I5" s="108">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L5" s="48"/>
       <c r="M5" s="48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="113"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="97"/>
+      <c r="O5" s="110"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="101"/>
+      <c r="U5" s="116"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -7991,22 +7989,22 @@
       <c r="E6" s="48"/>
       <c r="F6" s="47"/>
       <c r="G6" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="112"/>
+      <c r="I6" s="109"/>
       <c r="K6" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="113"/>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="119"/>
-      <c r="T6" s="120"/>
-      <c r="U6" s="97"/>
+      <c r="O6" s="110"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
+      <c r="S6" s="97"/>
+      <c r="T6" s="98"/>
+      <c r="U6" s="116"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -8016,40 +8014,40 @@
         <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="51"/>
       <c r="F7" s="52"/>
       <c r="G7" s="51"/>
       <c r="H7" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="I7" s="121">
+        <v>1</v>
+      </c>
+      <c r="K7" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="L7" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="N7" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="I7" s="102">
-        <v>1</v>
-      </c>
-      <c r="K7" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="L7" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="M7" s="53" t="s">
-        <v>242</v>
-      </c>
-      <c r="N7" s="53" t="s">
-        <v>239</v>
-      </c>
-      <c r="O7" s="101">
+      <c r="O7" s="120">
         <v>1</v>
       </c>
       <c r="Q7" s="54"/>
       <c r="R7" s="54"/>
       <c r="S7" s="54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T7" s="51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U7" s="81">
         <v>1</v>
@@ -8072,27 +8070,27 @@
       <c r="F8" s="52"/>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
-      <c r="I8" s="103"/>
+      <c r="I8" s="122"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M8" s="53" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N8" s="51"/>
-      <c r="O8" s="101"/>
+      <c r="O8" s="120"/>
       <c r="Q8" s="33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R8" s="33"/>
       <c r="S8" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T8" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="U8" s="98">
+        <v>188</v>
+      </c>
+      <c r="U8" s="117">
         <v>2</v>
       </c>
     </row>
@@ -8108,40 +8106,40 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="I9" s="122"/>
+      <c r="K9" s="51" t="s">
         <v>168</v>
-      </c>
-      <c r="F9" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="I9" s="103"/>
-      <c r="K9" s="51" t="s">
-        <v>169</v>
       </c>
       <c r="L9" s="51"/>
       <c r="M9" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="N9" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="N9" s="51" t="s">
+      <c r="O9" s="120"/>
+      <c r="Q9" s="33" t="s">
         <v>172</v>
-      </c>
-      <c r="O9" s="101"/>
-      <c r="Q9" s="33" t="s">
-        <v>173</v>
       </c>
       <c r="R9" s="33"/>
       <c r="S9" s="33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="T9" s="83" t="s">
-        <v>163</v>
-      </c>
-      <c r="U9" s="99"/>
+        <v>162</v>
+      </c>
+      <c r="U9" s="118"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
@@ -8153,36 +8151,36 @@
       <c r="C10" s="3"/>
       <c r="D10" s="1"/>
       <c r="E10" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="99">
+      <c r="I10" s="118">
         <v>2</v>
       </c>
       <c r="K10" s="57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L10" s="57"/>
       <c r="M10" s="57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="O10" s="98">
+        <v>138</v>
+      </c>
+      <c r="O10" s="117">
         <v>2</v>
       </c>
       <c r="Q10" s="33"/>
       <c r="R10" s="56"/>
       <c r="S10" s="56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T10" s="83" t="s">
-        <v>170</v>
-      </c>
-      <c r="U10" s="100"/>
+        <v>169</v>
+      </c>
+      <c r="U10" s="119"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -8194,34 +8192,34 @@
       <c r="C11" s="3"/>
       <c r="D11" s="1"/>
       <c r="E11" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="G11" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="H11" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="H11" s="55" t="s">
-        <v>144</v>
-      </c>
-      <c r="I11" s="99"/>
+      <c r="I11" s="118"/>
       <c r="K11" s="33"/>
       <c r="L11" s="56"/>
       <c r="M11" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="100"/>
+      <c r="O11" s="119"/>
       <c r="Q11" s="61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R11" s="61"/>
       <c r="S11" s="61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="104">
+      <c r="U11" s="123">
         <v>3</v>
       </c>
     </row>
@@ -8230,35 +8228,33 @@
         <v>3.2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="3" t="s">
         <v>115</v>
       </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="1"/>
       <c r="E12" s="33"/>
       <c r="F12" s="56"/>
       <c r="G12" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="99"/>
+      <c r="I12" s="118"/>
       <c r="K12" s="60"/>
       <c r="L12" s="60"/>
       <c r="M12" s="60" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N12" s="60"/>
-      <c r="O12" s="105">
+      <c r="O12" s="124">
         <v>3</v>
       </c>
       <c r="Q12" s="69" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="104"/>
+      <c r="U12" s="123"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -8271,39 +8267,39 @@
         <v>117</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E13" s="59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="107">
+      <c r="I13" s="126">
         <v>3</v>
       </c>
       <c r="K13" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="L13" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="60" t="s">
-        <v>146</v>
-      </c>
       <c r="M13" s="61" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N13" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="O13" s="125"/>
+      <c r="Q13" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="O13" s="106"/>
-      <c r="Q13" s="28" t="s">
+      <c r="R13" s="28" t="s">
         <v>183</v>
-      </c>
-      <c r="R13" s="28" t="s">
-        <v>184</v>
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="95">
+      <c r="U13" s="114">
         <v>4</v>
       </c>
     </row>
@@ -8312,61 +8308,61 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="66" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="107"/>
+      <c r="I14" s="126"/>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="93">
+      <c r="O14" s="112">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="95"/>
+      <c r="U14" s="114"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
         <v>4.2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="1"/>
       <c r="E15" s="58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="106"/>
+      <c r="I15" s="125"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="N15" s="63"/>
+      <c r="O15" s="113"/>
+      <c r="Q15" s="68" t="s">
         <v>150</v>
-      </c>
-      <c r="N15" s="63"/>
-      <c r="O15" s="94"/>
-      <c r="Q15" s="68" t="s">
-        <v>151</v>
       </c>
       <c r="R15" s="64"/>
       <c r="S15" s="64"/>
@@ -8376,10 +8372,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="111" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="92"/>
+      <c r="D18" s="111"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -8394,7 +8390,7 @@
     </row>
     <row r="20" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="3">
         <v>1.2</v>
@@ -8403,18 +8399,18 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E20" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>191</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21" s="1">
         <v>2.1</v>
@@ -8423,21 +8419,21 @@
         <v>1.4</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>196</v>
-      </c>
       <c r="H21" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C22" s="1">
         <v>3.1</v>
@@ -8446,18 +8442,18 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>199</v>
-      </c>
       <c r="G22" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C23" s="1">
         <v>4.0999999999999996</v>
@@ -8466,43 +8462,43 @@
         <v>3.3</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C24" s="1">
         <v>4.2</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="7" t="s">
         <v>202</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -8621,28 +8617,12 @@
         <v>55</v>
       </c>
       <c r="E35" s="70" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F35" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E3:H4"/>
-    <mergeCell ref="Q3:T6"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="O4:O6"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="O14:O15"/>
     <mergeCell ref="U13:U14"/>
@@ -8655,6 +8635,22 @@
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="I13:I15"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="O4:O6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E3:H4"/>
+    <mergeCell ref="Q3:T6"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8672,32 +8668,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="G1" s="137" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="G1" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+      <c r="W1" s="133"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -8870,11 +8866,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="133">
+      <c r="F10" s="130">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="92">
+      <c r="G10" s="111">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8894,11 +8890,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="133">
+      <c r="N10" s="130">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="92">
+      <c r="O10" s="111">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8918,7 +8914,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="130">
+      <c r="V10" s="134">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -8941,8 +8937,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="136"/>
-      <c r="G11" s="92"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="111"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8960,8 +8956,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="136"/>
-      <c r="O11" s="92"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="111"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8979,7 +8975,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="131"/>
+      <c r="V11" s="135"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -8999,8 +8995,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="136"/>
-      <c r="G12" s="92"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="111"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9018,8 +9014,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="136"/>
-      <c r="O12" s="92"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="111"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -9037,7 +9033,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="132"/>
+      <c r="V12" s="136"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -9057,8 +9053,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="134"/>
-      <c r="G13" s="92"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="111"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -9076,8 +9072,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="136"/>
-      <c r="O13" s="92"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="111"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -9097,11 +9093,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="133">
+      <c r="F14" s="130">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="92">
+      <c r="G14" s="111">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9121,8 +9117,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="136"/>
-      <c r="O14" s="92"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="111"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -9142,8 +9138,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="134"/>
-      <c r="G15" s="92"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="111"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9161,8 +9157,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="136"/>
-      <c r="O15" s="92"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="111"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -9193,8 +9189,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="134"/>
-      <c r="O16" s="92"/>
+      <c r="N16" s="132"/>
+      <c r="O16" s="111"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -9330,7 +9326,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="130">
+      <c r="N22" s="134">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9370,7 +9366,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="131"/>
+      <c r="N23" s="135"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -9407,7 +9403,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="132"/>
+      <c r="N24" s="136"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -9444,7 +9440,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="130">
+      <c r="N25" s="134">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -9467,7 +9463,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="132"/>
+      <c r="N26" s="136"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -9481,7 +9477,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="137" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="128"/>
@@ -9490,7 +9486,7 @@
       <c r="E30" s="128"/>
       <c r="F30" s="129"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="135" t="s">
+      <c r="I30" s="137" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="128"/>
@@ -9562,11 +9558,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="133">
+      <c r="F32" s="130">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="92">
+      <c r="G32" s="111">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9586,11 +9582,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="133">
+      <c r="N32" s="130">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="92">
+      <c r="O32" s="111">
         <v>4</v>
       </c>
     </row>
@@ -9612,8 +9608,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="136"/>
-      <c r="G33" s="92"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="111"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9631,8 +9627,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="136"/>
-      <c r="O33" s="92"/>
+      <c r="N33" s="131"/>
+      <c r="O33" s="111"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -9652,8 +9648,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="136"/>
-      <c r="G34" s="92"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="111"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9671,8 +9667,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="136"/>
-      <c r="O34" s="92"/>
+      <c r="N34" s="131"/>
+      <c r="O34" s="111"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -9692,8 +9688,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="134"/>
-      <c r="G35" s="92"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="111"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9711,8 +9707,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="136"/>
-      <c r="O35" s="92"/>
+      <c r="N35" s="131"/>
+      <c r="O35" s="111"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -9732,11 +9728,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="133">
+      <c r="F36" s="130">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="92">
+      <c r="G36" s="111">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9756,8 +9752,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="136"/>
-      <c r="O36" s="92"/>
+      <c r="N36" s="131"/>
+      <c r="O36" s="111"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -9777,8 +9773,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="134"/>
-      <c r="G37" s="92"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="111"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9796,8 +9792,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="136"/>
-      <c r="O37" s="92"/>
+      <c r="N37" s="131"/>
+      <c r="O37" s="111"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -9828,8 +9824,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="134"/>
-      <c r="O38" s="92"/>
+      <c r="N38" s="132"/>
+      <c r="O38" s="111"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -9959,7 +9955,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="130">
+      <c r="N45" s="134">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9998,7 +9994,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="131"/>
+      <c r="N46" s="135"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -10034,7 +10030,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="132"/>
+      <c r="N47" s="136"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -10070,7 +10066,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="130">
+      <c r="N48" s="134">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -10092,10 +10088,29 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="132"/>
+      <c r="N49" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -10105,25 +10120,6 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
+++ b/dev_docs/千界万锻数值表格-26_5_4_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20B6B5F-D079-4832-86F8-7BF845ECABC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FB8975-9026-445E-BF45-FD3979F00A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数值分配-新" sheetId="5" r:id="rId1"/>
@@ -1716,6 +1716,18 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1725,19 +1737,73 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1779,72 +1845,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1854,28 +1854,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2271,71 +2271,71 @@
     </row>
     <row r="3" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="87"/>
-      <c r="S3" s="87"/>
-      <c r="T3" s="87"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="90" t="s">
+      <c r="W3" s="86" t="s">
         <v>214</v>
       </c>
-      <c r="X3" s="91"/>
-      <c r="Y3" s="91"/>
-      <c r="Z3" s="91"/>
-      <c r="AA3" s="90" t="s">
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="86" t="s">
         <v>215</v>
       </c>
-      <c r="AB3" s="91"/>
-      <c r="AC3" s="91"/>
-      <c r="AD3" s="91"/>
-      <c r="AE3" s="90" t="s">
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="86" t="s">
         <v>216</v>
       </c>
-      <c r="AF3" s="91"/>
-      <c r="AG3" s="91"/>
-      <c r="AH3" s="91"/>
-      <c r="AJ3" s="84" t="s">
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AJ3" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" s="84"/>
-      <c r="AL3" s="84"/>
-      <c r="AM3" s="84"/>
-      <c r="AN3" s="84"/>
-      <c r="AO3" s="84"/>
-      <c r="AP3" s="84"/>
-      <c r="AQ3" s="84"/>
-      <c r="AR3" s="84"/>
-      <c r="AS3" s="84"/>
-      <c r="AT3" s="84"/>
-      <c r="AV3" s="86" t="s">
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="88"/>
+      <c r="AM3" s="88"/>
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88"/>
+      <c r="AS3" s="88"/>
+      <c r="AT3" s="88"/>
+      <c r="AV3" s="90" t="s">
         <v>233</v>
       </c>
-      <c r="AW3" s="87"/>
-      <c r="AX3" s="87"/>
-      <c r="AY3" s="87"/>
-      <c r="AZ3" s="87"/>
-      <c r="BA3" s="87"/>
-      <c r="BB3" s="87"/>
-      <c r="BC3" s="87"/>
-      <c r="BD3" s="87"/>
-      <c r="BE3" s="87"/>
-      <c r="BF3" s="87"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
+      <c r="AY3" s="85"/>
+      <c r="AZ3" s="85"/>
+      <c r="BA3" s="85"/>
+      <c r="BB3" s="85"/>
+      <c r="BC3" s="85"/>
+      <c r="BD3" s="85"/>
+      <c r="BE3" s="85"/>
+      <c r="BF3" s="85"/>
     </row>
     <row r="4" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
@@ -2394,28 +2394,28 @@
       <c r="AF4" s="71"/>
       <c r="AG4" s="71"/>
       <c r="AH4" s="71"/>
-      <c r="AJ4" s="85"/>
-      <c r="AK4" s="85"/>
-      <c r="AL4" s="85"/>
-      <c r="AM4" s="85"/>
-      <c r="AN4" s="85"/>
-      <c r="AO4" s="85"/>
-      <c r="AP4" s="85"/>
-      <c r="AQ4" s="85"/>
-      <c r="AR4" s="85"/>
-      <c r="AS4" s="85"/>
-      <c r="AT4" s="85"/>
-      <c r="AV4" s="85"/>
-      <c r="AW4" s="85"/>
-      <c r="AX4" s="85"/>
-      <c r="AY4" s="85"/>
-      <c r="AZ4" s="85"/>
-      <c r="BA4" s="85"/>
-      <c r="BB4" s="85"/>
-      <c r="BC4" s="85"/>
-      <c r="BD4" s="85"/>
-      <c r="BE4" s="85"/>
-      <c r="BF4" s="85"/>
+      <c r="AJ4" s="89"/>
+      <c r="AK4" s="89"/>
+      <c r="AL4" s="89"/>
+      <c r="AM4" s="89"/>
+      <c r="AN4" s="89"/>
+      <c r="AO4" s="89"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="89"/>
+      <c r="AR4" s="89"/>
+      <c r="AS4" s="89"/>
+      <c r="AT4" s="89"/>
+      <c r="AV4" s="89"/>
+      <c r="AW4" s="89"/>
+      <c r="AX4" s="89"/>
+      <c r="AY4" s="89"/>
+      <c r="AZ4" s="89"/>
+      <c r="BA4" s="89"/>
+      <c r="BB4" s="89"/>
+      <c r="BC4" s="89"/>
+      <c r="BD4" s="89"/>
+      <c r="BE4" s="89"/>
+      <c r="BF4" s="89"/>
     </row>
     <row r="5" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
@@ -2580,7 +2580,7 @@
       </c>
     </row>
     <row r="6" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="88">
+      <c r="B6" s="84">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2784,7 +2784,7 @@
       </c>
     </row>
     <row r="7" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="88"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
     </row>
     <row r="8" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="88">
+      <c r="B8" s="84">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3190,7 +3190,7 @@
       </c>
     </row>
     <row r="9" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="88"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3392,7 +3392,7 @@
       </c>
     </row>
     <row r="10" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="89">
+      <c r="B10" s="91">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3596,7 +3596,7 @@
       </c>
     </row>
     <row r="11" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="89"/>
+      <c r="B11" s="91"/>
       <c r="X11" s="76"/>
       <c r="Z11" s="76"/>
       <c r="AB11" s="76"/>
@@ -3611,7 +3611,7 @@
       <c r="BF11" s="76"/>
     </row>
     <row r="12" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="89"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3813,7 +3813,7 @@
       </c>
     </row>
     <row r="13" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="88">
+      <c r="B13" s="84">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -4017,7 +4017,7 @@
       </c>
     </row>
     <row r="14" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="88"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4233,7 +4233,7 @@
       <c r="BF15" s="76"/>
     </row>
     <row r="16" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="88">
+      <c r="B16" s="84">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4437,7 +4437,7 @@
       </c>
     </row>
     <row r="17" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="88"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4639,7 +4639,7 @@
       </c>
     </row>
     <row r="18" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4855,7 +4855,7 @@
       <c r="BF19" s="76"/>
     </row>
     <row r="20" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="88">
+      <c r="B20" s="84">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -5059,7 +5059,7 @@
       </c>
     </row>
     <row r="21" spans="2:58" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="88"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -5304,11 +5304,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D3:T3"/>
-    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="AJ3:AT4"/>
     <mergeCell ref="AV3:BF4"/>
     <mergeCell ref="B6:B7"/>
@@ -5316,6 +5311,11 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AA3:AD3"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D3:T3"/>
+    <mergeCell ref="W3:Z3"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5374,57 +5374,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="87" t="s">
+      <c r="V3" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="87"/>
-      <c r="X3" s="87"/>
-      <c r="Y3" s="87"/>
-      <c r="Z3" s="87"/>
-      <c r="AA3" s="87"/>
-      <c r="AB3" s="87"/>
-      <c r="AC3" s="87"/>
-      <c r="AD3" s="87"/>
-      <c r="AE3" s="87"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AI3" s="87"/>
-      <c r="AJ3" s="87"/>
-      <c r="AK3" s="87"/>
-      <c r="AL3" s="87"/>
-      <c r="AM3" s="87"/>
-      <c r="AN3" s="87"/>
-      <c r="AO3" s="87"/>
-      <c r="AP3" s="87"/>
-      <c r="AQ3" s="87"/>
-      <c r="AR3" s="87"/>
-      <c r="AS3" s="87"/>
-      <c r="AT3" s="87"/>
-      <c r="AU3" s="87"/>
-      <c r="AV3" s="87"/>
-      <c r="AW3" s="87"/>
-      <c r="AX3" s="87"/>
-      <c r="AY3" s="87"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="85"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="85"/>
+      <c r="AI3" s="85"/>
+      <c r="AJ3" s="85"/>
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="85"/>
+      <c r="AM3" s="85"/>
+      <c r="AN3" s="85"/>
+      <c r="AO3" s="85"/>
+      <c r="AP3" s="85"/>
+      <c r="AQ3" s="85"/>
+      <c r="AR3" s="85"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
+      <c r="AY3" s="85"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5470,44 +5470,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="85" t="s">
+      <c r="V4" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="85"/>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="85"/>
-      <c r="Z4" s="85"/>
-      <c r="AA4" s="85"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="85" t="s">
+      <c r="AD4" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="85"/>
-      <c r="AF4" s="85"/>
-      <c r="AG4" s="85"/>
+      <c r="AE4" s="89"/>
+      <c r="AF4" s="89"/>
+      <c r="AG4" s="89"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="85" t="s">
+      <c r="AL4" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="85"/>
-      <c r="AN4" s="85"/>
-      <c r="AO4" s="85"/>
-      <c r="AP4" s="85"/>
-      <c r="AQ4" s="85"/>
+      <c r="AM4" s="89"/>
+      <c r="AN4" s="89"/>
+      <c r="AO4" s="89"/>
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="89"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="85" t="s">
+      <c r="AT4" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="85"/>
-      <c r="AV4" s="85"/>
-      <c r="AW4" s="85"/>
-      <c r="AX4" s="85"/>
-      <c r="AY4" s="85"/>
+      <c r="AU4" s="89"/>
+      <c r="AV4" s="89"/>
+      <c r="AW4" s="89"/>
+      <c r="AX4" s="89"/>
+      <c r="AY4" s="89"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -5649,7 +5649,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="88">
+      <c r="B6" s="84">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="88"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -5975,7 +5975,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="88">
+      <c r="B8" s="84">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -6139,7 +6139,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="88"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -6301,7 +6301,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="89">
+      <c r="B10" s="91">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -6465,10 +6465,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="89"/>
+      <c r="B11" s="91"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="89"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -6630,7 +6630,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="88">
+      <c r="B13" s="84">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -6794,7 +6794,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="88"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -6956,7 +6956,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="88">
+      <c r="B16" s="84">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -7120,7 +7120,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="88"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -7282,7 +7282,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -7444,7 +7444,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="88">
+      <c r="B20" s="84">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -7608,7 +7608,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="88"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -7771,18 +7771,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="V3:AY3"/>
     <mergeCell ref="AT4:AY4"/>
     <mergeCell ref="AL4:AQ4"/>
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7810,30 +7810,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="105" t="s">
+      <c r="E1" s="108" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
       <c r="I1" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="106" t="s">
+      <c r="K1" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
       <c r="O1" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="Q1" s="107" t="s">
+      <c r="Q1" s="110" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
       <c r="U1" s="39" t="s">
         <v>157</v>
       </c>
@@ -7842,35 +7842,35 @@
       <c r="A2" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="114" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="104" t="s">
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104" t="s">
+      <c r="F2" s="126"/>
+      <c r="G2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="H2" s="104"/>
-      <c r="K2" s="104" t="s">
+      <c r="H2" s="126"/>
+      <c r="K2" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104" t="s">
+      <c r="L2" s="126"/>
+      <c r="M2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="N2" s="104"/>
-      <c r="Q2" s="104" t="s">
+      <c r="N2" s="126"/>
+      <c r="Q2" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="R2" s="104"/>
-      <c r="S2" s="104" t="s">
+      <c r="R2" s="126"/>
+      <c r="S2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="T2" s="104"/>
+      <c r="T2" s="126"/>
     </row>
     <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="41">
@@ -7883,25 +7883,25 @@
         <v>120</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="102" t="s">
+      <c r="E3" s="115"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="124" t="s">
         <v>127</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="95"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="117"/>
       <c r="O3" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="95"/>
-      <c r="U3" s="115" t="s">
+      <c r="Q3" s="115"/>
+      <c r="R3" s="116"/>
+      <c r="S3" s="116"/>
+      <c r="T3" s="117"/>
+      <c r="U3" s="96" t="s">
         <v>154</v>
       </c>
     </row>
@@ -7914,11 +7914,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="103"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="125"/>
       <c r="K4" s="49" t="s">
         <v>131</v>
       </c>
@@ -7927,14 +7927,14 @@
         <v>132</v>
       </c>
       <c r="N4" s="47"/>
-      <c r="O4" s="110">
+      <c r="O4" s="113">
         <v>0</v>
       </c>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="116"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="97"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
@@ -7959,7 +7959,7 @@
       <c r="H5" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="I5" s="108">
+      <c r="I5" s="111">
         <v>0</v>
       </c>
       <c r="K5" s="48" t="s">
@@ -7970,12 +7970,12 @@
         <v>185</v>
       </c>
       <c r="N5" s="47"/>
-      <c r="O5" s="110"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="101"/>
-      <c r="U5" s="116"/>
+      <c r="O5" s="113"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="97"/>
     </row>
     <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
@@ -7992,19 +7992,19 @@
         <v>158</v>
       </c>
       <c r="H6" s="47"/>
-      <c r="I6" s="109"/>
+      <c r="I6" s="112"/>
       <c r="K6" s="48" t="s">
         <v>161</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="47"/>
-      <c r="O6" s="110"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="97"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="98"/>
-      <c r="U6" s="116"/>
+      <c r="O6" s="113"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="119"/>
+      <c r="S6" s="119"/>
+      <c r="T6" s="120"/>
+      <c r="U6" s="97"/>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="42">
@@ -8023,7 +8023,7 @@
       <c r="H7" s="51" t="s">
         <v>237</v>
       </c>
-      <c r="I7" s="121">
+      <c r="I7" s="102">
         <v>1</v>
       </c>
       <c r="K7" s="53" t="s">
@@ -8038,7 +8038,7 @@
       <c r="N7" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="O7" s="120">
+      <c r="O7" s="101">
         <v>1</v>
       </c>
       <c r="Q7" s="54"/>
@@ -8070,7 +8070,7 @@
       <c r="F8" s="52"/>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
-      <c r="I8" s="122"/>
+      <c r="I8" s="103"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53" t="s">
         <v>135</v>
@@ -8079,7 +8079,7 @@
         <v>152</v>
       </c>
       <c r="N8" s="51"/>
-      <c r="O8" s="120"/>
+      <c r="O8" s="101"/>
       <c r="Q8" s="33" t="s">
         <v>163</v>
       </c>
@@ -8090,7 +8090,7 @@
       <c r="T8" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="U8" s="117">
+      <c r="U8" s="98">
         <v>2</v>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       <c r="H9" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="I9" s="122"/>
+      <c r="I9" s="103"/>
       <c r="K9" s="51" t="s">
         <v>168</v>
       </c>
@@ -8128,7 +8128,7 @@
       <c r="N9" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="O9" s="120"/>
+      <c r="O9" s="101"/>
       <c r="Q9" s="33" t="s">
         <v>172</v>
       </c>
@@ -8139,7 +8139,7 @@
       <c r="T9" s="83" t="s">
         <v>162</v>
       </c>
-      <c r="U9" s="118"/>
+      <c r="U9" s="99"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="43">
@@ -8156,7 +8156,7 @@
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="118">
+      <c r="I10" s="99">
         <v>2</v>
       </c>
       <c r="K10" s="57" t="s">
@@ -8169,7 +8169,7 @@
       <c r="N10" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="O10" s="117">
+      <c r="O10" s="98">
         <v>2</v>
       </c>
       <c r="Q10" s="33"/>
@@ -8180,7 +8180,7 @@
       <c r="T10" s="83" t="s">
         <v>169</v>
       </c>
-      <c r="U10" s="119"/>
+      <c r="U10" s="100"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="65">
@@ -8203,14 +8203,14 @@
       <c r="H11" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="I11" s="118"/>
+      <c r="I11" s="99"/>
       <c r="K11" s="33"/>
       <c r="L11" s="56"/>
       <c r="M11" s="33" t="s">
         <v>175</v>
       </c>
       <c r="N11" s="56"/>
-      <c r="O11" s="119"/>
+      <c r="O11" s="100"/>
       <c r="Q11" s="61" t="s">
         <v>174</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>176</v>
       </c>
       <c r="T11" s="59"/>
-      <c r="U11" s="123">
+      <c r="U11" s="104">
         <v>3</v>
       </c>
     </row>
@@ -8238,14 +8238,14 @@
         <v>177</v>
       </c>
       <c r="H12" s="56"/>
-      <c r="I12" s="118"/>
+      <c r="I12" s="99"/>
       <c r="K12" s="60"/>
       <c r="L12" s="60"/>
       <c r="M12" s="60" t="s">
         <v>178</v>
       </c>
       <c r="N12" s="60"/>
-      <c r="O12" s="124">
+      <c r="O12" s="105">
         <v>3</v>
       </c>
       <c r="Q12" s="69" t="s">
@@ -8254,7 +8254,7 @@
       <c r="R12" s="59"/>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
-      <c r="U12" s="123"/>
+      <c r="U12" s="104"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="65">
@@ -8275,7 +8275,7 @@
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="126">
+      <c r="I13" s="107">
         <v>3</v>
       </c>
       <c r="K13" s="60" t="s">
@@ -8290,7 +8290,7 @@
       <c r="N13" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="O13" s="125"/>
+      <c r="O13" s="106"/>
       <c r="Q13" s="28" t="s">
         <v>182</v>
       </c>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
-      <c r="U13" s="114">
+      <c r="U13" s="95">
         <v>4</v>
       </c>
     </row>
@@ -8320,14 +8320,14 @@
       <c r="F14" s="58"/>
       <c r="G14" s="61"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="126"/>
+      <c r="I14" s="107"/>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="28" t="s">
         <v>146</v>
       </c>
       <c r="N14" s="63"/>
-      <c r="O14" s="112">
+      <c r="O14" s="93">
         <v>4</v>
       </c>
       <c r="Q14" s="67" t="s">
@@ -8336,7 +8336,7 @@
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="T14" s="63"/>
-      <c r="U14" s="114"/>
+      <c r="U14" s="95"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="44">
@@ -8353,14 +8353,14 @@
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="125"/>
+      <c r="I15" s="106"/>
       <c r="K15" s="62"/>
       <c r="L15" s="63"/>
       <c r="M15" s="28" t="s">
         <v>149</v>
       </c>
       <c r="N15" s="63"/>
-      <c r="O15" s="113"/>
+      <c r="O15" s="94"/>
       <c r="Q15" s="68" t="s">
         <v>150</v>
       </c>
@@ -8372,10 +8372,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="111" t="s">
+      <c r="C18" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="111"/>
+      <c r="D18" s="92"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -8623,6 +8623,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E3:H4"/>
+    <mergeCell ref="Q3:T6"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="O4:O6"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="O14:O15"/>
     <mergeCell ref="U13:U14"/>
@@ -8635,22 +8651,6 @@
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="I13:I15"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="O4:O6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E3:H4"/>
-    <mergeCell ref="Q3:T6"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8668,32 +8668,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="G1" s="133" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="G1" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -8866,11 +8866,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>0.5</v>
       </c>
-      <c r="F10" s="130">
+      <c r="F10" s="133">
         <f>D10+D11+D12+D13</f>
         <v>2</v>
       </c>
-      <c r="G10" s="111">
+      <c r="G10" s="92">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -8890,11 +8890,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="130">
+      <c r="N10" s="133">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>3.5</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="92">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -8914,7 +8914,7 @@
         <f>T10*R10</f>
         <v>0.5</v>
       </c>
-      <c r="V10" s="134">
+      <c r="V10" s="130">
         <f>T10+T11+T12</f>
         <v>1.84</v>
       </c>
@@ -8937,8 +8937,8 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="131"/>
-      <c r="G11" s="111"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="92"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8956,8 +8956,8 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="N11" s="131"/>
-      <c r="O11" s="111"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="92"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -8975,7 +8975,7 @@
         <f>T11*R11</f>
         <v>0.5</v>
       </c>
-      <c r="V11" s="135"/>
+      <c r="V11" s="131"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -8995,8 +8995,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="131"/>
-      <c r="G12" s="111"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="92"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9014,8 +9014,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N12" s="131"/>
-      <c r="O12" s="111"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="92"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -9033,7 +9033,7 @@
         <f>T12*R12</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="V12" s="136"/>
+      <c r="V12" s="132"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -9053,8 +9053,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="132"/>
-      <c r="G13" s="111"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="92"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -9072,8 +9072,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N13" s="131"/>
-      <c r="O13" s="111"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="92"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -9093,11 +9093,11 @@
         <f t="shared" si="0"/>
         <v>1.575</v>
       </c>
-      <c r="F14" s="130">
+      <c r="F14" s="133">
         <f>D10+D11+D12+D14+D15</f>
         <v>3.09375</v>
       </c>
-      <c r="G14" s="111">
+      <c r="G14" s="92">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -9117,8 +9117,8 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="N14" s="131"/>
-      <c r="O14" s="111"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="92"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -9138,8 +9138,8 @@
         <f t="shared" si="0"/>
         <v>2.4187500000000002</v>
       </c>
-      <c r="F15" s="132"/>
-      <c r="G15" s="111"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="92"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -9157,8 +9157,8 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="131"/>
-      <c r="O15" s="111"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="92"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -9189,8 +9189,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="132"/>
-      <c r="O16" s="111"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="92"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -9326,7 +9326,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="134">
+      <c r="N22" s="130">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9366,7 +9366,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="135"/>
+      <c r="N23" s="131"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -9403,7 +9403,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="136"/>
+      <c r="N24" s="132"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -9440,7 +9440,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="134">
+      <c r="N25" s="130">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -9463,7 +9463,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="136"/>
+      <c r="N26" s="132"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -9477,7 +9477,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="137" t="s">
+      <c r="A30" s="135" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="128"/>
@@ -9486,7 +9486,7 @@
       <c r="E30" s="128"/>
       <c r="F30" s="129"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="137" t="s">
+      <c r="I30" s="135" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="128"/>
@@ -9558,11 +9558,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F32" s="130">
+      <c r="F32" s="133">
         <f>D32+D33+D34+D35</f>
         <v>2.8634999999999997</v>
       </c>
-      <c r="G32" s="111">
+      <c r="G32" s="92">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -9582,11 +9582,11 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N32" s="130">
+      <c r="N32" s="133">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>4.4731499999999995</v>
       </c>
-      <c r="O32" s="111">
+      <c r="O32" s="92">
         <v>4</v>
       </c>
     </row>
@@ -9608,8 +9608,8 @@
         <f t="shared" si="4"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="F33" s="131"/>
-      <c r="G33" s="111"/>
+      <c r="F33" s="136"/>
+      <c r="G33" s="92"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -9627,8 +9627,8 @@
         <f t="shared" si="6"/>
         <v>0.70724999999999993</v>
       </c>
-      <c r="N33" s="131"/>
-      <c r="O33" s="111"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="92"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -9648,8 +9648,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F34" s="131"/>
-      <c r="G34" s="111"/>
+      <c r="F34" s="136"/>
+      <c r="G34" s="92"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -9667,8 +9667,8 @@
         <f t="shared" si="6"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="N34" s="131"/>
-      <c r="O34" s="111"/>
+      <c r="N34" s="136"/>
+      <c r="O34" s="92"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -9688,8 +9688,8 @@
         <f t="shared" si="4"/>
         <v>1.4489999999999998</v>
       </c>
-      <c r="F35" s="132"/>
-      <c r="G35" s="111"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="92"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -9707,8 +9707,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N35" s="131"/>
-      <c r="O35" s="111"/>
+      <c r="N35" s="136"/>
+      <c r="O35" s="92"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -9728,11 +9728,11 @@
         <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
-      <c r="F36" s="130">
+      <c r="F36" s="133">
         <f>D32+D33+D34+D36+D37</f>
         <v>4.2640000000000002</v>
       </c>
-      <c r="G36" s="111">
+      <c r="G36" s="92">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -9752,8 +9752,8 @@
         <f t="shared" si="6"/>
         <v>4.0631500000000003</v>
       </c>
-      <c r="N36" s="131"/>
-      <c r="O36" s="111"/>
+      <c r="N36" s="136"/>
+      <c r="O36" s="92"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -9773,8 +9773,8 @@
         <f t="shared" si="4"/>
         <v>3.2249999999999996</v>
       </c>
-      <c r="F37" s="132"/>
-      <c r="G37" s="111"/>
+      <c r="F37" s="134"/>
+      <c r="G37" s="92"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -9792,8 +9792,8 @@
         <f t="shared" si="6"/>
         <v>6.1749999999999989</v>
       </c>
-      <c r="N37" s="131"/>
-      <c r="O37" s="111"/>
+      <c r="N37" s="136"/>
+      <c r="O37" s="92"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -9824,8 +9824,8 @@
         <f t="shared" si="6"/>
         <v>1.0373999999999999</v>
       </c>
-      <c r="N38" s="132"/>
-      <c r="O38" s="111"/>
+      <c r="N38" s="134"/>
+      <c r="O38" s="92"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -9955,7 +9955,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="134">
+      <c r="N45" s="130">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -9994,7 +9994,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="135"/>
+      <c r="N46" s="131"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -10030,7 +10030,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="136"/>
+      <c r="N47" s="132"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -10066,7 +10066,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="134">
+      <c r="N48" s="130">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -10088,29 +10088,10 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="136"/>
+      <c r="N49" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -10120,6 +10101,25 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
